--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFBAB19-2A38-4231-BAA3-8BE4D3434510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0BB36E-14C0-4EB0-A2EF-A957DFC52AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
+    <workbookView xWindow="40650" yWindow="2250" windowWidth="28800" windowHeight="15345" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2190" uniqueCount="482">
   <si>
     <t>AB</t>
   </si>
@@ -251,9 +251,6 @@
     <t>bcst</t>
   </si>
   <si>
-    <t>Adv</t>
-  </si>
-  <si>
     <t>1130-0330Z‡</t>
   </si>
   <si>
@@ -371,9 +368,6 @@
     <t>Toronto ctr</t>
   </si>
   <si>
-    <t>Windsor Area-Detroit Apch Ctl</t>
-  </si>
-  <si>
     <t>Barrie /Grenfel Field</t>
   </si>
   <si>
@@ -479,9 +473,6 @@
     <t>CYOW</t>
   </si>
   <si>
-    <t>Quebec rdo</t>
-  </si>
-  <si>
     <t>EN / FR</t>
   </si>
   <si>
@@ -695,9 +686,6 @@
     <t>CPJ5</t>
   </si>
   <si>
-    <t>London rdo (Campbellford)</t>
-  </si>
-  <si>
     <t>Stoney Creek</t>
   </si>
   <si>
@@ -782,9 +770,6 @@
     <t>Thunder Bay rdo</t>
   </si>
   <si>
-    <t>11-02Z‡ London rdo</t>
-  </si>
-  <si>
     <t>11-02Z‡ O/T tfc</t>
   </si>
   <si>
@@ -809,9 +794,6 @@
     <t>CYRO</t>
   </si>
   <si>
-    <t>Quebec rdo (Gatineau)</t>
-  </si>
-  <si>
     <t>Nakina</t>
   </si>
   <si>
@@ -866,9 +848,6 @@
     <t>CYMO</t>
   </si>
   <si>
-    <t>12-02Z‡ Timmins rdo</t>
-  </si>
-  <si>
     <t>Leamington</t>
   </si>
   <si>
@@ -1149,6 +1128,363 @@
   </si>
   <si>
     <t>CYIB</t>
+  </si>
+  <si>
+    <t>Aklavik / Freddie Carmichael</t>
+  </si>
+  <si>
+    <t>NT</t>
+  </si>
+  <si>
+    <t>CYKD</t>
+  </si>
+  <si>
+    <t>APRT RDO</t>
+  </si>
+  <si>
+    <t>aprt rdo</t>
+  </si>
+  <si>
+    <t>14-24Z‡ Mon - Sat, 15-20Z‡ Sun</t>
+  </si>
+  <si>
+    <t>Cable Head Airpark</t>
+  </si>
+  <si>
+    <t>CCA3</t>
+  </si>
+  <si>
+    <t>Alert</t>
+  </si>
+  <si>
+    <t>CYLT</t>
+  </si>
+  <si>
+    <t>NU</t>
+  </si>
+  <si>
+    <t>Alert Metro</t>
+  </si>
+  <si>
+    <t>CYAB</t>
+  </si>
+  <si>
+    <t>Arctic Bay</t>
+  </si>
+  <si>
+    <t>LWIS</t>
+  </si>
+  <si>
+    <t>12-23Z‡ Mon &amp; Thr, 12-21Z‡ Tue, Wed, &amp; Fri, 18-23Z‡ Sat</t>
+  </si>
+  <si>
+    <t>Actic Watch Lodge</t>
+  </si>
+  <si>
+    <t>CRW4</t>
+  </si>
+  <si>
+    <t>ARVIAT</t>
+  </si>
+  <si>
+    <t>CYEK</t>
+  </si>
+  <si>
+    <t>1245-2315Z‡ Mon -Fri, 1445-2115Z‡ Sat &amp; Sun</t>
+  </si>
+  <si>
+    <t>Baker Lake</t>
+  </si>
+  <si>
+    <t>CYBK</t>
+  </si>
+  <si>
+    <t>FISE Edmonton rdo</t>
+  </si>
+  <si>
+    <t>122.375, 5680</t>
+  </si>
+  <si>
+    <t>Beaver Creek</t>
+  </si>
+  <si>
+    <t>YT</t>
+  </si>
+  <si>
+    <t>CYXQ</t>
+  </si>
+  <si>
+    <t>FISE Whitehorse rdo</t>
+  </si>
+  <si>
+    <t>Braeburn</t>
+  </si>
+  <si>
+    <t>CEK2</t>
+  </si>
+  <si>
+    <t>Bridgewater / Dayspring Airpark</t>
+  </si>
+  <si>
+    <t>CDY6</t>
+  </si>
+  <si>
+    <t>Burwash</t>
+  </si>
+  <si>
+    <t>CYDB</t>
+  </si>
+  <si>
+    <t>Whitehorse rdo (W of A/D)</t>
+  </si>
+  <si>
+    <t>Whitehorse rdo (E of A/D)</t>
+  </si>
+  <si>
+    <t>Cambridge Bay</t>
+  </si>
+  <si>
+    <t>CYCB</t>
+  </si>
+  <si>
+    <t>Edmonton Ctr</t>
+  </si>
+  <si>
+    <t>228.900, 251.00, 270.400, 364.200</t>
+  </si>
+  <si>
+    <t>INTL AIR</t>
+  </si>
+  <si>
+    <t>Gander rdo</t>
+  </si>
+  <si>
+    <t>2971, 4675, 8891, 11279</t>
+  </si>
+  <si>
+    <t>Carcross</t>
+  </si>
+  <si>
+    <t>CFA4</t>
+  </si>
+  <si>
+    <t>Carmacks</t>
+  </si>
+  <si>
+    <t>CEX4</t>
+  </si>
+  <si>
+    <t>Centredale</t>
+  </si>
+  <si>
+    <t>CDL8</t>
+  </si>
+  <si>
+    <t>Adv Windsor Area-Detroit Apch Ctl</t>
+  </si>
+  <si>
+    <t>FISE Quebec rdo</t>
+  </si>
+  <si>
+    <t>FISE London rdo (Campbellford)</t>
+  </si>
+  <si>
+    <t>RAAS Thunder Bay rdo</t>
+  </si>
+  <si>
+    <t>11-02Z‡</t>
+  </si>
+  <si>
+    <t>FISE Quebec rdo (Gatineau)</t>
+  </si>
+  <si>
+    <t>12-02Z‡</t>
+  </si>
+  <si>
+    <t>RAAS Timmins rdo</t>
+  </si>
+  <si>
+    <t>Cherterfield Inlet</t>
+  </si>
+  <si>
+    <t>CYCS</t>
+  </si>
+  <si>
+    <t>ARPT RDO</t>
+  </si>
+  <si>
+    <t>Clyde River</t>
+  </si>
+  <si>
+    <t>CYCY</t>
+  </si>
+  <si>
+    <t>1424-2315Z‡ Mon &amp; Wed, 15-24Z‡ Tue, Wed, &amp; Fri, 14-23Z‡ Sat, 11-20Z‡ Sun</t>
+  </si>
+  <si>
+    <t>Colville Lake / Tommy Kochon</t>
+  </si>
+  <si>
+    <t>CYVL</t>
+  </si>
+  <si>
+    <t>Coral Harbour</t>
+  </si>
+  <si>
+    <t>CYZS</t>
+  </si>
+  <si>
+    <t>Dawson City</t>
+  </si>
+  <si>
+    <t>CYDA</t>
+  </si>
+  <si>
+    <t>14-24Z Dec 1-Jan 31, 14-23Z Feb 1-May 31, 12-02Z Jun 1-Sep 30, 14-23Z Oct 1-Nov 30</t>
+  </si>
+  <si>
+    <t>Debert</t>
+  </si>
+  <si>
+    <t>CCQ3</t>
+  </si>
+  <si>
+    <t>Halifax Tml</t>
+  </si>
+  <si>
+    <t>Deline</t>
+  </si>
+  <si>
+    <t>CYWJ</t>
+  </si>
+  <si>
+    <t>CDK2</t>
+  </si>
+  <si>
+    <t>Diavik</t>
+  </si>
+  <si>
+    <t>Digby Municipal Airport</t>
+  </si>
+  <si>
+    <t>CYID</t>
+  </si>
+  <si>
+    <t>East Gore ECO Airpark</t>
+  </si>
+  <si>
+    <t>CCY4</t>
+  </si>
+  <si>
+    <t>EKATI</t>
+  </si>
+  <si>
+    <t>CYOA</t>
+  </si>
+  <si>
+    <t>Eureka</t>
+  </si>
+  <si>
+    <t>CYEU</t>
+  </si>
+  <si>
+    <t>Faro</t>
+  </si>
+  <si>
+    <t>CZFA</t>
+  </si>
+  <si>
+    <t>13-01Z Jun 1-Sep 30, 14-22Z Oct 1-May 31</t>
+  </si>
+  <si>
+    <t>CDH3</t>
+  </si>
+  <si>
+    <t>Finlay Air Park</t>
+  </si>
+  <si>
+    <t>Finlayson Lake</t>
+  </si>
+  <si>
+    <t>CFT3</t>
+  </si>
+  <si>
+    <t>Ford Bay</t>
+  </si>
+  <si>
+    <t>CBC2</t>
+  </si>
+  <si>
+    <t>Fort Good Hope</t>
+  </si>
+  <si>
+    <t>CYGH</t>
+  </si>
+  <si>
+    <t>Fort Liard</t>
+  </si>
+  <si>
+    <t>CYJF</t>
+  </si>
+  <si>
+    <t>Fort McPherson</t>
+  </si>
+  <si>
+    <t>CZFM</t>
+  </si>
+  <si>
+    <t>14-24Z‡ Mon-Sat, 15-20Z‡ Sun</t>
+  </si>
+  <si>
+    <t>15-23Z‡ Mon-Fri</t>
+  </si>
+  <si>
+    <t>14-24Z‡ Mon-Sat, 14-19Z‡ Sun</t>
+  </si>
+  <si>
+    <t>14-00Z‡ Mon-Sat, 18-23Z‡ Sun</t>
+  </si>
+  <si>
+    <t>Fort Providence</t>
+  </si>
+  <si>
+    <t>CYJP</t>
+  </si>
+  <si>
+    <t>Fort Resolution</t>
+  </si>
+  <si>
+    <t>CYFR</t>
+  </si>
+  <si>
+    <t>Fort Simpson</t>
+  </si>
+  <si>
+    <t>CYFS</t>
+  </si>
+  <si>
+    <t>CNCL DEL</t>
+  </si>
+  <si>
+    <t>Fort Simpson Island</t>
+  </si>
+  <si>
+    <t>CET4</t>
+  </si>
+  <si>
+    <t>Fort Simpson aprt rdo</t>
+  </si>
+  <si>
+    <t>Fort Smith</t>
+  </si>
+  <si>
+    <t>CYSM</t>
+  </si>
+  <si>
+    <t>Fox Harbour</t>
+  </si>
+  <si>
+    <t>CFH4</t>
   </si>
 </sst>
 </file>
@@ -1538,7 +1874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G322"/>
+  <dimension ref="A1:G424"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -1564,7 +1900,7 @@
         <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>20</v>
@@ -1664,7 +2000,7 @@
         <v>65</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G6" s="3">
         <v>122.8</v>
@@ -1687,7 +2023,7 @@
         <v>65</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" s="3">
         <v>123.3</v>
@@ -1721,10 +2057,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>68</v>
+        <v>275</v>
       </c>
       <c r="G9" s="3">
         <v>123.55</v>
@@ -1741,7 +2077,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
         <v>69</v>
@@ -1778,10 +2114,10 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G12" s="3">
         <v>135.65</v>
@@ -1798,13 +2134,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G13">
         <v>123.27500000000001</v>
@@ -1838,10 +2174,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G15" s="3">
         <v>121.3</v>
@@ -1858,13 +2194,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E16" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1878,13 +2214,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="s">
+        <v>165</v>
+      </c>
+      <c r="E17" t="s">
         <v>168</v>
       </c>
-      <c r="E17" t="s">
-        <v>171</v>
-      </c>
       <c r="G17" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1898,13 +2234,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E18" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1918,10 +2254,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E19" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G19" s="3">
         <v>136.52500000000001</v>
@@ -1938,10 +2274,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E20" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G20" s="3">
         <v>122.27500000000001</v>
@@ -1958,10 +2294,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E21" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G21" s="3">
         <v>122.075</v>
@@ -2046,10 +2382,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" t="s">
         <v>78</v>
-      </c>
-      <c r="E26" t="s">
-        <v>79</v>
       </c>
       <c r="G26" t="s">
         <v>60</v>
@@ -2066,13 +2402,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="G27">
         <v>123.47499999999999</v>
@@ -2109,10 +2442,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G29">
         <v>134.375</v>
@@ -2146,7 +2479,7 @@
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
         <v>68</v>
@@ -2166,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E32" t="s">
         <v>69</v>
@@ -2192,7 +2525,7 @@
         <v>65</v>
       </c>
       <c r="F33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G33" s="3">
         <v>122.8</v>
@@ -2209,10 +2542,10 @@
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G34" s="3">
         <v>124.075</v>
@@ -2275,7 +2608,7 @@
         <v>65</v>
       </c>
       <c r="F37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G37" s="3">
         <v>123</v>
@@ -2295,7 +2628,7 @@
         <v>41</v>
       </c>
       <c r="F38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G38" s="3">
         <v>133.6</v>
@@ -2315,7 +2648,7 @@
         <v>14</v>
       </c>
       <c r="F39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G39" s="3">
         <v>121.7</v>
@@ -2352,7 +2685,7 @@
         <v>15</v>
       </c>
       <c r="F41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G41" s="3">
         <v>119.2</v>
@@ -2375,7 +2708,7 @@
         <v>67</v>
       </c>
       <c r="F42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G42" s="3">
         <v>118.2</v>
@@ -2438,7 +2771,7 @@
         <v>67</v>
       </c>
       <c r="F45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G45" s="3">
         <v>133.6</v>
@@ -2461,7 +2794,7 @@
         <v>65</v>
       </c>
       <c r="F46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G46" s="3">
         <v>123.5</v>
@@ -2506,7 +2839,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B49" t="s">
         <v>46</v>
@@ -2515,13 +2848,13 @@
         <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E49" t="s">
         <v>68</v>
       </c>
       <c r="F49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G49" s="3">
         <v>123.15</v>
@@ -2529,7 +2862,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B50" t="s">
         <v>46</v>
@@ -2541,7 +2874,7 @@
         <v>41</v>
       </c>
       <c r="F50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G50" s="3">
         <v>125.675</v>
@@ -2549,7 +2882,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B51" t="s">
         <v>46</v>
@@ -2561,7 +2894,7 @@
         <v>14</v>
       </c>
       <c r="F51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G51" s="3">
         <v>118.4</v>
@@ -2569,7 +2902,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B52" t="s">
         <v>46</v>
@@ -2581,7 +2914,7 @@
         <v>15</v>
       </c>
       <c r="F52" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G52" s="3">
         <v>120.1</v>
@@ -2589,7 +2922,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B53" t="s">
         <v>46</v>
@@ -2604,7 +2937,7 @@
         <v>67</v>
       </c>
       <c r="F53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G53" s="3">
         <v>120.1</v>
@@ -2612,7 +2945,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B54" t="s">
         <v>46</v>
@@ -2624,7 +2957,7 @@
         <v>16</v>
       </c>
       <c r="E54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G54" s="3">
         <v>133.4</v>
@@ -2632,7 +2965,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B55" t="s">
         <v>46</v>
@@ -2644,7 +2977,7 @@
         <v>17</v>
       </c>
       <c r="E55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G55" s="3">
         <v>133.4</v>
@@ -2652,7 +2985,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B56" t="s">
         <v>46</v>
@@ -2664,7 +2997,7 @@
         <v>2</v>
       </c>
       <c r="F56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G56" s="3">
         <v>125.675</v>
@@ -2684,7 +3017,7 @@
         <v>11</v>
       </c>
       <c r="F57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G57" s="3">
         <v>118.3</v>
@@ -2701,7 +3034,7 @@
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E58" t="s">
         <v>68</v>
@@ -2721,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E59" t="s">
         <v>69</v>
@@ -2744,7 +3077,7 @@
         <v>41</v>
       </c>
       <c r="F60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G60" s="3">
         <v>124.9</v>
@@ -2764,10 +3097,10 @@
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G61" s="3">
         <v>118.3</v>
@@ -2784,10 +3117,10 @@
         <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E62" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G62" s="3">
         <v>127.25</v>
@@ -2807,7 +3140,7 @@
         <v>2</v>
       </c>
       <c r="F63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G63" s="3">
         <v>124.9</v>
@@ -2844,13 +3177,10 @@
         <v>1</v>
       </c>
       <c r="D65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E65" t="s">
-        <v>68</v>
-      </c>
-      <c r="F65" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="G65" s="3">
         <v>123.375</v>
@@ -2867,7 +3197,7 @@
         <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E66" t="s">
         <v>69</v>
@@ -2907,10 +3237,10 @@
         <v>1</v>
       </c>
       <c r="D68" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E68" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G68" s="3">
         <v>132.57499999999999</v>
@@ -2927,13 +3257,10 @@
         <v>1</v>
       </c>
       <c r="D69" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E69" t="s">
-        <v>68</v>
-      </c>
-      <c r="F69" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="G69" s="3">
         <v>123.375</v>
@@ -2950,7 +3277,7 @@
         <v>1</v>
       </c>
       <c r="D70" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E70" t="s">
         <v>69</v>
@@ -2973,7 +3300,7 @@
         <v>41</v>
       </c>
       <c r="F71" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G71" s="3">
         <v>134.5</v>
@@ -2993,7 +3320,7 @@
         <v>14</v>
       </c>
       <c r="F72" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G72" s="3">
         <v>121.7</v>
@@ -3013,7 +3340,7 @@
         <v>15</v>
       </c>
       <c r="F73" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G73" s="3">
         <v>124.7</v>
@@ -3036,7 +3363,7 @@
         <v>67</v>
       </c>
       <c r="F74" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G74" s="3">
         <v>124.7</v>
@@ -3056,7 +3383,7 @@
         <v>55</v>
       </c>
       <c r="E75" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G75" t="s">
         <v>61</v>
@@ -3073,13 +3400,10 @@
         <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E76" t="s">
-        <v>70</v>
-      </c>
-      <c r="F76" t="s">
-        <v>110</v>
+        <v>413</v>
       </c>
       <c r="G76" s="3">
         <v>134.30000000000001</v>
@@ -3099,7 +3423,7 @@
         <v>2</v>
       </c>
       <c r="F77" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G77" s="3">
         <v>134.5</v>
@@ -3107,19 +3431,19 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>89</v>
+      </c>
+      <c r="B78" t="s">
         <v>90</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
+        <v>1</v>
+      </c>
+      <c r="D78" t="s">
+        <v>74</v>
+      </c>
+      <c r="F78" t="s">
         <v>91</v>
-      </c>
-      <c r="C78" t="s">
-        <v>1</v>
-      </c>
-      <c r="D78" t="s">
-        <v>75</v>
-      </c>
-      <c r="F78" t="s">
-        <v>92</v>
       </c>
       <c r="G78" s="3">
         <v>119.4</v>
@@ -3127,22 +3451,19 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>89</v>
+      </c>
+      <c r="B79" t="s">
         <v>90</v>
       </c>
-      <c r="B79" t="s">
-        <v>91</v>
-      </c>
       <c r="C79" t="s">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E79" t="s">
-        <v>68</v>
-      </c>
-      <c r="F79" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="G79" s="3">
         <v>123.55</v>
@@ -3150,16 +3471,16 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>89</v>
+      </c>
+      <c r="B80" t="s">
         <v>90</v>
       </c>
-      <c r="B80" t="s">
-        <v>91</v>
-      </c>
       <c r="C80" t="s">
         <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E80" t="s">
         <v>69</v>
@@ -3170,10 +3491,10 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" t="s">
         <v>90</v>
-      </c>
-      <c r="B81" t="s">
-        <v>91</v>
       </c>
       <c r="C81" t="s">
         <v>1</v>
@@ -3182,7 +3503,7 @@
         <v>41</v>
       </c>
       <c r="F81" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G81" s="3">
         <v>127.8</v>
@@ -3190,10 +3511,10 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82" t="s">
         <v>90</v>
-      </c>
-      <c r="B82" t="s">
-        <v>91</v>
       </c>
       <c r="C82" t="s">
         <v>1</v>
@@ -3202,7 +3523,7 @@
         <v>14</v>
       </c>
       <c r="F82" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G82" s="3">
         <v>121.9</v>
@@ -3210,10 +3531,10 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" t="s">
         <v>90</v>
-      </c>
-      <c r="B83" t="s">
-        <v>91</v>
       </c>
       <c r="C83" t="s">
         <v>1</v>
@@ -3222,18 +3543,18 @@
         <v>15</v>
       </c>
       <c r="F83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G83" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>89</v>
+      </c>
+      <c r="B84" t="s">
         <v>90</v>
-      </c>
-      <c r="B84" t="s">
-        <v>91</v>
       </c>
       <c r="C84" t="s">
         <v>1</v>
@@ -3242,10 +3563,10 @@
         <v>12</v>
       </c>
       <c r="E84" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G84" s="3">
         <v>119.4</v>
@@ -3253,39 +3574,39 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>89</v>
+      </c>
+      <c r="B85" t="s">
         <v>90</v>
       </c>
-      <c r="B85" t="s">
-        <v>91</v>
-      </c>
       <c r="C85" t="s">
         <v>1</v>
       </c>
       <c r="D85" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E85" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G85" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>96</v>
+      </c>
+      <c r="B86" t="s">
         <v>97</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
+        <v>1</v>
+      </c>
+      <c r="D86" t="s">
         <v>98</v>
       </c>
-      <c r="C86" t="s">
-        <v>1</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="F86" t="s">
         <v>99</v>
-      </c>
-      <c r="F86" t="s">
-        <v>100</v>
       </c>
       <c r="G86" s="3">
         <v>123.25</v>
@@ -3293,22 +3614,19 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>96</v>
+      </c>
+      <c r="B87" t="s">
         <v>97</v>
       </c>
-      <c r="B87" t="s">
-        <v>98</v>
-      </c>
       <c r="C87" t="s">
         <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E87" t="s">
-        <v>68</v>
-      </c>
-      <c r="F87" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="G87">
         <v>123.47499999999999</v>
@@ -3316,16 +3634,16 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" t="s">
         <v>97</v>
       </c>
-      <c r="B88" t="s">
-        <v>98</v>
-      </c>
       <c r="C88" t="s">
         <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E88" t="s">
         <v>69</v>
@@ -3336,10 +3654,10 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" t="s">
         <v>97</v>
-      </c>
-      <c r="B89" t="s">
-        <v>98</v>
       </c>
       <c r="C89" t="s">
         <v>1</v>
@@ -3348,7 +3666,7 @@
         <v>41</v>
       </c>
       <c r="F89" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G89">
         <v>128.52500000000001</v>
@@ -3356,10 +3674,10 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" t="s">
         <v>97</v>
-      </c>
-      <c r="B90" t="s">
-        <v>98</v>
       </c>
       <c r="C90" t="s">
         <v>1</v>
@@ -3368,10 +3686,10 @@
         <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F90" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G90" s="3">
         <v>123.25</v>
@@ -3379,10 +3697,10 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>96</v>
+      </c>
+      <c r="B91" t="s">
         <v>97</v>
-      </c>
-      <c r="B91" t="s">
-        <v>98</v>
       </c>
       <c r="C91" t="s">
         <v>1</v>
@@ -3394,7 +3712,7 @@
         <v>67</v>
       </c>
       <c r="F91" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G91" s="3">
         <v>123.25</v>
@@ -3402,10 +3720,10 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" t="s">
         <v>97</v>
-      </c>
-      <c r="B92" t="s">
-        <v>98</v>
       </c>
       <c r="C92" t="s">
         <v>1</v>
@@ -3414,7 +3732,7 @@
         <v>16</v>
       </c>
       <c r="E92" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G92" s="3">
         <v>133.4</v>
@@ -3422,10 +3740,10 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" t="s">
         <v>97</v>
-      </c>
-      <c r="B93" t="s">
-        <v>98</v>
       </c>
       <c r="C93" t="s">
         <v>1</v>
@@ -3434,7 +3752,7 @@
         <v>17</v>
       </c>
       <c r="E93" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G93" s="3">
         <v>133.4</v>
@@ -3442,16 +3760,16 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>96</v>
+      </c>
+      <c r="B94" t="s">
         <v>97</v>
       </c>
-      <c r="B94" t="s">
-        <v>98</v>
-      </c>
       <c r="C94" t="s">
         <v>1</v>
       </c>
       <c r="D94" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G94" s="3">
         <v>133.30000000000001</v>
@@ -3459,10 +3777,10 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B95" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C95" t="s">
         <v>1</v>
@@ -3471,7 +3789,7 @@
         <v>41</v>
       </c>
       <c r="F95" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G95" s="3">
         <v>125.1</v>
@@ -3479,10 +3797,10 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B96" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C96" t="s">
         <v>1</v>
@@ -3491,10 +3809,10 @@
         <v>14</v>
       </c>
       <c r="E96" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F96" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G96" s="3">
         <v>121.8</v>
@@ -3502,10 +3820,10 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B97" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C97" t="s">
         <v>1</v>
@@ -3514,21 +3832,21 @@
         <v>15</v>
       </c>
       <c r="E97" t="s">
+        <v>104</v>
+      </c>
+      <c r="F97" t="s">
+        <v>103</v>
+      </c>
+      <c r="G97" t="s">
         <v>105</v>
-      </c>
-      <c r="F97" t="s">
-        <v>104</v>
-      </c>
-      <c r="G97" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B98" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C98" t="s">
         <v>1</v>
@@ -3540,7 +3858,7 @@
         <v>67</v>
       </c>
       <c r="F98" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G98" s="3">
         <v>126</v>
@@ -3548,10 +3866,10 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C99" t="s">
         <v>1</v>
@@ -3560,7 +3878,7 @@
         <v>16</v>
       </c>
       <c r="E99" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G99">
         <v>128.27500000000001</v>
@@ -3568,10 +3886,10 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B100" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C100" t="s">
         <v>1</v>
@@ -3580,7 +3898,7 @@
         <v>17</v>
       </c>
       <c r="E100" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G100">
         <v>128.27500000000001</v>
@@ -3588,19 +3906,19 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B101" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C101" t="s">
         <v>1</v>
       </c>
       <c r="D101" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E101" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G101">
         <v>128.27500000000001</v>
@@ -3608,10 +3926,10 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C102" t="s">
         <v>1</v>
@@ -3620,7 +3938,7 @@
         <v>2</v>
       </c>
       <c r="F102" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G102" s="3">
         <v>125.1</v>
@@ -3628,10 +3946,10 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B103" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C103" t="s">
         <v>1</v>
@@ -3643,7 +3961,7 @@
         <v>65</v>
       </c>
       <c r="F103" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G103" s="3">
         <v>123</v>
@@ -3651,10 +3969,10 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B104" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C104" t="s">
         <v>1</v>
@@ -3666,7 +3984,7 @@
         <v>65</v>
       </c>
       <c r="F104" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G104" s="3">
         <v>122.7</v>
@@ -3674,16 +3992,16 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" t="s">
+        <v>112</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1</v>
+      </c>
+      <c r="D105" t="s">
         <v>113</v>
-      </c>
-      <c r="B105" t="s">
-        <v>114</v>
-      </c>
-      <c r="C105" t="s">
-        <v>1</v>
-      </c>
-      <c r="D105" t="s">
-        <v>115</v>
       </c>
       <c r="G105" s="3">
         <v>122.97499999999999</v>
@@ -3691,10 +4009,10 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B106" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C106" t="s">
         <v>1</v>
@@ -3706,7 +4024,7 @@
         <v>65</v>
       </c>
       <c r="F106" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G106" s="3">
         <v>122.85</v>
@@ -3714,10 +4032,10 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B107" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C107" t="s">
         <v>1</v>
@@ -3734,16 +4052,16 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B108" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C108" t="s">
         <v>1</v>
       </c>
       <c r="D108" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G108" s="3">
         <v>122.2</v>
@@ -3751,22 +4069,19 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B109" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C109" t="s">
         <v>1</v>
       </c>
       <c r="D109" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E109" t="s">
-        <v>68</v>
-      </c>
-      <c r="F109" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="G109">
         <v>123.375</v>
@@ -3774,16 +4089,16 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B110" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C110" t="s">
         <v>1</v>
       </c>
       <c r="D110" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E110" t="s">
         <v>69</v>
@@ -3794,10 +4109,10 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B111" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C111" t="s">
         <v>1</v>
@@ -3811,10 +4126,10 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B112" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C112" t="s">
         <v>1</v>
@@ -3823,7 +4138,7 @@
         <v>12</v>
       </c>
       <c r="E112" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G112" s="3">
         <v>122.2</v>
@@ -3831,10 +4146,10 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B113" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C113" t="s">
         <v>1</v>
@@ -3846,7 +4161,7 @@
         <v>65</v>
       </c>
       <c r="F113" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G113" s="3">
         <v>122.02500000000001</v>
@@ -3854,19 +4169,19 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B114" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C114" t="s">
         <v>1</v>
       </c>
       <c r="D114" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E114" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G114" s="3">
         <v>134.25</v>
@@ -3874,10 +4189,10 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C115" t="s">
         <v>1</v>
@@ -3891,19 +4206,19 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>122</v>
+      </c>
+      <c r="B116" t="s">
+        <v>123</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1</v>
+      </c>
+      <c r="D116" t="s">
+        <v>74</v>
+      </c>
+      <c r="E116" t="s">
         <v>124</v>
-      </c>
-      <c r="B116" t="s">
-        <v>125</v>
-      </c>
-      <c r="C116" t="s">
-        <v>1</v>
-      </c>
-      <c r="D116" t="s">
-        <v>75</v>
-      </c>
-      <c r="E116" t="s">
-        <v>126</v>
       </c>
       <c r="G116" s="3">
         <v>122.3</v>
@@ -3911,22 +4226,19 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C117" t="s">
         <v>1</v>
       </c>
       <c r="D117" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E117" t="s">
-        <v>68</v>
-      </c>
-      <c r="F117" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="G117">
         <v>123.47499999999999</v>
@@ -3934,16 +4246,16 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B118" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C118" t="s">
         <v>1</v>
       </c>
       <c r="D118" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E118" t="s">
         <v>69</v>
@@ -3954,10 +4266,10 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B119" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C119" t="s">
         <v>1</v>
@@ -3971,10 +4283,10 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B120" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C120" t="s">
         <v>1</v>
@@ -3988,10 +4300,10 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B121" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C121" t="s">
         <v>1</v>
@@ -4003,7 +4315,7 @@
         <v>65</v>
       </c>
       <c r="F121" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G121" s="3">
         <v>123</v>
@@ -4011,19 +4323,19 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B122" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C122" t="s">
         <v>1</v>
       </c>
       <c r="D122" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E122" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G122" s="3">
         <v>135.4</v>
@@ -4031,10 +4343,10 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B123" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C123" t="s">
         <v>1</v>
@@ -4051,10 +4363,10 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C124" t="s">
         <v>1</v>
@@ -4071,22 +4383,19 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B125" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C125" t="s">
         <v>1</v>
       </c>
       <c r="D125" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E125" t="s">
-        <v>68</v>
-      </c>
-      <c r="F125" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="G125">
         <v>123.47499999999999</v>
@@ -4094,16 +4403,16 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C126" t="s">
         <v>1</v>
       </c>
       <c r="D126" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E126" t="s">
         <v>69</v>
@@ -4114,10 +4423,10 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B127" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C127" t="s">
         <v>1</v>
@@ -4126,7 +4435,7 @@
         <v>41</v>
       </c>
       <c r="F127" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G127" s="3">
         <v>133.05000000000001</v>
@@ -4134,10 +4443,10 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B128" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C128" t="s">
         <v>1</v>
@@ -4146,7 +4455,7 @@
         <v>14</v>
       </c>
       <c r="F128" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G128" s="3">
         <v>121.7</v>
@@ -4154,10 +4463,10 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B129" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C129" t="s">
         <v>1</v>
@@ -4166,7 +4475,7 @@
         <v>15</v>
       </c>
       <c r="F129" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G129" s="3">
         <v>118.8</v>
@@ -4174,10 +4483,10 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B130" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C130" t="s">
         <v>1</v>
@@ -4189,7 +4498,7 @@
         <v>67</v>
       </c>
       <c r="F130" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G130" s="3">
         <v>118.8</v>
@@ -4197,30 +4506,30 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>131</v>
+      </c>
+      <c r="B131" t="s">
+        <v>132</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1</v>
+      </c>
+      <c r="D131" t="s">
+        <v>76</v>
+      </c>
+      <c r="E131" t="s">
+        <v>75</v>
+      </c>
+      <c r="G131" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="B131" t="s">
-        <v>134</v>
-      </c>
-      <c r="C131" t="s">
-        <v>1</v>
-      </c>
-      <c r="D131" t="s">
-        <v>77</v>
-      </c>
-      <c r="E131" t="s">
-        <v>76</v>
-      </c>
-      <c r="G131" s="3" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B132" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C132" t="s">
         <v>1</v>
@@ -4232,7 +4541,7 @@
         <v>65</v>
       </c>
       <c r="F132" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G132" s="3">
         <v>122.7</v>
@@ -4240,10 +4549,10 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B133" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C133" t="s">
         <v>1</v>
@@ -4255,7 +4564,7 @@
         <v>65</v>
       </c>
       <c r="F133" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G133" s="3">
         <v>122.85</v>
@@ -4263,16 +4572,16 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B134" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C134" t="s">
         <v>1</v>
       </c>
       <c r="D134" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G134" s="3">
         <v>122.175</v>
@@ -4280,10 +4589,10 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B135" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C135" t="s">
         <v>1</v>
@@ -4295,7 +4604,7 @@
         <v>65</v>
       </c>
       <c r="F135" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G135" s="3">
         <v>122.825</v>
@@ -4303,19 +4612,19 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B136" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C136" t="s">
         <v>1</v>
       </c>
       <c r="D136" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E136" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G136" s="3">
         <v>119.7</v>
@@ -4323,10 +4632,10 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B137" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C137" t="s">
         <v>1</v>
@@ -4338,7 +4647,7 @@
         <v>65</v>
       </c>
       <c r="F137" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G137" s="3">
         <v>123.2</v>
@@ -4346,10 +4655,10 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B138" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C138" t="s">
         <v>1</v>
@@ -4363,22 +4672,19 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B139" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C139" t="s">
         <v>1</v>
       </c>
       <c r="D139" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E139" t="s">
-        <v>68</v>
-      </c>
-      <c r="F139" t="s">
-        <v>146</v>
+        <v>414</v>
       </c>
       <c r="G139" s="3">
         <v>123.15</v>
@@ -4386,16 +4692,16 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B140" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C140" t="s">
         <v>1</v>
       </c>
       <c r="D140" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E140" t="s">
         <v>69</v>
@@ -4406,10 +4712,10 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B141" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C141" t="s">
         <v>1</v>
@@ -4418,27 +4724,27 @@
         <v>41</v>
       </c>
       <c r="E141" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C142" t="s">
         <v>1</v>
       </c>
       <c r="D142" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E142" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G142" s="3">
         <v>119.4</v>
@@ -4446,10 +4752,10 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C143" t="s">
         <v>1</v>
@@ -4458,7 +4764,7 @@
         <v>14</v>
       </c>
       <c r="E143" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G143" s="3">
         <v>121.9</v>
@@ -4466,10 +4772,10 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C144" t="s">
         <v>1</v>
@@ -4478,7 +4784,7 @@
         <v>15</v>
       </c>
       <c r="E144" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G144" s="3">
         <v>118.8</v>
@@ -4486,10 +4792,10 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C145" t="s">
         <v>1</v>
@@ -4498,18 +4804,18 @@
         <v>15</v>
       </c>
       <c r="E145" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B146" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C146" t="s">
         <v>1</v>
@@ -4518,7 +4824,7 @@
         <v>44</v>
       </c>
       <c r="E146" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G146" s="3">
         <v>127.7</v>
@@ -4526,10 +4832,10 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B147" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C147" t="s">
         <v>1</v>
@@ -4538,7 +4844,7 @@
         <v>16</v>
       </c>
       <c r="E147" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G147" s="3">
         <v>135.15</v>
@@ -4546,10 +4852,10 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B148" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C148" t="s">
         <v>1</v>
@@ -4558,7 +4864,7 @@
         <v>17</v>
       </c>
       <c r="E148" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G148" s="3">
         <v>128.16999999999999</v>
@@ -4566,10 +4872,10 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B149" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C149" t="s">
         <v>1</v>
@@ -4581,7 +4887,7 @@
         <v>65</v>
       </c>
       <c r="F149" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G149" s="3">
         <v>123.2</v>
@@ -4589,10 +4895,10 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B150" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C150" t="s">
         <v>1</v>
@@ -4604,7 +4910,7 @@
         <v>65</v>
       </c>
       <c r="F150" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G150" s="3">
         <v>123.5</v>
@@ -4612,10 +4918,10 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B151" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C151" t="s">
         <v>1</v>
@@ -4632,10 +4938,10 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C152" t="s">
         <v>1</v>
@@ -4647,7 +4953,7 @@
         <v>65</v>
       </c>
       <c r="F152" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G152" s="3">
         <v>123</v>
@@ -4655,10 +4961,10 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B153" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C153" t="s">
         <v>1</v>
@@ -4670,7 +4976,7 @@
         <v>65</v>
       </c>
       <c r="F153" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G153" s="3">
         <v>123</v>
@@ -4678,16 +4984,16 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C154" t="s">
         <v>1</v>
       </c>
       <c r="D154" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G154" s="3">
         <v>122.3</v>
@@ -4695,22 +5001,19 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B155" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C155" t="s">
         <v>1</v>
       </c>
       <c r="D155" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E155" t="s">
-        <v>68</v>
-      </c>
-      <c r="F155" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="G155" s="3">
         <v>123.55</v>
@@ -4718,16 +5021,16 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C156" t="s">
         <v>1</v>
       </c>
       <c r="D156" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E156" t="s">
         <v>69</v>
@@ -4738,10 +5041,10 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B157" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C157" t="s">
         <v>1</v>
@@ -4755,10 +5058,10 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B158" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C158" t="s">
         <v>1</v>
@@ -4767,7 +5070,7 @@
         <v>12</v>
       </c>
       <c r="E158" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G158" s="3">
         <v>122.3</v>
@@ -4775,19 +5078,19 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B159" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C159" t="s">
         <v>1</v>
       </c>
       <c r="D159" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E159" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G159" s="3">
         <v>128.30000000000001</v>
@@ -4795,10 +5098,10 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B160" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C160" t="s">
         <v>1</v>
@@ -4810,7 +5113,7 @@
         <v>65</v>
       </c>
       <c r="F160" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G160" s="3">
         <v>122.8</v>
@@ -4818,10 +5121,10 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B161" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C161" t="s">
         <v>1</v>
@@ -4838,10 +5141,10 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B162" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C162" t="s">
         <v>1</v>
@@ -4850,32 +5153,32 @@
         <v>41</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>178</v>
+      </c>
+      <c r="B163" t="s">
+        <v>179</v>
+      </c>
+      <c r="C163" t="s">
+        <v>1</v>
+      </c>
+      <c r="D163" t="s">
+        <v>146</v>
+      </c>
+      <c r="G163" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="B163" t="s">
-        <v>182</v>
-      </c>
-      <c r="C163" t="s">
-        <v>1</v>
-      </c>
-      <c r="D163" t="s">
-        <v>149</v>
-      </c>
-      <c r="G163" s="3" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B164" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C164" t="s">
         <v>1</v>
@@ -4884,15 +5187,15 @@
         <v>14</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B165" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C165" t="s">
         <v>1</v>
@@ -4901,15 +5204,15 @@
         <v>15</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B166" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C166" t="s">
         <v>1</v>
@@ -4918,47 +5221,47 @@
         <v>44</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B167" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C167" t="s">
         <v>1</v>
       </c>
       <c r="D167" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E167" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B168" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C168" t="s">
         <v>1</v>
       </c>
       <c r="D168" t="s">
+        <v>185</v>
+      </c>
+      <c r="E168" t="s">
         <v>188</v>
       </c>
-      <c r="E168" t="s">
-        <v>191</v>
-      </c>
       <c r="F168" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G168" s="3">
         <v>232.1</v>
@@ -4966,19 +5269,19 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B169" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C169" t="s">
         <v>1</v>
       </c>
       <c r="D169" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F169" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G169" s="3">
         <v>344.6</v>
@@ -4986,10 +5289,10 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B170" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C170" t="s">
         <v>1</v>
@@ -5006,10 +5309,10 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B171" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C171" t="s">
         <v>1</v>
@@ -5018,10 +5321,10 @@
         <v>64</v>
       </c>
       <c r="E171" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F171" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G171" s="3">
         <v>123.5</v>
@@ -5029,16 +5332,16 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B172" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C172" t="s">
         <v>1</v>
       </c>
       <c r="D172" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G172" s="3">
         <v>118.1</v>
@@ -5046,22 +5349,19 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B173" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C173" t="s">
         <v>1</v>
       </c>
       <c r="D173" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E173" t="s">
-        <v>68</v>
-      </c>
-      <c r="F173" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="G173" s="3">
         <v>122.375</v>
@@ -5069,16 +5369,16 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B174" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C174" t="s">
         <v>1</v>
       </c>
       <c r="D174" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E174" t="s">
         <v>69</v>
@@ -5089,10 +5389,10 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B175" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C175" t="s">
         <v>1</v>
@@ -5106,10 +5406,10 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B176" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C176" t="s">
         <v>1</v>
@@ -5118,7 +5418,7 @@
         <v>14</v>
       </c>
       <c r="F176" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G176" s="3">
         <v>121.9</v>
@@ -5126,10 +5426,10 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B177" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C177" t="s">
         <v>1</v>
@@ -5138,7 +5438,7 @@
         <v>15</v>
       </c>
       <c r="F177" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G177" s="3">
         <v>118.1</v>
@@ -5146,10 +5446,10 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B178" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C178" t="s">
         <v>1</v>
@@ -5158,10 +5458,10 @@
         <v>12</v>
       </c>
       <c r="E178" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F178" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G178" s="3">
         <v>118.1</v>
@@ -5169,10 +5469,10 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B179" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C179" t="s">
         <v>1</v>
@@ -5181,7 +5481,7 @@
         <v>16</v>
       </c>
       <c r="E179" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G179" s="3">
         <v>119.2</v>
@@ -5189,10 +5489,10 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B180" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C180" t="s">
         <v>1</v>
@@ -5201,7 +5501,7 @@
         <v>17</v>
       </c>
       <c r="E180" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G180" s="3">
         <v>119.2</v>
@@ -5209,19 +5509,19 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>197</v>
+      </c>
+      <c r="B181" t="s">
+        <v>198</v>
+      </c>
+      <c r="C181" t="s">
+        <v>1</v>
+      </c>
+      <c r="D181" t="s">
+        <v>76</v>
+      </c>
+      <c r="E181" t="s">
         <v>200</v>
-      </c>
-      <c r="B181" t="s">
-        <v>201</v>
-      </c>
-      <c r="C181" t="s">
-        <v>1</v>
-      </c>
-      <c r="D181" t="s">
-        <v>77</v>
-      </c>
-      <c r="E181" t="s">
-        <v>203</v>
       </c>
       <c r="G181" s="3">
         <v>132.125</v>
@@ -5229,10 +5529,10 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B182" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C182" t="s">
         <v>1</v>
@@ -5244,7 +5544,7 @@
         <v>65</v>
       </c>
       <c r="F182" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G182" s="3">
         <v>122.7</v>
@@ -5252,16 +5552,16 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B183" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C183" t="s">
         <v>1</v>
       </c>
       <c r="D183" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G183" s="3">
         <v>122.55</v>
@@ -5269,10 +5569,10 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B184" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C184" t="s">
         <v>1</v>
@@ -5286,22 +5586,19 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B185" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C185" t="s">
         <v>1</v>
       </c>
       <c r="D185" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E185" t="s">
-        <v>68</v>
-      </c>
-      <c r="F185" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="G185" s="3">
         <v>126</v>
@@ -5309,16 +5606,16 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B186" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C186" t="s">
         <v>1</v>
       </c>
       <c r="D186" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E186" t="s">
         <v>69</v>
@@ -5329,10 +5626,10 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B187" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C187" t="s">
         <v>1</v>
@@ -5346,10 +5643,10 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B188" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C188" t="s">
         <v>1</v>
@@ -5358,7 +5655,7 @@
         <v>12</v>
       </c>
       <c r="E188" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G188" s="3">
         <v>122</v>
@@ -5366,19 +5663,19 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B189" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C189" t="s">
         <v>1</v>
       </c>
       <c r="D189" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E189" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G189" s="3">
         <v>132.19999999999999</v>
@@ -5386,10 +5683,10 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B190" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C190" t="s">
         <v>1</v>
@@ -5401,7 +5698,7 @@
         <v>65</v>
       </c>
       <c r="F190" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G190" s="3">
         <v>122.7</v>
@@ -5409,10 +5706,10 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B191" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C191" t="s">
         <v>1</v>
@@ -5424,7 +5721,7 @@
         <v>65</v>
       </c>
       <c r="F191" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G191" s="3">
         <v>123.35</v>
@@ -5432,10 +5729,10 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B192" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C192" t="s">
         <v>1</v>
@@ -5447,7 +5744,7 @@
         <v>65</v>
       </c>
       <c r="F192" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G192" s="3">
         <v>122.8</v>
@@ -5455,10 +5752,10 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B193" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C193" t="s">
         <v>1</v>
@@ -5475,22 +5772,19 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B194" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C194" t="s">
         <v>1</v>
       </c>
       <c r="D194" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E194" t="s">
-        <v>68</v>
-      </c>
-      <c r="F194" t="s">
-        <v>218</v>
+        <v>415</v>
       </c>
       <c r="G194" s="3">
         <v>123.375</v>
@@ -5498,16 +5792,16 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B195" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C195" t="s">
         <v>1</v>
       </c>
       <c r="D195" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E195" t="s">
         <v>69</v>
@@ -5518,10 +5812,10 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B196" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C196" t="s">
         <v>1</v>
@@ -5530,7 +5824,7 @@
         <v>15</v>
       </c>
       <c r="E196" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G196" s="3">
         <v>128.69999999999999</v>
@@ -5538,10 +5832,10 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B197" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C197" t="s">
         <v>1</v>
@@ -5553,7 +5847,7 @@
         <v>65</v>
       </c>
       <c r="F197" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G197" s="3">
         <v>122.8</v>
@@ -5561,10 +5855,10 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B198" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C198" t="s">
         <v>1</v>
@@ -5581,10 +5875,10 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B199" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C199" t="s">
         <v>1</v>
@@ -5596,7 +5890,7 @@
         <v>65</v>
       </c>
       <c r="F199" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G199" s="3">
         <v>122.8</v>
@@ -5604,10 +5898,10 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B200" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C200" t="s">
         <v>1</v>
@@ -5619,7 +5913,7 @@
         <v>65</v>
       </c>
       <c r="F200" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G200" s="3">
         <v>122.8</v>
@@ -5627,22 +5921,22 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B201" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C201" t="s">
         <v>1</v>
       </c>
       <c r="D201" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E201" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F201" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G201" s="3">
         <v>122.3</v>
@@ -5650,22 +5944,19 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B202" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C202" t="s">
         <v>1</v>
       </c>
       <c r="D202" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E202" t="s">
-        <v>68</v>
-      </c>
-      <c r="F202" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="G202" s="3">
         <v>123.55</v>
@@ -5673,16 +5964,16 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B203" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C203" t="s">
         <v>1</v>
       </c>
       <c r="D203" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E203" t="s">
         <v>69</v>
@@ -5693,10 +5984,10 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B204" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C204" t="s">
         <v>1</v>
@@ -5705,10 +5996,10 @@
         <v>12</v>
       </c>
       <c r="E204" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F204" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G204" s="3">
         <v>122.3</v>
@@ -5716,19 +6007,19 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B205" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C205" t="s">
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E205" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G205" s="3">
         <v>135.32499999999999</v>
@@ -5736,10 +6027,10 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B206" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C206" t="s">
         <v>1</v>
@@ -5751,7 +6042,7 @@
         <v>65</v>
       </c>
       <c r="F206" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G206" s="3">
         <v>122.8</v>
@@ -5759,10 +6050,10 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B207" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C207" t="s">
         <v>1</v>
@@ -5779,10 +6070,10 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B208" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C208" t="s">
         <v>1</v>
@@ -5791,18 +6082,18 @@
         <v>16</v>
       </c>
       <c r="E208" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B209" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C209" t="s">
         <v>1</v>
@@ -5811,18 +6102,18 @@
         <v>17</v>
       </c>
       <c r="E209" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B210" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C210" t="s">
         <v>1</v>
@@ -5834,7 +6125,7 @@
         <v>65</v>
       </c>
       <c r="F210" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G210" s="3">
         <v>122.8</v>
@@ -5842,19 +6133,19 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B211" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C211" t="s">
         <v>1</v>
       </c>
       <c r="D211" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E211" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G211" s="3">
         <v>135.19999999999999</v>
@@ -5862,30 +6153,30 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>232</v>
+      </c>
+      <c r="B212" t="s">
+        <v>233</v>
+      </c>
+      <c r="C212" t="s">
+        <v>1</v>
+      </c>
+      <c r="D212" t="s">
+        <v>235</v>
+      </c>
+      <c r="E212" t="s">
         <v>236</v>
       </c>
-      <c r="B212" t="s">
+      <c r="G212" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="C212" t="s">
-        <v>1</v>
-      </c>
-      <c r="D212" t="s">
-        <v>239</v>
-      </c>
-      <c r="E212" t="s">
-        <v>240</v>
-      </c>
-      <c r="G212" s="3" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B213" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C213" t="s">
         <v>1</v>
@@ -5902,22 +6193,19 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B214" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C214" t="s">
         <v>1</v>
       </c>
       <c r="D214" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E214" t="s">
-        <v>228</v>
-      </c>
-      <c r="F214" t="s">
-        <v>246</v>
+        <v>416</v>
       </c>
       <c r="G214" s="3">
         <v>122.2</v>
@@ -5925,22 +6213,22 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B215" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C215" t="s">
         <v>1</v>
       </c>
       <c r="D215" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E215" t="s">
-        <v>68</v>
+        <v>275</v>
       </c>
       <c r="F215" t="s">
-        <v>247</v>
+        <v>417</v>
       </c>
       <c r="G215" s="3">
         <v>123.47499999999999</v>
@@ -5948,16 +6236,16 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B216" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C216" t="s">
         <v>1</v>
       </c>
       <c r="D216" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E216" t="s">
         <v>69</v>
@@ -5968,10 +6256,10 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B217" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C217" t="s">
         <v>1</v>
@@ -5980,10 +6268,10 @@
         <v>12</v>
       </c>
       <c r="E217" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F217" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G217" s="3">
         <v>122.2</v>
@@ -5991,10 +6279,10 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B218" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C218" t="s">
         <v>1</v>
@@ -6008,10 +6296,10 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B219" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C219" t="s">
         <v>1</v>
@@ -6023,7 +6311,7 @@
         <v>65</v>
       </c>
       <c r="F219" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G219" s="3">
         <v>122.8</v>
@@ -6031,10 +6319,10 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B220" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C220" t="s">
         <v>1</v>
@@ -6046,7 +6334,7 @@
         <v>65</v>
       </c>
       <c r="F220" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G220" s="3">
         <v>122.8</v>
@@ -6054,10 +6342,10 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B221" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C221" t="s">
         <v>1</v>
@@ -6071,22 +6359,19 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B222" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C222" t="s">
         <v>1</v>
       </c>
       <c r="D222" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E222" t="s">
-        <v>68</v>
-      </c>
-      <c r="F222" t="s">
-        <v>256</v>
+        <v>418</v>
       </c>
       <c r="G222" s="3">
         <v>123.375</v>
@@ -6094,10 +6379,10 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B223" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C223" t="s">
         <v>1</v>
@@ -6109,7 +6394,7 @@
         <v>65</v>
       </c>
       <c r="F223" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G223" s="3">
         <v>123.5</v>
@@ -6117,10 +6402,10 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B224" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C224" t="s">
         <v>1</v>
@@ -6132,7 +6417,7 @@
         <v>65</v>
       </c>
       <c r="F224" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G224" s="3">
         <v>128</v>
@@ -6140,10 +6425,10 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B225" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C225" t="s">
         <v>1</v>
@@ -6160,10 +6445,10 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B226" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C226" t="s">
         <v>1</v>
@@ -6175,7 +6460,7 @@
         <v>65</v>
       </c>
       <c r="F226" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G226" s="3">
         <v>123.5</v>
@@ -6183,16 +6468,16 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B227" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C227" t="s">
         <v>1</v>
       </c>
       <c r="D227" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G227" s="3">
         <v>129.15</v>
@@ -6200,10 +6485,10 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B228" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C228" t="s">
         <v>1</v>
@@ -6215,7 +6500,7 @@
         <v>65</v>
       </c>
       <c r="F228" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G228" s="3">
         <v>122.8</v>
@@ -6223,22 +6508,19 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B229" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C229" t="s">
         <v>1</v>
       </c>
       <c r="D229" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E229" t="s">
-        <v>68</v>
-      </c>
-      <c r="F229" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="G229" s="3">
         <v>123.55</v>
@@ -6246,10 +6528,10 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B230" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C230" t="s">
         <v>1</v>
@@ -6266,19 +6548,19 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B231" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C231" t="s">
         <v>1</v>
       </c>
       <c r="D231" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E231" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G231" s="3">
         <v>134.07499999999999</v>
@@ -6286,10 +6568,10 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B232" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C232" t="s">
         <v>1</v>
@@ -6306,10 +6588,10 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B233" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C233" t="s">
         <v>1</v>
@@ -6321,7 +6603,7 @@
         <v>65</v>
       </c>
       <c r="F233" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G233" s="3">
         <v>123</v>
@@ -6329,10 +6611,10 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B234" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C234" t="s">
         <v>1</v>
@@ -6344,7 +6626,7 @@
         <v>65</v>
       </c>
       <c r="F234" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G234" s="3">
         <v>122.8</v>
@@ -6352,22 +6634,22 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B235" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C235" t="s">
         <v>1</v>
       </c>
       <c r="D235" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E235" t="s">
-        <v>228</v>
+        <v>420</v>
       </c>
       <c r="F235" t="s">
-        <v>275</v>
+        <v>419</v>
       </c>
       <c r="G235" s="3">
         <v>122.5</v>
@@ -6375,22 +6657,19 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B236" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C236" t="s">
         <v>1</v>
       </c>
       <c r="D236" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E236" t="s">
-        <v>68</v>
-      </c>
-      <c r="F236" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="G236" s="3">
         <v>123.47499999999999</v>
@@ -6398,16 +6677,16 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B237" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C237" t="s">
         <v>1</v>
       </c>
       <c r="D237" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E237" t="s">
         <v>69</v>
@@ -6418,10 +6697,10 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B238" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C238" t="s">
         <v>1</v>
@@ -6430,10 +6709,10 @@
         <v>12</v>
       </c>
       <c r="E238" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F238" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G238" s="3">
         <v>122.5</v>
@@ -6441,19 +6720,19 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B239" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C239" t="s">
         <v>1</v>
       </c>
       <c r="D239" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E239" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G239" s="3">
         <v>133.72499999999999</v>
@@ -6461,10 +6740,10 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B240" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C240" t="s">
         <v>1</v>
@@ -6478,10 +6757,10 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B241" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C241" t="s">
         <v>1</v>
@@ -6498,10 +6777,10 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B242" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C242" t="s">
         <v>1</v>
@@ -6513,7 +6792,7 @@
         <v>65</v>
       </c>
       <c r="F242" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G242" s="3">
         <v>122.72499999999999</v>
@@ -6521,10 +6800,10 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B243" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C243" t="s">
         <v>1</v>
@@ -6533,7 +6812,7 @@
         <v>16</v>
       </c>
       <c r="E243" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G243" s="3">
         <v>134.25</v>
@@ -6541,10 +6820,10 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B244" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C244" t="s">
         <v>1</v>
@@ -6553,7 +6832,7 @@
         <v>17</v>
       </c>
       <c r="E244" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G244" s="3">
         <v>134.25</v>
@@ -6561,19 +6840,19 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B245" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C245" t="s">
         <v>1</v>
       </c>
       <c r="D245" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E245" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G245" s="3">
         <v>123.27500000000001</v>
@@ -6581,16 +6860,16 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B246" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C246" t="s">
         <v>1</v>
       </c>
       <c r="D246" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E246" t="s">
         <v>69</v>
@@ -6601,10 +6880,10 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B247" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C247" t="s">
         <v>1</v>
@@ -6621,19 +6900,19 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B248" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C248" t="s">
         <v>1</v>
       </c>
       <c r="D248" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E248" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G248" s="3">
         <v>132.69999999999999</v>
@@ -6641,10 +6920,10 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B249" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C249" t="s">
         <v>1</v>
@@ -6656,7 +6935,7 @@
         <v>65</v>
       </c>
       <c r="F249" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G249" s="3">
         <v>122.8</v>
@@ -6664,16 +6943,16 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B250" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C250" t="s">
         <v>1</v>
       </c>
       <c r="D250" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G250" s="3">
         <v>122.55</v>
@@ -6681,19 +6960,19 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B251" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C251" t="s">
         <v>1</v>
       </c>
       <c r="D251" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F251" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="G251" s="3">
         <v>122.5</v>
@@ -6701,22 +6980,19 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B252" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C252" t="s">
         <v>1</v>
       </c>
       <c r="D252" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E252" t="s">
-        <v>68</v>
-      </c>
-      <c r="F252" t="s">
-        <v>87</v>
+        <v>275</v>
       </c>
       <c r="G252" s="3">
         <v>123.55</v>
@@ -6724,16 +7000,16 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B253" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C253" t="s">
         <v>1</v>
       </c>
       <c r="D253" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E253" t="s">
         <v>69</v>
@@ -6744,10 +7020,10 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B254" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C254" t="s">
         <v>1</v>
@@ -6756,7 +7032,7 @@
         <v>41</v>
       </c>
       <c r="F254" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="G254" s="3">
         <v>135.55000000000001</v>
@@ -6764,10 +7040,10 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B255" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C255" t="s">
         <v>1</v>
@@ -6776,10 +7052,10 @@
         <v>12</v>
       </c>
       <c r="E255" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F255" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="G255" s="3">
         <v>122.5</v>
@@ -6787,10 +7063,10 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B256" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C256" t="s">
         <v>1</v>
@@ -6802,7 +7078,7 @@
         <v>67</v>
       </c>
       <c r="F256" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="G256" s="3">
         <v>122.5</v>
@@ -6810,10 +7086,10 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B257" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C257" t="s">
         <v>1</v>
@@ -6825,7 +7101,7 @@
         <v>65</v>
       </c>
       <c r="F257" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G257" s="3">
         <v>122.8</v>
@@ -6833,10 +7109,10 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B258" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="C258" t="s">
         <v>1</v>
@@ -6853,10 +7129,10 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B259" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C259" t="s">
         <v>1</v>
@@ -6868,7 +7144,7 @@
         <v>65</v>
       </c>
       <c r="F259" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G259" s="3">
         <v>122.8</v>
@@ -6876,10 +7152,10 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B260" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="C260" t="s">
         <v>1</v>
@@ -6891,7 +7167,7 @@
         <v>65</v>
       </c>
       <c r="F260" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="G260" s="3">
         <v>122.8</v>
@@ -6899,10 +7175,10 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B261" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C261" t="s">
         <v>1</v>
@@ -6916,10 +7192,10 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B262" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C262" t="s">
         <v>1</v>
@@ -6933,10 +7209,10 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B263" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C263" t="s">
         <v>1</v>
@@ -6950,10 +7226,10 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B264" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C264" t="s">
         <v>1</v>
@@ -6962,7 +7238,7 @@
         <v>16</v>
       </c>
       <c r="E264" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="G264" s="3">
         <v>119.7</v>
@@ -6970,10 +7246,10 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B265" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C265" t="s">
         <v>1</v>
@@ -6982,7 +7258,7 @@
         <v>17</v>
       </c>
       <c r="E265" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="G265" s="3">
         <v>119.7</v>
@@ -6990,19 +7266,19 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B266" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C266" t="s">
         <v>1</v>
       </c>
       <c r="D266" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E266" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="G266" s="3">
         <v>119.7</v>
@@ -7010,10 +7286,10 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B267" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="C267" t="s">
         <v>1</v>
@@ -7025,7 +7301,7 @@
         <v>65</v>
       </c>
       <c r="F267" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G267" s="3">
         <v>122.8</v>
@@ -7033,10 +7309,10 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B268" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C268" t="s">
         <v>1</v>
@@ -7048,7 +7324,7 @@
         <v>65</v>
       </c>
       <c r="F268" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G268" s="3">
         <v>122.8</v>
@@ -7056,19 +7332,19 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B269" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="C269" t="s">
         <v>1</v>
       </c>
       <c r="D269" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="E269" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G269" s="3">
         <v>126.7</v>
@@ -7076,10 +7352,10 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B270" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="C270" t="s">
         <v>1</v>
@@ -7091,7 +7367,7 @@
         <v>65</v>
       </c>
       <c r="F270" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G270" s="3">
         <v>122.8</v>
@@ -7099,10 +7375,10 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B271" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C271" t="s">
         <v>1</v>
@@ -7119,19 +7395,19 @@
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B272" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C272" t="s">
         <v>1</v>
       </c>
       <c r="D272" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E272" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G272" s="3">
         <v>123.47499999999999</v>
@@ -7139,16 +7415,16 @@
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B273" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C273" t="s">
         <v>1</v>
       </c>
       <c r="D273" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E273" t="s">
         <v>69</v>
@@ -7159,22 +7435,22 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B274" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C274" t="s">
         <v>1</v>
       </c>
       <c r="D274" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E274" t="s">
         <v>65</v>
       </c>
       <c r="F274" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G274" s="3">
         <v>122.8</v>
@@ -7182,10 +7458,10 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B275" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C275" t="s">
         <v>1</v>
@@ -7199,19 +7475,19 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B276" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C276" t="s">
         <v>1</v>
       </c>
       <c r="D276" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E276" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G276" s="3">
         <v>126.7</v>
@@ -7219,22 +7495,22 @@
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B277" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C277" t="s">
         <v>1</v>
       </c>
       <c r="D277" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E277" t="s">
         <v>65</v>
       </c>
       <c r="F277" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G277" s="3">
         <v>122.8</v>
@@ -7242,10 +7518,10 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B278" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C278" t="s">
         <v>1</v>
@@ -7259,10 +7535,10 @@
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B279" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C279" t="s">
         <v>1</v>
@@ -7279,10 +7555,10 @@
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B280" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C280" t="s">
         <v>1</v>
@@ -7299,10 +7575,10 @@
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B281" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C281" t="s">
         <v>1</v>
@@ -7319,10 +7595,10 @@
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B282" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C282" t="s">
         <v>1</v>
@@ -7339,10 +7615,10 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B283" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C283" t="s">
         <v>1</v>
@@ -7359,10 +7635,10 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B284" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C284" t="s">
         <v>1</v>
@@ -7379,10 +7655,10 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B285" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="C285" t="s">
         <v>1</v>
@@ -7399,19 +7675,19 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B286" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="C286" t="s">
         <v>1</v>
       </c>
       <c r="D286" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E286" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="G286" s="3">
         <v>119.7</v>
@@ -7419,19 +7695,19 @@
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B287" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C287" t="s">
         <v>1</v>
       </c>
       <c r="D287" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E287" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G287" s="3">
         <v>123.55</v>
@@ -7439,16 +7715,16 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B288" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C288" t="s">
         <v>1</v>
       </c>
       <c r="D288" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E288" t="s">
         <v>69</v>
@@ -7459,10 +7735,10 @@
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B289" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C289" t="s">
         <v>1</v>
@@ -7474,7 +7750,7 @@
         <v>65</v>
       </c>
       <c r="F289" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G289" s="3">
         <v>122.8</v>
@@ -7482,19 +7758,19 @@
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B290" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C290" t="s">
         <v>1</v>
       </c>
       <c r="D290" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E290" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="G290" s="3">
         <v>120</v>
@@ -7502,10 +7778,10 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B291" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C291" t="s">
         <v>1</v>
@@ -7522,19 +7798,19 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="B292" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C292" t="s">
         <v>1</v>
       </c>
       <c r="D292" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E292" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G292" s="3">
         <v>123.375</v>
@@ -7542,10 +7818,10 @@
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="B293" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C293" t="s">
         <v>1</v>
@@ -7562,10 +7838,10 @@
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="B294" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C294" t="s">
         <v>1</v>
@@ -7579,10 +7855,10 @@
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B295" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C295" t="s">
         <v>1</v>
@@ -7594,7 +7870,7 @@
         <v>65</v>
       </c>
       <c r="F295" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G295" s="3">
         <v>122.77500000000001</v>
@@ -7602,16 +7878,16 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B296" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C296" t="s">
         <v>1</v>
       </c>
       <c r="D296" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G296" s="3">
         <v>123.175</v>
@@ -7619,10 +7895,10 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B297" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C297" t="s">
         <v>1</v>
@@ -7639,10 +7915,10 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="B298" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C298" t="s">
         <v>1</v>
@@ -7654,7 +7930,7 @@
         <v>65</v>
       </c>
       <c r="F298" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G298" s="3">
         <v>122.8</v>
@@ -7662,10 +7938,10 @@
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B299" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C299" t="s">
         <v>1</v>
@@ -7682,19 +7958,19 @@
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B300" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C300" t="s">
         <v>1</v>
       </c>
       <c r="D300" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E300" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="G300" s="3">
         <v>122.1</v>
@@ -7702,10 +7978,10 @@
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B301" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C301" t="s">
         <v>1</v>
@@ -7714,7 +7990,7 @@
         <v>12</v>
       </c>
       <c r="E301" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="G301" s="3">
         <v>122.1</v>
@@ -7722,19 +7998,19 @@
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B302" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C302" t="s">
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E302" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G302" s="3">
         <v>132.19999999999999</v>
@@ -7742,19 +8018,19 @@
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B303" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C303" t="s">
         <v>1</v>
       </c>
       <c r="D303" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E303" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="G303" s="3">
         <v>122.9</v>
@@ -7762,10 +8038,10 @@
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B304" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C304" t="s">
         <v>1</v>
@@ -7779,10 +8055,10 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B305" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="C305" t="s">
         <v>1</v>
@@ -7799,10 +8075,10 @@
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B306" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C306" t="s">
         <v>1</v>
@@ -7819,10 +8095,10 @@
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B307" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C307" t="s">
         <v>1</v>
@@ -7834,7 +8110,7 @@
         <v>65</v>
       </c>
       <c r="F307" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G307" s="3">
         <v>122.8</v>
@@ -7842,10 +8118,10 @@
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B308" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C308" t="s">
         <v>1</v>
@@ -7862,10 +8138,10 @@
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B309" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C309" t="s">
         <v>1</v>
@@ -7882,16 +8158,16 @@
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B310" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C310" t="s">
         <v>1</v>
       </c>
       <c r="D310" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G310" s="3">
         <v>122.55</v>
@@ -7899,10 +8175,10 @@
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B311" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C311" t="s">
         <v>1</v>
@@ -7914,7 +8190,7 @@
         <v>65</v>
       </c>
       <c r="F311" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G311" s="3">
         <v>122.77500000000001</v>
@@ -7922,19 +8198,19 @@
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B312" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C312" t="s">
         <v>1</v>
       </c>
       <c r="D312" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E312" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="G312" s="3">
         <v>123.47499999999999</v>
@@ -7942,16 +8218,16 @@
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B313" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C313" t="s">
         <v>1</v>
       </c>
       <c r="D313" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E313" t="s">
         <v>69</v>
@@ -7962,10 +8238,10 @@
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B314" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C314" t="s">
         <v>1</v>
@@ -7977,7 +8253,7 @@
         <v>65</v>
       </c>
       <c r="F314" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G314" s="3">
         <v>122.8</v>
@@ -7985,10 +8261,10 @@
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B315" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C315" t="s">
         <v>1</v>
@@ -8000,7 +8276,7 @@
         <v>65</v>
       </c>
       <c r="F315" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G315" s="3">
         <v>123</v>
@@ -8008,10 +8284,10 @@
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B316" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C316" t="s">
         <v>1</v>
@@ -8020,7 +8296,7 @@
         <v>16</v>
       </c>
       <c r="E316" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G316" s="3">
         <v>134.67500000000001</v>
@@ -8028,10 +8304,10 @@
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B317" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C317" t="s">
         <v>1</v>
@@ -8040,7 +8316,7 @@
         <v>17</v>
       </c>
       <c r="E317" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G317" s="3">
         <v>134.67500000000001</v>
@@ -8048,19 +8324,19 @@
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B318" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C318" t="s">
         <v>1</v>
       </c>
       <c r="D318" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E318" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="G318" s="3">
         <v>118.52500000000001</v>
@@ -8068,10 +8344,10 @@
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B319" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C319" t="s">
         <v>1</v>
@@ -8083,7 +8359,7 @@
         <v>65</v>
       </c>
       <c r="F319" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G319" s="3">
         <v>122.7</v>
@@ -8091,19 +8367,19 @@
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B320" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C320" t="s">
         <v>1</v>
       </c>
       <c r="D320" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E320" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G320" s="3">
         <v>123.27500000000001</v>
@@ -8111,16 +8387,16 @@
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B321" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C321" t="s">
         <v>1</v>
       </c>
       <c r="D321" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E321" t="s">
         <v>69</v>
@@ -8131,10 +8407,10 @@
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B322" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C322" t="s">
         <v>1</v>
@@ -8146,10 +8422,2071 @@
         <v>67</v>
       </c>
       <c r="F322" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G322" s="3">
         <v>122.3</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>363</v>
+      </c>
+      <c r="B323" t="s">
+        <v>365</v>
+      </c>
+      <c r="C323" t="s">
+        <v>364</v>
+      </c>
+      <c r="D323" t="s">
+        <v>12</v>
+      </c>
+      <c r="E323" t="s">
+        <v>367</v>
+      </c>
+      <c r="F323" t="s">
+        <v>87</v>
+      </c>
+      <c r="G323" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>363</v>
+      </c>
+      <c r="B324" t="s">
+        <v>365</v>
+      </c>
+      <c r="C324" t="s">
+        <v>364</v>
+      </c>
+      <c r="D324" t="s">
+        <v>366</v>
+      </c>
+      <c r="F324" t="s">
+        <v>368</v>
+      </c>
+      <c r="G324" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>369</v>
+      </c>
+      <c r="B325" t="s">
+        <v>370</v>
+      </c>
+      <c r="C325" t="s">
+        <v>9</v>
+      </c>
+      <c r="D325" t="s">
+        <v>64</v>
+      </c>
+      <c r="E325" t="s">
+        <v>67</v>
+      </c>
+      <c r="G325" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>371</v>
+      </c>
+      <c r="B326" t="s">
+        <v>372</v>
+      </c>
+      <c r="C326" t="s">
+        <v>373</v>
+      </c>
+      <c r="D326" t="s">
+        <v>64</v>
+      </c>
+      <c r="E326" t="s">
+        <v>67</v>
+      </c>
+      <c r="G326" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>371</v>
+      </c>
+      <c r="B327" t="s">
+        <v>372</v>
+      </c>
+      <c r="C327" t="s">
+        <v>373</v>
+      </c>
+      <c r="D327" t="s">
+        <v>185</v>
+      </c>
+      <c r="E327" t="s">
+        <v>374</v>
+      </c>
+      <c r="G327" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>376</v>
+      </c>
+      <c r="B328" t="s">
+        <v>375</v>
+      </c>
+      <c r="C328" t="s">
+        <v>373</v>
+      </c>
+      <c r="D328" t="s">
+        <v>12</v>
+      </c>
+      <c r="E328" t="s">
+        <v>367</v>
+      </c>
+      <c r="F328" t="s">
+        <v>87</v>
+      </c>
+      <c r="G328" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>376</v>
+      </c>
+      <c r="B329" t="s">
+        <v>375</v>
+      </c>
+      <c r="C329" t="s">
+        <v>373</v>
+      </c>
+      <c r="D329" t="s">
+        <v>366</v>
+      </c>
+      <c r="F329" t="s">
+        <v>378</v>
+      </c>
+      <c r="G329" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>376</v>
+      </c>
+      <c r="B330" t="s">
+        <v>375</v>
+      </c>
+      <c r="C330" t="s">
+        <v>373</v>
+      </c>
+      <c r="D330" t="s">
+        <v>377</v>
+      </c>
+      <c r="G330" s="3">
+        <v>128.69999999999999</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>379</v>
+      </c>
+      <c r="B331" t="s">
+        <v>380</v>
+      </c>
+      <c r="C331" t="s">
+        <v>373</v>
+      </c>
+      <c r="D331" t="s">
+        <v>64</v>
+      </c>
+      <c r="E331" t="s">
+        <v>67</v>
+      </c>
+      <c r="G331" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>381</v>
+      </c>
+      <c r="B332" t="s">
+        <v>382</v>
+      </c>
+      <c r="C332" t="s">
+        <v>373</v>
+      </c>
+      <c r="D332" t="s">
+        <v>12</v>
+      </c>
+      <c r="E332" t="s">
+        <v>367</v>
+      </c>
+      <c r="F332" t="s">
+        <v>87</v>
+      </c>
+      <c r="G332" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>381</v>
+      </c>
+      <c r="B333" t="s">
+        <v>382</v>
+      </c>
+      <c r="C333" t="s">
+        <v>373</v>
+      </c>
+      <c r="D333" t="s">
+        <v>366</v>
+      </c>
+      <c r="F333" t="s">
+        <v>383</v>
+      </c>
+      <c r="G333" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>381</v>
+      </c>
+      <c r="B334" t="s">
+        <v>382</v>
+      </c>
+      <c r="C334" t="s">
+        <v>373</v>
+      </c>
+      <c r="D334" t="s">
+        <v>2</v>
+      </c>
+      <c r="G334" s="3">
+        <v>128.69999999999999</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>384</v>
+      </c>
+      <c r="B335" t="s">
+        <v>385</v>
+      </c>
+      <c r="C335" t="s">
+        <v>373</v>
+      </c>
+      <c r="D335" t="s">
+        <v>74</v>
+      </c>
+      <c r="E335" t="s">
+        <v>386</v>
+      </c>
+      <c r="G335" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>384</v>
+      </c>
+      <c r="B336" t="s">
+        <v>385</v>
+      </c>
+      <c r="C336" t="s">
+        <v>373</v>
+      </c>
+      <c r="D336" t="s">
+        <v>74</v>
+      </c>
+      <c r="E336" t="s">
+        <v>69</v>
+      </c>
+      <c r="G336" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>384</v>
+      </c>
+      <c r="B337" t="s">
+        <v>385</v>
+      </c>
+      <c r="C337" t="s">
+        <v>373</v>
+      </c>
+      <c r="D337" t="s">
+        <v>12</v>
+      </c>
+      <c r="E337" t="s">
+        <v>367</v>
+      </c>
+      <c r="F337" t="s">
+        <v>87</v>
+      </c>
+      <c r="G337" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>384</v>
+      </c>
+      <c r="B338" t="s">
+        <v>385</v>
+      </c>
+      <c r="C338" t="s">
+        <v>373</v>
+      </c>
+      <c r="D338" t="s">
+        <v>366</v>
+      </c>
+      <c r="G338" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>388</v>
+      </c>
+      <c r="B339" t="s">
+        <v>390</v>
+      </c>
+      <c r="C339" t="s">
+        <v>389</v>
+      </c>
+      <c r="D339" t="s">
+        <v>74</v>
+      </c>
+      <c r="E339" t="s">
+        <v>391</v>
+      </c>
+      <c r="G339" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>388</v>
+      </c>
+      <c r="B340" t="s">
+        <v>390</v>
+      </c>
+      <c r="C340" t="s">
+        <v>389</v>
+      </c>
+      <c r="D340" t="s">
+        <v>74</v>
+      </c>
+      <c r="E340" t="s">
+        <v>69</v>
+      </c>
+      <c r="G340" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>388</v>
+      </c>
+      <c r="B341" t="s">
+        <v>390</v>
+      </c>
+      <c r="C341" t="s">
+        <v>389</v>
+      </c>
+      <c r="D341" t="s">
+        <v>12</v>
+      </c>
+      <c r="E341" t="s">
+        <v>367</v>
+      </c>
+      <c r="F341" t="s">
+        <v>87</v>
+      </c>
+      <c r="G341" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>388</v>
+      </c>
+      <c r="B342" t="s">
+        <v>390</v>
+      </c>
+      <c r="C342" t="s">
+        <v>389</v>
+      </c>
+      <c r="D342" t="s">
+        <v>366</v>
+      </c>
+      <c r="G342" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>392</v>
+      </c>
+      <c r="B343" t="s">
+        <v>393</v>
+      </c>
+      <c r="C343" t="s">
+        <v>389</v>
+      </c>
+      <c r="D343" t="s">
+        <v>64</v>
+      </c>
+      <c r="E343" t="s">
+        <v>67</v>
+      </c>
+      <c r="G343" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>394</v>
+      </c>
+      <c r="B344" t="s">
+        <v>395</v>
+      </c>
+      <c r="C344" t="s">
+        <v>6</v>
+      </c>
+      <c r="D344" t="s">
+        <v>64</v>
+      </c>
+      <c r="E344" t="s">
+        <v>67</v>
+      </c>
+      <c r="G344" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>396</v>
+      </c>
+      <c r="B345" t="s">
+        <v>397</v>
+      </c>
+      <c r="C345" t="s">
+        <v>389</v>
+      </c>
+      <c r="D345" t="s">
+        <v>74</v>
+      </c>
+      <c r="E345" t="s">
+        <v>398</v>
+      </c>
+      <c r="G345" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>396</v>
+      </c>
+      <c r="B346" t="s">
+        <v>397</v>
+      </c>
+      <c r="C346" t="s">
+        <v>389</v>
+      </c>
+      <c r="D346" t="s">
+        <v>74</v>
+      </c>
+      <c r="E346" t="s">
+        <v>399</v>
+      </c>
+      <c r="G346" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>396</v>
+      </c>
+      <c r="B347" t="s">
+        <v>397</v>
+      </c>
+      <c r="C347" t="s">
+        <v>389</v>
+      </c>
+      <c r="D347" t="s">
+        <v>74</v>
+      </c>
+      <c r="E347" t="s">
+        <v>69</v>
+      </c>
+      <c r="G347" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>396</v>
+      </c>
+      <c r="B348" t="s">
+        <v>397</v>
+      </c>
+      <c r="C348" t="s">
+        <v>389</v>
+      </c>
+      <c r="D348" t="s">
+        <v>12</v>
+      </c>
+      <c r="E348" t="s">
+        <v>367</v>
+      </c>
+      <c r="F348" t="s">
+        <v>87</v>
+      </c>
+      <c r="G348" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>396</v>
+      </c>
+      <c r="B349" t="s">
+        <v>397</v>
+      </c>
+      <c r="C349" t="s">
+        <v>389</v>
+      </c>
+      <c r="D349" t="s">
+        <v>366</v>
+      </c>
+      <c r="G349" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>396</v>
+      </c>
+      <c r="B350" t="s">
+        <v>397</v>
+      </c>
+      <c r="C350" t="s">
+        <v>389</v>
+      </c>
+      <c r="D350" t="s">
+        <v>2</v>
+      </c>
+      <c r="G350" s="3">
+        <v>128.69999999999999</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>400</v>
+      </c>
+      <c r="B351" t="s">
+        <v>401</v>
+      </c>
+      <c r="C351" t="s">
+        <v>373</v>
+      </c>
+      <c r="D351" t="s">
+        <v>74</v>
+      </c>
+      <c r="E351" t="s">
+        <v>386</v>
+      </c>
+      <c r="G351" s="3">
+        <v>123.25</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>400</v>
+      </c>
+      <c r="B352" t="s">
+        <v>401</v>
+      </c>
+      <c r="C352" t="s">
+        <v>373</v>
+      </c>
+      <c r="D352" t="s">
+        <v>74</v>
+      </c>
+      <c r="E352" t="s">
+        <v>69</v>
+      </c>
+      <c r="G352" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>400</v>
+      </c>
+      <c r="B353" t="s">
+        <v>401</v>
+      </c>
+      <c r="C353" t="s">
+        <v>373</v>
+      </c>
+      <c r="D353" t="s">
+        <v>12</v>
+      </c>
+      <c r="E353" t="s">
+        <v>367</v>
+      </c>
+      <c r="G353" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>400</v>
+      </c>
+      <c r="B354" t="s">
+        <v>401</v>
+      </c>
+      <c r="C354" t="s">
+        <v>373</v>
+      </c>
+      <c r="D354" t="s">
+        <v>76</v>
+      </c>
+      <c r="E354" t="s">
+        <v>402</v>
+      </c>
+      <c r="G354" s="3">
+        <v>134.67500000000001</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>400</v>
+      </c>
+      <c r="B355" t="s">
+        <v>401</v>
+      </c>
+      <c r="C355" t="s">
+        <v>373</v>
+      </c>
+      <c r="D355" t="s">
+        <v>366</v>
+      </c>
+      <c r="G355" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>400</v>
+      </c>
+      <c r="B356" t="s">
+        <v>401</v>
+      </c>
+      <c r="C356" t="s">
+        <v>373</v>
+      </c>
+      <c r="D356" t="s">
+        <v>185</v>
+      </c>
+      <c r="G356" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>400</v>
+      </c>
+      <c r="B357" t="s">
+        <v>401</v>
+      </c>
+      <c r="C357" t="s">
+        <v>373</v>
+      </c>
+      <c r="D357" t="s">
+        <v>404</v>
+      </c>
+      <c r="E357" t="s">
+        <v>405</v>
+      </c>
+      <c r="G357" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>407</v>
+      </c>
+      <c r="B358" t="s">
+        <v>408</v>
+      </c>
+      <c r="C358" t="s">
+        <v>389</v>
+      </c>
+      <c r="D358" t="s">
+        <v>64</v>
+      </c>
+      <c r="E358" t="s">
+        <v>67</v>
+      </c>
+      <c r="G358" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>409</v>
+      </c>
+      <c r="B359" t="s">
+        <v>410</v>
+      </c>
+      <c r="C359" t="s">
+        <v>389</v>
+      </c>
+      <c r="D359" t="s">
+        <v>64</v>
+      </c>
+      <c r="E359" t="s">
+        <v>67</v>
+      </c>
+      <c r="G359" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>411</v>
+      </c>
+      <c r="B360" t="s">
+        <v>412</v>
+      </c>
+      <c r="C360" t="s">
+        <v>6</v>
+      </c>
+      <c r="D360" t="s">
+        <v>64</v>
+      </c>
+      <c r="E360" t="s">
+        <v>65</v>
+      </c>
+      <c r="F360" t="s">
+        <v>87</v>
+      </c>
+      <c r="G360" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>421</v>
+      </c>
+      <c r="B361" t="s">
+        <v>422</v>
+      </c>
+      <c r="C361" t="s">
+        <v>373</v>
+      </c>
+      <c r="D361" t="s">
+        <v>12</v>
+      </c>
+      <c r="E361" t="s">
+        <v>367</v>
+      </c>
+      <c r="F361" t="s">
+        <v>87</v>
+      </c>
+      <c r="G361" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>421</v>
+      </c>
+      <c r="B362" t="s">
+        <v>422</v>
+      </c>
+      <c r="C362" t="s">
+        <v>373</v>
+      </c>
+      <c r="D362" t="s">
+        <v>423</v>
+      </c>
+      <c r="F362" t="s">
+        <v>383</v>
+      </c>
+      <c r="G362" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>424</v>
+      </c>
+      <c r="B363" t="s">
+        <v>425</v>
+      </c>
+      <c r="C363" t="s">
+        <v>373</v>
+      </c>
+      <c r="D363" t="s">
+        <v>12</v>
+      </c>
+      <c r="E363" t="s">
+        <v>367</v>
+      </c>
+      <c r="F363" t="s">
+        <v>87</v>
+      </c>
+      <c r="G363" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>424</v>
+      </c>
+      <c r="B364" t="s">
+        <v>425</v>
+      </c>
+      <c r="C364" t="s">
+        <v>373</v>
+      </c>
+      <c r="D364" t="s">
+        <v>423</v>
+      </c>
+      <c r="F364" t="s">
+        <v>426</v>
+      </c>
+      <c r="G364" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>424</v>
+      </c>
+      <c r="B365" t="s">
+        <v>425</v>
+      </c>
+      <c r="C365" t="s">
+        <v>373</v>
+      </c>
+      <c r="D365" t="s">
+        <v>2</v>
+      </c>
+      <c r="G365" s="3">
+        <v>124.6</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>427</v>
+      </c>
+      <c r="B366" t="s">
+        <v>428</v>
+      </c>
+      <c r="C366" t="s">
+        <v>364</v>
+      </c>
+      <c r="D366" t="s">
+        <v>64</v>
+      </c>
+      <c r="E366" t="s">
+        <v>67</v>
+      </c>
+      <c r="G366" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>427</v>
+      </c>
+      <c r="B367" t="s">
+        <v>428</v>
+      </c>
+      <c r="C367" t="s">
+        <v>364</v>
+      </c>
+      <c r="D367" t="s">
+        <v>2</v>
+      </c>
+      <c r="G367" s="3">
+        <v>128.6</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>429</v>
+      </c>
+      <c r="B368" t="s">
+        <v>430</v>
+      </c>
+      <c r="C368" t="s">
+        <v>373</v>
+      </c>
+      <c r="D368" t="s">
+        <v>74</v>
+      </c>
+      <c r="E368" t="s">
+        <v>386</v>
+      </c>
+      <c r="G368" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>429</v>
+      </c>
+      <c r="B369" t="s">
+        <v>430</v>
+      </c>
+      <c r="C369" t="s">
+        <v>373</v>
+      </c>
+      <c r="D369" t="s">
+        <v>74</v>
+      </c>
+      <c r="E369" t="s">
+        <v>69</v>
+      </c>
+      <c r="G369" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>429</v>
+      </c>
+      <c r="B370" t="s">
+        <v>430</v>
+      </c>
+      <c r="C370" t="s">
+        <v>373</v>
+      </c>
+      <c r="D370" t="s">
+        <v>12</v>
+      </c>
+      <c r="E370" t="s">
+        <v>367</v>
+      </c>
+      <c r="G370" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>429</v>
+      </c>
+      <c r="B371" t="s">
+        <v>430</v>
+      </c>
+      <c r="C371" t="s">
+        <v>373</v>
+      </c>
+      <c r="D371" t="s">
+        <v>76</v>
+      </c>
+      <c r="E371" t="s">
+        <v>402</v>
+      </c>
+      <c r="G371" s="3">
+        <v>133.69999999999999</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>429</v>
+      </c>
+      <c r="B372" t="s">
+        <v>430</v>
+      </c>
+      <c r="C372" t="s">
+        <v>373</v>
+      </c>
+      <c r="D372" t="s">
+        <v>423</v>
+      </c>
+      <c r="G372" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>431</v>
+      </c>
+      <c r="B373" t="s">
+        <v>432</v>
+      </c>
+      <c r="C373" t="s">
+        <v>389</v>
+      </c>
+      <c r="D373" t="s">
+        <v>74</v>
+      </c>
+      <c r="E373" t="s">
+        <v>391</v>
+      </c>
+      <c r="G373" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>431</v>
+      </c>
+      <c r="B374" t="s">
+        <v>432</v>
+      </c>
+      <c r="C374" t="s">
+        <v>389</v>
+      </c>
+      <c r="D374" t="s">
+        <v>74</v>
+      </c>
+      <c r="E374" t="s">
+        <v>69</v>
+      </c>
+      <c r="G374" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>431</v>
+      </c>
+      <c r="B375" t="s">
+        <v>432</v>
+      </c>
+      <c r="C375" t="s">
+        <v>389</v>
+      </c>
+      <c r="D375" t="s">
+        <v>12</v>
+      </c>
+      <c r="E375" t="s">
+        <v>367</v>
+      </c>
+      <c r="F375" t="s">
+        <v>87</v>
+      </c>
+      <c r="G375" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>431</v>
+      </c>
+      <c r="B376" t="s">
+        <v>432</v>
+      </c>
+      <c r="C376" t="s">
+        <v>389</v>
+      </c>
+      <c r="D376" t="s">
+        <v>423</v>
+      </c>
+      <c r="F376" t="s">
+        <v>433</v>
+      </c>
+      <c r="G376" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>434</v>
+      </c>
+      <c r="B377" t="s">
+        <v>435</v>
+      </c>
+      <c r="C377" t="s">
+        <v>6</v>
+      </c>
+      <c r="D377" t="s">
+        <v>64</v>
+      </c>
+      <c r="E377" t="s">
+        <v>65</v>
+      </c>
+      <c r="F377" t="s">
+        <v>87</v>
+      </c>
+      <c r="G377" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>434</v>
+      </c>
+      <c r="B378" t="s">
+        <v>435</v>
+      </c>
+      <c r="C378" t="s">
+        <v>6</v>
+      </c>
+      <c r="D378" t="s">
+        <v>16</v>
+      </c>
+      <c r="E378" t="s">
+        <v>436</v>
+      </c>
+      <c r="G378" s="3">
+        <v>119.2</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>434</v>
+      </c>
+      <c r="B379" t="s">
+        <v>435</v>
+      </c>
+      <c r="C379" t="s">
+        <v>6</v>
+      </c>
+      <c r="D379" t="s">
+        <v>17</v>
+      </c>
+      <c r="E379" t="s">
+        <v>436</v>
+      </c>
+      <c r="G379" s="3">
+        <v>119.2</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>434</v>
+      </c>
+      <c r="B380" t="s">
+        <v>435</v>
+      </c>
+      <c r="C380" t="s">
+        <v>6</v>
+      </c>
+      <c r="D380" t="s">
+        <v>113</v>
+      </c>
+      <c r="G380" s="3">
+        <v>122.27500000000001</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>437</v>
+      </c>
+      <c r="B381" t="s">
+        <v>438</v>
+      </c>
+      <c r="C381" t="s">
+        <v>364</v>
+      </c>
+      <c r="D381" t="s">
+        <v>12</v>
+      </c>
+      <c r="E381" t="s">
+        <v>367</v>
+      </c>
+      <c r="F381" t="s">
+        <v>87</v>
+      </c>
+      <c r="G381" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>437</v>
+      </c>
+      <c r="B382" t="s">
+        <v>438</v>
+      </c>
+      <c r="C382" t="s">
+        <v>364</v>
+      </c>
+      <c r="D382" t="s">
+        <v>423</v>
+      </c>
+      <c r="F382" t="s">
+        <v>467</v>
+      </c>
+      <c r="G382" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>440</v>
+      </c>
+      <c r="B383" t="s">
+        <v>439</v>
+      </c>
+      <c r="C383" t="s">
+        <v>364</v>
+      </c>
+      <c r="D383" t="s">
+        <v>64</v>
+      </c>
+      <c r="E383" t="s">
+        <v>65</v>
+      </c>
+      <c r="F383" t="s">
+        <v>87</v>
+      </c>
+      <c r="G383" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>441</v>
+      </c>
+      <c r="B384" t="s">
+        <v>442</v>
+      </c>
+      <c r="C384" t="s">
+        <v>6</v>
+      </c>
+      <c r="D384" t="s">
+        <v>64</v>
+      </c>
+      <c r="E384" t="s">
+        <v>65</v>
+      </c>
+      <c r="G384" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>443</v>
+      </c>
+      <c r="B385" t="s">
+        <v>444</v>
+      </c>
+      <c r="C385" t="s">
+        <v>6</v>
+      </c>
+      <c r="D385" t="s">
+        <v>64</v>
+      </c>
+      <c r="E385" t="s">
+        <v>67</v>
+      </c>
+      <c r="G385" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>445</v>
+      </c>
+      <c r="B386" t="s">
+        <v>446</v>
+      </c>
+      <c r="C386" t="s">
+        <v>364</v>
+      </c>
+      <c r="D386" t="s">
+        <v>74</v>
+      </c>
+      <c r="E386" t="s">
+        <v>386</v>
+      </c>
+      <c r="G386" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>445</v>
+      </c>
+      <c r="B387" t="s">
+        <v>446</v>
+      </c>
+      <c r="C387" t="s">
+        <v>364</v>
+      </c>
+      <c r="D387" t="s">
+        <v>74</v>
+      </c>
+      <c r="E387" t="s">
+        <v>69</v>
+      </c>
+      <c r="G387" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>445</v>
+      </c>
+      <c r="B388" t="s">
+        <v>446</v>
+      </c>
+      <c r="C388" t="s">
+        <v>364</v>
+      </c>
+      <c r="D388" t="s">
+        <v>64</v>
+      </c>
+      <c r="E388" t="s">
+        <v>65</v>
+      </c>
+      <c r="F388" t="s">
+        <v>87</v>
+      </c>
+      <c r="G388" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>445</v>
+      </c>
+      <c r="B389" t="s">
+        <v>446</v>
+      </c>
+      <c r="C389" t="s">
+        <v>364</v>
+      </c>
+      <c r="D389" t="s">
+        <v>76</v>
+      </c>
+      <c r="E389" t="s">
+        <v>402</v>
+      </c>
+      <c r="G389" s="3">
+        <v>135.17500000000001</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>445</v>
+      </c>
+      <c r="B390" t="s">
+        <v>446</v>
+      </c>
+      <c r="C390" t="s">
+        <v>364</v>
+      </c>
+      <c r="D390" t="s">
+        <v>113</v>
+      </c>
+      <c r="G390" s="3">
+        <v>122.175</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>447</v>
+      </c>
+      <c r="B391" t="s">
+        <v>448</v>
+      </c>
+      <c r="C391" t="s">
+        <v>373</v>
+      </c>
+      <c r="D391" t="s">
+        <v>64</v>
+      </c>
+      <c r="E391" t="s">
+        <v>65</v>
+      </c>
+      <c r="F391" t="s">
+        <v>87</v>
+      </c>
+      <c r="G391" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>449</v>
+      </c>
+      <c r="B392" t="s">
+        <v>450</v>
+      </c>
+      <c r="C392" t="s">
+        <v>389</v>
+      </c>
+      <c r="D392" t="s">
+        <v>74</v>
+      </c>
+      <c r="E392" t="s">
+        <v>391</v>
+      </c>
+      <c r="G392" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>449</v>
+      </c>
+      <c r="B393" t="s">
+        <v>450</v>
+      </c>
+      <c r="C393" t="s">
+        <v>389</v>
+      </c>
+      <c r="D393" t="s">
+        <v>74</v>
+      </c>
+      <c r="E393" t="s">
+        <v>69</v>
+      </c>
+      <c r="G393" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>449</v>
+      </c>
+      <c r="B394" t="s">
+        <v>450</v>
+      </c>
+      <c r="C394" t="s">
+        <v>389</v>
+      </c>
+      <c r="D394" t="s">
+        <v>12</v>
+      </c>
+      <c r="E394" t="s">
+        <v>367</v>
+      </c>
+      <c r="F394" t="s">
+        <v>87</v>
+      </c>
+      <c r="G394" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>449</v>
+      </c>
+      <c r="B395" t="s">
+        <v>450</v>
+      </c>
+      <c r="C395" t="s">
+        <v>389</v>
+      </c>
+      <c r="D395" t="s">
+        <v>423</v>
+      </c>
+      <c r="F395" t="s">
+        <v>451</v>
+      </c>
+      <c r="G395" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>453</v>
+      </c>
+      <c r="B396" t="s">
+        <v>452</v>
+      </c>
+      <c r="C396" t="s">
+        <v>6</v>
+      </c>
+      <c r="D396" t="s">
+        <v>64</v>
+      </c>
+      <c r="E396" t="s">
+        <v>67</v>
+      </c>
+      <c r="G396" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>454</v>
+      </c>
+      <c r="B397" t="s">
+        <v>455</v>
+      </c>
+      <c r="C397" t="s">
+        <v>389</v>
+      </c>
+      <c r="D397" t="s">
+        <v>64</v>
+      </c>
+      <c r="E397" t="s">
+        <v>67</v>
+      </c>
+      <c r="G397" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>456</v>
+      </c>
+      <c r="B398" t="s">
+        <v>457</v>
+      </c>
+      <c r="C398" t="s">
+        <v>364</v>
+      </c>
+      <c r="D398" t="s">
+        <v>64</v>
+      </c>
+      <c r="E398" t="s">
+        <v>65</v>
+      </c>
+      <c r="F398" t="s">
+        <v>87</v>
+      </c>
+      <c r="G398" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>458</v>
+      </c>
+      <c r="B399" t="s">
+        <v>459</v>
+      </c>
+      <c r="C399" t="s">
+        <v>364</v>
+      </c>
+      <c r="D399" t="s">
+        <v>74</v>
+      </c>
+      <c r="E399" t="s">
+        <v>386</v>
+      </c>
+      <c r="G399" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>458</v>
+      </c>
+      <c r="B400" t="s">
+        <v>459</v>
+      </c>
+      <c r="C400" t="s">
+        <v>364</v>
+      </c>
+      <c r="D400" t="s">
+        <v>74</v>
+      </c>
+      <c r="E400" t="s">
+        <v>69</v>
+      </c>
+      <c r="G400" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>458</v>
+      </c>
+      <c r="B401" t="s">
+        <v>459</v>
+      </c>
+      <c r="C401" t="s">
+        <v>364</v>
+      </c>
+      <c r="D401" t="s">
+        <v>12</v>
+      </c>
+      <c r="E401" t="s">
+        <v>367</v>
+      </c>
+      <c r="F401" t="s">
+        <v>87</v>
+      </c>
+      <c r="G401" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>458</v>
+      </c>
+      <c r="B402" t="s">
+        <v>459</v>
+      </c>
+      <c r="C402" t="s">
+        <v>364</v>
+      </c>
+      <c r="D402" t="s">
+        <v>423</v>
+      </c>
+      <c r="F402" t="s">
+        <v>466</v>
+      </c>
+      <c r="G402" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>460</v>
+      </c>
+      <c r="B403" t="s">
+        <v>461</v>
+      </c>
+      <c r="C403" t="s">
+        <v>364</v>
+      </c>
+      <c r="D403" t="s">
+        <v>12</v>
+      </c>
+      <c r="E403" t="s">
+        <v>367</v>
+      </c>
+      <c r="F403" t="s">
+        <v>87</v>
+      </c>
+      <c r="G403" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>460</v>
+      </c>
+      <c r="B404" t="s">
+        <v>461</v>
+      </c>
+      <c r="C404" t="s">
+        <v>364</v>
+      </c>
+      <c r="D404" t="s">
+        <v>423</v>
+      </c>
+      <c r="F404" t="s">
+        <v>465</v>
+      </c>
+      <c r="G404" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>462</v>
+      </c>
+      <c r="B405" t="s">
+        <v>463</v>
+      </c>
+      <c r="C405" t="s">
+        <v>364</v>
+      </c>
+      <c r="D405" t="s">
+        <v>12</v>
+      </c>
+      <c r="E405" t="s">
+        <v>367</v>
+      </c>
+      <c r="F405" t="s">
+        <v>87</v>
+      </c>
+      <c r="G405" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>462</v>
+      </c>
+      <c r="B406" t="s">
+        <v>463</v>
+      </c>
+      <c r="C406" t="s">
+        <v>364</v>
+      </c>
+      <c r="D406" t="s">
+        <v>423</v>
+      </c>
+      <c r="F406" t="s">
+        <v>464</v>
+      </c>
+      <c r="G406" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>468</v>
+      </c>
+      <c r="B407" t="s">
+        <v>469</v>
+      </c>
+      <c r="C407" t="s">
+        <v>364</v>
+      </c>
+      <c r="D407" t="s">
+        <v>64</v>
+      </c>
+      <c r="E407" t="s">
+        <v>67</v>
+      </c>
+      <c r="G407" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>470</v>
+      </c>
+      <c r="B408" t="s">
+        <v>471</v>
+      </c>
+      <c r="C408" t="s">
+        <v>364</v>
+      </c>
+      <c r="D408" t="s">
+        <v>12</v>
+      </c>
+      <c r="E408" t="s">
+        <v>367</v>
+      </c>
+      <c r="F408" t="s">
+        <v>87</v>
+      </c>
+      <c r="G408" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>470</v>
+      </c>
+      <c r="B409" t="s">
+        <v>471</v>
+      </c>
+      <c r="C409" t="s">
+        <v>364</v>
+      </c>
+      <c r="D409" t="s">
+        <v>423</v>
+      </c>
+      <c r="F409" t="s">
+        <v>465</v>
+      </c>
+      <c r="G409" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>472</v>
+      </c>
+      <c r="B410" t="s">
+        <v>473</v>
+      </c>
+      <c r="C410" t="s">
+        <v>364</v>
+      </c>
+      <c r="D410" t="s">
+        <v>74</v>
+      </c>
+      <c r="E410" t="s">
+        <v>386</v>
+      </c>
+      <c r="G410" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>472</v>
+      </c>
+      <c r="B411" t="s">
+        <v>473</v>
+      </c>
+      <c r="C411" t="s">
+        <v>364</v>
+      </c>
+      <c r="D411" t="s">
+        <v>74</v>
+      </c>
+      <c r="E411" t="s">
+        <v>386</v>
+      </c>
+      <c r="G411" s="3">
+        <v>296.60000000000002</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>472</v>
+      </c>
+      <c r="B412" t="s">
+        <v>473</v>
+      </c>
+      <c r="C412" t="s">
+        <v>364</v>
+      </c>
+      <c r="D412" t="s">
+        <v>74</v>
+      </c>
+      <c r="E412" t="s">
+        <v>69</v>
+      </c>
+      <c r="G412" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>472</v>
+      </c>
+      <c r="B413" t="s">
+        <v>473</v>
+      </c>
+      <c r="C413" t="s">
+        <v>364</v>
+      </c>
+      <c r="D413" t="s">
+        <v>474</v>
+      </c>
+      <c r="E413" t="s">
+        <v>402</v>
+      </c>
+      <c r="G413" s="3">
+        <v>135.4</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>472</v>
+      </c>
+      <c r="B414" t="s">
+        <v>473</v>
+      </c>
+      <c r="C414" t="s">
+        <v>364</v>
+      </c>
+      <c r="D414" t="s">
+        <v>12</v>
+      </c>
+      <c r="E414" t="s">
+        <v>367</v>
+      </c>
+      <c r="G414" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>472</v>
+      </c>
+      <c r="B415" t="s">
+        <v>473</v>
+      </c>
+      <c r="C415" t="s">
+        <v>364</v>
+      </c>
+      <c r="D415" t="s">
+        <v>76</v>
+      </c>
+      <c r="E415" t="s">
+        <v>402</v>
+      </c>
+      <c r="G415" s="3">
+        <v>135.4</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>472</v>
+      </c>
+      <c r="B416" t="s">
+        <v>473</v>
+      </c>
+      <c r="C416" t="s">
+        <v>364</v>
+      </c>
+      <c r="D416" t="s">
+        <v>366</v>
+      </c>
+      <c r="G416" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>475</v>
+      </c>
+      <c r="B417" t="s">
+        <v>476</v>
+      </c>
+      <c r="C417" t="s">
+        <v>364</v>
+      </c>
+      <c r="D417" t="s">
+        <v>74</v>
+      </c>
+      <c r="E417" t="s">
+        <v>386</v>
+      </c>
+      <c r="G417" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>475</v>
+      </c>
+      <c r="B418" t="s">
+        <v>476</v>
+      </c>
+      <c r="C418" t="s">
+        <v>364</v>
+      </c>
+      <c r="D418" t="s">
+        <v>74</v>
+      </c>
+      <c r="E418" t="s">
+        <v>386</v>
+      </c>
+      <c r="G418" s="3">
+        <v>296.60000000000002</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>475</v>
+      </c>
+      <c r="B419" t="s">
+        <v>476</v>
+      </c>
+      <c r="C419" t="s">
+        <v>364</v>
+      </c>
+      <c r="D419" t="s">
+        <v>12</v>
+      </c>
+      <c r="E419" t="s">
+        <v>477</v>
+      </c>
+      <c r="G419" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>478</v>
+      </c>
+      <c r="B420" t="s">
+        <v>479</v>
+      </c>
+      <c r="C420" t="s">
+        <v>364</v>
+      </c>
+      <c r="D420" t="s">
+        <v>74</v>
+      </c>
+      <c r="E420" t="s">
+        <v>386</v>
+      </c>
+      <c r="G420" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>478</v>
+      </c>
+      <c r="B421" t="s">
+        <v>479</v>
+      </c>
+      <c r="C421" t="s">
+        <v>364</v>
+      </c>
+      <c r="D421" t="s">
+        <v>74</v>
+      </c>
+      <c r="E421" t="s">
+        <v>386</v>
+      </c>
+      <c r="G421" s="3">
+        <v>239.8</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>478</v>
+      </c>
+      <c r="B422" t="s">
+        <v>479</v>
+      </c>
+      <c r="C422" t="s">
+        <v>364</v>
+      </c>
+      <c r="D422" t="s">
+        <v>12</v>
+      </c>
+      <c r="E422" t="s">
+        <v>367</v>
+      </c>
+      <c r="G422" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>478</v>
+      </c>
+      <c r="B423" t="s">
+        <v>479</v>
+      </c>
+      <c r="C423" t="s">
+        <v>364</v>
+      </c>
+      <c r="D423" t="s">
+        <v>366</v>
+      </c>
+      <c r="G423" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>480</v>
+      </c>
+      <c r="B424" t="s">
+        <v>481</v>
+      </c>
+      <c r="C424" t="s">
+        <v>6</v>
+      </c>
+      <c r="D424" t="s">
+        <v>64</v>
+      </c>
+      <c r="E424" t="s">
+        <v>65</v>
+      </c>
+      <c r="F424" t="s">
+        <v>87</v>
+      </c>
+      <c r="G424" s="3">
+        <v>122.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0BB36E-14C0-4EB0-A2EF-A957DFC52AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8C79AB-379D-400B-9DAD-9C4F2AFD91AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40650" yWindow="2250" windowWidth="28800" windowHeight="15345" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2190" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2603" uniqueCount="561">
   <si>
     <t>AB</t>
   </si>
@@ -1485,6 +1485,243 @@
   </si>
   <si>
     <t>CFH4</t>
+  </si>
+  <si>
+    <t>Gahcho</t>
+  </si>
+  <si>
+    <t>CGK2</t>
+  </si>
+  <si>
+    <t>Gameti / RAE LAKES</t>
+  </si>
+  <si>
+    <t>15-01Z‡ Sun-Fri, 16-21Z‡ Sat</t>
+  </si>
+  <si>
+    <t>CYRA</t>
+  </si>
+  <si>
+    <t>George Lake</t>
+  </si>
+  <si>
+    <t>CGR3</t>
+  </si>
+  <si>
+    <t>Gjoa Haven</t>
+  </si>
+  <si>
+    <t>CYHK</t>
+  </si>
+  <si>
+    <t>13-01Z‡ Mon, Tue, Thr, Fri, &amp; Sun, 13-23Z‡ Wed</t>
+  </si>
+  <si>
+    <t>Goose Lake</t>
+  </si>
+  <si>
+    <t>CGS2</t>
+  </si>
+  <si>
+    <t>Great Bear Lake</t>
+  </si>
+  <si>
+    <t>CFF4</t>
+  </si>
+  <si>
+    <t>Gereenwood</t>
+  </si>
+  <si>
+    <t>CYZX</t>
+  </si>
+  <si>
+    <t>11-24Z‡</t>
+  </si>
+  <si>
+    <t>128.850, 244.300</t>
+  </si>
+  <si>
+    <t>128.025, 283.900</t>
+  </si>
+  <si>
+    <t>133.750, 289.400</t>
+  </si>
+  <si>
+    <t>119.500, 236.600, 324.300</t>
+  </si>
+  <si>
+    <t>120.600, 335.900</t>
+  </si>
+  <si>
+    <t>Grise Fiord</t>
+  </si>
+  <si>
+    <t>CYGZ</t>
+  </si>
+  <si>
+    <t>13-21Z‡ Mon, Tue, Thr, &amp; Fri, 17-01Z‡ Wed</t>
+  </si>
+  <si>
+    <t>Haines Junction</t>
+  </si>
+  <si>
+    <t>CYHT</t>
+  </si>
+  <si>
+    <t>Halifax</t>
+  </si>
+  <si>
+    <t>CYAW</t>
+  </si>
+  <si>
+    <t>129.175, 308.800</t>
+  </si>
+  <si>
+    <t>121.700, 250.100</t>
+  </si>
+  <si>
+    <t>126.200, 119.000, 340.200, 360.200</t>
+  </si>
+  <si>
+    <t>Shearwater advsy</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t>128.100, 134.100, 289.400, 346.600</t>
+  </si>
+  <si>
+    <t>Shearwater Mil</t>
+  </si>
+  <si>
+    <t>239.300, 231.950</t>
+  </si>
+  <si>
+    <t>11-24Z‡ Mon-Fri, clsd Sat &amp; Sun</t>
+  </si>
+  <si>
+    <t>Halifax / Stanfield Intl</t>
+  </si>
+  <si>
+    <t>CYHZ</t>
+  </si>
+  <si>
+    <t>118.400, 236.600</t>
+  </si>
+  <si>
+    <t>119.200, 118.700, 128.55, 363.800</t>
+  </si>
+  <si>
+    <t>Moncton Ctr</t>
+  </si>
+  <si>
+    <t>Hay River / Merlyn Carter Airport</t>
+  </si>
+  <si>
+    <t>CYHY</t>
+  </si>
+  <si>
+    <t>Hayes Camp</t>
+  </si>
+  <si>
+    <t>CHC5</t>
+  </si>
+  <si>
+    <t>Hillaton / Kings Aerodrome</t>
+  </si>
+  <si>
+    <t>CHL2</t>
+  </si>
+  <si>
+    <t>Hope Bay</t>
+  </si>
+  <si>
+    <t>CHB3</t>
+  </si>
+  <si>
+    <t>Hyland</t>
+  </si>
+  <si>
+    <t>CFT5</t>
+  </si>
+  <si>
+    <t>Igloolik</t>
+  </si>
+  <si>
+    <t>CYGT</t>
+  </si>
+  <si>
+    <t>17-2130Z‡ Sun, 11-22Z‡ Mon &amp; Tue, 10-21Z‡ Wed, 10-22Z‡ Thu, 11-22Z‡ Fri, 16-2030Z‡ Sat</t>
+  </si>
+  <si>
+    <t>Inuvik (Mike Zubko)</t>
+  </si>
+  <si>
+    <t>CYEV</t>
+  </si>
+  <si>
+    <t>122.300, 262.700</t>
+  </si>
+  <si>
+    <t>Iqaluit</t>
+  </si>
+  <si>
+    <t>CYFB</t>
+  </si>
+  <si>
+    <t>122.200, 296.200</t>
+  </si>
+  <si>
+    <t>Iqaluit rdo</t>
+  </si>
+  <si>
+    <t>126.900, 2971, 4675, 8891, 11279</t>
+  </si>
+  <si>
+    <t>Jean Marie River</t>
+  </si>
+  <si>
+    <t>CET9</t>
+  </si>
+  <si>
+    <t>Kasba Lake</t>
+  </si>
+  <si>
+    <t>CJL8</t>
+  </si>
+  <si>
+    <t>Kimmirut</t>
+  </si>
+  <si>
+    <t>CYLC</t>
+  </si>
+  <si>
+    <t>11-20Z‡ Mon &amp; Fri, 13-21Z‡ Tue, Wed, &amp; Thu</t>
+  </si>
+  <si>
+    <t>Kinngait Airport</t>
+  </si>
+  <si>
+    <t>CYTE</t>
+  </si>
+  <si>
+    <t>13-22Z‡ Mon &amp; Wed, 14-21Z‡ Tue, 12-17Z‡ Thu, 12-22Z‡ Fri</t>
+  </si>
+  <si>
+    <t>Kugaaruk</t>
+  </si>
+  <si>
+    <t>CYBB</t>
+  </si>
+  <si>
+    <t>13-24Z‡ Mon-Fri, 16-01Z‡ Sat, 18-24Z‡ Sun</t>
+  </si>
+  <si>
+    <t>Kugluktuk</t>
+  </si>
+  <si>
+    <t>CYCO</t>
   </si>
 </sst>
 </file>
@@ -1874,7 +2111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G424"/>
+  <dimension ref="A1:G504"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -10489,6 +10726,1597 @@
         <v>122.2</v>
       </c>
     </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>482</v>
+      </c>
+      <c r="B425" t="s">
+        <v>483</v>
+      </c>
+      <c r="C425" t="s">
+        <v>364</v>
+      </c>
+      <c r="D425" t="s">
+        <v>64</v>
+      </c>
+      <c r="E425" t="s">
+        <v>65</v>
+      </c>
+      <c r="F425" t="s">
+        <v>87</v>
+      </c>
+      <c r="G425" s="3">
+        <v>123.35</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>482</v>
+      </c>
+      <c r="B426" t="s">
+        <v>483</v>
+      </c>
+      <c r="C426" t="s">
+        <v>364</v>
+      </c>
+      <c r="D426" t="s">
+        <v>113</v>
+      </c>
+      <c r="G426" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>484</v>
+      </c>
+      <c r="B427" t="s">
+        <v>486</v>
+      </c>
+      <c r="C427" t="s">
+        <v>364</v>
+      </c>
+      <c r="D427" t="s">
+        <v>12</v>
+      </c>
+      <c r="E427" t="s">
+        <v>367</v>
+      </c>
+      <c r="F427" t="s">
+        <v>87</v>
+      </c>
+      <c r="G427" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>484</v>
+      </c>
+      <c r="B428" t="s">
+        <v>486</v>
+      </c>
+      <c r="C428" t="s">
+        <v>364</v>
+      </c>
+      <c r="D428" t="s">
+        <v>423</v>
+      </c>
+      <c r="F428" t="s">
+        <v>485</v>
+      </c>
+      <c r="G428" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>487</v>
+      </c>
+      <c r="B429" t="s">
+        <v>488</v>
+      </c>
+      <c r="C429" t="s">
+        <v>373</v>
+      </c>
+      <c r="D429" t="s">
+        <v>64</v>
+      </c>
+      <c r="E429" t="s">
+        <v>65</v>
+      </c>
+      <c r="F429" t="s">
+        <v>87</v>
+      </c>
+      <c r="G429" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>489</v>
+      </c>
+      <c r="B430" t="s">
+        <v>490</v>
+      </c>
+      <c r="C430" t="s">
+        <v>373</v>
+      </c>
+      <c r="D430" t="s">
+        <v>12</v>
+      </c>
+      <c r="E430" t="s">
+        <v>367</v>
+      </c>
+      <c r="F430" t="s">
+        <v>87</v>
+      </c>
+      <c r="G430" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>489</v>
+      </c>
+      <c r="B431" t="s">
+        <v>490</v>
+      </c>
+      <c r="C431" t="s">
+        <v>373</v>
+      </c>
+      <c r="D431" t="s">
+        <v>423</v>
+      </c>
+      <c r="F431" t="s">
+        <v>491</v>
+      </c>
+      <c r="G431" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>489</v>
+      </c>
+      <c r="B432" t="s">
+        <v>490</v>
+      </c>
+      <c r="C432" t="s">
+        <v>373</v>
+      </c>
+      <c r="D432" t="s">
+        <v>2</v>
+      </c>
+      <c r="G432" s="3">
+        <v>128.69999999999999</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>492</v>
+      </c>
+      <c r="B433" t="s">
+        <v>493</v>
+      </c>
+      <c r="C433" t="s">
+        <v>373</v>
+      </c>
+      <c r="D433" t="s">
+        <v>64</v>
+      </c>
+      <c r="E433" t="s">
+        <v>65</v>
+      </c>
+      <c r="F433" t="s">
+        <v>87</v>
+      </c>
+      <c r="G433" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>494</v>
+      </c>
+      <c r="B434" t="s">
+        <v>495</v>
+      </c>
+      <c r="C434" t="s">
+        <v>364</v>
+      </c>
+      <c r="D434" t="s">
+        <v>64</v>
+      </c>
+      <c r="E434" t="s">
+        <v>65</v>
+      </c>
+      <c r="F434" t="s">
+        <v>87</v>
+      </c>
+      <c r="G434" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>496</v>
+      </c>
+      <c r="B435" t="s">
+        <v>497</v>
+      </c>
+      <c r="C435" t="s">
+        <v>6</v>
+      </c>
+      <c r="D435" t="s">
+        <v>41</v>
+      </c>
+      <c r="F435" t="s">
+        <v>498</v>
+      </c>
+      <c r="G435" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>496</v>
+      </c>
+      <c r="B436" t="s">
+        <v>497</v>
+      </c>
+      <c r="C436" t="s">
+        <v>6</v>
+      </c>
+      <c r="D436" t="s">
+        <v>146</v>
+      </c>
+      <c r="G436" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>496</v>
+      </c>
+      <c r="B437" t="s">
+        <v>497</v>
+      </c>
+      <c r="C437" t="s">
+        <v>6</v>
+      </c>
+      <c r="D437" t="s">
+        <v>14</v>
+      </c>
+      <c r="G437" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>496</v>
+      </c>
+      <c r="B438" t="s">
+        <v>497</v>
+      </c>
+      <c r="C438" t="s">
+        <v>6</v>
+      </c>
+      <c r="D438" t="s">
+        <v>15</v>
+      </c>
+      <c r="G438" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>496</v>
+      </c>
+      <c r="B439" t="s">
+        <v>497</v>
+      </c>
+      <c r="C439" t="s">
+        <v>6</v>
+      </c>
+      <c r="D439" t="s">
+        <v>44</v>
+      </c>
+      <c r="G439" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>496</v>
+      </c>
+      <c r="B440" t="s">
+        <v>497</v>
+      </c>
+      <c r="C440" t="s">
+        <v>6</v>
+      </c>
+      <c r="D440" t="s">
+        <v>190</v>
+      </c>
+      <c r="F440" t="s">
+        <v>191</v>
+      </c>
+      <c r="G440" s="3">
+        <v>344.6</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>504</v>
+      </c>
+      <c r="B441" t="s">
+        <v>505</v>
+      </c>
+      <c r="C441" t="s">
+        <v>373</v>
+      </c>
+      <c r="D441" t="s">
+        <v>12</v>
+      </c>
+      <c r="E441" t="s">
+        <v>367</v>
+      </c>
+      <c r="F441" t="s">
+        <v>87</v>
+      </c>
+      <c r="G441" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>504</v>
+      </c>
+      <c r="B442" t="s">
+        <v>505</v>
+      </c>
+      <c r="C442" t="s">
+        <v>373</v>
+      </c>
+      <c r="D442" t="s">
+        <v>423</v>
+      </c>
+      <c r="F442" t="s">
+        <v>506</v>
+      </c>
+      <c r="G442" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>507</v>
+      </c>
+      <c r="B443" t="s">
+        <v>508</v>
+      </c>
+      <c r="C443" t="s">
+        <v>364</v>
+      </c>
+      <c r="D443" t="s">
+        <v>74</v>
+      </c>
+      <c r="E443" t="s">
+        <v>391</v>
+      </c>
+      <c r="G443" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>507</v>
+      </c>
+      <c r="B444" t="s">
+        <v>508</v>
+      </c>
+      <c r="C444" t="s">
+        <v>364</v>
+      </c>
+      <c r="D444" t="s">
+        <v>74</v>
+      </c>
+      <c r="E444" t="s">
+        <v>69</v>
+      </c>
+      <c r="G444" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>507</v>
+      </c>
+      <c r="B445" t="s">
+        <v>508</v>
+      </c>
+      <c r="C445" t="s">
+        <v>364</v>
+      </c>
+      <c r="D445" t="s">
+        <v>64</v>
+      </c>
+      <c r="E445" t="s">
+        <v>67</v>
+      </c>
+      <c r="G445" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>509</v>
+      </c>
+      <c r="B446" t="s">
+        <v>510</v>
+      </c>
+      <c r="C446" t="s">
+        <v>6</v>
+      </c>
+      <c r="D446" t="s">
+        <v>41</v>
+      </c>
+      <c r="F446" t="s">
+        <v>519</v>
+      </c>
+      <c r="G446" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>509</v>
+      </c>
+      <c r="B447" t="s">
+        <v>510</v>
+      </c>
+      <c r="C447" t="s">
+        <v>6</v>
+      </c>
+      <c r="D447" t="s">
+        <v>14</v>
+      </c>
+      <c r="F447" t="s">
+        <v>519</v>
+      </c>
+      <c r="G447" s="3" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>509</v>
+      </c>
+      <c r="B448" t="s">
+        <v>510</v>
+      </c>
+      <c r="C448" t="s">
+        <v>6</v>
+      </c>
+      <c r="D448" t="s">
+        <v>12</v>
+      </c>
+      <c r="E448" t="s">
+        <v>514</v>
+      </c>
+      <c r="F448" t="s">
+        <v>519</v>
+      </c>
+      <c r="G448" s="3" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>509</v>
+      </c>
+      <c r="B449" t="s">
+        <v>510</v>
+      </c>
+      <c r="C449" t="s">
+        <v>6</v>
+      </c>
+      <c r="D449" t="s">
+        <v>515</v>
+      </c>
+      <c r="F449" t="s">
+        <v>519</v>
+      </c>
+      <c r="G449" s="3" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>509</v>
+      </c>
+      <c r="B450" t="s">
+        <v>510</v>
+      </c>
+      <c r="C450" t="s">
+        <v>6</v>
+      </c>
+      <c r="D450" t="s">
+        <v>64</v>
+      </c>
+      <c r="E450" t="s">
+        <v>67</v>
+      </c>
+      <c r="G450" s="3">
+        <v>126.2</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>509</v>
+      </c>
+      <c r="B451" t="s">
+        <v>510</v>
+      </c>
+      <c r="C451" t="s">
+        <v>6</v>
+      </c>
+      <c r="D451" t="s">
+        <v>16</v>
+      </c>
+      <c r="G451" s="3">
+        <v>119.2</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>509</v>
+      </c>
+      <c r="B452" t="s">
+        <v>510</v>
+      </c>
+      <c r="C452" t="s">
+        <v>6</v>
+      </c>
+      <c r="D452" t="s">
+        <v>17</v>
+      </c>
+      <c r="G452" s="3">
+        <v>119.2</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>509</v>
+      </c>
+      <c r="B453" t="s">
+        <v>510</v>
+      </c>
+      <c r="C453" t="s">
+        <v>6</v>
+      </c>
+      <c r="D453" t="s">
+        <v>185</v>
+      </c>
+      <c r="E453" t="s">
+        <v>517</v>
+      </c>
+      <c r="G453" s="3" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>509</v>
+      </c>
+      <c r="B454" t="s">
+        <v>510</v>
+      </c>
+      <c r="C454" t="s">
+        <v>6</v>
+      </c>
+      <c r="D454" t="s">
+        <v>190</v>
+      </c>
+      <c r="F454" t="s">
+        <v>519</v>
+      </c>
+      <c r="G454" s="3">
+        <v>344.6</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>520</v>
+      </c>
+      <c r="B455" t="s">
+        <v>521</v>
+      </c>
+      <c r="C455" t="s">
+        <v>6</v>
+      </c>
+      <c r="D455" t="s">
+        <v>74</v>
+      </c>
+      <c r="E455" t="s">
+        <v>275</v>
+      </c>
+      <c r="G455" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>520</v>
+      </c>
+      <c r="B456" t="s">
+        <v>521</v>
+      </c>
+      <c r="C456" t="s">
+        <v>6</v>
+      </c>
+      <c r="D456" t="s">
+        <v>74</v>
+      </c>
+      <c r="E456" t="s">
+        <v>69</v>
+      </c>
+      <c r="G456" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>520</v>
+      </c>
+      <c r="B457" t="s">
+        <v>521</v>
+      </c>
+      <c r="C457" t="s">
+        <v>6</v>
+      </c>
+      <c r="D457" t="s">
+        <v>41</v>
+      </c>
+      <c r="G457" s="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>520</v>
+      </c>
+      <c r="B458" t="s">
+        <v>521</v>
+      </c>
+      <c r="C458" t="s">
+        <v>6</v>
+      </c>
+      <c r="D458" t="s">
+        <v>146</v>
+      </c>
+      <c r="G458" s="3">
+        <v>123.95</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>520</v>
+      </c>
+      <c r="B459" t="s">
+        <v>521</v>
+      </c>
+      <c r="C459" t="s">
+        <v>6</v>
+      </c>
+      <c r="D459" t="s">
+        <v>14</v>
+      </c>
+      <c r="G459" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>520</v>
+      </c>
+      <c r="B460" t="s">
+        <v>521</v>
+      </c>
+      <c r="C460" t="s">
+        <v>6</v>
+      </c>
+      <c r="D460" t="s">
+        <v>15</v>
+      </c>
+      <c r="G460" s="3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>520</v>
+      </c>
+      <c r="B461" t="s">
+        <v>521</v>
+      </c>
+      <c r="C461" t="s">
+        <v>6</v>
+      </c>
+      <c r="D461" t="s">
+        <v>44</v>
+      </c>
+      <c r="G461" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>520</v>
+      </c>
+      <c r="B462" t="s">
+        <v>521</v>
+      </c>
+      <c r="C462" t="s">
+        <v>6</v>
+      </c>
+      <c r="D462" t="s">
+        <v>76</v>
+      </c>
+      <c r="E462" t="s">
+        <v>524</v>
+      </c>
+      <c r="G462" s="3">
+        <v>135.30000000000001</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>525</v>
+      </c>
+      <c r="B463" t="s">
+        <v>526</v>
+      </c>
+      <c r="C463" t="s">
+        <v>364</v>
+      </c>
+      <c r="D463" t="s">
+        <v>74</v>
+      </c>
+      <c r="E463" t="s">
+        <v>386</v>
+      </c>
+      <c r="G463" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>525</v>
+      </c>
+      <c r="B464" t="s">
+        <v>526</v>
+      </c>
+      <c r="C464" t="s">
+        <v>364</v>
+      </c>
+      <c r="D464" t="s">
+        <v>74</v>
+      </c>
+      <c r="E464" t="s">
+        <v>69</v>
+      </c>
+      <c r="G464" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>525</v>
+      </c>
+      <c r="B465" t="s">
+        <v>526</v>
+      </c>
+      <c r="C465" t="s">
+        <v>364</v>
+      </c>
+      <c r="D465" t="s">
+        <v>146</v>
+      </c>
+      <c r="E465" t="s">
+        <v>402</v>
+      </c>
+      <c r="G465" s="3">
+        <v>133.85</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>525</v>
+      </c>
+      <c r="B466" t="s">
+        <v>526</v>
+      </c>
+      <c r="C466" t="s">
+        <v>364</v>
+      </c>
+      <c r="D466" t="s">
+        <v>12</v>
+      </c>
+      <c r="E466" t="s">
+        <v>367</v>
+      </c>
+      <c r="G466" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>525</v>
+      </c>
+      <c r="B467" t="s">
+        <v>526</v>
+      </c>
+      <c r="C467" t="s">
+        <v>364</v>
+      </c>
+      <c r="D467" t="s">
+        <v>76</v>
+      </c>
+      <c r="E467" t="s">
+        <v>402</v>
+      </c>
+      <c r="G467" s="3">
+        <v>133.85</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>525</v>
+      </c>
+      <c r="B468" t="s">
+        <v>526</v>
+      </c>
+      <c r="C468" t="s">
+        <v>364</v>
+      </c>
+      <c r="D468" t="s">
+        <v>366</v>
+      </c>
+      <c r="G468" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>527</v>
+      </c>
+      <c r="B469" t="s">
+        <v>528</v>
+      </c>
+      <c r="C469" t="s">
+        <v>373</v>
+      </c>
+      <c r="D469" t="s">
+        <v>64</v>
+      </c>
+      <c r="E469" t="s">
+        <v>65</v>
+      </c>
+      <c r="F469" t="s">
+        <v>87</v>
+      </c>
+      <c r="G469" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>529</v>
+      </c>
+      <c r="B470" t="s">
+        <v>530</v>
+      </c>
+      <c r="C470" t="s">
+        <v>6</v>
+      </c>
+      <c r="D470" t="s">
+        <v>64</v>
+      </c>
+      <c r="E470" t="s">
+        <v>67</v>
+      </c>
+      <c r="G470" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>531</v>
+      </c>
+      <c r="B471" t="s">
+        <v>532</v>
+      </c>
+      <c r="C471" t="s">
+        <v>373</v>
+      </c>
+      <c r="D471" t="s">
+        <v>64</v>
+      </c>
+      <c r="E471" t="s">
+        <v>65</v>
+      </c>
+      <c r="F471" t="s">
+        <v>87</v>
+      </c>
+      <c r="G471" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>533</v>
+      </c>
+      <c r="B472" t="s">
+        <v>534</v>
+      </c>
+      <c r="C472" t="s">
+        <v>389</v>
+      </c>
+      <c r="D472" t="s">
+        <v>64</v>
+      </c>
+      <c r="E472" t="s">
+        <v>67</v>
+      </c>
+      <c r="G472" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>535</v>
+      </c>
+      <c r="B473" t="s">
+        <v>536</v>
+      </c>
+      <c r="C473" t="s">
+        <v>373</v>
+      </c>
+      <c r="D473" t="s">
+        <v>12</v>
+      </c>
+      <c r="E473" t="s">
+        <v>367</v>
+      </c>
+      <c r="F473" t="s">
+        <v>87</v>
+      </c>
+      <c r="G473" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>535</v>
+      </c>
+      <c r="B474" t="s">
+        <v>536</v>
+      </c>
+      <c r="C474" t="s">
+        <v>373</v>
+      </c>
+      <c r="D474" t="s">
+        <v>423</v>
+      </c>
+      <c r="F474" t="s">
+        <v>537</v>
+      </c>
+      <c r="G474" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>538</v>
+      </c>
+      <c r="B475" t="s">
+        <v>539</v>
+      </c>
+      <c r="C475" t="s">
+        <v>364</v>
+      </c>
+      <c r="D475" t="s">
+        <v>11</v>
+      </c>
+      <c r="G475" s="3" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>538</v>
+      </c>
+      <c r="B476" t="s">
+        <v>539</v>
+      </c>
+      <c r="C476" t="s">
+        <v>364</v>
+      </c>
+      <c r="D476" t="s">
+        <v>74</v>
+      </c>
+      <c r="E476" t="s">
+        <v>386</v>
+      </c>
+      <c r="G476" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>538</v>
+      </c>
+      <c r="B477" t="s">
+        <v>539</v>
+      </c>
+      <c r="C477" t="s">
+        <v>364</v>
+      </c>
+      <c r="D477" t="s">
+        <v>74</v>
+      </c>
+      <c r="E477" t="s">
+        <v>69</v>
+      </c>
+      <c r="G477" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>538</v>
+      </c>
+      <c r="B478" t="s">
+        <v>539</v>
+      </c>
+      <c r="C478" t="s">
+        <v>364</v>
+      </c>
+      <c r="D478" t="s">
+        <v>74</v>
+      </c>
+      <c r="E478" t="s">
+        <v>386</v>
+      </c>
+      <c r="G478" s="3">
+        <v>5680</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>538</v>
+      </c>
+      <c r="B479" t="s">
+        <v>539</v>
+      </c>
+      <c r="C479" t="s">
+        <v>364</v>
+      </c>
+      <c r="D479" t="s">
+        <v>41</v>
+      </c>
+      <c r="F479" t="s">
+        <v>191</v>
+      </c>
+      <c r="G479" s="3">
+        <v>128.5</v>
+      </c>
+    </row>
+    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>538</v>
+      </c>
+      <c r="B480" t="s">
+        <v>539</v>
+      </c>
+      <c r="C480" t="s">
+        <v>364</v>
+      </c>
+      <c r="D480" t="s">
+        <v>12</v>
+      </c>
+      <c r="E480" t="s">
+        <v>100</v>
+      </c>
+      <c r="G480" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>538</v>
+      </c>
+      <c r="B481" t="s">
+        <v>539</v>
+      </c>
+      <c r="C481" t="s">
+        <v>364</v>
+      </c>
+      <c r="D481" t="s">
+        <v>76</v>
+      </c>
+      <c r="E481" t="s">
+        <v>402</v>
+      </c>
+      <c r="G481" s="3">
+        <v>132.4</v>
+      </c>
+    </row>
+    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>541</v>
+      </c>
+      <c r="B482" t="s">
+        <v>542</v>
+      </c>
+      <c r="C482" t="s">
+        <v>373</v>
+      </c>
+      <c r="D482" t="s">
+        <v>11</v>
+      </c>
+      <c r="E482" t="s">
+        <v>541</v>
+      </c>
+      <c r="G482" s="3" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>541</v>
+      </c>
+      <c r="B483" t="s">
+        <v>542</v>
+      </c>
+      <c r="C483" t="s">
+        <v>373</v>
+      </c>
+      <c r="D483" t="s">
+        <v>74</v>
+      </c>
+      <c r="E483" t="s">
+        <v>414</v>
+      </c>
+      <c r="G483" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>541</v>
+      </c>
+      <c r="B484" t="s">
+        <v>542</v>
+      </c>
+      <c r="C484" t="s">
+        <v>373</v>
+      </c>
+      <c r="D484" t="s">
+        <v>74</v>
+      </c>
+      <c r="E484" t="s">
+        <v>69</v>
+      </c>
+      <c r="G484" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>541</v>
+      </c>
+      <c r="B485" t="s">
+        <v>542</v>
+      </c>
+      <c r="C485" t="s">
+        <v>373</v>
+      </c>
+      <c r="D485" t="s">
+        <v>74</v>
+      </c>
+      <c r="E485" t="s">
+        <v>414</v>
+      </c>
+      <c r="G485" s="3">
+        <v>5680</v>
+      </c>
+    </row>
+    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>541</v>
+      </c>
+      <c r="B486" t="s">
+        <v>542</v>
+      </c>
+      <c r="C486" t="s">
+        <v>373</v>
+      </c>
+      <c r="D486" t="s">
+        <v>12</v>
+      </c>
+      <c r="E486" t="s">
+        <v>544</v>
+      </c>
+      <c r="G486" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>541</v>
+      </c>
+      <c r="B487" t="s">
+        <v>542</v>
+      </c>
+      <c r="C487" t="s">
+        <v>373</v>
+      </c>
+      <c r="D487" t="s">
+        <v>76</v>
+      </c>
+      <c r="E487" t="s">
+        <v>234</v>
+      </c>
+      <c r="G487" s="3">
+        <v>134.55000000000001</v>
+      </c>
+    </row>
+    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>541</v>
+      </c>
+      <c r="B488" t="s">
+        <v>542</v>
+      </c>
+      <c r="C488" t="s">
+        <v>373</v>
+      </c>
+      <c r="D488" t="s">
+        <v>404</v>
+      </c>
+      <c r="E488" t="s">
+        <v>405</v>
+      </c>
+      <c r="G488" s="3" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>546</v>
+      </c>
+      <c r="B489" t="s">
+        <v>547</v>
+      </c>
+      <c r="C489" t="s">
+        <v>364</v>
+      </c>
+      <c r="D489" t="s">
+        <v>64</v>
+      </c>
+      <c r="E489" t="s">
+        <v>67</v>
+      </c>
+      <c r="G489" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>548</v>
+      </c>
+      <c r="B490" t="s">
+        <v>549</v>
+      </c>
+      <c r="C490" t="s">
+        <v>364</v>
+      </c>
+      <c r="D490" t="s">
+        <v>64</v>
+      </c>
+      <c r="E490" t="s">
+        <v>65</v>
+      </c>
+      <c r="F490" t="s">
+        <v>87</v>
+      </c>
+      <c r="G490" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>550</v>
+      </c>
+      <c r="B491" t="s">
+        <v>551</v>
+      </c>
+      <c r="C491" t="s">
+        <v>373</v>
+      </c>
+      <c r="D491" t="s">
+        <v>12</v>
+      </c>
+      <c r="E491" t="s">
+        <v>367</v>
+      </c>
+      <c r="F491" t="s">
+        <v>87</v>
+      </c>
+      <c r="G491" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>550</v>
+      </c>
+      <c r="B492" t="s">
+        <v>551</v>
+      </c>
+      <c r="C492" t="s">
+        <v>373</v>
+      </c>
+      <c r="D492" t="s">
+        <v>366</v>
+      </c>
+      <c r="F492" t="s">
+        <v>552</v>
+      </c>
+      <c r="G492" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>553</v>
+      </c>
+      <c r="B493" t="s">
+        <v>554</v>
+      </c>
+      <c r="C493" t="s">
+        <v>373</v>
+      </c>
+      <c r="D493" t="s">
+        <v>74</v>
+      </c>
+      <c r="E493" t="s">
+        <v>414</v>
+      </c>
+      <c r="G493" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>553</v>
+      </c>
+      <c r="B494" t="s">
+        <v>554</v>
+      </c>
+      <c r="C494" t="s">
+        <v>373</v>
+      </c>
+      <c r="D494" t="s">
+        <v>74</v>
+      </c>
+      <c r="E494" t="s">
+        <v>69</v>
+      </c>
+      <c r="G494" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>553</v>
+      </c>
+      <c r="B495" t="s">
+        <v>554</v>
+      </c>
+      <c r="C495" t="s">
+        <v>373</v>
+      </c>
+      <c r="D495" t="s">
+        <v>12</v>
+      </c>
+      <c r="E495" t="s">
+        <v>367</v>
+      </c>
+      <c r="G495" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>553</v>
+      </c>
+      <c r="B496" t="s">
+        <v>554</v>
+      </c>
+      <c r="C496" t="s">
+        <v>373</v>
+      </c>
+      <c r="D496" t="s">
+        <v>366</v>
+      </c>
+      <c r="F496" t="s">
+        <v>555</v>
+      </c>
+      <c r="G496" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>553</v>
+      </c>
+      <c r="B497" t="s">
+        <v>554</v>
+      </c>
+      <c r="C497" t="s">
+        <v>373</v>
+      </c>
+      <c r="D497" t="s">
+        <v>2</v>
+      </c>
+      <c r="G497" s="3">
+        <v>128.69999999999999</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>556</v>
+      </c>
+      <c r="B498" t="s">
+        <v>557</v>
+      </c>
+      <c r="C498" t="s">
+        <v>373</v>
+      </c>
+      <c r="D498" t="s">
+        <v>12</v>
+      </c>
+      <c r="E498" t="s">
+        <v>367</v>
+      </c>
+      <c r="F498" t="s">
+        <v>87</v>
+      </c>
+      <c r="G498" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>556</v>
+      </c>
+      <c r="B499" t="s">
+        <v>557</v>
+      </c>
+      <c r="C499" t="s">
+        <v>373</v>
+      </c>
+      <c r="D499" t="s">
+        <v>366</v>
+      </c>
+      <c r="F499" t="s">
+        <v>558</v>
+      </c>
+      <c r="G499" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>559</v>
+      </c>
+      <c r="B500" t="s">
+        <v>560</v>
+      </c>
+      <c r="C500" t="s">
+        <v>373</v>
+      </c>
+      <c r="D500" t="s">
+        <v>74</v>
+      </c>
+      <c r="E500" t="s">
+        <v>386</v>
+      </c>
+      <c r="G500" s="3">
+        <v>123.15</v>
+      </c>
+    </row>
+    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>559</v>
+      </c>
+      <c r="B501" t="s">
+        <v>560</v>
+      </c>
+      <c r="C501" t="s">
+        <v>373</v>
+      </c>
+      <c r="D501" t="s">
+        <v>74</v>
+      </c>
+      <c r="E501" t="s">
+        <v>69</v>
+      </c>
+      <c r="G501" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
+        <v>559</v>
+      </c>
+      <c r="B502" t="s">
+        <v>560</v>
+      </c>
+      <c r="C502" t="s">
+        <v>373</v>
+      </c>
+      <c r="D502" t="s">
+        <v>12</v>
+      </c>
+      <c r="E502" t="s">
+        <v>367</v>
+      </c>
+      <c r="G502" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>559</v>
+      </c>
+      <c r="B503" t="s">
+        <v>560</v>
+      </c>
+      <c r="C503" t="s">
+        <v>373</v>
+      </c>
+      <c r="D503" t="s">
+        <v>76</v>
+      </c>
+      <c r="E503" t="s">
+        <v>402</v>
+      </c>
+      <c r="G503" s="3">
+        <v>124.25</v>
+      </c>
+    </row>
+    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>559</v>
+      </c>
+      <c r="B504" t="s">
+        <v>560</v>
+      </c>
+      <c r="C504" t="s">
+        <v>373</v>
+      </c>
+      <c r="D504" t="s">
+        <v>366</v>
+      </c>
+      <c r="G504" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8C79AB-379D-400B-9DAD-9C4F2AFD91AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E5CFAB-2563-4937-94C5-C27D6E8A6ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2603" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2771" uniqueCount="600">
   <si>
     <t>AB</t>
   </si>
@@ -1722,6 +1722,123 @@
   </si>
   <si>
     <t>CYCO</t>
+  </si>
+  <si>
+    <t>La Biche River</t>
+  </si>
+  <si>
+    <t>CFP6</t>
+  </si>
+  <si>
+    <t>Liverpool / South Shore Regional</t>
+  </si>
+  <si>
+    <t>CYAU</t>
+  </si>
+  <si>
+    <t>Lower East Pubnico (La Field)</t>
+  </si>
+  <si>
+    <t>CLE4</t>
+  </si>
+  <si>
+    <t>Lutselk'e</t>
+  </si>
+  <si>
+    <t>CYLK</t>
+  </si>
+  <si>
+    <t>MacMillan Pass</t>
+  </si>
+  <si>
+    <t>CFC4</t>
+  </si>
+  <si>
+    <t>Mary River</t>
+  </si>
+  <si>
+    <t>CMR2</t>
+  </si>
+  <si>
+    <t>Mayo</t>
+  </si>
+  <si>
+    <t>CYMA</t>
+  </si>
+  <si>
+    <t>McQuesten</t>
+  </si>
+  <si>
+    <t>CFP4</t>
+  </si>
+  <si>
+    <t>Meadowbank</t>
+  </si>
+  <si>
+    <t>CMB2</t>
+  </si>
+  <si>
+    <t>11-23Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Meteghan / Keizers Air Park</t>
+  </si>
+  <si>
+    <t>CKZ5</t>
+  </si>
+  <si>
+    <t>Minto</t>
+  </si>
+  <si>
+    <t>CMN4</t>
+  </si>
+  <si>
+    <t>Nahanni Butte</t>
+  </si>
+  <si>
+    <t>CBD6</t>
+  </si>
+  <si>
+    <t>Naujaat</t>
+  </si>
+  <si>
+    <t>CYUT</t>
+  </si>
+  <si>
+    <t>1245-2315Z‡ Mon-Fri, 1445-2115Z‡ Sat &amp; Sun</t>
+  </si>
+  <si>
+    <t>Norman Wells</t>
+  </si>
+  <si>
+    <t>CYVQ</t>
+  </si>
+  <si>
+    <t>122.200, 282.300</t>
+  </si>
+  <si>
+    <t>Obre Lake / North of sixty</t>
+  </si>
+  <si>
+    <t>CKV4</t>
+  </si>
+  <si>
+    <t>ltd hrs (Jun 01-Aug 15) O/T tfc</t>
+  </si>
+  <si>
+    <t>Ogilvie</t>
+  </si>
+  <si>
+    <t>CFS4</t>
+  </si>
+  <si>
+    <t>Old Crow</t>
+  </si>
+  <si>
+    <t>CYOC</t>
+  </si>
+  <si>
+    <t>13-01Z</t>
   </si>
 </sst>
 </file>
@@ -2111,7 +2228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G504"/>
+  <dimension ref="A1:G537"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -12317,6 +12434,672 @@
         <v>122.1</v>
       </c>
     </row>
+    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>561</v>
+      </c>
+      <c r="B505" t="s">
+        <v>562</v>
+      </c>
+      <c r="C505" t="s">
+        <v>389</v>
+      </c>
+      <c r="D505" t="s">
+        <v>64</v>
+      </c>
+      <c r="E505" t="s">
+        <v>65</v>
+      </c>
+      <c r="G505" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
+        <v>563</v>
+      </c>
+      <c r="B506" t="s">
+        <v>564</v>
+      </c>
+      <c r="C506" t="s">
+        <v>6</v>
+      </c>
+      <c r="D506" t="s">
+        <v>64</v>
+      </c>
+      <c r="E506" t="s">
+        <v>67</v>
+      </c>
+      <c r="G506" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
+        <v>563</v>
+      </c>
+      <c r="B507" t="s">
+        <v>564</v>
+      </c>
+      <c r="C507" t="s">
+        <v>6</v>
+      </c>
+      <c r="D507" t="s">
+        <v>16</v>
+      </c>
+      <c r="E507" t="s">
+        <v>524</v>
+      </c>
+      <c r="G507" s="3">
+        <v>123.9</v>
+      </c>
+    </row>
+    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>563</v>
+      </c>
+      <c r="B508" t="s">
+        <v>564</v>
+      </c>
+      <c r="C508" t="s">
+        <v>6</v>
+      </c>
+      <c r="D508" t="s">
+        <v>17</v>
+      </c>
+      <c r="E508" t="s">
+        <v>524</v>
+      </c>
+      <c r="G508" s="3">
+        <v>123.9</v>
+      </c>
+    </row>
+    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>565</v>
+      </c>
+      <c r="B509" t="s">
+        <v>566</v>
+      </c>
+      <c r="C509" t="s">
+        <v>6</v>
+      </c>
+      <c r="D509" t="s">
+        <v>64</v>
+      </c>
+      <c r="E509" t="s">
+        <v>67</v>
+      </c>
+      <c r="G509" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>567</v>
+      </c>
+      <c r="B510" t="s">
+        <v>568</v>
+      </c>
+      <c r="C510" t="s">
+        <v>364</v>
+      </c>
+      <c r="D510" t="s">
+        <v>12</v>
+      </c>
+      <c r="E510" t="s">
+        <v>367</v>
+      </c>
+      <c r="F510" t="s">
+        <v>87</v>
+      </c>
+      <c r="G510" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>567</v>
+      </c>
+      <c r="B511" t="s">
+        <v>568</v>
+      </c>
+      <c r="C511" t="s">
+        <v>364</v>
+      </c>
+      <c r="D511" t="s">
+        <v>366</v>
+      </c>
+      <c r="F511" t="s">
+        <v>485</v>
+      </c>
+      <c r="G511" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
+        <v>569</v>
+      </c>
+      <c r="B512" t="s">
+        <v>570</v>
+      </c>
+      <c r="C512" t="s">
+        <v>389</v>
+      </c>
+      <c r="D512" t="s">
+        <v>64</v>
+      </c>
+      <c r="E512" t="s">
+        <v>67</v>
+      </c>
+      <c r="G512" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
+        <v>571</v>
+      </c>
+      <c r="B513" t="s">
+        <v>572</v>
+      </c>
+      <c r="C513" t="s">
+        <v>373</v>
+      </c>
+      <c r="D513" t="s">
+        <v>64</v>
+      </c>
+      <c r="E513" t="s">
+        <v>65</v>
+      </c>
+      <c r="G513" s="3">
+        <v>123.35</v>
+      </c>
+    </row>
+    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
+        <v>571</v>
+      </c>
+      <c r="B514" t="s">
+        <v>572</v>
+      </c>
+      <c r="C514" t="s">
+        <v>373</v>
+      </c>
+      <c r="D514" t="s">
+        <v>113</v>
+      </c>
+      <c r="G514" s="3">
+        <v>122.35</v>
+      </c>
+    </row>
+    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
+        <v>573</v>
+      </c>
+      <c r="B515" t="s">
+        <v>574</v>
+      </c>
+      <c r="C515" t="s">
+        <v>389</v>
+      </c>
+      <c r="D515" t="s">
+        <v>74</v>
+      </c>
+      <c r="E515" t="s">
+        <v>391</v>
+      </c>
+      <c r="G515" s="3">
+        <v>122.375</v>
+      </c>
+    </row>
+    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>573</v>
+      </c>
+      <c r="B516" t="s">
+        <v>574</v>
+      </c>
+      <c r="C516" t="s">
+        <v>389</v>
+      </c>
+      <c r="D516" t="s">
+        <v>74</v>
+      </c>
+      <c r="E516" t="s">
+        <v>69</v>
+      </c>
+      <c r="G516" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
+        <v>573</v>
+      </c>
+      <c r="B517" t="s">
+        <v>574</v>
+      </c>
+      <c r="C517" t="s">
+        <v>389</v>
+      </c>
+      <c r="D517" t="s">
+        <v>12</v>
+      </c>
+      <c r="E517" t="s">
+        <v>367</v>
+      </c>
+      <c r="G517" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
+        <v>573</v>
+      </c>
+      <c r="B518" t="s">
+        <v>574</v>
+      </c>
+      <c r="C518" t="s">
+        <v>389</v>
+      </c>
+      <c r="D518" t="s">
+        <v>76</v>
+      </c>
+      <c r="E518" t="s">
+        <v>402</v>
+      </c>
+      <c r="G518" s="3">
+        <v>134.65</v>
+      </c>
+    </row>
+    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A519" t="s">
+        <v>573</v>
+      </c>
+      <c r="B519" t="s">
+        <v>574</v>
+      </c>
+      <c r="C519" t="s">
+        <v>389</v>
+      </c>
+      <c r="D519" t="s">
+        <v>366</v>
+      </c>
+      <c r="G519" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A520" t="s">
+        <v>575</v>
+      </c>
+      <c r="B520" t="s">
+        <v>576</v>
+      </c>
+      <c r="C520" t="s">
+        <v>389</v>
+      </c>
+      <c r="D520" t="s">
+        <v>64</v>
+      </c>
+      <c r="E520" t="s">
+        <v>67</v>
+      </c>
+      <c r="G520" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A521" t="s">
+        <v>577</v>
+      </c>
+      <c r="B521" t="s">
+        <v>578</v>
+      </c>
+      <c r="C521" t="s">
+        <v>373</v>
+      </c>
+      <c r="D521" t="s">
+        <v>64</v>
+      </c>
+      <c r="E521" t="s">
+        <v>65</v>
+      </c>
+      <c r="F521" t="s">
+        <v>579</v>
+      </c>
+      <c r="G521" s="3">
+        <v>123.35</v>
+      </c>
+    </row>
+    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A522" t="s">
+        <v>580</v>
+      </c>
+      <c r="B522" t="s">
+        <v>581</v>
+      </c>
+      <c r="C522" t="s">
+        <v>6</v>
+      </c>
+      <c r="D522" t="s">
+        <v>64</v>
+      </c>
+      <c r="E522" t="s">
+        <v>67</v>
+      </c>
+      <c r="G522" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A523" t="s">
+        <v>582</v>
+      </c>
+      <c r="B523" t="s">
+        <v>583</v>
+      </c>
+      <c r="C523" t="s">
+        <v>389</v>
+      </c>
+      <c r="D523" t="s">
+        <v>64</v>
+      </c>
+      <c r="E523" t="s">
+        <v>67</v>
+      </c>
+      <c r="G523" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A524" t="s">
+        <v>584</v>
+      </c>
+      <c r="B524" t="s">
+        <v>585</v>
+      </c>
+      <c r="C524" t="s">
+        <v>364</v>
+      </c>
+      <c r="D524" t="s">
+        <v>64</v>
+      </c>
+      <c r="E524" t="s">
+        <v>67</v>
+      </c>
+      <c r="G524" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
+        <v>586</v>
+      </c>
+      <c r="B525" t="s">
+        <v>587</v>
+      </c>
+      <c r="C525" t="s">
+        <v>373</v>
+      </c>
+      <c r="D525" t="s">
+        <v>12</v>
+      </c>
+      <c r="E525" t="s">
+        <v>367</v>
+      </c>
+      <c r="F525" t="s">
+        <v>87</v>
+      </c>
+      <c r="G525" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
+        <v>586</v>
+      </c>
+      <c r="B526" t="s">
+        <v>587</v>
+      </c>
+      <c r="C526" t="s">
+        <v>373</v>
+      </c>
+      <c r="D526" t="s">
+        <v>366</v>
+      </c>
+      <c r="F526" t="s">
+        <v>588</v>
+      </c>
+      <c r="G526" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A527" t="s">
+        <v>589</v>
+      </c>
+      <c r="B527" t="s">
+        <v>590</v>
+      </c>
+      <c r="C527" t="s">
+        <v>364</v>
+      </c>
+      <c r="D527" t="s">
+        <v>11</v>
+      </c>
+      <c r="G527" s="3" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A528" t="s">
+        <v>589</v>
+      </c>
+      <c r="B528" t="s">
+        <v>590</v>
+      </c>
+      <c r="C528" t="s">
+        <v>364</v>
+      </c>
+      <c r="D528" t="s">
+        <v>74</v>
+      </c>
+      <c r="E528" t="s">
+        <v>386</v>
+      </c>
+      <c r="G528" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A529" t="s">
+        <v>589</v>
+      </c>
+      <c r="B529" t="s">
+        <v>590</v>
+      </c>
+      <c r="C529" t="s">
+        <v>364</v>
+      </c>
+      <c r="D529" t="s">
+        <v>74</v>
+      </c>
+      <c r="E529" t="s">
+        <v>69</v>
+      </c>
+      <c r="G529" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A530" t="s">
+        <v>589</v>
+      </c>
+      <c r="B530" t="s">
+        <v>590</v>
+      </c>
+      <c r="C530" t="s">
+        <v>364</v>
+      </c>
+      <c r="D530" t="s">
+        <v>12</v>
+      </c>
+      <c r="E530" t="s">
+        <v>100</v>
+      </c>
+      <c r="G530" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
+        <v>589</v>
+      </c>
+      <c r="B531" t="s">
+        <v>590</v>
+      </c>
+      <c r="C531" t="s">
+        <v>364</v>
+      </c>
+      <c r="D531" t="s">
+        <v>76</v>
+      </c>
+      <c r="E531" t="s">
+        <v>402</v>
+      </c>
+      <c r="G531" s="3">
+        <v>134.82499999999999</v>
+      </c>
+    </row>
+    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A532" t="s">
+        <v>592</v>
+      </c>
+      <c r="B532" t="s">
+        <v>593</v>
+      </c>
+      <c r="C532" t="s">
+        <v>364</v>
+      </c>
+      <c r="D532" t="s">
+        <v>64</v>
+      </c>
+      <c r="E532" t="s">
+        <v>65</v>
+      </c>
+      <c r="F532" t="s">
+        <v>594</v>
+      </c>
+      <c r="G532" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A533" t="s">
+        <v>595</v>
+      </c>
+      <c r="B533" t="s">
+        <v>596</v>
+      </c>
+      <c r="C533" t="s">
+        <v>389</v>
+      </c>
+      <c r="D533" t="s">
+        <v>64</v>
+      </c>
+      <c r="E533" t="s">
+        <v>67</v>
+      </c>
+      <c r="G533" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A534" t="s">
+        <v>597</v>
+      </c>
+      <c r="B534" t="s">
+        <v>598</v>
+      </c>
+      <c r="C534" t="s">
+        <v>389</v>
+      </c>
+      <c r="D534" t="s">
+        <v>300</v>
+      </c>
+      <c r="E534" t="s">
+        <v>391</v>
+      </c>
+      <c r="G534" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="535" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A535" t="s">
+        <v>597</v>
+      </c>
+      <c r="B535" t="s">
+        <v>598</v>
+      </c>
+      <c r="C535" t="s">
+        <v>389</v>
+      </c>
+      <c r="D535" t="s">
+        <v>300</v>
+      </c>
+      <c r="E535" t="s">
+        <v>69</v>
+      </c>
+      <c r="G535" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="536" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A536" t="s">
+        <v>597</v>
+      </c>
+      <c r="B536" t="s">
+        <v>598</v>
+      </c>
+      <c r="C536" t="s">
+        <v>389</v>
+      </c>
+      <c r="D536" t="s">
+        <v>12</v>
+      </c>
+      <c r="E536" t="s">
+        <v>367</v>
+      </c>
+      <c r="F536" t="s">
+        <v>87</v>
+      </c>
+      <c r="G536" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A537" t="s">
+        <v>597</v>
+      </c>
+      <c r="B537" t="s">
+        <v>598</v>
+      </c>
+      <c r="C537" t="s">
+        <v>389</v>
+      </c>
+      <c r="D537" t="s">
+        <v>366</v>
+      </c>
+      <c r="F537" t="s">
+        <v>599</v>
+      </c>
+      <c r="G537" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E5CFAB-2563-4937-94C5-C27D6E8A6ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCAB91E-D49B-4373-91B3-8A1DAAA1C48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2771" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2877" uniqueCount="622">
   <si>
     <t>AB</t>
   </si>
@@ -1839,6 +1839,72 @@
   </si>
   <si>
     <t>13-01Z</t>
+  </si>
+  <si>
+    <t>Pangnirtung</t>
+  </si>
+  <si>
+    <t>CYXP</t>
+  </si>
+  <si>
+    <t>12-23Z‡ Mon-Fri, 15-20Z‡ Sat, 17-21Z‡ Sun</t>
+  </si>
+  <si>
+    <t>Paulatuk (Nora Aliqatchialuk Ruben)</t>
+  </si>
+  <si>
+    <t>CYPC</t>
+  </si>
+  <si>
+    <t>Pelly Crossing</t>
+  </si>
+  <si>
+    <t>CFQ6</t>
+  </si>
+  <si>
+    <t>Pine Lake</t>
+  </si>
+  <si>
+    <t>CFY5</t>
+  </si>
+  <si>
+    <t>Pond Inlet</t>
+  </si>
+  <si>
+    <t>CYIO</t>
+  </si>
+  <si>
+    <t>16-23Z‡ Mon, 16-24Z‡ Tue, Thu, &amp; Fri, 16-22Z‡ Wed, 19-22Z‡ Sat</t>
+  </si>
+  <si>
+    <t>Porters Lake</t>
+  </si>
+  <si>
+    <t>CCF4</t>
+  </si>
+  <si>
+    <t>Port Hawkesbury</t>
+  </si>
+  <si>
+    <t>CYPD</t>
+  </si>
+  <si>
+    <t>1230-2130Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Prairie Creek</t>
+  </si>
+  <si>
+    <t>CBH4</t>
+  </si>
+  <si>
+    <t>Qikiqtarjuaq</t>
+  </si>
+  <si>
+    <t>CYVM</t>
+  </si>
+  <si>
+    <t>11-21Z‡ Mon &amp; Wed, 13-23Z‡ Tue, 14-23Z‡ Thu, 13-22Z‡ Fri, &amp; Sat, 11-18Z‡ Sun</t>
   </si>
 </sst>
 </file>
@@ -2228,7 +2294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G537"/>
+  <dimension ref="A1:G559"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -13100,6 +13166,434 @@
         <v>122.1</v>
       </c>
     </row>
+    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A538" t="s">
+        <v>600</v>
+      </c>
+      <c r="B538" t="s">
+        <v>601</v>
+      </c>
+      <c r="C538" t="s">
+        <v>373</v>
+      </c>
+      <c r="D538" t="s">
+        <v>12</v>
+      </c>
+      <c r="E538" t="s">
+        <v>367</v>
+      </c>
+      <c r="F538" t="s">
+        <v>87</v>
+      </c>
+      <c r="G538" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A539" t="s">
+        <v>600</v>
+      </c>
+      <c r="B539" t="s">
+        <v>601</v>
+      </c>
+      <c r="C539" t="s">
+        <v>373</v>
+      </c>
+      <c r="D539" t="s">
+        <v>366</v>
+      </c>
+      <c r="F539" t="s">
+        <v>602</v>
+      </c>
+      <c r="G539" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="540" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A540" t="s">
+        <v>600</v>
+      </c>
+      <c r="B540" t="s">
+        <v>601</v>
+      </c>
+      <c r="C540" t="s">
+        <v>373</v>
+      </c>
+      <c r="D540" t="s">
+        <v>377</v>
+      </c>
+      <c r="G540" s="3">
+        <v>125.1</v>
+      </c>
+    </row>
+    <row r="541" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A541" t="s">
+        <v>603</v>
+      </c>
+      <c r="B541" t="s">
+        <v>604</v>
+      </c>
+      <c r="C541" t="s">
+        <v>364</v>
+      </c>
+      <c r="D541" t="s">
+        <v>12</v>
+      </c>
+      <c r="E541" t="s">
+        <v>367</v>
+      </c>
+      <c r="F541" t="s">
+        <v>87</v>
+      </c>
+      <c r="G541" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="542" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A542" t="s">
+        <v>603</v>
+      </c>
+      <c r="B542" t="s">
+        <v>604</v>
+      </c>
+      <c r="C542" t="s">
+        <v>364</v>
+      </c>
+      <c r="D542" t="s">
+        <v>366</v>
+      </c>
+      <c r="F542" t="s">
+        <v>466</v>
+      </c>
+      <c r="G542" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A543" t="s">
+        <v>605</v>
+      </c>
+      <c r="B543" t="s">
+        <v>606</v>
+      </c>
+      <c r="C543" t="s">
+        <v>389</v>
+      </c>
+      <c r="D543" t="s">
+        <v>64</v>
+      </c>
+      <c r="E543" t="s">
+        <v>67</v>
+      </c>
+      <c r="G543" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="544" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A544" t="s">
+        <v>607</v>
+      </c>
+      <c r="B544" t="s">
+        <v>608</v>
+      </c>
+      <c r="C544" t="s">
+        <v>389</v>
+      </c>
+      <c r="D544" t="s">
+        <v>64</v>
+      </c>
+      <c r="E544" t="s">
+        <v>67</v>
+      </c>
+      <c r="G544" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A545" t="s">
+        <v>609</v>
+      </c>
+      <c r="B545" t="s">
+        <v>610</v>
+      </c>
+      <c r="C545" t="s">
+        <v>373</v>
+      </c>
+      <c r="D545" t="s">
+        <v>74</v>
+      </c>
+      <c r="E545" t="s">
+        <v>414</v>
+      </c>
+      <c r="G545" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A546" t="s">
+        <v>609</v>
+      </c>
+      <c r="B546" t="s">
+        <v>610</v>
+      </c>
+      <c r="C546" t="s">
+        <v>373</v>
+      </c>
+      <c r="D546" t="s">
+        <v>74</v>
+      </c>
+      <c r="E546" t="s">
+        <v>69</v>
+      </c>
+      <c r="G546" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A547" t="s">
+        <v>609</v>
+      </c>
+      <c r="B547" t="s">
+        <v>610</v>
+      </c>
+      <c r="C547" t="s">
+        <v>373</v>
+      </c>
+      <c r="D547" t="s">
+        <v>12</v>
+      </c>
+      <c r="E547" t="s">
+        <v>367</v>
+      </c>
+      <c r="F547" t="s">
+        <v>87</v>
+      </c>
+      <c r="G547" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A548" t="s">
+        <v>609</v>
+      </c>
+      <c r="B548" t="s">
+        <v>610</v>
+      </c>
+      <c r="C548" t="s">
+        <v>373</v>
+      </c>
+      <c r="D548" t="s">
+        <v>366</v>
+      </c>
+      <c r="F548" t="s">
+        <v>611</v>
+      </c>
+      <c r="G548" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A549" t="s">
+        <v>609</v>
+      </c>
+      <c r="B549" t="s">
+        <v>610</v>
+      </c>
+      <c r="C549" t="s">
+        <v>373</v>
+      </c>
+      <c r="D549" t="s">
+        <v>2</v>
+      </c>
+      <c r="G549" s="3">
+        <v>128.30000000000001</v>
+      </c>
+    </row>
+    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
+        <v>612</v>
+      </c>
+      <c r="B550" t="s">
+        <v>613</v>
+      </c>
+      <c r="C550" t="s">
+        <v>6</v>
+      </c>
+      <c r="D550" t="s">
+        <v>64</v>
+      </c>
+      <c r="E550" t="s">
+        <v>67</v>
+      </c>
+      <c r="G550" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A551" t="s">
+        <v>614</v>
+      </c>
+      <c r="B551" t="s">
+        <v>615</v>
+      </c>
+      <c r="C551" t="s">
+        <v>6</v>
+      </c>
+      <c r="D551" t="s">
+        <v>74</v>
+      </c>
+      <c r="E551" t="s">
+        <v>275</v>
+      </c>
+      <c r="G551" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A552" t="s">
+        <v>614</v>
+      </c>
+      <c r="B552" t="s">
+        <v>615</v>
+      </c>
+      <c r="C552" t="s">
+        <v>6</v>
+      </c>
+      <c r="D552" t="s">
+        <v>74</v>
+      </c>
+      <c r="E552" t="s">
+        <v>69</v>
+      </c>
+      <c r="G552" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A553" t="s">
+        <v>614</v>
+      </c>
+      <c r="B553" t="s">
+        <v>615</v>
+      </c>
+      <c r="C553" t="s">
+        <v>6</v>
+      </c>
+      <c r="D553" t="s">
+        <v>64</v>
+      </c>
+      <c r="E553" t="s">
+        <v>65</v>
+      </c>
+      <c r="F553" t="s">
+        <v>616</v>
+      </c>
+      <c r="G553" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
+        <v>614</v>
+      </c>
+      <c r="B554" t="s">
+        <v>615</v>
+      </c>
+      <c r="C554" t="s">
+        <v>6</v>
+      </c>
+      <c r="D554" t="s">
+        <v>76</v>
+      </c>
+      <c r="E554" t="s">
+        <v>524</v>
+      </c>
+      <c r="G554" s="3">
+        <v>135.1</v>
+      </c>
+    </row>
+    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A555" t="s">
+        <v>614</v>
+      </c>
+      <c r="B555" t="s">
+        <v>615</v>
+      </c>
+      <c r="C555" t="s">
+        <v>6</v>
+      </c>
+      <c r="D555" t="s">
+        <v>2</v>
+      </c>
+      <c r="G555" s="3">
+        <v>128.30000000000001</v>
+      </c>
+    </row>
+    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
+        <v>617</v>
+      </c>
+      <c r="B556" t="s">
+        <v>618</v>
+      </c>
+      <c r="C556" t="s">
+        <v>364</v>
+      </c>
+      <c r="D556" t="s">
+        <v>64</v>
+      </c>
+      <c r="E556" t="s">
+        <v>65</v>
+      </c>
+      <c r="F556" t="s">
+        <v>87</v>
+      </c>
+      <c r="G556" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
+        <v>619</v>
+      </c>
+      <c r="B557" t="s">
+        <v>620</v>
+      </c>
+      <c r="C557" t="s">
+        <v>373</v>
+      </c>
+      <c r="D557" t="s">
+        <v>12</v>
+      </c>
+      <c r="E557" t="s">
+        <v>367</v>
+      </c>
+      <c r="F557" t="s">
+        <v>87</v>
+      </c>
+      <c r="G557" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D558" t="s">
+        <v>366</v>
+      </c>
+      <c r="F558" t="s">
+        <v>621</v>
+      </c>
+      <c r="G558" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D559" t="s">
+        <v>2</v>
+      </c>
+      <c r="G559" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCAB91E-D49B-4373-91B3-8A1DAAA1C48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D086D4-327A-4EF2-BD7F-FBEEB4A2023E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2877" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3070" uniqueCount="659">
   <si>
     <t>AB</t>
   </si>
@@ -1905,6 +1905,117 @@
   </si>
   <si>
     <t>11-21Z‡ Mon &amp; Wed, 13-23Z‡ Tue, 14-23Z‡ Thu, 13-22Z‡ Fri, &amp; Sat, 11-18Z‡ Sun</t>
+  </si>
+  <si>
+    <t>Rae/ Edzo</t>
+  </si>
+  <si>
+    <t>CRE</t>
+  </si>
+  <si>
+    <t>Rankin Inlet</t>
+  </si>
+  <si>
+    <t>CYRT</t>
+  </si>
+  <si>
+    <t>Rankin rdo</t>
+  </si>
+  <si>
+    <t>Resolute Bay</t>
+  </si>
+  <si>
+    <t>CYRB</t>
+  </si>
+  <si>
+    <t>126.7, 5680</t>
+  </si>
+  <si>
+    <t>Ross River</t>
+  </si>
+  <si>
+    <t>CYDM</t>
+  </si>
+  <si>
+    <t>Sable Island</t>
+  </si>
+  <si>
+    <t>CSB2</t>
+  </si>
+  <si>
+    <t>Ltd hrs</t>
+  </si>
+  <si>
+    <t>Sachs Harbour (David Nasogaluak Jr. Saaryuaq)</t>
+  </si>
+  <si>
+    <t>CYSY</t>
+  </si>
+  <si>
+    <t>Sambaa K'E</t>
+  </si>
+  <si>
+    <t>CEU9</t>
+  </si>
+  <si>
+    <t>Sanikiluaq</t>
+  </si>
+  <si>
+    <t>CYSK</t>
+  </si>
+  <si>
+    <t>MF/ATF</t>
+  </si>
+  <si>
+    <t>Sanirajak Airport</t>
+  </si>
+  <si>
+    <t>CYUX</t>
+  </si>
+  <si>
+    <t>12-24Z</t>
+  </si>
+  <si>
+    <t>228.900, 256.600, 263.200, 364.200</t>
+  </si>
+  <si>
+    <t>Silver City</t>
+  </si>
+  <si>
+    <t>CFQ5</t>
+  </si>
+  <si>
+    <t>Snare River</t>
+  </si>
+  <si>
+    <t>CEV9</t>
+  </si>
+  <si>
+    <t>Stanley</t>
+  </si>
+  <si>
+    <t>CCW4</t>
+  </si>
+  <si>
+    <t>Summerside</t>
+  </si>
+  <si>
+    <t>CYSU</t>
+  </si>
+  <si>
+    <t>Sydney / J. A. Douglas McCurdy</t>
+  </si>
+  <si>
+    <t>CYQY</t>
+  </si>
+  <si>
+    <t>RAAS Charlottetown rdo</t>
+  </si>
+  <si>
+    <t>Charlottetown rdo</t>
+  </si>
+  <si>
+    <t>188.600, 266.300</t>
   </si>
 </sst>
 </file>
@@ -2294,7 +2405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G559"/>
+  <dimension ref="A1:G596"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -13576,6 +13687,15 @@
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A558" t="s">
+        <v>619</v>
+      </c>
+      <c r="B558" t="s">
+        <v>620</v>
+      </c>
+      <c r="C558" t="s">
+        <v>373</v>
+      </c>
       <c r="D558" t="s">
         <v>366</v>
       </c>
@@ -13587,11 +13707,755 @@
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A559" t="s">
+        <v>619</v>
+      </c>
+      <c r="B559" t="s">
+        <v>620</v>
+      </c>
+      <c r="C559" t="s">
+        <v>373</v>
+      </c>
       <c r="D559" t="s">
         <v>2</v>
       </c>
       <c r="G559" s="3">
         <v>122.55</v>
+      </c>
+    </row>
+    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A560" t="s">
+        <v>622</v>
+      </c>
+      <c r="B560" t="s">
+        <v>623</v>
+      </c>
+      <c r="C560" t="s">
+        <v>364</v>
+      </c>
+      <c r="D560" t="s">
+        <v>64</v>
+      </c>
+      <c r="E560" t="s">
+        <v>67</v>
+      </c>
+      <c r="G560" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A561" t="s">
+        <v>624</v>
+      </c>
+      <c r="B561" t="s">
+        <v>625</v>
+      </c>
+      <c r="C561" t="s">
+        <v>373</v>
+      </c>
+      <c r="D561" t="s">
+        <v>11</v>
+      </c>
+      <c r="E561" t="s">
+        <v>626</v>
+      </c>
+      <c r="G561" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="562" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>624</v>
+      </c>
+      <c r="B562" t="s">
+        <v>625</v>
+      </c>
+      <c r="C562" t="s">
+        <v>373</v>
+      </c>
+      <c r="D562" t="s">
+        <v>74</v>
+      </c>
+      <c r="E562" t="s">
+        <v>386</v>
+      </c>
+      <c r="G562" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
+        <v>624</v>
+      </c>
+      <c r="B563" t="s">
+        <v>625</v>
+      </c>
+      <c r="C563" t="s">
+        <v>373</v>
+      </c>
+      <c r="D563" t="s">
+        <v>74</v>
+      </c>
+      <c r="E563" t="s">
+        <v>69</v>
+      </c>
+      <c r="G563" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
+        <v>624</v>
+      </c>
+      <c r="B564" t="s">
+        <v>625</v>
+      </c>
+      <c r="C564" t="s">
+        <v>373</v>
+      </c>
+      <c r="D564" t="s">
+        <v>12</v>
+      </c>
+      <c r="E564" t="s">
+        <v>626</v>
+      </c>
+      <c r="G564" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A565" t="s">
+        <v>624</v>
+      </c>
+      <c r="B565" t="s">
+        <v>625</v>
+      </c>
+      <c r="C565" t="s">
+        <v>373</v>
+      </c>
+      <c r="D565" t="s">
+        <v>76</v>
+      </c>
+      <c r="E565" t="s">
+        <v>402</v>
+      </c>
+      <c r="G565" s="3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="566" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A566" t="s">
+        <v>627</v>
+      </c>
+      <c r="B566" t="s">
+        <v>628</v>
+      </c>
+      <c r="C566" t="s">
+        <v>373</v>
+      </c>
+      <c r="D566" t="s">
+        <v>74</v>
+      </c>
+      <c r="E566" t="s">
+        <v>386</v>
+      </c>
+      <c r="G566" s="3" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="567" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A567" t="s">
+        <v>627</v>
+      </c>
+      <c r="B567" t="s">
+        <v>628</v>
+      </c>
+      <c r="C567" t="s">
+        <v>373</v>
+      </c>
+      <c r="D567" t="s">
+        <v>74</v>
+      </c>
+      <c r="E567" t="s">
+        <v>69</v>
+      </c>
+      <c r="G567" s="3"/>
+    </row>
+    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A568" t="s">
+        <v>627</v>
+      </c>
+      <c r="B568" t="s">
+        <v>628</v>
+      </c>
+      <c r="C568" t="s">
+        <v>373</v>
+      </c>
+      <c r="D568" t="s">
+        <v>12</v>
+      </c>
+      <c r="E568" t="s">
+        <v>367</v>
+      </c>
+      <c r="G568" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A569" t="s">
+        <v>627</v>
+      </c>
+      <c r="B569" t="s">
+        <v>628</v>
+      </c>
+      <c r="C569" t="s">
+        <v>373</v>
+      </c>
+      <c r="D569" t="s">
+        <v>366</v>
+      </c>
+      <c r="G569" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="570" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A570" t="s">
+        <v>630</v>
+      </c>
+      <c r="B570" t="s">
+        <v>631</v>
+      </c>
+      <c r="C570" t="s">
+        <v>389</v>
+      </c>
+      <c r="D570" t="s">
+        <v>64</v>
+      </c>
+      <c r="E570" t="s">
+        <v>67</v>
+      </c>
+      <c r="G570" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A571" t="s">
+        <v>632</v>
+      </c>
+      <c r="B571" t="s">
+        <v>633</v>
+      </c>
+      <c r="C571" t="s">
+        <v>6</v>
+      </c>
+      <c r="D571" t="s">
+        <v>12</v>
+      </c>
+      <c r="E571" t="s">
+        <v>67</v>
+      </c>
+      <c r="G571" s="3">
+        <v>122.75</v>
+      </c>
+    </row>
+    <row r="572" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A572" t="s">
+        <v>632</v>
+      </c>
+      <c r="B572" t="s">
+        <v>633</v>
+      </c>
+      <c r="C572" t="s">
+        <v>6</v>
+      </c>
+      <c r="D572" t="s">
+        <v>235</v>
+      </c>
+      <c r="F572" t="s">
+        <v>634</v>
+      </c>
+      <c r="G572" s="3">
+        <v>122.9</v>
+      </c>
+    </row>
+    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A573" t="s">
+        <v>632</v>
+      </c>
+      <c r="B573" t="s">
+        <v>633</v>
+      </c>
+      <c r="C573" t="s">
+        <v>6</v>
+      </c>
+      <c r="D573" t="s">
+        <v>2</v>
+      </c>
+      <c r="G573" s="3">
+        <v>118.2</v>
+      </c>
+    </row>
+    <row r="574" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A574" t="s">
+        <v>635</v>
+      </c>
+      <c r="B574" t="s">
+        <v>636</v>
+      </c>
+      <c r="C574" t="s">
+        <v>364</v>
+      </c>
+      <c r="D574" t="s">
+        <v>74</v>
+      </c>
+      <c r="E574" t="s">
+        <v>386</v>
+      </c>
+      <c r="G574" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A575" t="s">
+        <v>635</v>
+      </c>
+      <c r="B575" t="s">
+        <v>636</v>
+      </c>
+      <c r="C575" t="s">
+        <v>364</v>
+      </c>
+      <c r="D575" t="s">
+        <v>74</v>
+      </c>
+      <c r="E575" t="s">
+        <v>69</v>
+      </c>
+      <c r="G575" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="576" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A576" t="s">
+        <v>635</v>
+      </c>
+      <c r="B576" t="s">
+        <v>636</v>
+      </c>
+      <c r="C576" t="s">
+        <v>364</v>
+      </c>
+      <c r="D576" t="s">
+        <v>12</v>
+      </c>
+      <c r="E576" t="s">
+        <v>367</v>
+      </c>
+      <c r="F576" t="s">
+        <v>87</v>
+      </c>
+      <c r="G576" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="577" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A577" t="s">
+        <v>635</v>
+      </c>
+      <c r="B577" t="s">
+        <v>636</v>
+      </c>
+      <c r="C577" t="s">
+        <v>364</v>
+      </c>
+      <c r="D577" t="s">
+        <v>366</v>
+      </c>
+      <c r="G577" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="578" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A578" t="s">
+        <v>637</v>
+      </c>
+      <c r="B578" t="s">
+        <v>638</v>
+      </c>
+      <c r="C578" t="s">
+        <v>364</v>
+      </c>
+      <c r="D578" t="s">
+        <v>64</v>
+      </c>
+      <c r="E578" t="s">
+        <v>67</v>
+      </c>
+      <c r="G578" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="579" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A579" t="s">
+        <v>639</v>
+      </c>
+      <c r="B579" t="s">
+        <v>640</v>
+      </c>
+      <c r="C579" t="s">
+        <v>373</v>
+      </c>
+      <c r="D579" t="s">
+        <v>641</v>
+      </c>
+      <c r="E579" t="s">
+        <v>367</v>
+      </c>
+      <c r="F579" t="s">
+        <v>87</v>
+      </c>
+      <c r="G579" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="580" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A580" t="s">
+        <v>639</v>
+      </c>
+      <c r="B580" t="s">
+        <v>640</v>
+      </c>
+      <c r="C580" t="s">
+        <v>373</v>
+      </c>
+      <c r="D580" t="s">
+        <v>366</v>
+      </c>
+      <c r="G580" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="581" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A581" t="s">
+        <v>642</v>
+      </c>
+      <c r="B581" t="s">
+        <v>643</v>
+      </c>
+      <c r="C581" t="s">
+        <v>373</v>
+      </c>
+      <c r="D581" t="s">
+        <v>74</v>
+      </c>
+      <c r="E581" t="s">
+        <v>386</v>
+      </c>
+      <c r="G581" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="582" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A582" t="s">
+        <v>642</v>
+      </c>
+      <c r="B582" t="s">
+        <v>643</v>
+      </c>
+      <c r="C582" t="s">
+        <v>373</v>
+      </c>
+      <c r="D582" t="s">
+        <v>74</v>
+      </c>
+      <c r="E582" t="s">
+        <v>69</v>
+      </c>
+      <c r="G582" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="583" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A583" t="s">
+        <v>642</v>
+      </c>
+      <c r="B583" t="s">
+        <v>643</v>
+      </c>
+      <c r="C583" t="s">
+        <v>373</v>
+      </c>
+      <c r="D583" t="s">
+        <v>12</v>
+      </c>
+      <c r="E583" t="s">
+        <v>367</v>
+      </c>
+      <c r="F583" t="s">
+        <v>87</v>
+      </c>
+      <c r="G583" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="584" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A584" t="s">
+        <v>642</v>
+      </c>
+      <c r="B584" t="s">
+        <v>643</v>
+      </c>
+      <c r="C584" t="s">
+        <v>373</v>
+      </c>
+      <c r="D584" t="s">
+        <v>366</v>
+      </c>
+      <c r="F584" t="s">
+        <v>644</v>
+      </c>
+      <c r="G584" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="585" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A585" t="s">
+        <v>642</v>
+      </c>
+      <c r="B585" t="s">
+        <v>643</v>
+      </c>
+      <c r="C585" t="s">
+        <v>373</v>
+      </c>
+      <c r="D585" t="s">
+        <v>185</v>
+      </c>
+      <c r="G585" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="586" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A586" t="s">
+        <v>642</v>
+      </c>
+      <c r="B586" t="s">
+        <v>643</v>
+      </c>
+      <c r="C586" t="s">
+        <v>373</v>
+      </c>
+      <c r="D586" t="s">
+        <v>2</v>
+      </c>
+      <c r="G586" s="3">
+        <v>128.69999999999999</v>
+      </c>
+    </row>
+    <row r="587" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A587" t="s">
+        <v>646</v>
+      </c>
+      <c r="B587" t="s">
+        <v>647</v>
+      </c>
+      <c r="C587" t="s">
+        <v>389</v>
+      </c>
+      <c r="D587" t="s">
+        <v>64</v>
+      </c>
+      <c r="E587" t="s">
+        <v>67</v>
+      </c>
+      <c r="G587" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="588" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A588" t="s">
+        <v>648</v>
+      </c>
+      <c r="B588" t="s">
+        <v>649</v>
+      </c>
+      <c r="C588" t="s">
+        <v>364</v>
+      </c>
+      <c r="D588" t="s">
+        <v>64</v>
+      </c>
+      <c r="E588" t="s">
+        <v>65</v>
+      </c>
+      <c r="F588" t="s">
+        <v>87</v>
+      </c>
+      <c r="G588" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="589" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A589" t="s">
+        <v>650</v>
+      </c>
+      <c r="B589" t="s">
+        <v>651</v>
+      </c>
+      <c r="C589" t="s">
+        <v>6</v>
+      </c>
+      <c r="D589" t="s">
+        <v>64</v>
+      </c>
+      <c r="E589" t="s">
+        <v>65</v>
+      </c>
+      <c r="F589" t="s">
+        <v>87</v>
+      </c>
+      <c r="G589" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="590" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A590" t="s">
+        <v>652</v>
+      </c>
+      <c r="B590" t="s">
+        <v>653</v>
+      </c>
+      <c r="C590" t="s">
+        <v>9</v>
+      </c>
+      <c r="D590" t="s">
+        <v>64</v>
+      </c>
+      <c r="E590" t="s">
+        <v>65</v>
+      </c>
+      <c r="F590" t="s">
+        <v>87</v>
+      </c>
+      <c r="G590" s="3">
+        <v>122.95</v>
+      </c>
+    </row>
+    <row r="591" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A591" t="s">
+        <v>652</v>
+      </c>
+      <c r="B591" t="s">
+        <v>653</v>
+      </c>
+      <c r="C591" t="s">
+        <v>9</v>
+      </c>
+      <c r="D591" t="s">
+        <v>113</v>
+      </c>
+      <c r="G591" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="592" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A592" t="s">
+        <v>654</v>
+      </c>
+      <c r="B592" t="s">
+        <v>655</v>
+      </c>
+      <c r="C592" t="s">
+        <v>6</v>
+      </c>
+      <c r="D592" t="s">
+        <v>74</v>
+      </c>
+      <c r="E592" t="s">
+        <v>656</v>
+      </c>
+      <c r="G592" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="593" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A593" t="s">
+        <v>654</v>
+      </c>
+      <c r="B593" t="s">
+        <v>655</v>
+      </c>
+      <c r="C593" t="s">
+        <v>6</v>
+      </c>
+      <c r="D593" t="s">
+        <v>74</v>
+      </c>
+      <c r="E593" t="s">
+        <v>275</v>
+      </c>
+      <c r="G593" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="594" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A594" t="s">
+        <v>654</v>
+      </c>
+      <c r="B594" t="s">
+        <v>655</v>
+      </c>
+      <c r="C594" t="s">
+        <v>6</v>
+      </c>
+      <c r="D594" t="s">
+        <v>74</v>
+      </c>
+      <c r="E594" t="s">
+        <v>69</v>
+      </c>
+      <c r="G594" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="595" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A595" t="s">
+        <v>654</v>
+      </c>
+      <c r="B595" t="s">
+        <v>655</v>
+      </c>
+      <c r="C595" t="s">
+        <v>6</v>
+      </c>
+      <c r="D595" t="s">
+        <v>12</v>
+      </c>
+      <c r="E595" t="s">
+        <v>657</v>
+      </c>
+      <c r="G595" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="596" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A596" t="s">
+        <v>654</v>
+      </c>
+      <c r="B596" t="s">
+        <v>655</v>
+      </c>
+      <c r="C596" t="s">
+        <v>6</v>
+      </c>
+      <c r="D596" t="s">
+        <v>76</v>
+      </c>
+      <c r="E596" t="s">
+        <v>524</v>
+      </c>
+      <c r="G596" t="s">
+        <v>658</v>
       </c>
     </row>
   </sheetData>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D086D4-327A-4EF2-BD7F-FBEEB4A2023E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50297736-6FC0-480D-93D9-E8D45363776A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3070" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3349" uniqueCount="718">
   <si>
     <t>AB</t>
   </si>
@@ -2016,6 +2016,183 @@
   </si>
   <si>
     <t>188.600, 266.300</t>
+  </si>
+  <si>
+    <t>Taloyoak</t>
+  </si>
+  <si>
+    <t>CYYH</t>
+  </si>
+  <si>
+    <t>Taltheilei Narrows</t>
+  </si>
+  <si>
+    <t>CFA7</t>
+  </si>
+  <si>
+    <t>Taltson River</t>
+  </si>
+  <si>
+    <t>CFW5</t>
+  </si>
+  <si>
+    <t>Tanquary Fiord</t>
+  </si>
+  <si>
+    <t>CJQ6</t>
+  </si>
+  <si>
+    <t>4472.5, 4960.0, 4441.0</t>
+  </si>
+  <si>
+    <t>Teslin</t>
+  </si>
+  <si>
+    <t>CYZW</t>
+  </si>
+  <si>
+    <t>CYTN</t>
+  </si>
+  <si>
+    <t>12-21Z‡ Mon-Fri O/T tfc</t>
+  </si>
+  <si>
+    <t>135.300, 135.650</t>
+  </si>
+  <si>
+    <t>Tuktoyaktuk / James Gruben</t>
+  </si>
+  <si>
+    <t>CYUB</t>
+  </si>
+  <si>
+    <t>TUK aprt rdo</t>
+  </si>
+  <si>
+    <t>14-06Z‡</t>
+  </si>
+  <si>
+    <t>Tulita</t>
+  </si>
+  <si>
+    <t>CZFN</t>
+  </si>
+  <si>
+    <t>16-24Z‡ Mon-Fri</t>
+  </si>
+  <si>
+    <t>Tundra Mine / Salamita Mine</t>
+  </si>
+  <si>
+    <t>CTM7</t>
+  </si>
+  <si>
+    <t>Tungsten (Cantung)</t>
+  </si>
+  <si>
+    <t>CBX5</t>
+  </si>
+  <si>
+    <t>Twin Creeks</t>
+  </si>
+  <si>
+    <t>CFS7</t>
+  </si>
+  <si>
+    <t>Ulukhaktok</t>
+  </si>
+  <si>
+    <t>CYHI</t>
+  </si>
+  <si>
+    <t>15-01Z‡ Mon-Sat, 15-20Z‡ Sun</t>
+  </si>
+  <si>
+    <t>Watson Lake</t>
+  </si>
+  <si>
+    <t>CYQH</t>
+  </si>
+  <si>
+    <t>Wekweeti</t>
+  </si>
+  <si>
+    <t>CYWE</t>
+  </si>
+  <si>
+    <t>Whale Cove</t>
+  </si>
+  <si>
+    <t>CYXN</t>
+  </si>
+  <si>
+    <t>1245-2315Z‡ Mon-Fri, 1445-2115Z‡ Sat-Sun</t>
+  </si>
+  <si>
+    <t>Whati</t>
+  </si>
+  <si>
+    <t>CEM3</t>
+  </si>
+  <si>
+    <t>Whitehorse / Erik Nielsen Intl</t>
+  </si>
+  <si>
+    <t>CYXY</t>
+  </si>
+  <si>
+    <t>14-04Z</t>
+  </si>
+  <si>
+    <t>118.300, 236.600</t>
+  </si>
+  <si>
+    <t>132.100, 134.150</t>
+  </si>
+  <si>
+    <t>Whitehorse / Cousins</t>
+  </si>
+  <si>
+    <t>CFP8</t>
+  </si>
+  <si>
+    <t>Wiley</t>
+  </si>
+  <si>
+    <t>CAJ2</t>
+  </si>
+  <si>
+    <t>Wrigley</t>
+  </si>
+  <si>
+    <t>CYWY</t>
+  </si>
+  <si>
+    <t>Yarmouth</t>
+  </si>
+  <si>
+    <t>CYQI</t>
+  </si>
+  <si>
+    <t>123.900, 368.500</t>
+  </si>
+  <si>
+    <t>Yellowknife</t>
+  </si>
+  <si>
+    <t>CYZF</t>
+  </si>
+  <si>
+    <t>5680, 262.000, 123.375</t>
+  </si>
+  <si>
+    <t>14-05Z‡</t>
+  </si>
+  <si>
+    <t>05-14Z‡</t>
+  </si>
+  <si>
+    <t>118.500, 340.800</t>
   </si>
 </sst>
 </file>
@@ -2405,7 +2582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G596"/>
+  <dimension ref="A1:G798"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -14458,6 +14635,1534 @@
         <v>658</v>
       </c>
     </row>
+    <row r="597" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A597" t="s">
+        <v>659</v>
+      </c>
+      <c r="B597" t="s">
+        <v>660</v>
+      </c>
+      <c r="C597" t="s">
+        <v>373</v>
+      </c>
+      <c r="D597" t="s">
+        <v>74</v>
+      </c>
+      <c r="E597" t="s">
+        <v>386</v>
+      </c>
+      <c r="G597" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="598" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A598" t="s">
+        <v>659</v>
+      </c>
+      <c r="B598" t="s">
+        <v>660</v>
+      </c>
+      <c r="C598" t="s">
+        <v>373</v>
+      </c>
+      <c r="D598" t="s">
+        <v>74</v>
+      </c>
+      <c r="E598" t="s">
+        <v>69</v>
+      </c>
+      <c r="G598" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="599" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A599" t="s">
+        <v>659</v>
+      </c>
+      <c r="B599" t="s">
+        <v>660</v>
+      </c>
+      <c r="C599" t="s">
+        <v>373</v>
+      </c>
+      <c r="D599" t="s">
+        <v>12</v>
+      </c>
+      <c r="E599" t="s">
+        <v>367</v>
+      </c>
+      <c r="G599" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="600" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A600" t="s">
+        <v>661</v>
+      </c>
+      <c r="B600" t="s">
+        <v>662</v>
+      </c>
+      <c r="C600" t="s">
+        <v>364</v>
+      </c>
+      <c r="D600" t="s">
+        <v>64</v>
+      </c>
+      <c r="E600" t="s">
+        <v>65</v>
+      </c>
+      <c r="F600" t="s">
+        <v>87</v>
+      </c>
+      <c r="G600" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="601" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A601" t="s">
+        <v>663</v>
+      </c>
+      <c r="B601" t="s">
+        <v>664</v>
+      </c>
+      <c r="C601" t="s">
+        <v>364</v>
+      </c>
+      <c r="D601" t="s">
+        <v>64</v>
+      </c>
+      <c r="E601" t="s">
+        <v>67</v>
+      </c>
+      <c r="G601" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="602" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A602" t="s">
+        <v>665</v>
+      </c>
+      <c r="B602" t="s">
+        <v>666</v>
+      </c>
+      <c r="C602" t="s">
+        <v>373</v>
+      </c>
+      <c r="D602" t="s">
+        <v>64</v>
+      </c>
+      <c r="E602" t="s">
+        <v>67</v>
+      </c>
+      <c r="G602" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="603" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A603" t="s">
+        <v>665</v>
+      </c>
+      <c r="B603" t="s">
+        <v>666</v>
+      </c>
+      <c r="C603" t="s">
+        <v>373</v>
+      </c>
+      <c r="D603" t="s">
+        <v>235</v>
+      </c>
+      <c r="G603" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="604" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A604" t="s">
+        <v>668</v>
+      </c>
+      <c r="B604" t="s">
+        <v>669</v>
+      </c>
+      <c r="C604" t="s">
+        <v>389</v>
+      </c>
+      <c r="D604" t="s">
+        <v>12</v>
+      </c>
+      <c r="E604" t="s">
+        <v>367</v>
+      </c>
+      <c r="F604" t="s">
+        <v>87</v>
+      </c>
+      <c r="G604" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="605" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A605" t="s">
+        <v>668</v>
+      </c>
+      <c r="B605" t="s">
+        <v>669</v>
+      </c>
+      <c r="C605" t="s">
+        <v>389</v>
+      </c>
+      <c r="D605" t="s">
+        <v>366</v>
+      </c>
+      <c r="G605" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="606" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A606" t="s">
+        <v>178</v>
+      </c>
+      <c r="B606" t="s">
+        <v>670</v>
+      </c>
+      <c r="C606" t="s">
+        <v>6</v>
+      </c>
+      <c r="D606" t="s">
+        <v>64</v>
+      </c>
+      <c r="E606" t="s">
+        <v>65</v>
+      </c>
+      <c r="F606" t="s">
+        <v>671</v>
+      </c>
+      <c r="G606" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="607" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A607" t="s">
+        <v>178</v>
+      </c>
+      <c r="B607" t="s">
+        <v>670</v>
+      </c>
+      <c r="C607" t="s">
+        <v>6</v>
+      </c>
+      <c r="D607" t="s">
+        <v>76</v>
+      </c>
+      <c r="E607" t="s">
+        <v>524</v>
+      </c>
+      <c r="G607" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="608" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A608" t="s">
+        <v>673</v>
+      </c>
+      <c r="B608" t="s">
+        <v>674</v>
+      </c>
+      <c r="C608" t="s">
+        <v>364</v>
+      </c>
+      <c r="D608" t="s">
+        <v>12</v>
+      </c>
+      <c r="E608" t="s">
+        <v>367</v>
+      </c>
+      <c r="F608" t="s">
+        <v>87</v>
+      </c>
+      <c r="G608" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="609" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A609" t="s">
+        <v>673</v>
+      </c>
+      <c r="B609" t="s">
+        <v>674</v>
+      </c>
+      <c r="C609" t="s">
+        <v>364</v>
+      </c>
+      <c r="D609" t="s">
+        <v>366</v>
+      </c>
+      <c r="E609" t="s">
+        <v>675</v>
+      </c>
+      <c r="F609" t="s">
+        <v>676</v>
+      </c>
+      <c r="G609" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="610" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A610" t="s">
+        <v>677</v>
+      </c>
+      <c r="B610" t="s">
+        <v>678</v>
+      </c>
+      <c r="C610" t="s">
+        <v>364</v>
+      </c>
+      <c r="D610" t="s">
+        <v>12</v>
+      </c>
+      <c r="E610" t="s">
+        <v>367</v>
+      </c>
+      <c r="F610" t="s">
+        <v>87</v>
+      </c>
+      <c r="G610" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="611" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A611" t="s">
+        <v>677</v>
+      </c>
+      <c r="B611" t="s">
+        <v>678</v>
+      </c>
+      <c r="C611" t="s">
+        <v>364</v>
+      </c>
+      <c r="D611" t="s">
+        <v>366</v>
+      </c>
+      <c r="F611" t="s">
+        <v>679</v>
+      </c>
+      <c r="G611" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="612" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A612" t="s">
+        <v>680</v>
+      </c>
+      <c r="B612" t="s">
+        <v>681</v>
+      </c>
+      <c r="C612" t="s">
+        <v>364</v>
+      </c>
+      <c r="D612" t="s">
+        <v>64</v>
+      </c>
+      <c r="E612" t="s">
+        <v>67</v>
+      </c>
+      <c r="G612" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="613" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A613" t="s">
+        <v>682</v>
+      </c>
+      <c r="B613" t="s">
+        <v>683</v>
+      </c>
+      <c r="C613" t="s">
+        <v>364</v>
+      </c>
+      <c r="D613" t="s">
+        <v>64</v>
+      </c>
+      <c r="E613" t="s">
+        <v>67</v>
+      </c>
+      <c r="G613" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="614" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A614" t="s">
+        <v>684</v>
+      </c>
+      <c r="B614" t="s">
+        <v>685</v>
+      </c>
+      <c r="C614" t="s">
+        <v>389</v>
+      </c>
+      <c r="D614" t="s">
+        <v>64</v>
+      </c>
+      <c r="E614" t="s">
+        <v>67</v>
+      </c>
+      <c r="G614" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="615" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A615" t="s">
+        <v>686</v>
+      </c>
+      <c r="B615" t="s">
+        <v>687</v>
+      </c>
+      <c r="C615" t="s">
+        <v>364</v>
+      </c>
+      <c r="D615" t="s">
+        <v>74</v>
+      </c>
+      <c r="E615" t="s">
+        <v>386</v>
+      </c>
+      <c r="G615" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="616" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A616" t="s">
+        <v>686</v>
+      </c>
+      <c r="B616" t="s">
+        <v>687</v>
+      </c>
+      <c r="C616" t="s">
+        <v>364</v>
+      </c>
+      <c r="D616" t="s">
+        <v>74</v>
+      </c>
+      <c r="E616" t="s">
+        <v>69</v>
+      </c>
+      <c r="G616" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="617" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A617" t="s">
+        <v>686</v>
+      </c>
+      <c r="B617" t="s">
+        <v>687</v>
+      </c>
+      <c r="C617" t="s">
+        <v>364</v>
+      </c>
+      <c r="D617" t="s">
+        <v>12</v>
+      </c>
+      <c r="E617" t="s">
+        <v>367</v>
+      </c>
+      <c r="F617" t="s">
+        <v>87</v>
+      </c>
+      <c r="G617" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="618" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A618" t="s">
+        <v>686</v>
+      </c>
+      <c r="B618" t="s">
+        <v>687</v>
+      </c>
+      <c r="C618" t="s">
+        <v>364</v>
+      </c>
+      <c r="D618" t="s">
+        <v>366</v>
+      </c>
+      <c r="F618" t="s">
+        <v>688</v>
+      </c>
+      <c r="G618" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="619" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A619" t="s">
+        <v>689</v>
+      </c>
+      <c r="B619" t="s">
+        <v>690</v>
+      </c>
+      <c r="C619" t="s">
+        <v>389</v>
+      </c>
+      <c r="D619" t="s">
+        <v>74</v>
+      </c>
+      <c r="E619" t="s">
+        <v>391</v>
+      </c>
+      <c r="G619" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="620" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A620" t="s">
+        <v>689</v>
+      </c>
+      <c r="B620" t="s">
+        <v>690</v>
+      </c>
+      <c r="C620" t="s">
+        <v>389</v>
+      </c>
+      <c r="D620" t="s">
+        <v>74</v>
+      </c>
+      <c r="E620" t="s">
+        <v>69</v>
+      </c>
+      <c r="G620" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="621" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A621" t="s">
+        <v>689</v>
+      </c>
+      <c r="B621" t="s">
+        <v>690</v>
+      </c>
+      <c r="C621" t="s">
+        <v>389</v>
+      </c>
+      <c r="D621" t="s">
+        <v>12</v>
+      </c>
+      <c r="E621" t="s">
+        <v>367</v>
+      </c>
+      <c r="G621" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="622" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A622" t="s">
+        <v>689</v>
+      </c>
+      <c r="B622" t="s">
+        <v>690</v>
+      </c>
+      <c r="C622" t="s">
+        <v>389</v>
+      </c>
+      <c r="D622" t="s">
+        <v>366</v>
+      </c>
+      <c r="G622" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="623" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A623" t="s">
+        <v>691</v>
+      </c>
+      <c r="B623" t="s">
+        <v>692</v>
+      </c>
+      <c r="C623" t="s">
+        <v>364</v>
+      </c>
+      <c r="D623" t="s">
+        <v>64</v>
+      </c>
+      <c r="E623" t="s">
+        <v>67</v>
+      </c>
+      <c r="G623" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="624" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A624" t="s">
+        <v>691</v>
+      </c>
+      <c r="B624" t="s">
+        <v>692</v>
+      </c>
+      <c r="C624" t="s">
+        <v>364</v>
+      </c>
+      <c r="D624" t="s">
+        <v>2</v>
+      </c>
+      <c r="G624" s="3">
+        <v>128.69999999999999</v>
+      </c>
+    </row>
+    <row r="625" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A625" t="s">
+        <v>693</v>
+      </c>
+      <c r="B625" t="s">
+        <v>694</v>
+      </c>
+      <c r="C625" t="s">
+        <v>373</v>
+      </c>
+      <c r="D625" t="s">
+        <v>12</v>
+      </c>
+      <c r="E625" t="s">
+        <v>367</v>
+      </c>
+      <c r="F625" t="s">
+        <v>87</v>
+      </c>
+      <c r="G625" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="626" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A626" t="s">
+        <v>693</v>
+      </c>
+      <c r="B626" t="s">
+        <v>694</v>
+      </c>
+      <c r="C626" t="s">
+        <v>373</v>
+      </c>
+      <c r="D626" t="s">
+        <v>366</v>
+      </c>
+      <c r="F626" t="s">
+        <v>695</v>
+      </c>
+      <c r="G626" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="627" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A627" t="s">
+        <v>696</v>
+      </c>
+      <c r="B627" t="s">
+        <v>697</v>
+      </c>
+      <c r="C627" t="s">
+        <v>364</v>
+      </c>
+      <c r="D627" t="s">
+        <v>64</v>
+      </c>
+      <c r="E627" t="s">
+        <v>67</v>
+      </c>
+      <c r="G627" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="628" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A628" t="s">
+        <v>698</v>
+      </c>
+      <c r="B628" t="s">
+        <v>699</v>
+      </c>
+      <c r="C628" t="s">
+        <v>389</v>
+      </c>
+      <c r="D628" t="s">
+        <v>74</v>
+      </c>
+      <c r="E628" t="s">
+        <v>68</v>
+      </c>
+      <c r="G628" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="629" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A629" t="s">
+        <v>698</v>
+      </c>
+      <c r="B629" t="s">
+        <v>699</v>
+      </c>
+      <c r="C629" t="s">
+        <v>389</v>
+      </c>
+      <c r="D629" t="s">
+        <v>74</v>
+      </c>
+      <c r="E629" t="s">
+        <v>69</v>
+      </c>
+      <c r="G629" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="630" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A630" t="s">
+        <v>698</v>
+      </c>
+      <c r="B630" t="s">
+        <v>699</v>
+      </c>
+      <c r="C630" t="s">
+        <v>389</v>
+      </c>
+      <c r="D630" t="s">
+        <v>41</v>
+      </c>
+      <c r="G630" s="3">
+        <v>125.25</v>
+      </c>
+    </row>
+    <row r="631" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A631" t="s">
+        <v>698</v>
+      </c>
+      <c r="B631" t="s">
+        <v>699</v>
+      </c>
+      <c r="C631" t="s">
+        <v>389</v>
+      </c>
+      <c r="D631" t="s">
+        <v>14</v>
+      </c>
+      <c r="F631" t="s">
+        <v>700</v>
+      </c>
+      <c r="G631" s="3">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="632" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A632" t="s">
+        <v>698</v>
+      </c>
+      <c r="B632" t="s">
+        <v>699</v>
+      </c>
+      <c r="C632" t="s">
+        <v>389</v>
+      </c>
+      <c r="D632" t="s">
+        <v>15</v>
+      </c>
+      <c r="F632" t="s">
+        <v>700</v>
+      </c>
+      <c r="G632" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="633" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A633" t="s">
+        <v>698</v>
+      </c>
+      <c r="B633" t="s">
+        <v>699</v>
+      </c>
+      <c r="C633" t="s">
+        <v>389</v>
+      </c>
+      <c r="D633" t="s">
+        <v>12</v>
+      </c>
+      <c r="E633" t="s">
+        <v>100</v>
+      </c>
+      <c r="F633" t="s">
+        <v>700</v>
+      </c>
+      <c r="G633" s="3">
+        <v>118.3</v>
+      </c>
+    </row>
+    <row r="634" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A634" t="s">
+        <v>698</v>
+      </c>
+      <c r="B634" t="s">
+        <v>699</v>
+      </c>
+      <c r="C634" t="s">
+        <v>389</v>
+      </c>
+      <c r="D634" t="s">
+        <v>76</v>
+      </c>
+      <c r="E634" t="s">
+        <v>402</v>
+      </c>
+      <c r="G634" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="635" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A635" t="s">
+        <v>703</v>
+      </c>
+      <c r="B635" t="s">
+        <v>704</v>
+      </c>
+      <c r="C635" t="s">
+        <v>389</v>
+      </c>
+      <c r="D635" t="s">
+        <v>64</v>
+      </c>
+      <c r="E635" t="s">
+        <v>67</v>
+      </c>
+      <c r="G635" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="636" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A636" t="s">
+        <v>705</v>
+      </c>
+      <c r="B636" t="s">
+        <v>706</v>
+      </c>
+      <c r="C636" t="s">
+        <v>389</v>
+      </c>
+      <c r="D636" t="s">
+        <v>64</v>
+      </c>
+      <c r="E636" t="s">
+        <v>67</v>
+      </c>
+      <c r="G636" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="637" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A637" t="s">
+        <v>707</v>
+      </c>
+      <c r="B637" t="s">
+        <v>708</v>
+      </c>
+      <c r="C637" t="s">
+        <v>364</v>
+      </c>
+      <c r="D637" t="s">
+        <v>12</v>
+      </c>
+      <c r="E637" t="s">
+        <v>367</v>
+      </c>
+      <c r="F637" t="s">
+        <v>87</v>
+      </c>
+      <c r="G637" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="638" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A638" t="s">
+        <v>707</v>
+      </c>
+      <c r="B638" t="s">
+        <v>708</v>
+      </c>
+      <c r="C638" t="s">
+        <v>364</v>
+      </c>
+      <c r="D638" t="s">
+        <v>366</v>
+      </c>
+      <c r="F638" t="s">
+        <v>465</v>
+      </c>
+      <c r="G638" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="639" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A639" t="s">
+        <v>709</v>
+      </c>
+      <c r="B639" t="s">
+        <v>710</v>
+      </c>
+      <c r="C639" t="s">
+        <v>6</v>
+      </c>
+      <c r="D639" t="s">
+        <v>74</v>
+      </c>
+      <c r="E639" t="s">
+        <v>275</v>
+      </c>
+      <c r="G639" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="640" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A640" t="s">
+        <v>709</v>
+      </c>
+      <c r="B640" t="s">
+        <v>710</v>
+      </c>
+      <c r="C640" t="s">
+        <v>6</v>
+      </c>
+      <c r="D640" t="s">
+        <v>12</v>
+      </c>
+      <c r="E640" t="s">
+        <v>65</v>
+      </c>
+      <c r="F640" t="s">
+        <v>671</v>
+      </c>
+      <c r="G640" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="641" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A641" t="s">
+        <v>709</v>
+      </c>
+      <c r="B641" t="s">
+        <v>710</v>
+      </c>
+      <c r="C641" t="s">
+        <v>6</v>
+      </c>
+      <c r="D641" t="s">
+        <v>76</v>
+      </c>
+      <c r="E641" t="s">
+        <v>524</v>
+      </c>
+      <c r="G641" s="3" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="642" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A642" t="s">
+        <v>712</v>
+      </c>
+      <c r="B642" t="s">
+        <v>713</v>
+      </c>
+      <c r="C642" t="s">
+        <v>364</v>
+      </c>
+      <c r="D642" t="s">
+        <v>11</v>
+      </c>
+      <c r="E642" t="s">
+        <v>100</v>
+      </c>
+      <c r="F642" t="s">
+        <v>716</v>
+      </c>
+      <c r="G642" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="643" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A643" t="s">
+        <v>712</v>
+      </c>
+      <c r="B643" t="s">
+        <v>713</v>
+      </c>
+      <c r="C643" t="s">
+        <v>364</v>
+      </c>
+      <c r="D643" t="s">
+        <v>74</v>
+      </c>
+      <c r="E643" t="s">
+        <v>386</v>
+      </c>
+      <c r="G643" s="3" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="644" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A644" t="s">
+        <v>712</v>
+      </c>
+      <c r="B644" t="s">
+        <v>713</v>
+      </c>
+      <c r="C644" t="s">
+        <v>364</v>
+      </c>
+      <c r="D644" t="s">
+        <v>74</v>
+      </c>
+      <c r="E644" t="s">
+        <v>69</v>
+      </c>
+      <c r="G644" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="645" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A645" t="s">
+        <v>712</v>
+      </c>
+      <c r="B645" t="s">
+        <v>713</v>
+      </c>
+      <c r="C645" t="s">
+        <v>364</v>
+      </c>
+      <c r="D645" t="s">
+        <v>41</v>
+      </c>
+      <c r="G645" s="3">
+        <v>128.4</v>
+      </c>
+    </row>
+    <row r="646" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A646" t="s">
+        <v>712</v>
+      </c>
+      <c r="B646" t="s">
+        <v>713</v>
+      </c>
+      <c r="C646" t="s">
+        <v>364</v>
+      </c>
+      <c r="D646" t="s">
+        <v>14</v>
+      </c>
+      <c r="F646" t="s">
+        <v>715</v>
+      </c>
+      <c r="G646" s="3">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="647" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A647" t="s">
+        <v>712</v>
+      </c>
+      <c r="B647" t="s">
+        <v>713</v>
+      </c>
+      <c r="C647" t="s">
+        <v>364</v>
+      </c>
+      <c r="D647" t="s">
+        <v>15</v>
+      </c>
+      <c r="F647" t="s">
+        <v>715</v>
+      </c>
+      <c r="G647" s="3" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="648" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A648" t="s">
+        <v>712</v>
+      </c>
+      <c r="B648" t="s">
+        <v>713</v>
+      </c>
+      <c r="C648" t="s">
+        <v>364</v>
+      </c>
+      <c r="D648" t="s">
+        <v>12</v>
+      </c>
+      <c r="E648" t="s">
+        <v>100</v>
+      </c>
+      <c r="F648" t="s">
+        <v>716</v>
+      </c>
+      <c r="G648" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="649" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A649" t="s">
+        <v>712</v>
+      </c>
+      <c r="B649" t="s">
+        <v>713</v>
+      </c>
+      <c r="C649" t="s">
+        <v>364</v>
+      </c>
+      <c r="D649" t="s">
+        <v>76</v>
+      </c>
+      <c r="E649" t="s">
+        <v>402</v>
+      </c>
+      <c r="G649" s="3">
+        <v>135.80000000000001</v>
+      </c>
+    </row>
+    <row r="650" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G650" s="3"/>
+    </row>
+    <row r="651" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G651" s="3"/>
+    </row>
+    <row r="652" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G652" s="3"/>
+    </row>
+    <row r="653" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G653" s="3"/>
+    </row>
+    <row r="654" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G654" s="3"/>
+    </row>
+    <row r="655" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G655" s="3"/>
+    </row>
+    <row r="656" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G656" s="3"/>
+    </row>
+    <row r="657" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G657" s="3"/>
+    </row>
+    <row r="658" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G658" s="3"/>
+    </row>
+    <row r="659" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G659" s="3"/>
+    </row>
+    <row r="660" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G660" s="3"/>
+    </row>
+    <row r="661" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G661" s="3"/>
+    </row>
+    <row r="662" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G662" s="3"/>
+    </row>
+    <row r="663" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G663" s="3"/>
+    </row>
+    <row r="664" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G664" s="3"/>
+    </row>
+    <row r="665" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G665" s="3"/>
+    </row>
+    <row r="666" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G666" s="3"/>
+    </row>
+    <row r="667" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G667" s="3"/>
+    </row>
+    <row r="668" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G668" s="3"/>
+    </row>
+    <row r="669" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G669" s="3"/>
+    </row>
+    <row r="670" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G670" s="3"/>
+    </row>
+    <row r="671" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G671" s="3"/>
+    </row>
+    <row r="672" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G672" s="3"/>
+    </row>
+    <row r="673" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G673" s="3"/>
+    </row>
+    <row r="674" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G674" s="3"/>
+    </row>
+    <row r="675" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G675" s="3"/>
+    </row>
+    <row r="676" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G676" s="3"/>
+    </row>
+    <row r="677" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G677" s="3"/>
+    </row>
+    <row r="678" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G678" s="3"/>
+    </row>
+    <row r="679" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G679" s="3"/>
+    </row>
+    <row r="680" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G680" s="3"/>
+    </row>
+    <row r="681" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G681" s="3"/>
+    </row>
+    <row r="682" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G682" s="3"/>
+    </row>
+    <row r="683" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G683" s="3"/>
+    </row>
+    <row r="684" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G684" s="3"/>
+    </row>
+    <row r="685" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G685" s="3"/>
+    </row>
+    <row r="686" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G686" s="3"/>
+    </row>
+    <row r="687" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G687" s="3"/>
+    </row>
+    <row r="688" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G688" s="3"/>
+    </row>
+    <row r="689" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G689" s="3"/>
+    </row>
+    <row r="690" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G690" s="3"/>
+    </row>
+    <row r="691" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G691" s="3"/>
+    </row>
+    <row r="692" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G692" s="3"/>
+    </row>
+    <row r="693" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G693" s="3"/>
+    </row>
+    <row r="694" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G694" s="3"/>
+    </row>
+    <row r="695" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G695" s="3"/>
+    </row>
+    <row r="696" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G696" s="3"/>
+    </row>
+    <row r="697" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G697" s="3"/>
+    </row>
+    <row r="698" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G698" s="3"/>
+    </row>
+    <row r="699" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G699" s="3"/>
+    </row>
+    <row r="700" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G700" s="3"/>
+    </row>
+    <row r="701" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G701" s="3"/>
+    </row>
+    <row r="702" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G702" s="3"/>
+    </row>
+    <row r="703" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G703" s="3"/>
+    </row>
+    <row r="704" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G704" s="3"/>
+    </row>
+    <row r="705" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G705" s="3"/>
+    </row>
+    <row r="706" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G706" s="3"/>
+    </row>
+    <row r="707" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G707" s="3"/>
+    </row>
+    <row r="708" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G708" s="3"/>
+    </row>
+    <row r="709" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G709" s="3"/>
+    </row>
+    <row r="710" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G710" s="3"/>
+    </row>
+    <row r="711" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G711" s="3"/>
+    </row>
+    <row r="712" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G712" s="3"/>
+    </row>
+    <row r="713" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G713" s="3"/>
+    </row>
+    <row r="714" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G714" s="3"/>
+    </row>
+    <row r="715" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G715" s="3"/>
+    </row>
+    <row r="716" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G716" s="3"/>
+    </row>
+    <row r="717" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G717" s="3"/>
+    </row>
+    <row r="718" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G718" s="3"/>
+    </row>
+    <row r="719" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G719" s="3"/>
+    </row>
+    <row r="720" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G720" s="3"/>
+    </row>
+    <row r="721" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G721" s="3"/>
+    </row>
+    <row r="722" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G722" s="3"/>
+    </row>
+    <row r="723" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G723" s="3"/>
+    </row>
+    <row r="724" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G724" s="3"/>
+    </row>
+    <row r="725" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G725" s="3"/>
+    </row>
+    <row r="726" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G726" s="3"/>
+    </row>
+    <row r="727" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G727" s="3"/>
+    </row>
+    <row r="728" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G728" s="3"/>
+    </row>
+    <row r="729" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G729" s="3"/>
+    </row>
+    <row r="730" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G730" s="3"/>
+    </row>
+    <row r="731" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G731" s="3"/>
+    </row>
+    <row r="732" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G732" s="3"/>
+    </row>
+    <row r="733" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G733" s="3"/>
+    </row>
+    <row r="734" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G734" s="3"/>
+    </row>
+    <row r="735" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G735" s="3"/>
+    </row>
+    <row r="736" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G736" s="3"/>
+    </row>
+    <row r="737" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G737" s="3"/>
+    </row>
+    <row r="738" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G738" s="3"/>
+    </row>
+    <row r="739" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G739" s="3"/>
+    </row>
+    <row r="740" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G740" s="3"/>
+    </row>
+    <row r="741" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G741" s="3"/>
+    </row>
+    <row r="742" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G742" s="3"/>
+    </row>
+    <row r="743" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G743" s="3"/>
+    </row>
+    <row r="744" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G744" s="3"/>
+    </row>
+    <row r="745" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G745" s="3"/>
+    </row>
+    <row r="746" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G746" s="3"/>
+    </row>
+    <row r="747" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G747" s="3"/>
+    </row>
+    <row r="748" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G748" s="3"/>
+    </row>
+    <row r="749" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G749" s="3"/>
+    </row>
+    <row r="750" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G750" s="3"/>
+    </row>
+    <row r="751" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G751" s="3"/>
+    </row>
+    <row r="752" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G752" s="3"/>
+    </row>
+    <row r="753" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G753" s="3"/>
+    </row>
+    <row r="754" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G754" s="3"/>
+    </row>
+    <row r="755" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G755" s="3"/>
+    </row>
+    <row r="756" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G756" s="3"/>
+    </row>
+    <row r="757" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G757" s="3"/>
+    </row>
+    <row r="758" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G758" s="3"/>
+    </row>
+    <row r="759" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G759" s="3"/>
+    </row>
+    <row r="760" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G760" s="3"/>
+    </row>
+    <row r="761" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G761" s="3"/>
+    </row>
+    <row r="762" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G762" s="3"/>
+    </row>
+    <row r="763" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G763" s="3"/>
+    </row>
+    <row r="764" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G764" s="3"/>
+    </row>
+    <row r="765" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G765" s="3"/>
+    </row>
+    <row r="766" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G766" s="3"/>
+    </row>
+    <row r="767" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G767" s="3"/>
+    </row>
+    <row r="768" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G768" s="3"/>
+    </row>
+    <row r="769" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G769" s="3"/>
+    </row>
+    <row r="770" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G770" s="3"/>
+    </row>
+    <row r="771" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G771" s="3"/>
+    </row>
+    <row r="772" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G772" s="3"/>
+    </row>
+    <row r="773" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G773" s="3"/>
+    </row>
+    <row r="774" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G774" s="3"/>
+    </row>
+    <row r="775" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G775" s="3"/>
+    </row>
+    <row r="776" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G776" s="3"/>
+    </row>
+    <row r="777" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G777" s="3"/>
+    </row>
+    <row r="778" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G778" s="3"/>
+    </row>
+    <row r="779" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G779" s="3"/>
+    </row>
+    <row r="780" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G780" s="3"/>
+    </row>
+    <row r="781" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G781" s="3"/>
+    </row>
+    <row r="782" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G782" s="3"/>
+    </row>
+    <row r="783" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G783" s="3"/>
+    </row>
+    <row r="784" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G784" s="3"/>
+    </row>
+    <row r="785" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G785" s="3"/>
+    </row>
+    <row r="786" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G786" s="3"/>
+    </row>
+    <row r="787" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G787" s="3"/>
+    </row>
+    <row r="788" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G788" s="3"/>
+    </row>
+    <row r="789" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G789" s="3"/>
+    </row>
+    <row r="790" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G790" s="3"/>
+    </row>
+    <row r="791" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G791" s="3"/>
+    </row>
+    <row r="792" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G792" s="3"/>
+    </row>
+    <row r="793" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G793" s="3"/>
+    </row>
+    <row r="794" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G794" s="3"/>
+    </row>
+    <row r="795" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G795" s="3"/>
+    </row>
+    <row r="796" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G796" s="3"/>
+    </row>
+    <row r="797" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G797" s="3"/>
+    </row>
+    <row r="798" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G798" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50297736-6FC0-480D-93D9-E8D45363776A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD410C1-77D0-498E-A34D-D750D97A7831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3349" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3386" uniqueCount="734">
   <si>
     <t>AB</t>
   </si>
@@ -2193,6 +2193,54 @@
   </si>
   <si>
     <t>118.500, 340.800</t>
+  </si>
+  <si>
+    <t>Allan</t>
+  </si>
+  <si>
+    <t>SK</t>
+  </si>
+  <si>
+    <t>CAN5</t>
+  </si>
+  <si>
+    <t>Altona Muni</t>
+  </si>
+  <si>
+    <t>MB</t>
+  </si>
+  <si>
+    <t>CJL6</t>
+  </si>
+  <si>
+    <t>Arborfield</t>
+  </si>
+  <si>
+    <t>CJM6</t>
+  </si>
+  <si>
+    <t>Arcola</t>
+  </si>
+  <si>
+    <t>CJA7</t>
+  </si>
+  <si>
+    <t>Arborg</t>
+  </si>
+  <si>
+    <t>CJU6</t>
+  </si>
+  <si>
+    <t>Ashern</t>
+  </si>
+  <si>
+    <t>CJE7</t>
+  </si>
+  <si>
+    <t>Assiniboia</t>
+  </si>
+  <si>
+    <t>CJN4</t>
   </si>
 </sst>
 </file>
@@ -15717,25 +15765,150 @@
       </c>
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G650" s="3"/>
+      <c r="A650" t="s">
+        <v>718</v>
+      </c>
+      <c r="B650" t="s">
+        <v>720</v>
+      </c>
+      <c r="C650" t="s">
+        <v>719</v>
+      </c>
+      <c r="D650" t="s">
+        <v>64</v>
+      </c>
+      <c r="E650" t="s">
+        <v>67</v>
+      </c>
+      <c r="G650" s="3">
+        <v>123.2</v>
+      </c>
     </row>
     <row r="651" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G651" s="3"/>
+      <c r="A651" t="s">
+        <v>721</v>
+      </c>
+      <c r="B651" t="s">
+        <v>723</v>
+      </c>
+      <c r="C651" t="s">
+        <v>722</v>
+      </c>
+      <c r="D651" t="s">
+        <v>64</v>
+      </c>
+      <c r="E651" t="s">
+        <v>67</v>
+      </c>
+      <c r="G651" s="3">
+        <v>123.2</v>
+      </c>
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G652" s="3"/>
+      <c r="A652" t="s">
+        <v>724</v>
+      </c>
+      <c r="B652" t="s">
+        <v>725</v>
+      </c>
+      <c r="C652" t="s">
+        <v>719</v>
+      </c>
+      <c r="D652" t="s">
+        <v>64</v>
+      </c>
+      <c r="E652" t="s">
+        <v>67</v>
+      </c>
+      <c r="G652" s="3">
+        <v>123.2</v>
+      </c>
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G653" s="3"/>
+      <c r="A653" t="s">
+        <v>728</v>
+      </c>
+      <c r="B653" t="s">
+        <v>729</v>
+      </c>
+      <c r="C653" t="s">
+        <v>722</v>
+      </c>
+      <c r="D653" t="s">
+        <v>64</v>
+      </c>
+      <c r="E653" t="s">
+        <v>65</v>
+      </c>
+      <c r="F653" t="s">
+        <v>87</v>
+      </c>
+      <c r="G653" s="3">
+        <v>122.8</v>
+      </c>
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G654" s="3"/>
+      <c r="A654" t="s">
+        <v>726</v>
+      </c>
+      <c r="B654" t="s">
+        <v>727</v>
+      </c>
+      <c r="C654" t="s">
+        <v>719</v>
+      </c>
+      <c r="D654" t="s">
+        <v>64</v>
+      </c>
+      <c r="E654" t="s">
+        <v>67</v>
+      </c>
+      <c r="G654" s="3">
+        <v>122.8</v>
+      </c>
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G655" s="3"/>
+      <c r="A655" t="s">
+        <v>730</v>
+      </c>
+      <c r="B655" t="s">
+        <v>731</v>
+      </c>
+      <c r="C655" t="s">
+        <v>722</v>
+      </c>
+      <c r="D655" t="s">
+        <v>64</v>
+      </c>
+      <c r="E655" t="s">
+        <v>67</v>
+      </c>
+      <c r="G655" s="3">
+        <v>123.2</v>
+      </c>
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G656" s="3"/>
+      <c r="A656" t="s">
+        <v>732</v>
+      </c>
+      <c r="B656" t="s">
+        <v>733</v>
+      </c>
+      <c r="C656" t="s">
+        <v>719</v>
+      </c>
+      <c r="D656" t="s">
+        <v>64</v>
+      </c>
+      <c r="E656" t="s">
+        <v>65</v>
+      </c>
+      <c r="F656" t="s">
+        <v>87</v>
+      </c>
+      <c r="G656" s="3">
+        <v>122.8</v>
+      </c>
     </row>
     <row r="657" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G657" s="3"/>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD410C1-77D0-498E-A34D-D750D97A7831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4B7FE2-A1F1-4D32-BA07-95A710D7129B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3386" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3780" uniqueCount="838">
   <si>
     <t>AB</t>
   </si>
@@ -2241,6 +2241,318 @@
   </si>
   <si>
     <t>CJN4</t>
+  </si>
+  <si>
+    <t>CZBF</t>
+  </si>
+  <si>
+    <t>Bathurst</t>
+  </si>
+  <si>
+    <t>NB</t>
+  </si>
+  <si>
+    <t>12-23Z‡ OT 2 hr PN</t>
+  </si>
+  <si>
+    <t>Beauval</t>
+  </si>
+  <si>
+    <t>CJK3</t>
+  </si>
+  <si>
+    <t>Bell Island</t>
+  </si>
+  <si>
+    <t>NL</t>
+  </si>
+  <si>
+    <t>CCV4</t>
+  </si>
+  <si>
+    <t>Berens River</t>
+  </si>
+  <si>
+    <t>CYBV</t>
+  </si>
+  <si>
+    <t>Biggar</t>
+  </si>
+  <si>
+    <t>CJF8</t>
+  </si>
+  <si>
+    <t>Big River</t>
+  </si>
+  <si>
+    <t>CKX8</t>
+  </si>
+  <si>
+    <t>Big Sand Lake</t>
+  </si>
+  <si>
+    <t>CJQ9</t>
+  </si>
+  <si>
+    <t>CJP7</t>
+  </si>
+  <si>
+    <t>Birch Hills</t>
+  </si>
+  <si>
+    <t>Bird River (Lac Du Bonnet)</t>
+  </si>
+  <si>
+    <t>CJD3</t>
+  </si>
+  <si>
+    <t>Black Tickle</t>
+  </si>
+  <si>
+    <t>CCE4</t>
+  </si>
+  <si>
+    <t>Bloodvein River</t>
+  </si>
+  <si>
+    <t>CZTA</t>
+  </si>
+  <si>
+    <t>Boston Brook</t>
+  </si>
+  <si>
+    <t>CCJ3</t>
+  </si>
+  <si>
+    <t>Bouctouche</t>
+  </si>
+  <si>
+    <t>CDT5</t>
+  </si>
+  <si>
+    <t>Brandon Muni</t>
+  </si>
+  <si>
+    <t>CYBR</t>
+  </si>
+  <si>
+    <t>13-04Z‡</t>
+  </si>
+  <si>
+    <t>04-13Z‡</t>
+  </si>
+  <si>
+    <t>Briercrest South</t>
+  </si>
+  <si>
+    <t>CBS7</t>
+  </si>
+  <si>
+    <t>Bristol</t>
+  </si>
+  <si>
+    <t>CDA6</t>
+  </si>
+  <si>
+    <t>Brochet</t>
+  </si>
+  <si>
+    <t>CYBT</t>
+  </si>
+  <si>
+    <t>Brockway</t>
+  </si>
+  <si>
+    <t>CCX3</t>
+  </si>
+  <si>
+    <t>Buffalo Narrows</t>
+  </si>
+  <si>
+    <t>CYVT</t>
+  </si>
+  <si>
+    <t>RAAS Regina rdo</t>
+  </si>
+  <si>
+    <t>14-02Z</t>
+  </si>
+  <si>
+    <t>Regina rdo</t>
+  </si>
+  <si>
+    <t>13-04Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>14-02Z O/T tfc</t>
+  </si>
+  <si>
+    <t>Cabri</t>
+  </si>
+  <si>
+    <t>CJJ5</t>
+  </si>
+  <si>
+    <t>Camsell Portage</t>
+  </si>
+  <si>
+    <t>CJP6</t>
+  </si>
+  <si>
+    <t>Candle Lake Airpark</t>
+  </si>
+  <si>
+    <t>CCL2</t>
+  </si>
+  <si>
+    <t>Carlyle</t>
+  </si>
+  <si>
+    <t>CJQ3</t>
+  </si>
+  <si>
+    <t>Carman (South)</t>
+  </si>
+  <si>
+    <t>CJS7</t>
+  </si>
+  <si>
+    <t>Cartwright</t>
+  </si>
+  <si>
+    <t>CYCA</t>
+  </si>
+  <si>
+    <t>Central Butte</t>
+  </si>
+  <si>
+    <t>CJC4</t>
+  </si>
+  <si>
+    <t>Centreville / Graham Field</t>
+  </si>
+  <si>
+    <t>CGR7</t>
+  </si>
+  <si>
+    <t>Charlot River</t>
+  </si>
+  <si>
+    <t>CJP9</t>
+  </si>
+  <si>
+    <t>CCH4</t>
+  </si>
+  <si>
+    <t>Chipman</t>
+  </si>
+  <si>
+    <t>CCS4</t>
+  </si>
+  <si>
+    <t>Churchill</t>
+  </si>
+  <si>
+    <t>CYYQ</t>
+  </si>
+  <si>
+    <t>Churchill Falls</t>
+  </si>
+  <si>
+    <t>CZUM</t>
+  </si>
+  <si>
+    <t>Gander Ctr</t>
+  </si>
+  <si>
+    <t>Cigar Lake</t>
+  </si>
+  <si>
+    <t>CJW7</t>
+  </si>
+  <si>
+    <t>Cameco dispatch</t>
+  </si>
+  <si>
+    <t>Clarenville</t>
+  </si>
+  <si>
+    <t>CCZ3</t>
+  </si>
+  <si>
+    <t>Clearwater</t>
+  </si>
+  <si>
+    <t>CDJ4</t>
+  </si>
+  <si>
+    <t>Collins Bay</t>
+  </si>
+  <si>
+    <t>CYKC</t>
+  </si>
+  <si>
+    <t>FISE Edmonton rdo (Wollaston Lake)</t>
+  </si>
+  <si>
+    <t>Cooks Creek</t>
+  </si>
+  <si>
+    <t>CCC3</t>
+  </si>
+  <si>
+    <t>Cormier</t>
+  </si>
+  <si>
+    <t>CRM4</t>
+  </si>
+  <si>
+    <t>Coronach / Scobey Border Station</t>
+  </si>
+  <si>
+    <t>CKK3</t>
+  </si>
+  <si>
+    <t>Craik</t>
+  </si>
+  <si>
+    <t>CJC2</t>
+  </si>
+  <si>
+    <t>Cree Lake / Crystal Lodge (Midgett Field)</t>
+  </si>
+  <si>
+    <t>CKS8</t>
+  </si>
+  <si>
+    <t>Cross Lake (Charlie Sinclair Mem)</t>
+  </si>
+  <si>
+    <t>CYCR</t>
+  </si>
+  <si>
+    <t>Cross Lake UNICOM</t>
+  </si>
+  <si>
+    <t>Crystal City-Pilot Mound / Louise Muni</t>
+  </si>
+  <si>
+    <t>CKZ6</t>
+  </si>
+  <si>
+    <t>Louise Munitfc</t>
+  </si>
+  <si>
+    <t>Cudworth Muni</t>
+  </si>
+  <si>
+    <t>CJD2</t>
+  </si>
+  <si>
+    <t>Cumberland House</t>
+  </si>
+  <si>
+    <t>CJT4</t>
   </si>
 </sst>
 </file>
@@ -15910,244 +16222,1582 @@
         <v>122.8</v>
       </c>
     </row>
-    <row r="657" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G657" s="3"/>
-    </row>
-    <row r="658" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G658" s="3"/>
-    </row>
-    <row r="659" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G659" s="3"/>
-    </row>
-    <row r="660" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G660" s="3"/>
-    </row>
-    <row r="661" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G661" s="3"/>
-    </row>
-    <row r="662" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G662" s="3"/>
-    </row>
-    <row r="663" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G663" s="3"/>
-    </row>
-    <row r="664" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G664" s="3"/>
-    </row>
-    <row r="665" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G665" s="3"/>
-    </row>
-    <row r="666" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G666" s="3"/>
-    </row>
-    <row r="667" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G667" s="3"/>
-    </row>
-    <row r="668" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G668" s="3"/>
-    </row>
-    <row r="669" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G669" s="3"/>
-    </row>
-    <row r="670" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G670" s="3"/>
-    </row>
-    <row r="671" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G671" s="3"/>
-    </row>
-    <row r="672" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G672" s="3"/>
-    </row>
-    <row r="673" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G673" s="3"/>
-    </row>
-    <row r="674" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G674" s="3"/>
-    </row>
-    <row r="675" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G675" s="3"/>
-    </row>
-    <row r="676" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G676" s="3"/>
-    </row>
-    <row r="677" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G677" s="3"/>
-    </row>
-    <row r="678" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G678" s="3"/>
-    </row>
-    <row r="679" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G679" s="3"/>
-    </row>
-    <row r="680" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G680" s="3"/>
-    </row>
-    <row r="681" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G681" s="3"/>
-    </row>
-    <row r="682" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G682" s="3"/>
-    </row>
-    <row r="683" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G683" s="3"/>
-    </row>
-    <row r="684" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G684" s="3"/>
-    </row>
-    <row r="685" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G685" s="3"/>
-    </row>
-    <row r="686" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G686" s="3"/>
-    </row>
-    <row r="687" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G687" s="3"/>
-    </row>
-    <row r="688" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G688" s="3"/>
-    </row>
-    <row r="689" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G689" s="3"/>
-    </row>
-    <row r="690" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G690" s="3"/>
-    </row>
-    <row r="691" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G691" s="3"/>
-    </row>
-    <row r="692" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G692" s="3"/>
-    </row>
-    <row r="693" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G693" s="3"/>
-    </row>
-    <row r="694" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G694" s="3"/>
-    </row>
-    <row r="695" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G695" s="3"/>
-    </row>
-    <row r="696" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G696" s="3"/>
-    </row>
-    <row r="697" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G697" s="3"/>
-    </row>
-    <row r="698" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G698" s="3"/>
-    </row>
-    <row r="699" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G699" s="3"/>
-    </row>
-    <row r="700" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G700" s="3"/>
-    </row>
-    <row r="701" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G701" s="3"/>
-    </row>
-    <row r="702" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G702" s="3"/>
-    </row>
-    <row r="703" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G703" s="3"/>
-    </row>
-    <row r="704" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G704" s="3"/>
-    </row>
-    <row r="705" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G705" s="3"/>
-    </row>
-    <row r="706" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G706" s="3"/>
-    </row>
-    <row r="707" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G707" s="3"/>
-    </row>
-    <row r="708" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G708" s="3"/>
-    </row>
-    <row r="709" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G709" s="3"/>
-    </row>
-    <row r="710" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G710" s="3"/>
-    </row>
-    <row r="711" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G711" s="3"/>
-    </row>
-    <row r="712" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G712" s="3"/>
-    </row>
-    <row r="713" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G713" s="3"/>
-    </row>
-    <row r="714" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G714" s="3"/>
-    </row>
-    <row r="715" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G715" s="3"/>
-    </row>
-    <row r="716" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G716" s="3"/>
-    </row>
-    <row r="717" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G717" s="3"/>
-    </row>
-    <row r="718" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G718" s="3"/>
-    </row>
-    <row r="719" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G719" s="3"/>
-    </row>
-    <row r="720" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G720" s="3"/>
-    </row>
-    <row r="721" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G721" s="3"/>
-    </row>
-    <row r="722" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G722" s="3"/>
-    </row>
-    <row r="723" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G723" s="3"/>
-    </row>
-    <row r="724" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G724" s="3"/>
-    </row>
-    <row r="725" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G725" s="3"/>
-    </row>
-    <row r="726" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G726" s="3"/>
-    </row>
-    <row r="727" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G727" s="3"/>
-    </row>
-    <row r="728" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G728" s="3"/>
-    </row>
-    <row r="729" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G729" s="3"/>
-    </row>
-    <row r="730" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G730" s="3"/>
-    </row>
-    <row r="731" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G731" s="3"/>
-    </row>
-    <row r="732" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G732" s="3"/>
-    </row>
-    <row r="733" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G733" s="3"/>
-    </row>
-    <row r="734" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G734" s="3"/>
-    </row>
-    <row r="735" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A657" t="s">
+        <v>735</v>
+      </c>
+      <c r="B657" t="s">
+        <v>734</v>
+      </c>
+      <c r="C657" t="s">
+        <v>736</v>
+      </c>
+      <c r="D657" t="s">
+        <v>74</v>
+      </c>
+      <c r="E657" t="s">
+        <v>414</v>
+      </c>
+      <c r="G657" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="658" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A658" t="s">
+        <v>735</v>
+      </c>
+      <c r="B658" t="s">
+        <v>734</v>
+      </c>
+      <c r="C658" t="s">
+        <v>736</v>
+      </c>
+      <c r="D658" t="s">
+        <v>74</v>
+      </c>
+      <c r="E658" t="s">
+        <v>69</v>
+      </c>
+      <c r="G658" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="659" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A659" t="s">
+        <v>735</v>
+      </c>
+      <c r="B659" t="s">
+        <v>734</v>
+      </c>
+      <c r="C659" t="s">
+        <v>736</v>
+      </c>
+      <c r="D659" t="s">
+        <v>64</v>
+      </c>
+      <c r="E659" t="s">
+        <v>65</v>
+      </c>
+      <c r="F659" t="s">
+        <v>737</v>
+      </c>
+      <c r="G659" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="660" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A660" t="s">
+        <v>735</v>
+      </c>
+      <c r="B660" t="s">
+        <v>734</v>
+      </c>
+      <c r="C660" t="s">
+        <v>736</v>
+      </c>
+      <c r="D660" t="s">
+        <v>2</v>
+      </c>
+      <c r="G660" s="3">
+        <v>127.925</v>
+      </c>
+    </row>
+    <row r="661" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A661" t="s">
+        <v>738</v>
+      </c>
+      <c r="B661" t="s">
+        <v>739</v>
+      </c>
+      <c r="C661" t="s">
+        <v>719</v>
+      </c>
+      <c r="D661" t="s">
+        <v>64</v>
+      </c>
+      <c r="E661" t="s">
+        <v>67</v>
+      </c>
+      <c r="G661" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="662" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A662" t="s">
+        <v>740</v>
+      </c>
+      <c r="B662" t="s">
+        <v>742</v>
+      </c>
+      <c r="C662" t="s">
+        <v>741</v>
+      </c>
+      <c r="D662" t="s">
+        <v>64</v>
+      </c>
+      <c r="E662" t="s">
+        <v>67</v>
+      </c>
+      <c r="G662" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="663" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A663" t="s">
+        <v>743</v>
+      </c>
+      <c r="B663" t="s">
+        <v>744</v>
+      </c>
+      <c r="C663" t="s">
+        <v>722</v>
+      </c>
+      <c r="D663" t="s">
+        <v>74</v>
+      </c>
+      <c r="E663" t="s">
+        <v>386</v>
+      </c>
+      <c r="G663" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="664" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A664" t="s">
+        <v>743</v>
+      </c>
+      <c r="B664" t="s">
+        <v>744</v>
+      </c>
+      <c r="C664" t="s">
+        <v>722</v>
+      </c>
+      <c r="D664" t="s">
+        <v>74</v>
+      </c>
+      <c r="E664" t="s">
+        <v>69</v>
+      </c>
+      <c r="G664" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="665" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A665" t="s">
+        <v>743</v>
+      </c>
+      <c r="B665" t="s">
+        <v>744</v>
+      </c>
+      <c r="C665" t="s">
+        <v>722</v>
+      </c>
+      <c r="D665" t="s">
+        <v>64</v>
+      </c>
+      <c r="E665" t="s">
+        <v>65</v>
+      </c>
+      <c r="F665" t="s">
+        <v>87</v>
+      </c>
+      <c r="G665" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="666" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A666" t="s">
+        <v>745</v>
+      </c>
+      <c r="B666" t="s">
+        <v>746</v>
+      </c>
+      <c r="C666" t="s">
+        <v>719</v>
+      </c>
+      <c r="D666" t="s">
+        <v>64</v>
+      </c>
+      <c r="E666" t="s">
+        <v>67</v>
+      </c>
+      <c r="G666" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="667" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A667" t="s">
+        <v>747</v>
+      </c>
+      <c r="B667" t="s">
+        <v>748</v>
+      </c>
+      <c r="C667" t="s">
+        <v>719</v>
+      </c>
+      <c r="D667" t="s">
+        <v>64</v>
+      </c>
+      <c r="E667" t="s">
+        <v>67</v>
+      </c>
+      <c r="G667" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="668" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A668" t="s">
+        <v>749</v>
+      </c>
+      <c r="B668" t="s">
+        <v>750</v>
+      </c>
+      <c r="C668" t="s">
+        <v>722</v>
+      </c>
+      <c r="D668" t="s">
+        <v>64</v>
+      </c>
+      <c r="E668" t="s">
+        <v>67</v>
+      </c>
+      <c r="G668" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="669" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A669" t="s">
+        <v>752</v>
+      </c>
+      <c r="B669" t="s">
+        <v>754</v>
+      </c>
+      <c r="C669" t="s">
+        <v>719</v>
+      </c>
+      <c r="D669" t="s">
+        <v>64</v>
+      </c>
+      <c r="E669" t="s">
+        <v>67</v>
+      </c>
+      <c r="G669" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="670" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A670" t="s">
+        <v>753</v>
+      </c>
+      <c r="B670" t="s">
+        <v>751</v>
+      </c>
+      <c r="C670" t="s">
+        <v>722</v>
+      </c>
+      <c r="D670" t="s">
+        <v>64</v>
+      </c>
+      <c r="E670" t="s">
+        <v>65</v>
+      </c>
+      <c r="F670" t="s">
+        <v>87</v>
+      </c>
+      <c r="G670" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="671" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A671" t="s">
+        <v>755</v>
+      </c>
+      <c r="B671" t="s">
+        <v>756</v>
+      </c>
+      <c r="C671" t="s">
+        <v>741</v>
+      </c>
+      <c r="D671" t="s">
+        <v>64</v>
+      </c>
+      <c r="E671" t="s">
+        <v>67</v>
+      </c>
+      <c r="G671" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="672" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A672" t="s">
+        <v>757</v>
+      </c>
+      <c r="B672" t="s">
+        <v>758</v>
+      </c>
+      <c r="C672" t="s">
+        <v>722</v>
+      </c>
+      <c r="D672" t="s">
+        <v>64</v>
+      </c>
+      <c r="E672" t="s">
+        <v>65</v>
+      </c>
+      <c r="F672" t="s">
+        <v>87</v>
+      </c>
+      <c r="G672" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="673" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A673" t="s">
+        <v>759</v>
+      </c>
+      <c r="B673" t="s">
+        <v>760</v>
+      </c>
+      <c r="C673" t="s">
+        <v>736</v>
+      </c>
+      <c r="D673" t="s">
+        <v>64</v>
+      </c>
+      <c r="E673" t="s">
+        <v>67</v>
+      </c>
+      <c r="G673" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="674" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A674" t="s">
+        <v>761</v>
+      </c>
+      <c r="B674" t="s">
+        <v>762</v>
+      </c>
+      <c r="C674" t="s">
+        <v>736</v>
+      </c>
+      <c r="D674" t="s">
+        <v>64</v>
+      </c>
+      <c r="E674" t="s">
+        <v>67</v>
+      </c>
+      <c r="G674" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="675" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A675" t="s">
+        <v>763</v>
+      </c>
+      <c r="B675" t="s">
+        <v>764</v>
+      </c>
+      <c r="C675" t="s">
+        <v>722</v>
+      </c>
+      <c r="D675" t="s">
+        <v>11</v>
+      </c>
+      <c r="F675" t="s">
+        <v>765</v>
+      </c>
+      <c r="G675" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="676" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A676" t="s">
+        <v>763</v>
+      </c>
+      <c r="B676" t="s">
+        <v>764</v>
+      </c>
+      <c r="C676" t="s">
+        <v>722</v>
+      </c>
+      <c r="D676" t="s">
+        <v>74</v>
+      </c>
+      <c r="E676" t="s">
+        <v>386</v>
+      </c>
+      <c r="G676" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="677" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A677" t="s">
+        <v>763</v>
+      </c>
+      <c r="B677" t="s">
+        <v>764</v>
+      </c>
+      <c r="C677" t="s">
+        <v>722</v>
+      </c>
+      <c r="D677" t="s">
+        <v>74</v>
+      </c>
+      <c r="E677" t="s">
+        <v>69</v>
+      </c>
+      <c r="G677" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="678" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A678" t="s">
+        <v>763</v>
+      </c>
+      <c r="B678" t="s">
+        <v>764</v>
+      </c>
+      <c r="C678" t="s">
+        <v>722</v>
+      </c>
+      <c r="D678" t="s">
+        <v>12</v>
+      </c>
+      <c r="E678" t="s">
+        <v>100</v>
+      </c>
+      <c r="F678" t="s">
+        <v>780</v>
+      </c>
+      <c r="G678" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="679" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A679" t="s">
+        <v>763</v>
+      </c>
+      <c r="B679" t="s">
+        <v>764</v>
+      </c>
+      <c r="C679" t="s">
+        <v>722</v>
+      </c>
+      <c r="D679" t="s">
+        <v>16</v>
+      </c>
+      <c r="E679" t="s">
+        <v>200</v>
+      </c>
+      <c r="G679" s="3">
+        <v>132.25</v>
+      </c>
+    </row>
+    <row r="680" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A680" t="s">
+        <v>763</v>
+      </c>
+      <c r="B680" t="s">
+        <v>764</v>
+      </c>
+      <c r="C680" t="s">
+        <v>722</v>
+      </c>
+      <c r="D680" t="s">
+        <v>17</v>
+      </c>
+      <c r="E680" t="s">
+        <v>200</v>
+      </c>
+      <c r="G680" s="3">
+        <v>132.25</v>
+      </c>
+    </row>
+    <row r="681" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A681" t="s">
+        <v>763</v>
+      </c>
+      <c r="B681" t="s">
+        <v>764</v>
+      </c>
+      <c r="C681" t="s">
+        <v>722</v>
+      </c>
+      <c r="D681" t="s">
+        <v>76</v>
+      </c>
+      <c r="E681" t="s">
+        <v>200</v>
+      </c>
+      <c r="G681" s="3">
+        <v>132.25</v>
+      </c>
+    </row>
+    <row r="682" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A682" t="s">
+        <v>763</v>
+      </c>
+      <c r="B682" t="s">
+        <v>764</v>
+      </c>
+      <c r="C682" t="s">
+        <v>722</v>
+      </c>
+      <c r="D682" t="s">
+        <v>2</v>
+      </c>
+      <c r="F682" t="s">
+        <v>766</v>
+      </c>
+      <c r="G682" s="3">
+        <v>128.17500000000001</v>
+      </c>
+    </row>
+    <row r="683" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A683" t="s">
+        <v>767</v>
+      </c>
+      <c r="B683" t="s">
+        <v>768</v>
+      </c>
+      <c r="C683" t="s">
+        <v>719</v>
+      </c>
+      <c r="D683" t="s">
+        <v>64</v>
+      </c>
+      <c r="E683" t="s">
+        <v>67</v>
+      </c>
+      <c r="G683" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="684" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A684" t="s">
+        <v>769</v>
+      </c>
+      <c r="B684" t="s">
+        <v>770</v>
+      </c>
+      <c r="C684" t="s">
+        <v>736</v>
+      </c>
+      <c r="D684" t="s">
+        <v>64</v>
+      </c>
+      <c r="E684" t="s">
+        <v>67</v>
+      </c>
+      <c r="G684" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="685" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A685" t="s">
+        <v>771</v>
+      </c>
+      <c r="B685" t="s">
+        <v>772</v>
+      </c>
+      <c r="C685" t="s">
+        <v>722</v>
+      </c>
+      <c r="D685" t="s">
+        <v>64</v>
+      </c>
+      <c r="E685" t="s">
+        <v>65</v>
+      </c>
+      <c r="F685" t="s">
+        <v>87</v>
+      </c>
+      <c r="G685" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="686" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A686" t="s">
+        <v>773</v>
+      </c>
+      <c r="B686" t="s">
+        <v>774</v>
+      </c>
+      <c r="C686" t="s">
+        <v>736</v>
+      </c>
+      <c r="D686" t="s">
+        <v>64</v>
+      </c>
+      <c r="E686" t="s">
+        <v>67</v>
+      </c>
+      <c r="G686" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="687" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A687" t="s">
+        <v>775</v>
+      </c>
+      <c r="B687" t="s">
+        <v>776</v>
+      </c>
+      <c r="C687" t="s">
+        <v>719</v>
+      </c>
+      <c r="D687" t="s">
+        <v>74</v>
+      </c>
+      <c r="E687" t="s">
+        <v>777</v>
+      </c>
+      <c r="F687" t="s">
+        <v>778</v>
+      </c>
+      <c r="G687" s="3">
+        <v>118.65</v>
+      </c>
+    </row>
+    <row r="688" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A688" t="s">
+        <v>775</v>
+      </c>
+      <c r="B688" t="s">
+        <v>776</v>
+      </c>
+      <c r="C688" t="s">
+        <v>719</v>
+      </c>
+      <c r="D688" t="s">
+        <v>74</v>
+      </c>
+      <c r="E688" t="s">
+        <v>386</v>
+      </c>
+      <c r="G688" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="689" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A689" t="s">
+        <v>775</v>
+      </c>
+      <c r="B689" t="s">
+        <v>776</v>
+      </c>
+      <c r="C689" t="s">
+        <v>719</v>
+      </c>
+      <c r="D689" t="s">
+        <v>74</v>
+      </c>
+      <c r="E689" t="s">
+        <v>69</v>
+      </c>
+      <c r="G689" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="690" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A690" t="s">
+        <v>775</v>
+      </c>
+      <c r="B690" t="s">
+        <v>776</v>
+      </c>
+      <c r="C690" t="s">
+        <v>719</v>
+      </c>
+      <c r="D690" t="s">
+        <v>12</v>
+      </c>
+      <c r="E690" t="s">
+        <v>779</v>
+      </c>
+      <c r="F690" t="s">
+        <v>781</v>
+      </c>
+      <c r="G690" s="3">
+        <v>118.65</v>
+      </c>
+    </row>
+    <row r="691" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A691" t="s">
+        <v>775</v>
+      </c>
+      <c r="B691" t="s">
+        <v>776</v>
+      </c>
+      <c r="C691" t="s">
+        <v>719</v>
+      </c>
+      <c r="D691" t="s">
+        <v>2</v>
+      </c>
+      <c r="G691" s="3">
+        <v>128.6</v>
+      </c>
+    </row>
+    <row r="692" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A692" t="s">
+        <v>782</v>
+      </c>
+      <c r="B692" t="s">
+        <v>783</v>
+      </c>
+      <c r="C692" t="s">
+        <v>719</v>
+      </c>
+      <c r="D692" t="s">
+        <v>64</v>
+      </c>
+      <c r="E692" t="s">
+        <v>67</v>
+      </c>
+      <c r="G692" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="693" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A693" t="s">
+        <v>784</v>
+      </c>
+      <c r="B693" t="s">
+        <v>785</v>
+      </c>
+      <c r="C693" t="s">
+        <v>719</v>
+      </c>
+      <c r="D693" t="s">
+        <v>64</v>
+      </c>
+      <c r="E693" t="s">
+        <v>67</v>
+      </c>
+      <c r="G693" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="694" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A694" t="s">
+        <v>786</v>
+      </c>
+      <c r="B694" t="s">
+        <v>787</v>
+      </c>
+      <c r="C694" t="s">
+        <v>719</v>
+      </c>
+      <c r="D694" t="s">
+        <v>64</v>
+      </c>
+      <c r="E694" t="s">
+        <v>67</v>
+      </c>
+      <c r="G694" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="695" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A695" t="s">
+        <v>788</v>
+      </c>
+      <c r="B695" t="s">
+        <v>789</v>
+      </c>
+      <c r="C695" t="s">
+        <v>719</v>
+      </c>
+      <c r="D695" t="s">
+        <v>64</v>
+      </c>
+      <c r="E695" t="s">
+        <v>67</v>
+      </c>
+      <c r="G695" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="696" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A696" t="s">
+        <v>788</v>
+      </c>
+      <c r="B696" t="s">
+        <v>789</v>
+      </c>
+      <c r="C696" t="s">
+        <v>719</v>
+      </c>
+      <c r="D696" t="s">
+        <v>113</v>
+      </c>
+      <c r="G696" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="697" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A697" t="s">
+        <v>790</v>
+      </c>
+      <c r="B697" t="s">
+        <v>791</v>
+      </c>
+      <c r="C697" t="s">
+        <v>722</v>
+      </c>
+      <c r="D697" t="s">
+        <v>64</v>
+      </c>
+      <c r="E697" t="s">
+        <v>67</v>
+      </c>
+      <c r="G697" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="698" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A698" t="s">
+        <v>792</v>
+      </c>
+      <c r="B698" t="s">
+        <v>793</v>
+      </c>
+      <c r="C698" t="s">
+        <v>741</v>
+      </c>
+      <c r="D698" t="s">
+        <v>64</v>
+      </c>
+      <c r="E698" t="s">
+        <v>67</v>
+      </c>
+      <c r="G698" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="699" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A699" t="s">
+        <v>792</v>
+      </c>
+      <c r="B699" t="s">
+        <v>793</v>
+      </c>
+      <c r="C699" t="s">
+        <v>741</v>
+      </c>
+      <c r="D699" t="s">
+        <v>2</v>
+      </c>
+      <c r="G699" s="3">
+        <v>128.75</v>
+      </c>
+    </row>
+    <row r="700" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A700" t="s">
+        <v>794</v>
+      </c>
+      <c r="B700" t="s">
+        <v>795</v>
+      </c>
+      <c r="C700" t="s">
+        <v>719</v>
+      </c>
+      <c r="D700" t="s">
+        <v>64</v>
+      </c>
+      <c r="E700" t="s">
+        <v>67</v>
+      </c>
+      <c r="G700" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="701" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A701" t="s">
+        <v>796</v>
+      </c>
+      <c r="B701" t="s">
+        <v>797</v>
+      </c>
+      <c r="C701" t="s">
+        <v>736</v>
+      </c>
+      <c r="D701" t="s">
+        <v>64</v>
+      </c>
+      <c r="E701" t="s">
+        <v>67</v>
+      </c>
+      <c r="G701" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="702" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A702" t="s">
+        <v>798</v>
+      </c>
+      <c r="B702" t="s">
+        <v>799</v>
+      </c>
+      <c r="C702" t="s">
+        <v>719</v>
+      </c>
+      <c r="D702" t="s">
+        <v>64</v>
+      </c>
+      <c r="E702" t="s">
+        <v>65</v>
+      </c>
+      <c r="F702" t="s">
+        <v>87</v>
+      </c>
+      <c r="G702" s="3">
+        <v>122.72499999999999</v>
+      </c>
+    </row>
+    <row r="703" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A703" t="s">
+        <v>27</v>
+      </c>
+      <c r="B703" t="s">
+        <v>800</v>
+      </c>
+      <c r="C703" t="s">
+        <v>741</v>
+      </c>
+      <c r="D703" t="s">
+        <v>64</v>
+      </c>
+      <c r="E703" t="s">
+        <v>67</v>
+      </c>
+      <c r="G703" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="704" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A704" t="s">
+        <v>801</v>
+      </c>
+      <c r="B704" t="s">
+        <v>802</v>
+      </c>
+      <c r="C704" t="s">
+        <v>736</v>
+      </c>
+      <c r="D704" t="s">
+        <v>64</v>
+      </c>
+      <c r="E704" t="s">
+        <v>67</v>
+      </c>
+      <c r="G704" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="705" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A705" t="s">
+        <v>803</v>
+      </c>
+      <c r="B705" t="s">
+        <v>804</v>
+      </c>
+      <c r="C705" t="s">
+        <v>722</v>
+      </c>
+      <c r="D705" t="s">
+        <v>11</v>
+      </c>
+      <c r="G705" s="3">
+        <v>126.9</v>
+      </c>
+    </row>
+    <row r="706" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A706" t="s">
+        <v>803</v>
+      </c>
+      <c r="B706" t="s">
+        <v>804</v>
+      </c>
+      <c r="C706" t="s">
+        <v>722</v>
+      </c>
+      <c r="D706" t="s">
+        <v>74</v>
+      </c>
+      <c r="E706" t="s">
+        <v>386</v>
+      </c>
+      <c r="G706" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="707" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A707" t="s">
+        <v>803</v>
+      </c>
+      <c r="B707" t="s">
+        <v>804</v>
+      </c>
+      <c r="C707" t="s">
+        <v>722</v>
+      </c>
+      <c r="D707" t="s">
+        <v>74</v>
+      </c>
+      <c r="E707" t="s">
+        <v>69</v>
+      </c>
+      <c r="G707" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="708" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A708" t="s">
+        <v>803</v>
+      </c>
+      <c r="B708" t="s">
+        <v>804</v>
+      </c>
+      <c r="C708" t="s">
+        <v>722</v>
+      </c>
+      <c r="D708" t="s">
+        <v>41</v>
+      </c>
+      <c r="G708" s="3">
+        <v>118.2</v>
+      </c>
+    </row>
+    <row r="709" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A709" t="s">
+        <v>803</v>
+      </c>
+      <c r="B709" t="s">
+        <v>804</v>
+      </c>
+      <c r="C709" t="s">
+        <v>722</v>
+      </c>
+      <c r="D709" t="s">
+        <v>12</v>
+      </c>
+      <c r="E709" t="s">
+        <v>100</v>
+      </c>
+      <c r="G709" s="3">
+        <v>126.9</v>
+      </c>
+    </row>
+    <row r="710" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A710" t="s">
+        <v>803</v>
+      </c>
+      <c r="B710" t="s">
+        <v>804</v>
+      </c>
+      <c r="C710" t="s">
+        <v>722</v>
+      </c>
+      <c r="D710" t="s">
+        <v>76</v>
+      </c>
+      <c r="E710" t="s">
+        <v>200</v>
+      </c>
+      <c r="G710" s="3">
+        <v>134.6</v>
+      </c>
+    </row>
+    <row r="711" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A711" t="s">
+        <v>805</v>
+      </c>
+      <c r="B711" t="s">
+        <v>806</v>
+      </c>
+      <c r="C711" t="s">
+        <v>741</v>
+      </c>
+      <c r="D711" t="s">
+        <v>74</v>
+      </c>
+      <c r="E711" t="s">
+        <v>275</v>
+      </c>
+      <c r="G711" s="3">
+        <v>123.25</v>
+      </c>
+    </row>
+    <row r="712" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A712" t="s">
+        <v>805</v>
+      </c>
+      <c r="B712" t="s">
+        <v>806</v>
+      </c>
+      <c r="C712" t="s">
+        <v>741</v>
+      </c>
+      <c r="D712" t="s">
+        <v>74</v>
+      </c>
+      <c r="E712" t="s">
+        <v>69</v>
+      </c>
+      <c r="G712" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="713" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A713" t="s">
+        <v>805</v>
+      </c>
+      <c r="B713" t="s">
+        <v>806</v>
+      </c>
+      <c r="C713" t="s">
+        <v>741</v>
+      </c>
+      <c r="D713" t="s">
+        <v>64</v>
+      </c>
+      <c r="E713" t="s">
+        <v>67</v>
+      </c>
+      <c r="G713" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="714" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A714" t="s">
+        <v>805</v>
+      </c>
+      <c r="B714" t="s">
+        <v>806</v>
+      </c>
+      <c r="C714" t="s">
+        <v>741</v>
+      </c>
+      <c r="D714" t="s">
+        <v>76</v>
+      </c>
+      <c r="E714" t="s">
+        <v>807</v>
+      </c>
+      <c r="G714" s="3">
+        <v>126.02500000000001</v>
+      </c>
+    </row>
+    <row r="715" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A715" t="s">
+        <v>805</v>
+      </c>
+      <c r="B715" t="s">
+        <v>806</v>
+      </c>
+      <c r="C715" t="s">
+        <v>741</v>
+      </c>
+      <c r="D715" t="s">
+        <v>2</v>
+      </c>
+      <c r="G715" s="3">
+        <v>118.95</v>
+      </c>
+    </row>
+    <row r="716" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A716" t="s">
+        <v>808</v>
+      </c>
+      <c r="B716" t="s">
+        <v>809</v>
+      </c>
+      <c r="C716" t="s">
+        <v>719</v>
+      </c>
+      <c r="D716" t="s">
+        <v>64</v>
+      </c>
+      <c r="E716" t="s">
+        <v>65</v>
+      </c>
+      <c r="F716" t="s">
+        <v>87</v>
+      </c>
+      <c r="G716" s="3">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="717" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A717" t="s">
+        <v>808</v>
+      </c>
+      <c r="B717" t="s">
+        <v>809</v>
+      </c>
+      <c r="C717" t="s">
+        <v>719</v>
+      </c>
+      <c r="D717" t="s">
+        <v>235</v>
+      </c>
+      <c r="E717" t="s">
+        <v>810</v>
+      </c>
+      <c r="G717" s="3">
+        <v>122.875</v>
+      </c>
+    </row>
+    <row r="718" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A718" t="s">
+        <v>808</v>
+      </c>
+      <c r="B718" t="s">
+        <v>809</v>
+      </c>
+      <c r="C718" t="s">
+        <v>719</v>
+      </c>
+      <c r="D718" t="s">
+        <v>113</v>
+      </c>
+      <c r="G718" s="3">
+        <v>122.97499999999999</v>
+      </c>
+    </row>
+    <row r="719" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A719" t="s">
+        <v>811</v>
+      </c>
+      <c r="B719" t="s">
+        <v>812</v>
+      </c>
+      <c r="C719" t="s">
+        <v>741</v>
+      </c>
+      <c r="D719" t="s">
+        <v>64</v>
+      </c>
+      <c r="E719" t="s">
+        <v>67</v>
+      </c>
+      <c r="G719" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="720" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A720" t="s">
+        <v>813</v>
+      </c>
+      <c r="B720" t="s">
+        <v>814</v>
+      </c>
+      <c r="C720" t="s">
+        <v>736</v>
+      </c>
+      <c r="D720" t="s">
+        <v>64</v>
+      </c>
+      <c r="E720" t="s">
+        <v>67</v>
+      </c>
+      <c r="G720" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="721" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A721" t="s">
+        <v>815</v>
+      </c>
+      <c r="B721" t="s">
+        <v>816</v>
+      </c>
+      <c r="C721" t="s">
+        <v>719</v>
+      </c>
+      <c r="D721" t="s">
+        <v>300</v>
+      </c>
+      <c r="E721" t="s">
+        <v>817</v>
+      </c>
+      <c r="G721" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="722" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A722" t="s">
+        <v>815</v>
+      </c>
+      <c r="B722" t="s">
+        <v>816</v>
+      </c>
+      <c r="C722" t="s">
+        <v>719</v>
+      </c>
+      <c r="D722" t="s">
+        <v>64</v>
+      </c>
+      <c r="E722" t="s">
+        <v>65</v>
+      </c>
+      <c r="F722" t="s">
+        <v>87</v>
+      </c>
+      <c r="G722" s="3">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="723" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A723" t="s">
+        <v>815</v>
+      </c>
+      <c r="B723" t="s">
+        <v>816</v>
+      </c>
+      <c r="C723" t="s">
+        <v>719</v>
+      </c>
+      <c r="D723" t="s">
+        <v>235</v>
+      </c>
+      <c r="E723" t="s">
+        <v>810</v>
+      </c>
+      <c r="G723" s="3">
+        <v>122.875</v>
+      </c>
+    </row>
+    <row r="724" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A724" t="s">
+        <v>815</v>
+      </c>
+      <c r="B724" t="s">
+        <v>816</v>
+      </c>
+      <c r="C724" t="s">
+        <v>719</v>
+      </c>
+      <c r="D724" t="s">
+        <v>113</v>
+      </c>
+      <c r="G724" s="3">
+        <v>122.35</v>
+      </c>
+    </row>
+    <row r="725" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A725" t="s">
+        <v>818</v>
+      </c>
+      <c r="B725" t="s">
+        <v>819</v>
+      </c>
+      <c r="C725" t="s">
+        <v>722</v>
+      </c>
+      <c r="D725" t="s">
+        <v>64</v>
+      </c>
+      <c r="E725" t="s">
+        <v>67</v>
+      </c>
+      <c r="G725" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="726" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A726" t="s">
+        <v>820</v>
+      </c>
+      <c r="B726" t="s">
+        <v>821</v>
+      </c>
+      <c r="C726" t="s">
+        <v>736</v>
+      </c>
+      <c r="D726" t="s">
+        <v>64</v>
+      </c>
+      <c r="E726" t="s">
+        <v>67</v>
+      </c>
+      <c r="G726" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="727" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A727" t="s">
+        <v>822</v>
+      </c>
+      <c r="B727" t="s">
+        <v>823</v>
+      </c>
+      <c r="C727" t="s">
+        <v>719</v>
+      </c>
+      <c r="D727" t="s">
+        <v>64</v>
+      </c>
+      <c r="E727" t="s">
+        <v>65</v>
+      </c>
+      <c r="F727" t="s">
+        <v>87</v>
+      </c>
+      <c r="G727" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="728" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A728" t="s">
+        <v>824</v>
+      </c>
+      <c r="B728" t="s">
+        <v>825</v>
+      </c>
+      <c r="C728" t="s">
+        <v>719</v>
+      </c>
+      <c r="D728" t="s">
+        <v>64</v>
+      </c>
+      <c r="E728" t="s">
+        <v>67</v>
+      </c>
+      <c r="G728" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="729" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A729" t="s">
+        <v>826</v>
+      </c>
+      <c r="B729" t="s">
+        <v>827</v>
+      </c>
+      <c r="C729" t="s">
+        <v>719</v>
+      </c>
+      <c r="D729" t="s">
+        <v>64</v>
+      </c>
+      <c r="E729" t="s">
+        <v>65</v>
+      </c>
+      <c r="F729" t="s">
+        <v>87</v>
+      </c>
+      <c r="G729" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="730" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A730" t="s">
+        <v>828</v>
+      </c>
+      <c r="B730" t="s">
+        <v>829</v>
+      </c>
+      <c r="C730" t="s">
+        <v>722</v>
+      </c>
+      <c r="D730" t="s">
+        <v>64</v>
+      </c>
+      <c r="E730" t="s">
+        <v>830</v>
+      </c>
+      <c r="F730" t="s">
+        <v>87</v>
+      </c>
+      <c r="G730" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="731" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A731" t="s">
+        <v>831</v>
+      </c>
+      <c r="B731" t="s">
+        <v>832</v>
+      </c>
+      <c r="C731" t="s">
+        <v>722</v>
+      </c>
+      <c r="D731" t="s">
+        <v>64</v>
+      </c>
+      <c r="E731" t="s">
+        <v>833</v>
+      </c>
+      <c r="G731" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="732" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A732" t="s">
+        <v>834</v>
+      </c>
+      <c r="B732" t="s">
+        <v>835</v>
+      </c>
+      <c r="C732" t="s">
+        <v>719</v>
+      </c>
+      <c r="D732" t="s">
+        <v>64</v>
+      </c>
+      <c r="E732" t="s">
+        <v>67</v>
+      </c>
+      <c r="G732" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="733" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A733" t="s">
+        <v>836</v>
+      </c>
+      <c r="B733" t="s">
+        <v>837</v>
+      </c>
+      <c r="C733" t="s">
+        <v>719</v>
+      </c>
+      <c r="D733" t="s">
+        <v>64</v>
+      </c>
+      <c r="E733" t="s">
+        <v>67</v>
+      </c>
+      <c r="G733" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="734" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A734" t="s">
+        <v>836</v>
+      </c>
+      <c r="B734" t="s">
+        <v>837</v>
+      </c>
+      <c r="C734" t="s">
+        <v>719</v>
+      </c>
+      <c r="D734" t="s">
+        <v>113</v>
+      </c>
+      <c r="G734" s="3">
+        <v>122.97499999999999</v>
+      </c>
+    </row>
+    <row r="735" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G735" s="3"/>
     </row>
-    <row r="736" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G736" s="3"/>
     </row>
     <row r="737" spans="7:7" x14ac:dyDescent="0.25">

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4B7FE2-A1F1-4D32-BA07-95A710D7129B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD3A9652-97F4-4C52-84AF-D2B00CD9E5D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3780" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4387" uniqueCount="1001">
   <si>
     <t>AB</t>
   </si>
@@ -2553,6 +2553,495 @@
   </si>
   <si>
     <t>CJT4</t>
+  </si>
+  <si>
+    <t>Dauphin (lt. Col W.G. (Billy) Baker, VC)</t>
+  </si>
+  <si>
+    <t>CYDN</t>
+  </si>
+  <si>
+    <t>RAAS Brandon rdo</t>
+  </si>
+  <si>
+    <t>13-02Z‡</t>
+  </si>
+  <si>
+    <t>Brandon rdo</t>
+  </si>
+  <si>
+    <t>13-02Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Davidson Muni</t>
+  </si>
+  <si>
+    <t>CJC3</t>
+  </si>
+  <si>
+    <t>Debden</t>
+  </si>
+  <si>
+    <t>CKH3</t>
+  </si>
+  <si>
+    <t>Deer Lake</t>
+  </si>
+  <si>
+    <t>CYDF</t>
+  </si>
+  <si>
+    <t>122.200, 239.600</t>
+  </si>
+  <si>
+    <t>Deloraine</t>
+  </si>
+  <si>
+    <t>CJJ4</t>
+  </si>
+  <si>
+    <t>Dinsmore</t>
+  </si>
+  <si>
+    <t>CKX5</t>
+  </si>
+  <si>
+    <t>Disley</t>
+  </si>
+  <si>
+    <t>CDS2</t>
+  </si>
+  <si>
+    <t>Doaktown</t>
+  </si>
+  <si>
+    <t>CDU6</t>
+  </si>
+  <si>
+    <t>Downs Gulch</t>
+  </si>
+  <si>
+    <t>CDV2</t>
+  </si>
+  <si>
+    <t>Easterville</t>
+  </si>
+  <si>
+    <t>CKM6</t>
+  </si>
+  <si>
+    <t>Eatonia (Elvie Smith) Muni</t>
+  </si>
+  <si>
+    <t>CJG2</t>
+  </si>
+  <si>
+    <t>Edam</t>
+  </si>
+  <si>
+    <t>CJU7</t>
+  </si>
+  <si>
+    <t>Edmundston</t>
+  </si>
+  <si>
+    <t>CYES</t>
+  </si>
+  <si>
+    <t>Elk Island</t>
+  </si>
+  <si>
+    <t>CKZ3</t>
+  </si>
+  <si>
+    <t>Elstow / Combine World Field</t>
+  </si>
+  <si>
+    <t>CEW2</t>
+  </si>
+  <si>
+    <t>Erickson Muni</t>
+  </si>
+  <si>
+    <t>CKQ6</t>
+  </si>
+  <si>
+    <t>Esterhazy</t>
+  </si>
+  <si>
+    <t>CJK4</t>
+  </si>
+  <si>
+    <t>Estevan Regional</t>
+  </si>
+  <si>
+    <t>CYEN</t>
+  </si>
+  <si>
+    <t>Estevan (Blue Sky</t>
+  </si>
+  <si>
+    <t>CBS2</t>
+  </si>
+  <si>
+    <t>Eston</t>
+  </si>
+  <si>
+    <t>CJR4</t>
+  </si>
+  <si>
+    <t>Exploits Valley (Botwood)</t>
+  </si>
+  <si>
+    <t>CCP2</t>
+  </si>
+  <si>
+    <t>Fillmore</t>
+  </si>
+  <si>
+    <t>CKN5</t>
+  </si>
+  <si>
+    <t>Fisher Branch</t>
+  </si>
+  <si>
+    <t>CKX4</t>
+  </si>
+  <si>
+    <t>Flin Flon</t>
+  </si>
+  <si>
+    <t>CYFO</t>
+  </si>
+  <si>
+    <t>RAAS Saskatoon rdo</t>
+  </si>
+  <si>
+    <t>14-02Z‡</t>
+  </si>
+  <si>
+    <t>Saskatoon rdo</t>
+  </si>
+  <si>
+    <t>14-02Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Florenceville</t>
+  </si>
+  <si>
+    <t>CCR3</t>
+  </si>
+  <si>
+    <t>Fogo</t>
+  </si>
+  <si>
+    <t>CDY3</t>
+  </si>
+  <si>
+    <t>Fond-Du-Lac</t>
+  </si>
+  <si>
+    <t>CZFD</t>
+  </si>
+  <si>
+    <t>Fraserwood / Tribble Ranch Field</t>
+  </si>
+  <si>
+    <t>CTR8</t>
+  </si>
+  <si>
+    <t>Fredericton Intl</t>
+  </si>
+  <si>
+    <t>CYFC</t>
+  </si>
+  <si>
+    <t>Saint John rdo</t>
+  </si>
+  <si>
+    <t>RAAS Saint John rdo</t>
+  </si>
+  <si>
+    <t>0345-1045Z‡</t>
+  </si>
+  <si>
+    <t>1045-0345Z‡ (O/T AWOS)</t>
+  </si>
+  <si>
+    <t>1045-0345Z‡</t>
+  </si>
+  <si>
+    <t>124.300, 135.500, 270.800</t>
+  </si>
+  <si>
+    <t>Frontier</t>
+  </si>
+  <si>
+    <t>CJM5</t>
+  </si>
+  <si>
+    <t>Gander Intl</t>
+  </si>
+  <si>
+    <t>CYQX</t>
+  </si>
+  <si>
+    <t>121.800, 275.800</t>
+  </si>
+  <si>
+    <t>118.100, 236.600</t>
+  </si>
+  <si>
+    <t>Outcast ops</t>
+  </si>
+  <si>
+    <t>128.850, 252.800</t>
+  </si>
+  <si>
+    <t>Gillam</t>
+  </si>
+  <si>
+    <t>CYGX</t>
+  </si>
+  <si>
+    <t>tfc (no ground station)</t>
+  </si>
+  <si>
+    <t>Gimli Industrial Airpark Airport</t>
+  </si>
+  <si>
+    <t>CYGM</t>
+  </si>
+  <si>
+    <t>Gladstone</t>
+  </si>
+  <si>
+    <t>CJR5</t>
+  </si>
+  <si>
+    <t>Glenboro</t>
+  </si>
+  <si>
+    <t>CJJ2</t>
+  </si>
+  <si>
+    <t>Glaslyn</t>
+  </si>
+  <si>
+    <t>CJE5</t>
+  </si>
+  <si>
+    <t>Gods Lake</t>
+  </si>
+  <si>
+    <t>CJB6</t>
+  </si>
+  <si>
+    <t>Gods Lake Narrows</t>
+  </si>
+  <si>
+    <t>CYGO</t>
+  </si>
+  <si>
+    <t>Gods River</t>
+  </si>
+  <si>
+    <t>CZGI</t>
+  </si>
+  <si>
+    <t>Goodsoil</t>
+  </si>
+  <si>
+    <t>CKF4</t>
+  </si>
+  <si>
+    <t>Goose Bay</t>
+  </si>
+  <si>
+    <t>CYYR</t>
+  </si>
+  <si>
+    <t>128.100, 340.800</t>
+  </si>
+  <si>
+    <t>118.100, 336.500</t>
+  </si>
+  <si>
+    <t>132.000, 275.800</t>
+  </si>
+  <si>
+    <t>124.500, 236.600</t>
+  </si>
+  <si>
+    <t>119.500, 267.100, 257T</t>
+  </si>
+  <si>
+    <t>11-03Z‡ Mon-Sat O/T Gander Ctr</t>
+  </si>
+  <si>
+    <t>120.400, 294.500</t>
+  </si>
+  <si>
+    <t>Grand Falls</t>
+  </si>
+  <si>
+    <t>CCK3</t>
+  </si>
+  <si>
+    <t>Grand Manan</t>
+  </si>
+  <si>
+    <t>CCN2</t>
+  </si>
+  <si>
+    <t>Grand Rapids</t>
+  </si>
+  <si>
+    <t>CJV8</t>
+  </si>
+  <si>
+    <t>Gravelbourg</t>
+  </si>
+  <si>
+    <t>CJM4</t>
+  </si>
+  <si>
+    <t>Gull Lake</t>
+  </si>
+  <si>
+    <t>CJK5</t>
+  </si>
+  <si>
+    <t>Gunisao Lake</t>
+  </si>
+  <si>
+    <t>CJK2</t>
+  </si>
+  <si>
+    <t>Hafford</t>
+  </si>
+  <si>
+    <t>CJC6</t>
+  </si>
+  <si>
+    <t>Harbour Grace</t>
+  </si>
+  <si>
+    <t>CHG2</t>
+  </si>
+  <si>
+    <t>Hatchet Lake</t>
+  </si>
+  <si>
+    <t>CJL2</t>
+  </si>
+  <si>
+    <t>00-15Z Jun 1-Aug 22 O/T tfc</t>
+  </si>
+  <si>
+    <t>Havelock</t>
+  </si>
+  <si>
+    <t>CCS5</t>
+  </si>
+  <si>
+    <t>Homewood</t>
+  </si>
+  <si>
+    <t>CJT8</t>
+  </si>
+  <si>
+    <t>Hopedale</t>
+  </si>
+  <si>
+    <t>CYHO</t>
+  </si>
+  <si>
+    <t>Hudson Bay</t>
+  </si>
+  <si>
+    <t>CYHB</t>
+  </si>
+  <si>
+    <t>Humboldt</t>
+  </si>
+  <si>
+    <t>CJU4</t>
+  </si>
+  <si>
+    <t>Ile-A-La-Crosse</t>
+  </si>
+  <si>
+    <t>CJF3</t>
+  </si>
+  <si>
+    <t>FISE Edmonton rdo (Buffalo Narrows)</t>
+  </si>
+  <si>
+    <t>Ilford</t>
+  </si>
+  <si>
+    <t>CZBD</t>
+  </si>
+  <si>
+    <t>Island Lake</t>
+  </si>
+  <si>
+    <t>CYIV</t>
+  </si>
+  <si>
+    <t>Ituna</t>
+  </si>
+  <si>
+    <t>CJM2</t>
+  </si>
+  <si>
+    <t>Jenpeg</t>
+  </si>
+  <si>
+    <t>CZJG</t>
+  </si>
+  <si>
+    <t>Juniper</t>
+  </si>
+  <si>
+    <t>CCE3</t>
+  </si>
+  <si>
+    <t>Kamsack</t>
+  </si>
+  <si>
+    <t>CJN2</t>
+  </si>
+  <si>
+    <t>Kaskattama River</t>
+  </si>
+  <si>
+    <t>CAS3</t>
+  </si>
+  <si>
+    <t>Kelsey</t>
+  </si>
+  <si>
+    <t>CZEE</t>
+  </si>
+  <si>
+    <t>14-23Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Kelvington</t>
+  </si>
+  <si>
+    <t>CKV2</t>
+  </si>
+  <si>
+    <t>Kel Vington / Clayton Air 2</t>
+  </si>
+  <si>
+    <t>CKA2</t>
+  </si>
+  <si>
+    <t>123.550, 123.450</t>
   </si>
 </sst>
 </file>
@@ -2942,7 +3431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G798"/>
+  <dimension ref="A1:G853"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -17795,196 +18284,2384 @@
       </c>
     </row>
     <row r="735" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G735" s="3"/>
+      <c r="A735" t="s">
+        <v>838</v>
+      </c>
+      <c r="B735" t="s">
+        <v>839</v>
+      </c>
+      <c r="C735" t="s">
+        <v>722</v>
+      </c>
+      <c r="D735" t="s">
+        <v>74</v>
+      </c>
+      <c r="E735" t="s">
+        <v>840</v>
+      </c>
+      <c r="F735" t="s">
+        <v>841</v>
+      </c>
+      <c r="G735" s="3">
+        <v>122.3</v>
+      </c>
     </row>
     <row r="736" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G736" s="3"/>
-    </row>
-    <row r="737" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G737" s="3"/>
-    </row>
-    <row r="738" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G738" s="3"/>
-    </row>
-    <row r="739" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G739" s="3"/>
-    </row>
-    <row r="740" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G740" s="3"/>
-    </row>
-    <row r="741" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G741" s="3"/>
-    </row>
-    <row r="742" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G742" s="3"/>
-    </row>
-    <row r="743" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G743" s="3"/>
-    </row>
-    <row r="744" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G744" s="3"/>
-    </row>
-    <row r="745" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G745" s="3"/>
-    </row>
-    <row r="746" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G746" s="3"/>
-    </row>
-    <row r="747" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G747" s="3"/>
-    </row>
-    <row r="748" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G748" s="3"/>
-    </row>
-    <row r="749" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G749" s="3"/>
-    </row>
-    <row r="750" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G750" s="3"/>
-    </row>
-    <row r="751" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G751" s="3"/>
-    </row>
-    <row r="752" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G752" s="3"/>
-    </row>
-    <row r="753" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G753" s="3"/>
-    </row>
-    <row r="754" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G754" s="3"/>
-    </row>
-    <row r="755" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G755" s="3"/>
-    </row>
-    <row r="756" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G756" s="3"/>
-    </row>
-    <row r="757" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G757" s="3"/>
-    </row>
-    <row r="758" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G758" s="3"/>
-    </row>
-    <row r="759" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G759" s="3"/>
-    </row>
-    <row r="760" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G760" s="3"/>
-    </row>
-    <row r="761" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G761" s="3"/>
-    </row>
-    <row r="762" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G762" s="3"/>
-    </row>
-    <row r="763" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G763" s="3"/>
-    </row>
-    <row r="764" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G764" s="3"/>
-    </row>
-    <row r="765" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G765" s="3"/>
-    </row>
-    <row r="766" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G766" s="3"/>
-    </row>
-    <row r="767" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G767" s="3"/>
-    </row>
-    <row r="768" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G768" s="3"/>
-    </row>
-    <row r="769" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G769" s="3"/>
-    </row>
-    <row r="770" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G770" s="3"/>
-    </row>
-    <row r="771" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G771" s="3"/>
-    </row>
-    <row r="772" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G772" s="3"/>
-    </row>
-    <row r="773" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G773" s="3"/>
-    </row>
-    <row r="774" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G774" s="3"/>
-    </row>
-    <row r="775" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G775" s="3"/>
-    </row>
-    <row r="776" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G776" s="3"/>
-    </row>
-    <row r="777" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G777" s="3"/>
-    </row>
-    <row r="778" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G778" s="3"/>
-    </row>
-    <row r="779" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G779" s="3"/>
-    </row>
-    <row r="780" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G780" s="3"/>
-    </row>
-    <row r="781" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G781" s="3"/>
-    </row>
-    <row r="782" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G782" s="3"/>
-    </row>
-    <row r="783" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G783" s="3"/>
-    </row>
-    <row r="784" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G784" s="3"/>
-    </row>
-    <row r="785" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G785" s="3"/>
-    </row>
-    <row r="786" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G786" s="3"/>
-    </row>
-    <row r="787" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G787" s="3"/>
-    </row>
-    <row r="788" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G788" s="3"/>
-    </row>
-    <row r="789" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G789" s="3"/>
-    </row>
-    <row r="790" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G790" s="3"/>
-    </row>
-    <row r="791" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G791" s="3"/>
-    </row>
-    <row r="792" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G792" s="3"/>
-    </row>
-    <row r="793" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G793" s="3"/>
-    </row>
-    <row r="794" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G794" s="3"/>
-    </row>
-    <row r="795" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G795" s="3"/>
-    </row>
-    <row r="796" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G796" s="3"/>
-    </row>
-    <row r="797" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G797" s="3"/>
-    </row>
-    <row r="798" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G798" s="3"/>
+      <c r="A736" t="s">
+        <v>838</v>
+      </c>
+      <c r="B736" t="s">
+        <v>839</v>
+      </c>
+      <c r="C736" t="s">
+        <v>722</v>
+      </c>
+      <c r="D736" t="s">
+        <v>74</v>
+      </c>
+      <c r="E736" t="s">
+        <v>386</v>
+      </c>
+      <c r="G736" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="737" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A737" t="s">
+        <v>838</v>
+      </c>
+      <c r="B737" t="s">
+        <v>839</v>
+      </c>
+      <c r="C737" t="s">
+        <v>722</v>
+      </c>
+      <c r="D737" t="s">
+        <v>74</v>
+      </c>
+      <c r="E737" t="s">
+        <v>69</v>
+      </c>
+      <c r="G737" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="738" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A738" t="s">
+        <v>838</v>
+      </c>
+      <c r="B738" t="s">
+        <v>839</v>
+      </c>
+      <c r="C738" t="s">
+        <v>722</v>
+      </c>
+      <c r="D738" t="s">
+        <v>12</v>
+      </c>
+      <c r="E738" t="s">
+        <v>842</v>
+      </c>
+      <c r="F738" t="s">
+        <v>843</v>
+      </c>
+      <c r="G738" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="739" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A739" t="s">
+        <v>838</v>
+      </c>
+      <c r="B739" t="s">
+        <v>839</v>
+      </c>
+      <c r="C739" t="s">
+        <v>722</v>
+      </c>
+      <c r="D739" t="s">
+        <v>2</v>
+      </c>
+      <c r="G739" s="3">
+        <v>128.6</v>
+      </c>
+    </row>
+    <row r="740" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A740" t="s">
+        <v>844</v>
+      </c>
+      <c r="B740" t="s">
+        <v>845</v>
+      </c>
+      <c r="C740" t="s">
+        <v>719</v>
+      </c>
+      <c r="D740" t="s">
+        <v>64</v>
+      </c>
+      <c r="E740" t="s">
+        <v>67</v>
+      </c>
+      <c r="G740" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="741" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A741" t="s">
+        <v>846</v>
+      </c>
+      <c r="B741" t="s">
+        <v>847</v>
+      </c>
+      <c r="C741" t="s">
+        <v>719</v>
+      </c>
+      <c r="D741" t="s">
+        <v>64</v>
+      </c>
+      <c r="E741" t="s">
+        <v>67</v>
+      </c>
+      <c r="G741" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="742" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A742" t="s">
+        <v>848</v>
+      </c>
+      <c r="B742" t="s">
+        <v>849</v>
+      </c>
+      <c r="C742" t="s">
+        <v>741</v>
+      </c>
+      <c r="D742" t="s">
+        <v>11</v>
+      </c>
+      <c r="G742" s="3" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="743" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A743" t="s">
+        <v>848</v>
+      </c>
+      <c r="B743" t="s">
+        <v>849</v>
+      </c>
+      <c r="C743" t="s">
+        <v>741</v>
+      </c>
+      <c r="D743" t="s">
+        <v>74</v>
+      </c>
+      <c r="E743" t="s">
+        <v>275</v>
+      </c>
+      <c r="G743" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="744" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A744" t="s">
+        <v>848</v>
+      </c>
+      <c r="B744" t="s">
+        <v>849</v>
+      </c>
+      <c r="C744" t="s">
+        <v>741</v>
+      </c>
+      <c r="D744" t="s">
+        <v>74</v>
+      </c>
+      <c r="E744" t="s">
+        <v>69</v>
+      </c>
+      <c r="G744" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="745" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A745" t="s">
+        <v>848</v>
+      </c>
+      <c r="B745" t="s">
+        <v>849</v>
+      </c>
+      <c r="C745" t="s">
+        <v>741</v>
+      </c>
+      <c r="D745" t="s">
+        <v>12</v>
+      </c>
+      <c r="E745" t="s">
+        <v>100</v>
+      </c>
+      <c r="G745" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="746" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A746" t="s">
+        <v>848</v>
+      </c>
+      <c r="B746" t="s">
+        <v>849</v>
+      </c>
+      <c r="C746" t="s">
+        <v>741</v>
+      </c>
+      <c r="D746" t="s">
+        <v>76</v>
+      </c>
+      <c r="E746" t="s">
+        <v>807</v>
+      </c>
+      <c r="G746" s="3">
+        <v>134.6</v>
+      </c>
+    </row>
+    <row r="747" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A747" t="s">
+        <v>851</v>
+      </c>
+      <c r="B747" t="s">
+        <v>852</v>
+      </c>
+      <c r="C747" t="s">
+        <v>722</v>
+      </c>
+      <c r="D747" t="s">
+        <v>64</v>
+      </c>
+      <c r="E747" t="s">
+        <v>67</v>
+      </c>
+      <c r="G747" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="748" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A748" t="s">
+        <v>853</v>
+      </c>
+      <c r="B748" t="s">
+        <v>854</v>
+      </c>
+      <c r="C748" t="s">
+        <v>719</v>
+      </c>
+      <c r="D748" t="s">
+        <v>64</v>
+      </c>
+      <c r="E748" t="s">
+        <v>67</v>
+      </c>
+      <c r="G748" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="749" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A749" t="s">
+        <v>855</v>
+      </c>
+      <c r="B749" t="s">
+        <v>856</v>
+      </c>
+      <c r="C749" t="s">
+        <v>719</v>
+      </c>
+      <c r="D749" t="s">
+        <v>64</v>
+      </c>
+      <c r="E749" t="s">
+        <v>67</v>
+      </c>
+      <c r="G749" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="750" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A750" t="s">
+        <v>857</v>
+      </c>
+      <c r="B750" t="s">
+        <v>858</v>
+      </c>
+      <c r="C750" t="s">
+        <v>736</v>
+      </c>
+      <c r="D750" t="s">
+        <v>64</v>
+      </c>
+      <c r="E750" t="s">
+        <v>67</v>
+      </c>
+      <c r="G750" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="751" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A751" t="s">
+        <v>859</v>
+      </c>
+      <c r="B751" t="s">
+        <v>860</v>
+      </c>
+      <c r="C751" t="s">
+        <v>736</v>
+      </c>
+      <c r="D751" t="s">
+        <v>64</v>
+      </c>
+      <c r="E751" t="s">
+        <v>67</v>
+      </c>
+      <c r="G751" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="752" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A752" t="s">
+        <v>861</v>
+      </c>
+      <c r="B752" t="s">
+        <v>862</v>
+      </c>
+      <c r="C752" t="s">
+        <v>722</v>
+      </c>
+      <c r="D752" t="s">
+        <v>64</v>
+      </c>
+      <c r="E752" t="s">
+        <v>67</v>
+      </c>
+      <c r="G752" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="753" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A753" t="s">
+        <v>863</v>
+      </c>
+      <c r="B753" t="s">
+        <v>864</v>
+      </c>
+      <c r="C753" t="s">
+        <v>719</v>
+      </c>
+      <c r="D753" t="s">
+        <v>64</v>
+      </c>
+      <c r="E753" t="s">
+        <v>67</v>
+      </c>
+      <c r="G753" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="754" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A754" t="s">
+        <v>865</v>
+      </c>
+      <c r="B754" t="s">
+        <v>866</v>
+      </c>
+      <c r="C754" t="s">
+        <v>719</v>
+      </c>
+      <c r="D754" t="s">
+        <v>64</v>
+      </c>
+      <c r="E754" t="s">
+        <v>67</v>
+      </c>
+      <c r="G754" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="755" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A755" t="s">
+        <v>867</v>
+      </c>
+      <c r="B755" t="s">
+        <v>868</v>
+      </c>
+      <c r="C755" t="s">
+        <v>736</v>
+      </c>
+      <c r="D755" t="s">
+        <v>64</v>
+      </c>
+      <c r="E755" t="s">
+        <v>65</v>
+      </c>
+      <c r="F755" t="s">
+        <v>87</v>
+      </c>
+      <c r="G755" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="756" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A756" t="s">
+        <v>869</v>
+      </c>
+      <c r="B756" t="s">
+        <v>870</v>
+      </c>
+      <c r="C756" t="s">
+        <v>722</v>
+      </c>
+      <c r="D756" t="s">
+        <v>64</v>
+      </c>
+      <c r="E756" t="s">
+        <v>65</v>
+      </c>
+      <c r="F756" t="s">
+        <v>87</v>
+      </c>
+      <c r="G756" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="757" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A757" t="s">
+        <v>871</v>
+      </c>
+      <c r="B757" t="s">
+        <v>872</v>
+      </c>
+      <c r="C757" t="s">
+        <v>719</v>
+      </c>
+      <c r="D757" t="s">
+        <v>64</v>
+      </c>
+      <c r="E757" t="s">
+        <v>67</v>
+      </c>
+      <c r="G757" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="758" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A758" t="s">
+        <v>873</v>
+      </c>
+      <c r="B758" t="s">
+        <v>874</v>
+      </c>
+      <c r="C758" t="s">
+        <v>722</v>
+      </c>
+      <c r="D758" t="s">
+        <v>64</v>
+      </c>
+      <c r="E758" t="s">
+        <v>67</v>
+      </c>
+      <c r="G758" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="759" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A759" t="s">
+        <v>875</v>
+      </c>
+      <c r="B759" t="s">
+        <v>876</v>
+      </c>
+      <c r="C759" t="s">
+        <v>719</v>
+      </c>
+      <c r="D759" t="s">
+        <v>64</v>
+      </c>
+      <c r="E759" t="s">
+        <v>67</v>
+      </c>
+      <c r="G759" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="760" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A760" t="s">
+        <v>877</v>
+      </c>
+      <c r="B760" t="s">
+        <v>878</v>
+      </c>
+      <c r="C760" t="s">
+        <v>719</v>
+      </c>
+      <c r="D760" t="s">
+        <v>64</v>
+      </c>
+      <c r="E760" t="s">
+        <v>65</v>
+      </c>
+      <c r="F760" t="s">
+        <v>87</v>
+      </c>
+      <c r="G760" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="761" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A761" t="s">
+        <v>877</v>
+      </c>
+      <c r="B761" t="s">
+        <v>878</v>
+      </c>
+      <c r="C761" t="s">
+        <v>719</v>
+      </c>
+      <c r="D761" t="s">
+        <v>2</v>
+      </c>
+      <c r="G761" s="3">
+        <v>127.8</v>
+      </c>
+    </row>
+    <row r="762" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A762" t="s">
+        <v>879</v>
+      </c>
+      <c r="B762" t="s">
+        <v>880</v>
+      </c>
+      <c r="C762" t="s">
+        <v>719</v>
+      </c>
+      <c r="D762" t="s">
+        <v>64</v>
+      </c>
+      <c r="E762" t="s">
+        <v>67</v>
+      </c>
+      <c r="G762" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="763" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A763" t="s">
+        <v>881</v>
+      </c>
+      <c r="B763" t="s">
+        <v>882</v>
+      </c>
+      <c r="C763" t="s">
+        <v>719</v>
+      </c>
+      <c r="D763" t="s">
+        <v>64</v>
+      </c>
+      <c r="E763" t="s">
+        <v>67</v>
+      </c>
+      <c r="G763" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="764" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A764" t="s">
+        <v>883</v>
+      </c>
+      <c r="B764" t="s">
+        <v>884</v>
+      </c>
+      <c r="C764" t="s">
+        <v>741</v>
+      </c>
+      <c r="D764" t="s">
+        <v>64</v>
+      </c>
+      <c r="E764" t="s">
+        <v>67</v>
+      </c>
+      <c r="G764" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="765" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A765" t="s">
+        <v>885</v>
+      </c>
+      <c r="B765" t="s">
+        <v>886</v>
+      </c>
+      <c r="C765" t="s">
+        <v>719</v>
+      </c>
+      <c r="D765" t="s">
+        <v>64</v>
+      </c>
+      <c r="E765" t="s">
+        <v>67</v>
+      </c>
+      <c r="G765" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="766" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A766" t="s">
+        <v>887</v>
+      </c>
+      <c r="B766" t="s">
+        <v>888</v>
+      </c>
+      <c r="C766" t="s">
+        <v>722</v>
+      </c>
+      <c r="D766" t="s">
+        <v>64</v>
+      </c>
+      <c r="E766" t="s">
+        <v>67</v>
+      </c>
+      <c r="G766" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="767" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A767" t="s">
+        <v>889</v>
+      </c>
+      <c r="B767" t="s">
+        <v>890</v>
+      </c>
+      <c r="C767" t="s">
+        <v>722</v>
+      </c>
+      <c r="D767" t="s">
+        <v>74</v>
+      </c>
+      <c r="E767" t="s">
+        <v>891</v>
+      </c>
+      <c r="F767" t="s">
+        <v>892</v>
+      </c>
+      <c r="G767" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="768" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A768" t="s">
+        <v>889</v>
+      </c>
+      <c r="B768" t="s">
+        <v>890</v>
+      </c>
+      <c r="C768" t="s">
+        <v>722</v>
+      </c>
+      <c r="D768" t="s">
+        <v>74</v>
+      </c>
+      <c r="E768" t="s">
+        <v>386</v>
+      </c>
+      <c r="G768" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="769" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A769" t="s">
+        <v>889</v>
+      </c>
+      <c r="B769" t="s">
+        <v>890</v>
+      </c>
+      <c r="C769" t="s">
+        <v>722</v>
+      </c>
+      <c r="D769" t="s">
+        <v>74</v>
+      </c>
+      <c r="E769" t="s">
+        <v>69</v>
+      </c>
+      <c r="G769" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="770" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A770" t="s">
+        <v>889</v>
+      </c>
+      <c r="B770" t="s">
+        <v>890</v>
+      </c>
+      <c r="C770" t="s">
+        <v>722</v>
+      </c>
+      <c r="D770" t="s">
+        <v>12</v>
+      </c>
+      <c r="E770" t="s">
+        <v>893</v>
+      </c>
+      <c r="F770" t="s">
+        <v>894</v>
+      </c>
+      <c r="G770" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="771" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A771" t="s">
+        <v>895</v>
+      </c>
+      <c r="B771" t="s">
+        <v>896</v>
+      </c>
+      <c r="C771" t="s">
+        <v>736</v>
+      </c>
+      <c r="D771" t="s">
+        <v>64</v>
+      </c>
+      <c r="E771" t="s">
+        <v>67</v>
+      </c>
+      <c r="G771" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="772" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A772" t="s">
+        <v>897</v>
+      </c>
+      <c r="B772" t="s">
+        <v>898</v>
+      </c>
+      <c r="C772" t="s">
+        <v>741</v>
+      </c>
+      <c r="D772" t="s">
+        <v>64</v>
+      </c>
+      <c r="E772" t="s">
+        <v>67</v>
+      </c>
+      <c r="G772" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="773" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A773" t="s">
+        <v>899</v>
+      </c>
+      <c r="B773" t="s">
+        <v>900</v>
+      </c>
+      <c r="C773" t="s">
+        <v>719</v>
+      </c>
+      <c r="D773" t="s">
+        <v>64</v>
+      </c>
+      <c r="E773" t="s">
+        <v>67</v>
+      </c>
+      <c r="G773" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="774" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A774" t="s">
+        <v>899</v>
+      </c>
+      <c r="B774" t="s">
+        <v>900</v>
+      </c>
+      <c r="C774" t="s">
+        <v>719</v>
+      </c>
+      <c r="D774" t="s">
+        <v>45</v>
+      </c>
+      <c r="G774" s="3">
+        <v>122.175</v>
+      </c>
+    </row>
+    <row r="775" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A775" t="s">
+        <v>901</v>
+      </c>
+      <c r="B775" t="s">
+        <v>902</v>
+      </c>
+      <c r="C775" t="s">
+        <v>722</v>
+      </c>
+      <c r="D775" t="s">
+        <v>64</v>
+      </c>
+      <c r="E775" t="s">
+        <v>67</v>
+      </c>
+      <c r="G775" s="3">
+        <v>122.15</v>
+      </c>
+    </row>
+    <row r="776" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A776" t="s">
+        <v>903</v>
+      </c>
+      <c r="B776" t="s">
+        <v>904</v>
+      </c>
+      <c r="C776" t="s">
+        <v>736</v>
+      </c>
+      <c r="D776" t="s">
+        <v>74</v>
+      </c>
+      <c r="E776" t="s">
+        <v>906</v>
+      </c>
+      <c r="F776" t="s">
+        <v>907</v>
+      </c>
+      <c r="G776" s="3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="777" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A777" t="s">
+        <v>903</v>
+      </c>
+      <c r="B777" t="s">
+        <v>904</v>
+      </c>
+      <c r="C777" t="s">
+        <v>736</v>
+      </c>
+      <c r="D777" t="s">
+        <v>41</v>
+      </c>
+      <c r="F777" t="s">
+        <v>908</v>
+      </c>
+      <c r="G777" s="3">
+        <v>127.55</v>
+      </c>
+    </row>
+    <row r="778" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A778" t="s">
+        <v>903</v>
+      </c>
+      <c r="B778" t="s">
+        <v>904</v>
+      </c>
+      <c r="C778" t="s">
+        <v>736</v>
+      </c>
+      <c r="D778" t="s">
+        <v>14</v>
+      </c>
+      <c r="F778" t="s">
+        <v>909</v>
+      </c>
+      <c r="G778" s="3">
+        <v>121.7</v>
+      </c>
+    </row>
+    <row r="779" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A779" t="s">
+        <v>903</v>
+      </c>
+      <c r="B779" t="s">
+        <v>904</v>
+      </c>
+      <c r="C779" t="s">
+        <v>736</v>
+      </c>
+      <c r="D779" t="s">
+        <v>15</v>
+      </c>
+      <c r="F779" t="s">
+        <v>909</v>
+      </c>
+      <c r="G779" s="3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="780" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A780" t="s">
+        <v>903</v>
+      </c>
+      <c r="B780" t="s">
+        <v>904</v>
+      </c>
+      <c r="C780" t="s">
+        <v>736</v>
+      </c>
+      <c r="D780" t="s">
+        <v>12</v>
+      </c>
+      <c r="E780" t="s">
+        <v>905</v>
+      </c>
+      <c r="F780" t="s">
+        <v>909</v>
+      </c>
+      <c r="G780" s="3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="781" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A781" t="s">
+        <v>903</v>
+      </c>
+      <c r="B781" t="s">
+        <v>904</v>
+      </c>
+      <c r="C781" t="s">
+        <v>736</v>
+      </c>
+      <c r="D781" t="s">
+        <v>76</v>
+      </c>
+      <c r="E781" t="s">
+        <v>524</v>
+      </c>
+      <c r="G781" s="3" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="782" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A782" t="s">
+        <v>911</v>
+      </c>
+      <c r="B782" t="s">
+        <v>912</v>
+      </c>
+      <c r="C782" t="s">
+        <v>719</v>
+      </c>
+      <c r="D782" t="s">
+        <v>64</v>
+      </c>
+      <c r="E782" t="s">
+        <v>67</v>
+      </c>
+      <c r="G782" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="783" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A783" t="s">
+        <v>913</v>
+      </c>
+      <c r="B783" t="s">
+        <v>914</v>
+      </c>
+      <c r="C783" t="s">
+        <v>741</v>
+      </c>
+      <c r="D783" t="s">
+        <v>74</v>
+      </c>
+      <c r="E783" t="s">
+        <v>275</v>
+      </c>
+      <c r="G783" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="784" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A784" t="s">
+        <v>913</v>
+      </c>
+      <c r="B784" t="s">
+        <v>914</v>
+      </c>
+      <c r="C784" t="s">
+        <v>741</v>
+      </c>
+      <c r="D784" t="s">
+        <v>74</v>
+      </c>
+      <c r="E784" t="s">
+        <v>69</v>
+      </c>
+      <c r="G784" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="785" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A785" t="s">
+        <v>913</v>
+      </c>
+      <c r="B785" t="s">
+        <v>914</v>
+      </c>
+      <c r="C785" t="s">
+        <v>741</v>
+      </c>
+      <c r="D785" t="s">
+        <v>41</v>
+      </c>
+      <c r="G785" s="3">
+        <v>124.8</v>
+      </c>
+    </row>
+    <row r="786" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A786" t="s">
+        <v>913</v>
+      </c>
+      <c r="B786" t="s">
+        <v>914</v>
+      </c>
+      <c r="C786" t="s">
+        <v>741</v>
+      </c>
+      <c r="D786" t="s">
+        <v>14</v>
+      </c>
+      <c r="G786" s="3" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="787" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A787" t="s">
+        <v>913</v>
+      </c>
+      <c r="B787" t="s">
+        <v>914</v>
+      </c>
+      <c r="C787" t="s">
+        <v>741</v>
+      </c>
+      <c r="D787" t="s">
+        <v>15</v>
+      </c>
+      <c r="G787" s="3" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="788" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A788" t="s">
+        <v>913</v>
+      </c>
+      <c r="B788" t="s">
+        <v>914</v>
+      </c>
+      <c r="C788" t="s">
+        <v>741</v>
+      </c>
+      <c r="D788" t="s">
+        <v>16</v>
+      </c>
+      <c r="G788" s="3">
+        <v>132.1</v>
+      </c>
+    </row>
+    <row r="789" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A789" t="s">
+        <v>913</v>
+      </c>
+      <c r="B789" t="s">
+        <v>914</v>
+      </c>
+      <c r="C789" t="s">
+        <v>741</v>
+      </c>
+      <c r="D789" t="s">
+        <v>17</v>
+      </c>
+      <c r="G789" s="3">
+        <v>132.1</v>
+      </c>
+    </row>
+    <row r="790" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A790" t="s">
+        <v>913</v>
+      </c>
+      <c r="B790" t="s">
+        <v>914</v>
+      </c>
+      <c r="C790" t="s">
+        <v>741</v>
+      </c>
+      <c r="D790" t="s">
+        <v>185</v>
+      </c>
+      <c r="E790" t="s">
+        <v>917</v>
+      </c>
+      <c r="G790" s="3" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="791" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A791" t="s">
+        <v>919</v>
+      </c>
+      <c r="B791" t="s">
+        <v>920</v>
+      </c>
+      <c r="C791" t="s">
+        <v>722</v>
+      </c>
+      <c r="D791" t="s">
+        <v>74</v>
+      </c>
+      <c r="E791" t="s">
+        <v>386</v>
+      </c>
+      <c r="G791" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="792" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A792" t="s">
+        <v>919</v>
+      </c>
+      <c r="B792" t="s">
+        <v>920</v>
+      </c>
+      <c r="C792" t="s">
+        <v>722</v>
+      </c>
+      <c r="D792" t="s">
+        <v>74</v>
+      </c>
+      <c r="E792" t="s">
+        <v>69</v>
+      </c>
+      <c r="G792" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="793" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A793" t="s">
+        <v>919</v>
+      </c>
+      <c r="B793" t="s">
+        <v>920</v>
+      </c>
+      <c r="C793" t="s">
+        <v>722</v>
+      </c>
+      <c r="D793" t="s">
+        <v>12</v>
+      </c>
+      <c r="E793" t="s">
+        <v>921</v>
+      </c>
+      <c r="G793" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="794" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A794" t="s">
+        <v>919</v>
+      </c>
+      <c r="B794" t="s">
+        <v>920</v>
+      </c>
+      <c r="C794" t="s">
+        <v>722</v>
+      </c>
+      <c r="D794" t="s">
+        <v>76</v>
+      </c>
+      <c r="E794" t="s">
+        <v>200</v>
+      </c>
+      <c r="G794" s="3">
+        <v>134.65</v>
+      </c>
+    </row>
+    <row r="795" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A795" t="s">
+        <v>922</v>
+      </c>
+      <c r="B795" t="s">
+        <v>923</v>
+      </c>
+      <c r="C795" t="s">
+        <v>722</v>
+      </c>
+      <c r="D795" t="s">
+        <v>12</v>
+      </c>
+      <c r="E795" t="s">
+        <v>65</v>
+      </c>
+      <c r="F795" t="s">
+        <v>87</v>
+      </c>
+      <c r="G795" s="3">
+        <v>122.15</v>
+      </c>
+    </row>
+    <row r="796" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A796" t="s">
+        <v>922</v>
+      </c>
+      <c r="B796" t="s">
+        <v>923</v>
+      </c>
+      <c r="C796" t="s">
+        <v>722</v>
+      </c>
+      <c r="D796" t="s">
+        <v>113</v>
+      </c>
+      <c r="G796" s="3">
+        <v>122.97499999999999</v>
+      </c>
+    </row>
+    <row r="797" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A797" t="s">
+        <v>924</v>
+      </c>
+      <c r="B797" t="s">
+        <v>925</v>
+      </c>
+      <c r="C797" t="s">
+        <v>722</v>
+      </c>
+      <c r="D797" t="s">
+        <v>64</v>
+      </c>
+      <c r="E797" t="s">
+        <v>65</v>
+      </c>
+      <c r="F797" t="s">
+        <v>87</v>
+      </c>
+      <c r="G797" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="798" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A798" t="s">
+        <v>928</v>
+      </c>
+      <c r="B798" t="s">
+        <v>929</v>
+      </c>
+      <c r="C798" t="s">
+        <v>719</v>
+      </c>
+      <c r="D798" t="s">
+        <v>64</v>
+      </c>
+      <c r="E798" t="s">
+        <v>67</v>
+      </c>
+      <c r="G798" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="799" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A799" t="s">
+        <v>926</v>
+      </c>
+      <c r="B799" t="s">
+        <v>927</v>
+      </c>
+      <c r="C799" t="s">
+        <v>722</v>
+      </c>
+      <c r="D799" t="s">
+        <v>64</v>
+      </c>
+      <c r="E799" t="s">
+        <v>67</v>
+      </c>
+      <c r="G799" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="800" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A800" t="s">
+        <v>930</v>
+      </c>
+      <c r="B800" t="s">
+        <v>931</v>
+      </c>
+      <c r="C800" t="s">
+        <v>722</v>
+      </c>
+      <c r="D800" t="s">
+        <v>64</v>
+      </c>
+      <c r="E800" t="s">
+        <v>67</v>
+      </c>
+      <c r="G800" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="801" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A801" t="s">
+        <v>932</v>
+      </c>
+      <c r="B801" t="s">
+        <v>933</v>
+      </c>
+      <c r="C801" t="s">
+        <v>722</v>
+      </c>
+      <c r="D801" t="s">
+        <v>64</v>
+      </c>
+      <c r="E801" t="s">
+        <v>65</v>
+      </c>
+      <c r="F801" t="s">
+        <v>87</v>
+      </c>
+      <c r="G801" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="802" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A802" t="s">
+        <v>934</v>
+      </c>
+      <c r="B802" t="s">
+        <v>935</v>
+      </c>
+      <c r="C802" t="s">
+        <v>722</v>
+      </c>
+      <c r="D802" t="s">
+        <v>64</v>
+      </c>
+      <c r="E802" t="s">
+        <v>65</v>
+      </c>
+      <c r="F802" t="s">
+        <v>87</v>
+      </c>
+      <c r="G802" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="803" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A803" t="s">
+        <v>936</v>
+      </c>
+      <c r="B803" t="s">
+        <v>937</v>
+      </c>
+      <c r="C803" t="s">
+        <v>719</v>
+      </c>
+      <c r="D803" t="s">
+        <v>64</v>
+      </c>
+      <c r="E803" t="s">
+        <v>67</v>
+      </c>
+      <c r="G803" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="804" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A804" t="s">
+        <v>938</v>
+      </c>
+      <c r="B804" t="s">
+        <v>939</v>
+      </c>
+      <c r="C804" t="s">
+        <v>741</v>
+      </c>
+      <c r="D804" t="s">
+        <v>74</v>
+      </c>
+      <c r="E804" t="s">
+        <v>275</v>
+      </c>
+      <c r="G804" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="805" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A805" t="s">
+        <v>938</v>
+      </c>
+      <c r="B805" t="s">
+        <v>939</v>
+      </c>
+      <c r="C805" t="s">
+        <v>741</v>
+      </c>
+      <c r="D805" t="s">
+        <v>74</v>
+      </c>
+      <c r="E805" t="s">
+        <v>69</v>
+      </c>
+      <c r="G805" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="806" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A806" t="s">
+        <v>938</v>
+      </c>
+      <c r="B806" t="s">
+        <v>939</v>
+      </c>
+      <c r="C806" t="s">
+        <v>741</v>
+      </c>
+      <c r="D806" t="s">
+        <v>41</v>
+      </c>
+      <c r="G806" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="807" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A807" t="s">
+        <v>938</v>
+      </c>
+      <c r="B807" t="s">
+        <v>939</v>
+      </c>
+      <c r="C807" t="s">
+        <v>741</v>
+      </c>
+      <c r="D807" t="s">
+        <v>146</v>
+      </c>
+      <c r="G807" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="808" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A808" t="s">
+        <v>938</v>
+      </c>
+      <c r="B808" t="s">
+        <v>939</v>
+      </c>
+      <c r="C808" t="s">
+        <v>741</v>
+      </c>
+      <c r="D808" t="s">
+        <v>14</v>
+      </c>
+      <c r="G808" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="809" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A809" t="s">
+        <v>938</v>
+      </c>
+      <c r="B809" t="s">
+        <v>939</v>
+      </c>
+      <c r="C809" t="s">
+        <v>741</v>
+      </c>
+      <c r="D809" t="s">
+        <v>15</v>
+      </c>
+      <c r="G809" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="810" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A810" t="s">
+        <v>938</v>
+      </c>
+      <c r="B810" t="s">
+        <v>939</v>
+      </c>
+      <c r="C810" t="s">
+        <v>741</v>
+      </c>
+      <c r="D810" t="s">
+        <v>44</v>
+      </c>
+      <c r="F810" t="s">
+        <v>945</v>
+      </c>
+      <c r="G810" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="811" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A811" t="s">
+        <v>938</v>
+      </c>
+      <c r="B811" t="s">
+        <v>939</v>
+      </c>
+      <c r="C811" t="s">
+        <v>741</v>
+      </c>
+      <c r="D811" t="s">
+        <v>76</v>
+      </c>
+      <c r="E811" t="s">
+        <v>807</v>
+      </c>
+      <c r="G811" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="812" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A812" t="s">
+        <v>938</v>
+      </c>
+      <c r="B812" t="s">
+        <v>939</v>
+      </c>
+      <c r="C812" t="s">
+        <v>741</v>
+      </c>
+      <c r="D812" t="s">
+        <v>190</v>
+      </c>
+      <c r="G812" s="3">
+        <v>344.6</v>
+      </c>
+    </row>
+    <row r="813" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A813" t="s">
+        <v>947</v>
+      </c>
+      <c r="B813" t="s">
+        <v>948</v>
+      </c>
+      <c r="C813" t="s">
+        <v>736</v>
+      </c>
+      <c r="D813" t="s">
+        <v>300</v>
+      </c>
+      <c r="E813" t="s">
+        <v>414</v>
+      </c>
+      <c r="G813" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="814" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A814" t="s">
+        <v>947</v>
+      </c>
+      <c r="B814" t="s">
+        <v>948</v>
+      </c>
+      <c r="C814" t="s">
+        <v>736</v>
+      </c>
+      <c r="D814" t="s">
+        <v>64</v>
+      </c>
+      <c r="E814" t="s">
+        <v>65</v>
+      </c>
+      <c r="F814" t="s">
+        <v>87</v>
+      </c>
+      <c r="G814" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="815" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A815" t="s">
+        <v>949</v>
+      </c>
+      <c r="B815" t="s">
+        <v>950</v>
+      </c>
+      <c r="C815" t="s">
+        <v>736</v>
+      </c>
+      <c r="D815" t="s">
+        <v>64</v>
+      </c>
+      <c r="E815" t="s">
+        <v>67</v>
+      </c>
+      <c r="G815" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="816" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A816" t="s">
+        <v>949</v>
+      </c>
+      <c r="B816" t="s">
+        <v>950</v>
+      </c>
+      <c r="C816" t="s">
+        <v>736</v>
+      </c>
+      <c r="D816" t="s">
+        <v>113</v>
+      </c>
+      <c r="G816" s="3">
+        <v>122.175</v>
+      </c>
+    </row>
+    <row r="817" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A817" t="s">
+        <v>951</v>
+      </c>
+      <c r="B817" t="s">
+        <v>952</v>
+      </c>
+      <c r="C817" t="s">
+        <v>722</v>
+      </c>
+      <c r="D817" t="s">
+        <v>64</v>
+      </c>
+      <c r="E817" t="s">
+        <v>65</v>
+      </c>
+      <c r="F817" t="s">
+        <v>87</v>
+      </c>
+      <c r="G817" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="818" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A818" t="s">
+        <v>951</v>
+      </c>
+      <c r="B818" t="s">
+        <v>952</v>
+      </c>
+      <c r="C818" t="s">
+        <v>722</v>
+      </c>
+      <c r="D818" t="s">
+        <v>113</v>
+      </c>
+      <c r="G818" s="3">
+        <v>129.17500000000001</v>
+      </c>
+    </row>
+    <row r="819" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A819" t="s">
+        <v>953</v>
+      </c>
+      <c r="B819" t="s">
+        <v>954</v>
+      </c>
+      <c r="C819" t="s">
+        <v>719</v>
+      </c>
+      <c r="D819" t="s">
+        <v>64</v>
+      </c>
+      <c r="E819" t="s">
+        <v>65</v>
+      </c>
+      <c r="F819" t="s">
+        <v>87</v>
+      </c>
+      <c r="G819" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="820" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A820" t="s">
+        <v>955</v>
+      </c>
+      <c r="B820" t="s">
+        <v>956</v>
+      </c>
+      <c r="C820" t="s">
+        <v>719</v>
+      </c>
+      <c r="D820" t="s">
+        <v>64</v>
+      </c>
+      <c r="E820" t="s">
+        <v>67</v>
+      </c>
+      <c r="G820" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="821" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A821" t="s">
+        <v>957</v>
+      </c>
+      <c r="B821" t="s">
+        <v>958</v>
+      </c>
+      <c r="C821" t="s">
+        <v>722</v>
+      </c>
+      <c r="D821" t="s">
+        <v>64</v>
+      </c>
+      <c r="E821" t="s">
+        <v>65</v>
+      </c>
+      <c r="F821" t="s">
+        <v>87</v>
+      </c>
+      <c r="G821" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="822" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A822" t="s">
+        <v>959</v>
+      </c>
+      <c r="B822" t="s">
+        <v>960</v>
+      </c>
+      <c r="C822" t="s">
+        <v>719</v>
+      </c>
+      <c r="D822" t="s">
+        <v>64</v>
+      </c>
+      <c r="E822" t="s">
+        <v>67</v>
+      </c>
+      <c r="G822" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="823" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A823" t="s">
+        <v>961</v>
+      </c>
+      <c r="B823" t="s">
+        <v>962</v>
+      </c>
+      <c r="C823" t="s">
+        <v>741</v>
+      </c>
+      <c r="D823" t="s">
+        <v>64</v>
+      </c>
+      <c r="E823" t="s">
+        <v>67</v>
+      </c>
+      <c r="G823" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="824" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A824" t="s">
+        <v>963</v>
+      </c>
+      <c r="B824" t="s">
+        <v>964</v>
+      </c>
+      <c r="C824" t="s">
+        <v>719</v>
+      </c>
+      <c r="D824" t="s">
+        <v>64</v>
+      </c>
+      <c r="E824" t="s">
+        <v>65</v>
+      </c>
+      <c r="F824" t="s">
+        <v>965</v>
+      </c>
+      <c r="G824" s="3">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="825" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A825" t="s">
+        <v>966</v>
+      </c>
+      <c r="B825" t="s">
+        <v>967</v>
+      </c>
+      <c r="C825" t="s">
+        <v>736</v>
+      </c>
+      <c r="D825" t="s">
+        <v>64</v>
+      </c>
+      <c r="E825" t="s">
+        <v>67</v>
+      </c>
+      <c r="G825" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="826" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A826" t="s">
+        <v>968</v>
+      </c>
+      <c r="B826" t="s">
+        <v>969</v>
+      </c>
+      <c r="C826" t="s">
+        <v>722</v>
+      </c>
+      <c r="D826" t="s">
+        <v>64</v>
+      </c>
+      <c r="E826" t="s">
+        <v>67</v>
+      </c>
+      <c r="G826" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="827" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A827" t="s">
+        <v>970</v>
+      </c>
+      <c r="B827" t="s">
+        <v>971</v>
+      </c>
+      <c r="C827" t="s">
+        <v>741</v>
+      </c>
+      <c r="D827" t="s">
+        <v>74</v>
+      </c>
+      <c r="E827" t="s">
+        <v>275</v>
+      </c>
+      <c r="G827" s="3">
+        <v>123.65</v>
+      </c>
+    </row>
+    <row r="828" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A828" t="s">
+        <v>970</v>
+      </c>
+      <c r="B828" t="s">
+        <v>971</v>
+      </c>
+      <c r="C828" t="s">
+        <v>741</v>
+      </c>
+      <c r="D828" t="s">
+        <v>74</v>
+      </c>
+      <c r="E828" t="s">
+        <v>69</v>
+      </c>
+      <c r="G828" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="829" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A829" t="s">
+        <v>970</v>
+      </c>
+      <c r="B829" t="s">
+        <v>971</v>
+      </c>
+      <c r="C829" t="s">
+        <v>741</v>
+      </c>
+      <c r="D829" t="s">
+        <v>64</v>
+      </c>
+      <c r="E829" t="s">
+        <v>67</v>
+      </c>
+      <c r="G829" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="830" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A830" t="s">
+        <v>970</v>
+      </c>
+      <c r="B830" t="s">
+        <v>971</v>
+      </c>
+      <c r="C830" t="s">
+        <v>741</v>
+      </c>
+      <c r="D830" t="s">
+        <v>76</v>
+      </c>
+      <c r="E830" t="s">
+        <v>807</v>
+      </c>
+      <c r="G830" s="3">
+        <v>135.4</v>
+      </c>
+    </row>
+    <row r="831" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A831" t="s">
+        <v>970</v>
+      </c>
+      <c r="B831" t="s">
+        <v>971</v>
+      </c>
+      <c r="C831" t="s">
+        <v>741</v>
+      </c>
+      <c r="D831" t="s">
+        <v>404</v>
+      </c>
+      <c r="E831" t="s">
+        <v>405</v>
+      </c>
+      <c r="G831" s="3">
+        <v>120.55</v>
+      </c>
+    </row>
+    <row r="832" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A832" t="s">
+        <v>972</v>
+      </c>
+      <c r="B832" t="s">
+        <v>973</v>
+      </c>
+      <c r="C832" t="s">
+        <v>719</v>
+      </c>
+      <c r="D832" t="s">
+        <v>64</v>
+      </c>
+      <c r="E832" t="s">
+        <v>67</v>
+      </c>
+      <c r="G832" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="833" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A833" t="s">
+        <v>974</v>
+      </c>
+      <c r="B833" t="s">
+        <v>975</v>
+      </c>
+      <c r="C833" t="s">
+        <v>719</v>
+      </c>
+      <c r="D833" t="s">
+        <v>64</v>
+      </c>
+      <c r="E833" t="s">
+        <v>67</v>
+      </c>
+      <c r="G833" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="834" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A834" t="s">
+        <v>976</v>
+      </c>
+      <c r="B834" t="s">
+        <v>977</v>
+      </c>
+      <c r="C834" t="s">
+        <v>719</v>
+      </c>
+      <c r="D834" t="s">
+        <v>74</v>
+      </c>
+      <c r="E834" t="s">
+        <v>978</v>
+      </c>
+      <c r="G834" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="835" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A835" t="s">
+        <v>976</v>
+      </c>
+      <c r="B835" t="s">
+        <v>977</v>
+      </c>
+      <c r="C835" t="s">
+        <v>719</v>
+      </c>
+      <c r="D835" t="s">
+        <v>64</v>
+      </c>
+      <c r="E835" t="s">
+        <v>67</v>
+      </c>
+      <c r="G835" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="836" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A836" t="s">
+        <v>976</v>
+      </c>
+      <c r="B836" t="s">
+        <v>977</v>
+      </c>
+      <c r="C836" t="s">
+        <v>719</v>
+      </c>
+      <c r="D836" t="s">
+        <v>113</v>
+      </c>
+      <c r="G836" s="3">
+        <v>122.075</v>
+      </c>
+    </row>
+    <row r="837" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A837" t="s">
+        <v>979</v>
+      </c>
+      <c r="B837" t="s">
+        <v>980</v>
+      </c>
+      <c r="C837" t="s">
+        <v>722</v>
+      </c>
+      <c r="D837" t="s">
+        <v>64</v>
+      </c>
+      <c r="E837" t="s">
+        <v>65</v>
+      </c>
+      <c r="F837" t="s">
+        <v>87</v>
+      </c>
+      <c r="G837" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="838" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A838" t="s">
+        <v>981</v>
+      </c>
+      <c r="B838" t="s">
+        <v>982</v>
+      </c>
+      <c r="C838" t="s">
+        <v>722</v>
+      </c>
+      <c r="D838" t="s">
+        <v>74</v>
+      </c>
+      <c r="E838" t="s">
+        <v>416</v>
+      </c>
+      <c r="G838" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="839" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A839" t="s">
+        <v>981</v>
+      </c>
+      <c r="B839" t="s">
+        <v>982</v>
+      </c>
+      <c r="C839" t="s">
+        <v>722</v>
+      </c>
+      <c r="D839" t="s">
+        <v>74</v>
+      </c>
+      <c r="E839" t="s">
+        <v>386</v>
+      </c>
+      <c r="G839" s="3">
+        <v>122.375</v>
+      </c>
+    </row>
+    <row r="840" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A840" t="s">
+        <v>981</v>
+      </c>
+      <c r="B840" t="s">
+        <v>982</v>
+      </c>
+      <c r="C840" t="s">
+        <v>722</v>
+      </c>
+      <c r="D840" t="s">
+        <v>74</v>
+      </c>
+      <c r="E840" t="s">
+        <v>69</v>
+      </c>
+      <c r="G840" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="841" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A841" t="s">
+        <v>981</v>
+      </c>
+      <c r="B841" t="s">
+        <v>982</v>
+      </c>
+      <c r="C841" t="s">
+        <v>722</v>
+      </c>
+      <c r="D841" t="s">
+        <v>12</v>
+      </c>
+      <c r="E841" t="s">
+        <v>242</v>
+      </c>
+      <c r="G841" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="842" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A842" t="s">
+        <v>981</v>
+      </c>
+      <c r="B842" t="s">
+        <v>982</v>
+      </c>
+      <c r="C842" t="s">
+        <v>722</v>
+      </c>
+      <c r="D842" t="s">
+        <v>76</v>
+      </c>
+      <c r="E842" t="s">
+        <v>200</v>
+      </c>
+      <c r="G842" s="3">
+        <v>132.82499999999999</v>
+      </c>
+    </row>
+    <row r="843" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A843" t="s">
+        <v>981</v>
+      </c>
+      <c r="B843" t="s">
+        <v>982</v>
+      </c>
+      <c r="C843" t="s">
+        <v>722</v>
+      </c>
+      <c r="D843" t="s">
+        <v>2</v>
+      </c>
+      <c r="G843" s="3">
+        <v>128.1</v>
+      </c>
+    </row>
+    <row r="844" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A844" t="s">
+        <v>983</v>
+      </c>
+      <c r="B844" t="s">
+        <v>984</v>
+      </c>
+      <c r="C844" t="s">
+        <v>719</v>
+      </c>
+      <c r="D844" t="s">
+        <v>64</v>
+      </c>
+      <c r="E844" t="s">
+        <v>67</v>
+      </c>
+      <c r="G844" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="845" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A845" t="s">
+        <v>985</v>
+      </c>
+      <c r="B845" t="s">
+        <v>986</v>
+      </c>
+      <c r="C845" t="s">
+        <v>722</v>
+      </c>
+      <c r="D845" t="s">
+        <v>64</v>
+      </c>
+      <c r="E845" t="s">
+        <v>65</v>
+      </c>
+      <c r="F845" t="s">
+        <v>87</v>
+      </c>
+      <c r="G845" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="846" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A846" t="s">
+        <v>987</v>
+      </c>
+      <c r="B846" t="s">
+        <v>988</v>
+      </c>
+      <c r="C846" t="s">
+        <v>736</v>
+      </c>
+      <c r="D846" t="s">
+        <v>64</v>
+      </c>
+      <c r="E846" t="s">
+        <v>67</v>
+      </c>
+      <c r="G846" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="847" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A847" t="s">
+        <v>989</v>
+      </c>
+      <c r="B847" t="s">
+        <v>990</v>
+      </c>
+      <c r="C847" t="s">
+        <v>719</v>
+      </c>
+      <c r="D847" t="s">
+        <v>64</v>
+      </c>
+      <c r="E847" t="s">
+        <v>67</v>
+      </c>
+      <c r="G847" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="848" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A848" t="s">
+        <v>991</v>
+      </c>
+      <c r="B848" t="s">
+        <v>992</v>
+      </c>
+      <c r="C848" t="s">
+        <v>722</v>
+      </c>
+      <c r="D848" t="s">
+        <v>64</v>
+      </c>
+      <c r="E848" t="s">
+        <v>67</v>
+      </c>
+      <c r="G848" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="849" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A849" t="s">
+        <v>993</v>
+      </c>
+      <c r="B849" t="s">
+        <v>994</v>
+      </c>
+      <c r="C849" t="s">
+        <v>722</v>
+      </c>
+      <c r="D849" t="s">
+        <v>64</v>
+      </c>
+      <c r="E849" t="s">
+        <v>65</v>
+      </c>
+      <c r="F849" t="s">
+        <v>995</v>
+      </c>
+      <c r="G849" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="850" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A850" t="s">
+        <v>993</v>
+      </c>
+      <c r="B850" t="s">
+        <v>994</v>
+      </c>
+      <c r="C850" t="s">
+        <v>722</v>
+      </c>
+      <c r="D850" t="s">
+        <v>113</v>
+      </c>
+      <c r="G850" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="851" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A851" t="s">
+        <v>996</v>
+      </c>
+      <c r="B851" t="s">
+        <v>997</v>
+      </c>
+      <c r="C851" t="s">
+        <v>719</v>
+      </c>
+      <c r="D851" t="s">
+        <v>64</v>
+      </c>
+      <c r="E851" t="s">
+        <v>67</v>
+      </c>
+      <c r="G851" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="852" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A852" t="s">
+        <v>998</v>
+      </c>
+      <c r="B852" t="s">
+        <v>999</v>
+      </c>
+      <c r="C852" t="s">
+        <v>719</v>
+      </c>
+      <c r="D852" t="s">
+        <v>64</v>
+      </c>
+      <c r="E852" t="s">
+        <v>67</v>
+      </c>
+      <c r="G852" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="853" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A853" t="s">
+        <v>998</v>
+      </c>
+      <c r="B853" t="s">
+        <v>999</v>
+      </c>
+      <c r="C853" t="s">
+        <v>719</v>
+      </c>
+      <c r="D853" t="s">
+        <v>235</v>
+      </c>
+      <c r="G853" s="3" t="s">
+        <v>1000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD3A9652-97F4-4C52-84AF-D2B00CD9E5D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45BAE97-9BC2-4A82-A4A1-37DAD1C6D5DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4387" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4628" uniqueCount="1065">
   <si>
     <t>AB</t>
   </si>
@@ -3042,6 +3042,198 @@
   </si>
   <si>
     <t>123.550, 123.450</t>
+  </si>
+  <si>
+    <t>Kerrobert</t>
+  </si>
+  <si>
+    <t>CJP2</t>
+  </si>
+  <si>
+    <t>Key Lake</t>
+  </si>
+  <si>
+    <t>CYKJ</t>
+  </si>
+  <si>
+    <t>Killarney Muni</t>
+  </si>
+  <si>
+    <t>CJS5</t>
+  </si>
+  <si>
+    <t>Kindersley Regional</t>
+  </si>
+  <si>
+    <t>CYKY</t>
+  </si>
+  <si>
+    <t>Kipling</t>
+  </si>
+  <si>
+    <t>CKD5</t>
+  </si>
+  <si>
+    <t>Kisbey / Brigden Field</t>
+  </si>
+  <si>
+    <t>CBR3</t>
+  </si>
+  <si>
+    <t>Knee Lake</t>
+  </si>
+  <si>
+    <t>CJT3</t>
+  </si>
+  <si>
+    <t>ltd hrs May 15-Sep 1 O/T tfc</t>
+  </si>
+  <si>
+    <t>Kyle</t>
+  </si>
+  <si>
+    <t>CJB8</t>
+  </si>
+  <si>
+    <t>Lac Brochet</t>
+  </si>
+  <si>
+    <t>CZWH</t>
+  </si>
+  <si>
+    <t>Lac Du Bonnet</t>
+  </si>
+  <si>
+    <t>CYAX</t>
+  </si>
+  <si>
+    <t>La Loche</t>
+  </si>
+  <si>
+    <t>CJL4</t>
+  </si>
+  <si>
+    <t>Lampman</t>
+  </si>
+  <si>
+    <t>CJQ2</t>
+  </si>
+  <si>
+    <t>Lampman / Spitfire Air</t>
+  </si>
+  <si>
+    <t>CSF8</t>
+  </si>
+  <si>
+    <t>Lanigan</t>
+  </si>
+  <si>
+    <t>CKC6</t>
+  </si>
+  <si>
+    <t>La Ronge (Barber Field)</t>
+  </si>
+  <si>
+    <t>CYVC</t>
+  </si>
+  <si>
+    <t>Laurie River</t>
+  </si>
+  <si>
+    <t>CJC8</t>
+  </si>
+  <si>
+    <t>Leaf Rapids</t>
+  </si>
+  <si>
+    <t>CYLR</t>
+  </si>
+  <si>
+    <t>Leask</t>
+  </si>
+  <si>
+    <t>CJH8</t>
+  </si>
+  <si>
+    <t>Lemberg</t>
+  </si>
+  <si>
+    <t>CKJ9</t>
+  </si>
+  <si>
+    <t>Little Bear Lake</t>
+  </si>
+  <si>
+    <t>CKL6</t>
+  </si>
+  <si>
+    <t>Little Churchill River</t>
+  </si>
+  <si>
+    <t>CJN7</t>
+  </si>
+  <si>
+    <t>Little Grand Rapids</t>
+  </si>
+  <si>
+    <t>CZGR</t>
+  </si>
+  <si>
+    <t>Lloydminster / Fort Pitt Farms</t>
+  </si>
+  <si>
+    <t>CFP3</t>
+  </si>
+  <si>
+    <t>Loon Creek Airfield</t>
+  </si>
+  <si>
+    <t>CLC4</t>
+  </si>
+  <si>
+    <t>Loon Lake</t>
+  </si>
+  <si>
+    <t>CJW3</t>
+  </si>
+  <si>
+    <t>Lucky Lake</t>
+  </si>
+  <si>
+    <t>CKQ5</t>
+  </si>
+  <si>
+    <t>Lumsden (Colhoun)</t>
+  </si>
+  <si>
+    <t>CKH8</t>
+  </si>
+  <si>
+    <t>Lumsden Colhoun tfc</t>
+  </si>
+  <si>
+    <t>Lundar</t>
+  </si>
+  <si>
+    <t>CKR4</t>
+  </si>
+  <si>
+    <t>Luseland</t>
+  </si>
+  <si>
+    <t>CJR2</t>
+  </si>
+  <si>
+    <t>Lynn Lake</t>
+  </si>
+  <si>
+    <t>CYYL</t>
+  </si>
+  <si>
+    <t>MacDonald</t>
+  </si>
+  <si>
+    <t>CJU3</t>
   </si>
 </sst>
 </file>
@@ -3431,7 +3623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G853"/>
+  <dimension ref="A1:G901"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -20663,6 +20855,969 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="854" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A854" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B854" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C854" t="s">
+        <v>719</v>
+      </c>
+      <c r="D854" t="s">
+        <v>64</v>
+      </c>
+      <c r="E854" t="s">
+        <v>67</v>
+      </c>
+      <c r="G854" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="855" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A855" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B855" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C855" t="s">
+        <v>719</v>
+      </c>
+      <c r="D855" t="s">
+        <v>300</v>
+      </c>
+      <c r="E855" t="s">
+        <v>386</v>
+      </c>
+      <c r="G855" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="856" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A856" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B856" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C856" t="s">
+        <v>719</v>
+      </c>
+      <c r="D856" t="s">
+        <v>300</v>
+      </c>
+      <c r="E856" t="s">
+        <v>69</v>
+      </c>
+      <c r="G856" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="857" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A857" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B857" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C857" t="s">
+        <v>719</v>
+      </c>
+      <c r="D857" t="s">
+        <v>64</v>
+      </c>
+      <c r="E857" t="s">
+        <v>65</v>
+      </c>
+      <c r="F857" t="s">
+        <v>87</v>
+      </c>
+      <c r="G857" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="858" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A858" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B858" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C858" t="s">
+        <v>719</v>
+      </c>
+      <c r="D858" t="s">
+        <v>235</v>
+      </c>
+      <c r="E858" t="s">
+        <v>810</v>
+      </c>
+      <c r="G858" s="3">
+        <v>122.875</v>
+      </c>
+    </row>
+    <row r="859" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A859" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B859" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C859" t="s">
+        <v>719</v>
+      </c>
+      <c r="D859" t="s">
+        <v>2</v>
+      </c>
+      <c r="G859" s="3">
+        <v>127.7</v>
+      </c>
+    </row>
+    <row r="860" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A860" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B860" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C860" t="s">
+        <v>722</v>
+      </c>
+      <c r="D860" t="s">
+        <v>64</v>
+      </c>
+      <c r="E860" t="s">
+        <v>67</v>
+      </c>
+      <c r="G860" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="861" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A861" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B861" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C861" t="s">
+        <v>719</v>
+      </c>
+      <c r="D861" t="s">
+        <v>74</v>
+      </c>
+      <c r="E861" t="s">
+        <v>386</v>
+      </c>
+      <c r="G861" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="862" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A862" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B862" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C862" t="s">
+        <v>719</v>
+      </c>
+      <c r="D862" t="s">
+        <v>74</v>
+      </c>
+      <c r="E862" t="s">
+        <v>69</v>
+      </c>
+      <c r="G862" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="863" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A863" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B863" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C863" t="s">
+        <v>719</v>
+      </c>
+      <c r="D863" t="s">
+        <v>64</v>
+      </c>
+      <c r="E863" t="s">
+        <v>65</v>
+      </c>
+      <c r="F863" t="s">
+        <v>87</v>
+      </c>
+      <c r="G863" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="864" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A864" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B864" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C864" t="s">
+        <v>719</v>
+      </c>
+      <c r="D864" t="s">
+        <v>64</v>
+      </c>
+      <c r="E864" t="s">
+        <v>67</v>
+      </c>
+      <c r="G864" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="865" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A865" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B865" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C865" t="s">
+        <v>719</v>
+      </c>
+      <c r="D865" t="s">
+        <v>64</v>
+      </c>
+      <c r="E865" t="s">
+        <v>67</v>
+      </c>
+      <c r="G865" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="866" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A866" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B866" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C866" t="s">
+        <v>722</v>
+      </c>
+      <c r="D866" t="s">
+        <v>64</v>
+      </c>
+      <c r="E866" t="s">
+        <v>65</v>
+      </c>
+      <c r="F866" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G866" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="867" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A867" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B867" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C867" t="s">
+        <v>719</v>
+      </c>
+      <c r="D867" t="s">
+        <v>64</v>
+      </c>
+      <c r="E867" t="s">
+        <v>67</v>
+      </c>
+      <c r="G867" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="868" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A868" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B868" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C868" t="s">
+        <v>722</v>
+      </c>
+      <c r="D868" t="s">
+        <v>64</v>
+      </c>
+      <c r="E868" t="s">
+        <v>65</v>
+      </c>
+      <c r="F868" t="s">
+        <v>87</v>
+      </c>
+      <c r="G868" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="869" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A869" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B869" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C869" t="s">
+        <v>722</v>
+      </c>
+      <c r="D869" t="s">
+        <v>113</v>
+      </c>
+      <c r="G869" s="3">
+        <v>122.125</v>
+      </c>
+    </row>
+    <row r="870" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A870" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B870" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C870" t="s">
+        <v>722</v>
+      </c>
+      <c r="D870" t="s">
+        <v>64</v>
+      </c>
+      <c r="E870" t="s">
+        <v>67</v>
+      </c>
+      <c r="G870" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="871" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A871" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B871" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C871" t="s">
+        <v>719</v>
+      </c>
+      <c r="D871" t="s">
+        <v>64</v>
+      </c>
+      <c r="E871" t="s">
+        <v>67</v>
+      </c>
+      <c r="G871" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="872" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A872" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B872" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C872" t="s">
+        <v>719</v>
+      </c>
+      <c r="D872" t="s">
+        <v>113</v>
+      </c>
+      <c r="G872" s="3">
+        <v>122.97499999999999</v>
+      </c>
+    </row>
+    <row r="873" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A873" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B873" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C873" t="s">
+        <v>719</v>
+      </c>
+      <c r="D873" t="s">
+        <v>64</v>
+      </c>
+      <c r="E873" t="s">
+        <v>67</v>
+      </c>
+      <c r="G873" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="874" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A874" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B874" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C874" t="s">
+        <v>719</v>
+      </c>
+      <c r="D874" t="s">
+        <v>64</v>
+      </c>
+      <c r="E874" t="s">
+        <v>67</v>
+      </c>
+      <c r="G874" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="875" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A875" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B875" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C875" t="s">
+        <v>719</v>
+      </c>
+      <c r="D875" t="s">
+        <v>64</v>
+      </c>
+      <c r="E875" t="s">
+        <v>67</v>
+      </c>
+      <c r="G875" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="876" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A876" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B876" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C876" t="s">
+        <v>719</v>
+      </c>
+      <c r="D876" t="s">
+        <v>11</v>
+      </c>
+      <c r="G876" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="877" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A877" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B877" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C877" t="s">
+        <v>719</v>
+      </c>
+      <c r="D877" t="s">
+        <v>74</v>
+      </c>
+      <c r="E877" t="s">
+        <v>386</v>
+      </c>
+      <c r="G877" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="878" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A878" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B878" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C878" t="s">
+        <v>719</v>
+      </c>
+      <c r="D878" t="s">
+        <v>74</v>
+      </c>
+      <c r="E878" t="s">
+        <v>69</v>
+      </c>
+      <c r="G878" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="879" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A879" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B879" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C879" t="s">
+        <v>719</v>
+      </c>
+      <c r="D879" t="s">
+        <v>41</v>
+      </c>
+      <c r="G879" s="3">
+        <v>128.25</v>
+      </c>
+    </row>
+    <row r="880" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A880" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B880" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C880" t="s">
+        <v>719</v>
+      </c>
+      <c r="D880" t="s">
+        <v>12</v>
+      </c>
+      <c r="E880" t="s">
+        <v>100</v>
+      </c>
+      <c r="G880" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="881" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A881" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B881" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C881" t="s">
+        <v>719</v>
+      </c>
+      <c r="D881" t="s">
+        <v>76</v>
+      </c>
+      <c r="E881" t="s">
+        <v>200</v>
+      </c>
+      <c r="G881" s="3">
+        <v>126.4</v>
+      </c>
+    </row>
+    <row r="882" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A882" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B882" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C882" t="s">
+        <v>722</v>
+      </c>
+      <c r="D882" t="s">
+        <v>64</v>
+      </c>
+      <c r="E882" t="s">
+        <v>67</v>
+      </c>
+      <c r="G882" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="883" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A883" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B883" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C883" t="s">
+        <v>722</v>
+      </c>
+      <c r="D883" t="s">
+        <v>64</v>
+      </c>
+      <c r="E883" t="s">
+        <v>67</v>
+      </c>
+      <c r="G883" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="884" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A884" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B884" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C884" t="s">
+        <v>719</v>
+      </c>
+      <c r="D884" t="s">
+        <v>64</v>
+      </c>
+      <c r="E884" t="s">
+        <v>67</v>
+      </c>
+      <c r="G884" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="885" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A885" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B885" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C885" t="s">
+        <v>719</v>
+      </c>
+      <c r="D885" t="s">
+        <v>64</v>
+      </c>
+      <c r="E885" t="s">
+        <v>67</v>
+      </c>
+      <c r="G885" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="886" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A886" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B886" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C886" t="s">
+        <v>719</v>
+      </c>
+      <c r="D886" t="s">
+        <v>64</v>
+      </c>
+      <c r="E886" t="s">
+        <v>67</v>
+      </c>
+      <c r="G886" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="887" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A887" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B887" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C887" t="s">
+        <v>722</v>
+      </c>
+      <c r="D887" t="s">
+        <v>64</v>
+      </c>
+      <c r="E887" t="s">
+        <v>65</v>
+      </c>
+      <c r="F887" t="s">
+        <v>87</v>
+      </c>
+      <c r="G887" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="888" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A888" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B888" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C888" t="s">
+        <v>722</v>
+      </c>
+      <c r="D888" t="s">
+        <v>64</v>
+      </c>
+      <c r="E888" t="s">
+        <v>65</v>
+      </c>
+      <c r="F888" t="s">
+        <v>87</v>
+      </c>
+      <c r="G888" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="889" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A889" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B889" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C889" t="s">
+        <v>719</v>
+      </c>
+      <c r="D889" t="s">
+        <v>64</v>
+      </c>
+      <c r="E889" t="s">
+        <v>67</v>
+      </c>
+      <c r="G889" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="890" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A890" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B890" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C890" t="s">
+        <v>719</v>
+      </c>
+      <c r="D890" t="s">
+        <v>64</v>
+      </c>
+      <c r="E890" t="s">
+        <v>67</v>
+      </c>
+      <c r="G890" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="891" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A891" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B891" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C891" t="s">
+        <v>719</v>
+      </c>
+      <c r="D891" t="s">
+        <v>64</v>
+      </c>
+      <c r="E891" t="s">
+        <v>67</v>
+      </c>
+      <c r="G891" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="892" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A892" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B892" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C892" t="s">
+        <v>719</v>
+      </c>
+      <c r="D892" t="s">
+        <v>64</v>
+      </c>
+      <c r="E892" t="s">
+        <v>67</v>
+      </c>
+      <c r="G892" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="893" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A893" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B893" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C893" t="s">
+        <v>719</v>
+      </c>
+      <c r="D893" t="s">
+        <v>64</v>
+      </c>
+      <c r="E893" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G893" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="894" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A894" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B894" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C894" t="s">
+        <v>722</v>
+      </c>
+      <c r="D894" t="s">
+        <v>64</v>
+      </c>
+      <c r="E894" t="s">
+        <v>67</v>
+      </c>
+      <c r="G894" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="895" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A895" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B895" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C895" t="s">
+        <v>719</v>
+      </c>
+      <c r="D895" t="s">
+        <v>64</v>
+      </c>
+      <c r="E895" t="s">
+        <v>67</v>
+      </c>
+      <c r="G895" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="896" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A896" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B896" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C896" t="s">
+        <v>722</v>
+      </c>
+      <c r="D896" t="s">
+        <v>74</v>
+      </c>
+      <c r="E896" t="s">
+        <v>386</v>
+      </c>
+      <c r="G896" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="897" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A897" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B897" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C897" t="s">
+        <v>722</v>
+      </c>
+      <c r="D897" t="s">
+        <v>74</v>
+      </c>
+      <c r="E897" t="s">
+        <v>69</v>
+      </c>
+      <c r="G897" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="898" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A898" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B898" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C898" t="s">
+        <v>722</v>
+      </c>
+      <c r="D898" t="s">
+        <v>12</v>
+      </c>
+      <c r="E898" t="s">
+        <v>65</v>
+      </c>
+      <c r="F898" t="s">
+        <v>87</v>
+      </c>
+      <c r="G898" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="899" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A899" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B899" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C899" t="s">
+        <v>722</v>
+      </c>
+      <c r="D899" t="s">
+        <v>76</v>
+      </c>
+      <c r="E899" t="s">
+        <v>200</v>
+      </c>
+      <c r="G899" s="3">
+        <v>135.05000000000001</v>
+      </c>
+    </row>
+    <row r="900" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A900" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B900" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C900" t="s">
+        <v>722</v>
+      </c>
+      <c r="D900" t="s">
+        <v>2</v>
+      </c>
+      <c r="G900" s="3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="901" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A901" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B901" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C901" t="s">
+        <v>722</v>
+      </c>
+      <c r="D901" t="s">
+        <v>64</v>
+      </c>
+      <c r="E901" t="s">
+        <v>67</v>
+      </c>
+      <c r="G901" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45BAE97-9BC2-4A82-A4A1-37DAD1C6D5DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03AA406E-AB04-4D71-AD62-0DC2A88CC050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4628" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4732" uniqueCount="1098">
   <si>
     <t>AB</t>
   </si>
@@ -3234,6 +3234,105 @@
   </si>
   <si>
     <t>CJU3</t>
+  </si>
+  <si>
+    <t>MacGregor Airfield</t>
+  </si>
+  <si>
+    <t>CKF6</t>
+  </si>
+  <si>
+    <t>Macklin</t>
+  </si>
+  <si>
+    <t>CJJ8</t>
+  </si>
+  <si>
+    <t>Maidstone</t>
+  </si>
+  <si>
+    <t>CJH3</t>
+  </si>
+  <si>
+    <t>Makkovik</t>
+  </si>
+  <si>
+    <t>CYFT</t>
+  </si>
+  <si>
+    <t>Malcolm Island</t>
+  </si>
+  <si>
+    <t>CJS2</t>
+  </si>
+  <si>
+    <t>Manitou</t>
+  </si>
+  <si>
+    <t>CKG5</t>
+  </si>
+  <si>
+    <t>Maple Creek</t>
+  </si>
+  <si>
+    <t>CJQ4</t>
+  </si>
+  <si>
+    <t>Marcelin / Clayton Air</t>
+  </si>
+  <si>
+    <t>CMC4</t>
+  </si>
+  <si>
+    <t>123.450, 123.550</t>
+  </si>
+  <si>
+    <t>Maryfield</t>
+  </si>
+  <si>
+    <t>CJQ8</t>
+  </si>
+  <si>
+    <t>Mary's Harbour</t>
+  </si>
+  <si>
+    <t>CYMH</t>
+  </si>
+  <si>
+    <t>McArthur River</t>
+  </si>
+  <si>
+    <t>CKQ8</t>
+  </si>
+  <si>
+    <t>McCreary</t>
+  </si>
+  <si>
+    <t>CJR8</t>
+  </si>
+  <si>
+    <t>Meadow Lake</t>
+  </si>
+  <si>
+    <t>CYLJ</t>
+  </si>
+  <si>
+    <t>Melfort (Miller Field)</t>
+  </si>
+  <si>
+    <t>CJZ3</t>
+  </si>
+  <si>
+    <t>Melita</t>
+  </si>
+  <si>
+    <t>CJT5</t>
+  </si>
+  <si>
+    <t>Minnedosa</t>
+  </si>
+  <si>
+    <t>CJU5</t>
   </si>
 </sst>
 </file>
@@ -3623,7 +3722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G901"/>
+  <dimension ref="A1:G921"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -21818,6 +21917,409 @@
         <v>123.2</v>
       </c>
     </row>
+    <row r="902" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A902" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B902" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C902" t="s">
+        <v>722</v>
+      </c>
+      <c r="D902" t="s">
+        <v>64</v>
+      </c>
+      <c r="E902" t="s">
+        <v>67</v>
+      </c>
+      <c r="G902" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="903" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A903" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B903" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C903" t="s">
+        <v>719</v>
+      </c>
+      <c r="D903" t="s">
+        <v>64</v>
+      </c>
+      <c r="E903" t="s">
+        <v>67</v>
+      </c>
+      <c r="G903" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="904" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A904" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B904" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C904" t="s">
+        <v>719</v>
+      </c>
+      <c r="D904" t="s">
+        <v>64</v>
+      </c>
+      <c r="E904" t="s">
+        <v>67</v>
+      </c>
+      <c r="G904" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="905" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A905" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B905" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C905" t="s">
+        <v>741</v>
+      </c>
+      <c r="D905" t="s">
+        <v>64</v>
+      </c>
+      <c r="E905" t="s">
+        <v>67</v>
+      </c>
+      <c r="G905" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="906" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A906" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B906" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C906" t="s">
+        <v>719</v>
+      </c>
+      <c r="D906" t="s">
+        <v>64</v>
+      </c>
+      <c r="E906" t="s">
+        <v>65</v>
+      </c>
+      <c r="F906" t="s">
+        <v>87</v>
+      </c>
+      <c r="G906" s="3">
+        <v>128.85</v>
+      </c>
+    </row>
+    <row r="907" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A907" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B907" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C907" t="s">
+        <v>722</v>
+      </c>
+      <c r="D907" t="s">
+        <v>64</v>
+      </c>
+      <c r="E907" t="s">
+        <v>67</v>
+      </c>
+      <c r="G907" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="908" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A908" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B908" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C908" t="s">
+        <v>719</v>
+      </c>
+      <c r="D908" t="s">
+        <v>64</v>
+      </c>
+      <c r="E908" t="s">
+        <v>65</v>
+      </c>
+      <c r="F908" t="s">
+        <v>87</v>
+      </c>
+      <c r="G908" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="909" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A909" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B909" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C909" t="s">
+        <v>719</v>
+      </c>
+      <c r="D909" t="s">
+        <v>64</v>
+      </c>
+      <c r="E909" t="s">
+        <v>67</v>
+      </c>
+      <c r="G909" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="910" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A910" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B910" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C910" t="s">
+        <v>719</v>
+      </c>
+      <c r="D910" t="s">
+        <v>235</v>
+      </c>
+      <c r="G910" s="3" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="911" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A911" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B911" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C911" t="s">
+        <v>719</v>
+      </c>
+      <c r="D911" t="s">
+        <v>64</v>
+      </c>
+      <c r="E911" t="s">
+        <v>65</v>
+      </c>
+      <c r="G911" s="3">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="912" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A912" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B912" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C912" t="s">
+        <v>741</v>
+      </c>
+      <c r="D912" t="s">
+        <v>64</v>
+      </c>
+      <c r="E912" t="s">
+        <v>67</v>
+      </c>
+      <c r="G912" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="913" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A913" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B913" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C913" t="s">
+        <v>741</v>
+      </c>
+      <c r="D913" t="s">
+        <v>2</v>
+      </c>
+      <c r="G913" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="914" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A914" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B914" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C914" t="s">
+        <v>719</v>
+      </c>
+      <c r="D914" t="s">
+        <v>64</v>
+      </c>
+      <c r="E914" t="s">
+        <v>65</v>
+      </c>
+      <c r="F914" t="s">
+        <v>87</v>
+      </c>
+      <c r="G914" s="3">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="915" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A915" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B915" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C915" t="s">
+        <v>719</v>
+      </c>
+      <c r="D915" t="s">
+        <v>235</v>
+      </c>
+      <c r="E915" t="s">
+        <v>810</v>
+      </c>
+      <c r="G915" s="3">
+        <v>122.875</v>
+      </c>
+    </row>
+    <row r="916" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A916" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B916" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C916" t="s">
+        <v>719</v>
+      </c>
+      <c r="D916" t="s">
+        <v>113</v>
+      </c>
+      <c r="G916" s="3">
+        <v>122.27500000000001</v>
+      </c>
+    </row>
+    <row r="917" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A917" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B917" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C917" t="s">
+        <v>722</v>
+      </c>
+      <c r="D917" t="s">
+        <v>64</v>
+      </c>
+      <c r="E917" t="s">
+        <v>67</v>
+      </c>
+      <c r="G917" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="918" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A918" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B918" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C918" t="s">
+        <v>719</v>
+      </c>
+      <c r="D918" t="s">
+        <v>64</v>
+      </c>
+      <c r="E918" t="s">
+        <v>67</v>
+      </c>
+      <c r="G918" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="919" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A919" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B919" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C919" t="s">
+        <v>719</v>
+      </c>
+      <c r="D919" t="s">
+        <v>64</v>
+      </c>
+      <c r="E919" t="s">
+        <v>65</v>
+      </c>
+      <c r="F919" t="s">
+        <v>87</v>
+      </c>
+      <c r="G919" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="920" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A920" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B920" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C920" t="s">
+        <v>722</v>
+      </c>
+      <c r="D920" t="s">
+        <v>64</v>
+      </c>
+      <c r="E920" t="s">
+        <v>67</v>
+      </c>
+      <c r="G920" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="921" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A921" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B921" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C921" t="s">
+        <v>722</v>
+      </c>
+      <c r="D921" t="s">
+        <v>64</v>
+      </c>
+      <c r="E921" t="s">
+        <v>67</v>
+      </c>
+      <c r="G921" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03AA406E-AB04-4D71-AD62-0DC2A88CC050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600E26E5-C34F-4145-8C11-1B3B1C7C8123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4732" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4893" uniqueCount="1141">
   <si>
     <t>AB</t>
   </si>
@@ -3333,6 +3333,135 @@
   </si>
   <si>
     <t>CJU5</t>
+  </si>
+  <si>
+    <t>Miramichi</t>
+  </si>
+  <si>
+    <t>CYCH</t>
+  </si>
+  <si>
+    <t>11-23Z‡ ltd hrs O/T tfc</t>
+  </si>
+  <si>
+    <t>Misaw Lake</t>
+  </si>
+  <si>
+    <t>CAM2</t>
+  </si>
+  <si>
+    <t>Molson Lake</t>
+  </si>
+  <si>
+    <t>CKJ8</t>
+  </si>
+  <si>
+    <t>Moncton / Greater Moncton Romeo Leblanc Intl</t>
+  </si>
+  <si>
+    <t>CYQM</t>
+  </si>
+  <si>
+    <t>Apron VIII</t>
+  </si>
+  <si>
+    <t>120.800, 236.600</t>
+  </si>
+  <si>
+    <t>124.400, 127.125, 132.200</t>
+  </si>
+  <si>
+    <t>Moncton / McEwen</t>
+  </si>
+  <si>
+    <t>CCG4</t>
+  </si>
+  <si>
+    <t>Moncton</t>
+  </si>
+  <si>
+    <t>Moose Jaw / Air Vice Marshal C. M. McEwen</t>
+  </si>
+  <si>
+    <t>CYMJ</t>
+  </si>
+  <si>
+    <t>131.300, 257.800</t>
+  </si>
+  <si>
+    <t>135.300, 234.400</t>
+  </si>
+  <si>
+    <t>126.200, 295.600, 310.800, 322.600</t>
+  </si>
+  <si>
+    <t>119.000, 227.600, 342.900</t>
+  </si>
+  <si>
+    <t>119.000, 129.100, 134.1x</t>
+  </si>
+  <si>
+    <t>14-0030Z Mon-Fri (fr 1st Mon Nov to 3rd Mon Feb 1430-01Z Mon-Fri), A/D frequently clsd Sat &amp; Sun.</t>
+  </si>
+  <si>
+    <t>COMM</t>
+  </si>
+  <si>
+    <t>Moose Jaw Muni</t>
+  </si>
+  <si>
+    <t>CJS4</t>
+  </si>
+  <si>
+    <t>Moosomin / Marshall McLeod Field</t>
+  </si>
+  <si>
+    <t>CJB5</t>
+  </si>
+  <si>
+    <t>Morden Regional</t>
+  </si>
+  <si>
+    <t>CJA3</t>
+  </si>
+  <si>
+    <t>Nain</t>
+  </si>
+  <si>
+    <t>CYDP</t>
+  </si>
+  <si>
+    <t>Natuashish</t>
+  </si>
+  <si>
+    <t>CNH2</t>
+  </si>
+  <si>
+    <t>Neepawa</t>
+  </si>
+  <si>
+    <t>CJV5</t>
+  </si>
+  <si>
+    <t>Neilburg</t>
+  </si>
+  <si>
+    <t>CJV2</t>
+  </si>
+  <si>
+    <t>Nejanilini Lake</t>
+  </si>
+  <si>
+    <t>CYNN</t>
+  </si>
+  <si>
+    <t>ltd hrs Jun 30-Oct 30 O/T tfc</t>
+  </si>
+  <si>
+    <t>Nekweaga Bay</t>
+  </si>
+  <si>
+    <t>CKN 8</t>
   </si>
 </sst>
 </file>
@@ -3722,7 +3851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G921"/>
+  <dimension ref="A1:G1128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -22320,6 +22449,1144 @@
         <v>123.2</v>
       </c>
     </row>
+    <row r="922" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A922" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B922" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C922" t="s">
+        <v>736</v>
+      </c>
+      <c r="D922" t="s">
+        <v>64</v>
+      </c>
+      <c r="E922" t="s">
+        <v>65</v>
+      </c>
+      <c r="F922" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G922" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="923" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A923" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B923" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C923" t="s">
+        <v>719</v>
+      </c>
+      <c r="D923" t="s">
+        <v>64</v>
+      </c>
+      <c r="E923" t="s">
+        <v>67</v>
+      </c>
+      <c r="G923" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="924" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A924" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B924" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C924" t="s">
+        <v>722</v>
+      </c>
+      <c r="D924" t="s">
+        <v>64</v>
+      </c>
+      <c r="E924" t="s">
+        <v>67</v>
+      </c>
+      <c r="G924" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="925" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A925" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B925" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C925" t="s">
+        <v>736</v>
+      </c>
+      <c r="D925" t="s">
+        <v>74</v>
+      </c>
+      <c r="E925" t="s">
+        <v>275</v>
+      </c>
+      <c r="G925" s="3">
+        <v>122.5</v>
+      </c>
+    </row>
+    <row r="926" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A926" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B926" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C926" t="s">
+        <v>736</v>
+      </c>
+      <c r="D926" t="s">
+        <v>74</v>
+      </c>
+      <c r="E926" t="s">
+        <v>69</v>
+      </c>
+      <c r="G926" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="927" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A927" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B927" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C927" t="s">
+        <v>736</v>
+      </c>
+      <c r="D927" t="s">
+        <v>41</v>
+      </c>
+      <c r="G927" s="3">
+        <v>128.65</v>
+      </c>
+    </row>
+    <row r="928" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A928" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B928" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C928" t="s">
+        <v>736</v>
+      </c>
+      <c r="D928" t="s">
+        <v>165</v>
+      </c>
+      <c r="E928" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G928" s="3">
+        <v>122.075</v>
+      </c>
+    </row>
+    <row r="929" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A929" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B929" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C929" t="s">
+        <v>736</v>
+      </c>
+      <c r="D929" t="s">
+        <v>14</v>
+      </c>
+      <c r="G929" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="930" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A930" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B930" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C930" t="s">
+        <v>736</v>
+      </c>
+      <c r="D930" t="s">
+        <v>15</v>
+      </c>
+      <c r="G930" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="931" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A931" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B931" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C931" t="s">
+        <v>736</v>
+      </c>
+      <c r="D931" t="s">
+        <v>16</v>
+      </c>
+      <c r="G931" s="3">
+        <v>124.4</v>
+      </c>
+    </row>
+    <row r="932" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A932" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B932" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C932" t="s">
+        <v>736</v>
+      </c>
+      <c r="D932" t="s">
+        <v>17</v>
+      </c>
+      <c r="G932" s="3">
+        <v>124.4</v>
+      </c>
+    </row>
+    <row r="933" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A933" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B933" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C933" t="s">
+        <v>736</v>
+      </c>
+      <c r="D933" t="s">
+        <v>76</v>
+      </c>
+      <c r="G933" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="934" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A934" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B934" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C934" t="s">
+        <v>736</v>
+      </c>
+      <c r="D934" t="s">
+        <v>15</v>
+      </c>
+      <c r="E934" t="s">
+        <v>1112</v>
+      </c>
+      <c r="G934" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="935" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A935" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B935" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C935" t="s">
+        <v>719</v>
+      </c>
+      <c r="D935" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E935" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="936" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A936" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B936" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C936" t="s">
+        <v>719</v>
+      </c>
+      <c r="D936" t="s">
+        <v>41</v>
+      </c>
+      <c r="G936" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="937" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A937" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B937" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C937" t="s">
+        <v>719</v>
+      </c>
+      <c r="D937" t="s">
+        <v>146</v>
+      </c>
+      <c r="G937" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="938" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A938" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B938" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C938" t="s">
+        <v>719</v>
+      </c>
+      <c r="D938" t="s">
+        <v>14</v>
+      </c>
+      <c r="G938" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="939" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A939" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B939" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C939" t="s">
+        <v>719</v>
+      </c>
+      <c r="D939" t="s">
+        <v>15</v>
+      </c>
+      <c r="G939" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="940" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A940" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B940" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C940" t="s">
+        <v>719</v>
+      </c>
+      <c r="D940" t="s">
+        <v>44</v>
+      </c>
+      <c r="G940" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="941" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A941" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B941" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C941" t="s">
+        <v>719</v>
+      </c>
+      <c r="D941" t="s">
+        <v>16</v>
+      </c>
+      <c r="G941" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="942" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A942" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B942" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C942" t="s">
+        <v>719</v>
+      </c>
+      <c r="D942" t="s">
+        <v>17</v>
+      </c>
+      <c r="G942" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="943" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A943" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B943" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C943" t="s">
+        <v>719</v>
+      </c>
+      <c r="D943" t="s">
+        <v>190</v>
+      </c>
+      <c r="F943" t="s">
+        <v>634</v>
+      </c>
+      <c r="G943" s="3">
+        <v>344.6</v>
+      </c>
+    </row>
+    <row r="944" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A944" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B944" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C944" t="s">
+        <v>719</v>
+      </c>
+      <c r="D944" t="s">
+        <v>64</v>
+      </c>
+      <c r="E944" t="s">
+        <v>65</v>
+      </c>
+      <c r="F944" t="s">
+        <v>87</v>
+      </c>
+      <c r="G944" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="945" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A945" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B945" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C945" t="s">
+        <v>719</v>
+      </c>
+      <c r="D945" t="s">
+        <v>64</v>
+      </c>
+      <c r="E945" t="s">
+        <v>65</v>
+      </c>
+      <c r="F945" t="s">
+        <v>87</v>
+      </c>
+      <c r="G945" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="946" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A946" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B946" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C946" t="s">
+        <v>722</v>
+      </c>
+      <c r="D946" t="s">
+        <v>64</v>
+      </c>
+      <c r="E946" t="s">
+        <v>67</v>
+      </c>
+      <c r="G946" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="947" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A947" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B947" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C947" t="s">
+        <v>741</v>
+      </c>
+      <c r="D947" t="s">
+        <v>74</v>
+      </c>
+      <c r="E947" t="s">
+        <v>275</v>
+      </c>
+      <c r="G947" s="3">
+        <v>123.65</v>
+      </c>
+    </row>
+    <row r="948" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A948" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B948" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C948" t="s">
+        <v>741</v>
+      </c>
+      <c r="D948" t="s">
+        <v>64</v>
+      </c>
+      <c r="E948" t="s">
+        <v>67</v>
+      </c>
+      <c r="G948" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="949" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A949" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B949" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C949" t="s">
+        <v>741</v>
+      </c>
+      <c r="D949" t="s">
+        <v>64</v>
+      </c>
+      <c r="E949" t="s">
+        <v>67</v>
+      </c>
+      <c r="G949" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="950" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A950" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B950" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C950" t="s">
+        <v>722</v>
+      </c>
+      <c r="D950" t="s">
+        <v>64</v>
+      </c>
+      <c r="E950" t="s">
+        <v>65</v>
+      </c>
+      <c r="F950" t="s">
+        <v>87</v>
+      </c>
+      <c r="G950" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="951" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A951" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B951" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C951" t="s">
+        <v>719</v>
+      </c>
+      <c r="D951" t="s">
+        <v>64</v>
+      </c>
+      <c r="E951" t="s">
+        <v>67</v>
+      </c>
+      <c r="G951" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="952" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A952" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B952" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C952" t="s">
+        <v>722</v>
+      </c>
+      <c r="D952" t="s">
+        <v>64</v>
+      </c>
+      <c r="E952" t="s">
+        <v>65</v>
+      </c>
+      <c r="F952" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G952" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="953" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A953" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B953" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C953" t="s">
+        <v>719</v>
+      </c>
+      <c r="D953" t="s">
+        <v>64</v>
+      </c>
+      <c r="E953" t="s">
+        <v>67</v>
+      </c>
+      <c r="G953" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="954" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G954" s="3"/>
+    </row>
+    <row r="955" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G955" s="3"/>
+    </row>
+    <row r="956" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G956" s="3"/>
+    </row>
+    <row r="957" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G957" s="3"/>
+    </row>
+    <row r="958" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G958" s="3"/>
+    </row>
+    <row r="959" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G959" s="3"/>
+    </row>
+    <row r="960" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G960" s="3"/>
+    </row>
+    <row r="961" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G961" s="3"/>
+    </row>
+    <row r="962" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G962" s="3"/>
+    </row>
+    <row r="963" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G963" s="3"/>
+    </row>
+    <row r="964" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G964" s="3"/>
+    </row>
+    <row r="965" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G965" s="3"/>
+    </row>
+    <row r="966" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G966" s="3"/>
+    </row>
+    <row r="967" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G967" s="3"/>
+    </row>
+    <row r="968" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G968" s="3"/>
+    </row>
+    <row r="969" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G969" s="3"/>
+    </row>
+    <row r="970" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G970" s="3"/>
+    </row>
+    <row r="971" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G971" s="3"/>
+    </row>
+    <row r="972" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G972" s="3"/>
+    </row>
+    <row r="973" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G973" s="3"/>
+    </row>
+    <row r="974" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G974" s="3"/>
+    </row>
+    <row r="975" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G975" s="3"/>
+    </row>
+    <row r="976" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G976" s="3"/>
+    </row>
+    <row r="977" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G977" s="3"/>
+    </row>
+    <row r="978" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G978" s="3"/>
+    </row>
+    <row r="979" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G979" s="3"/>
+    </row>
+    <row r="980" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G980" s="3"/>
+    </row>
+    <row r="981" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G981" s="3"/>
+    </row>
+    <row r="982" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G982" s="3"/>
+    </row>
+    <row r="983" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G983" s="3"/>
+    </row>
+    <row r="984" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G984" s="3"/>
+    </row>
+    <row r="985" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G985" s="3"/>
+    </row>
+    <row r="986" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G986" s="3"/>
+    </row>
+    <row r="987" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G987" s="3"/>
+    </row>
+    <row r="988" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G988" s="3"/>
+    </row>
+    <row r="989" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G989" s="3"/>
+    </row>
+    <row r="990" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G990" s="3"/>
+    </row>
+    <row r="991" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G991" s="3"/>
+    </row>
+    <row r="992" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G992" s="3"/>
+    </row>
+    <row r="993" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G993" s="3"/>
+    </row>
+    <row r="994" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G994" s="3"/>
+    </row>
+    <row r="995" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G995" s="3"/>
+    </row>
+    <row r="996" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G996" s="3"/>
+    </row>
+    <row r="997" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G997" s="3"/>
+    </row>
+    <row r="998" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G998" s="3"/>
+    </row>
+    <row r="999" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G999" s="3"/>
+    </row>
+    <row r="1000" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1000" s="3"/>
+    </row>
+    <row r="1001" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1001" s="3"/>
+    </row>
+    <row r="1002" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1002" s="3"/>
+    </row>
+    <row r="1003" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1003" s="3"/>
+    </row>
+    <row r="1004" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1004" s="3"/>
+    </row>
+    <row r="1005" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1005" s="3"/>
+    </row>
+    <row r="1006" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1006" s="3"/>
+    </row>
+    <row r="1007" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1007" s="3"/>
+    </row>
+    <row r="1008" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1008" s="3"/>
+    </row>
+    <row r="1009" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1009" s="3"/>
+    </row>
+    <row r="1010" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1010" s="3"/>
+    </row>
+    <row r="1011" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1011" s="3"/>
+    </row>
+    <row r="1012" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1012" s="3"/>
+    </row>
+    <row r="1013" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1013" s="3"/>
+    </row>
+    <row r="1014" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1014" s="3"/>
+    </row>
+    <row r="1015" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1015" s="3"/>
+    </row>
+    <row r="1016" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1016" s="3"/>
+    </row>
+    <row r="1017" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1017" s="3"/>
+    </row>
+    <row r="1018" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1018" s="3"/>
+    </row>
+    <row r="1019" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1019" s="3"/>
+    </row>
+    <row r="1020" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1020" s="3"/>
+    </row>
+    <row r="1021" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1021" s="3"/>
+    </row>
+    <row r="1022" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1022" s="3"/>
+    </row>
+    <row r="1023" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1023" s="3"/>
+    </row>
+    <row r="1024" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1024" s="3"/>
+    </row>
+    <row r="1025" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1025" s="3"/>
+    </row>
+    <row r="1026" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1026" s="3"/>
+    </row>
+    <row r="1027" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1027" s="3"/>
+    </row>
+    <row r="1028" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1028" s="3"/>
+    </row>
+    <row r="1029" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1029" s="3"/>
+    </row>
+    <row r="1030" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1030" s="3"/>
+    </row>
+    <row r="1031" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1031" s="3"/>
+    </row>
+    <row r="1032" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1032" s="3"/>
+    </row>
+    <row r="1033" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1033" s="3"/>
+    </row>
+    <row r="1034" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1034" s="3"/>
+    </row>
+    <row r="1035" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1035" s="3"/>
+    </row>
+    <row r="1036" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1036" s="3"/>
+    </row>
+    <row r="1037" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1037" s="3"/>
+    </row>
+    <row r="1038" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1038" s="3"/>
+    </row>
+    <row r="1039" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1039" s="3"/>
+    </row>
+    <row r="1040" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1040" s="3"/>
+    </row>
+    <row r="1041" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1041" s="3"/>
+    </row>
+    <row r="1042" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1042" s="3"/>
+    </row>
+    <row r="1043" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1043" s="3"/>
+    </row>
+    <row r="1044" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1044" s="3"/>
+    </row>
+    <row r="1045" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1045" s="3"/>
+    </row>
+    <row r="1046" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1046" s="3"/>
+    </row>
+    <row r="1047" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1047" s="3"/>
+    </row>
+    <row r="1048" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1048" s="3"/>
+    </row>
+    <row r="1049" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1049" s="3"/>
+    </row>
+    <row r="1050" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1050" s="3"/>
+    </row>
+    <row r="1051" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1051" s="3"/>
+    </row>
+    <row r="1052" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1052" s="3"/>
+    </row>
+    <row r="1053" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1053" s="3"/>
+    </row>
+    <row r="1054" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1054" s="3"/>
+    </row>
+    <row r="1055" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1055" s="3"/>
+    </row>
+    <row r="1056" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1056" s="3"/>
+    </row>
+    <row r="1057" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1057" s="3"/>
+    </row>
+    <row r="1058" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1058" s="3"/>
+    </row>
+    <row r="1059" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1059" s="3"/>
+    </row>
+    <row r="1060" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1060" s="3"/>
+    </row>
+    <row r="1061" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1061" s="3"/>
+    </row>
+    <row r="1062" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1062" s="3"/>
+    </row>
+    <row r="1063" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1063" s="3"/>
+    </row>
+    <row r="1064" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1064" s="3"/>
+    </row>
+    <row r="1065" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1065" s="3"/>
+    </row>
+    <row r="1066" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1066" s="3"/>
+    </row>
+    <row r="1067" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1067" s="3"/>
+    </row>
+    <row r="1068" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1068" s="3"/>
+    </row>
+    <row r="1069" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1069" s="3"/>
+    </row>
+    <row r="1070" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1070" s="3"/>
+    </row>
+    <row r="1071" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1071" s="3"/>
+    </row>
+    <row r="1072" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1072" s="3"/>
+    </row>
+    <row r="1073" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1073" s="3"/>
+    </row>
+    <row r="1074" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1074" s="3"/>
+    </row>
+    <row r="1075" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1075" s="3"/>
+    </row>
+    <row r="1076" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1076" s="3"/>
+    </row>
+    <row r="1077" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1077" s="3"/>
+    </row>
+    <row r="1078" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1078" s="3"/>
+    </row>
+    <row r="1079" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1079" s="3"/>
+    </row>
+    <row r="1080" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1080" s="3"/>
+    </row>
+    <row r="1081" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1081" s="3"/>
+    </row>
+    <row r="1082" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1082" s="3"/>
+    </row>
+    <row r="1083" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1083" s="3"/>
+    </row>
+    <row r="1084" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1084" s="3"/>
+    </row>
+    <row r="1085" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1085" s="3"/>
+    </row>
+    <row r="1086" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1086" s="3"/>
+    </row>
+    <row r="1087" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1087" s="3"/>
+    </row>
+    <row r="1088" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1088" s="3"/>
+    </row>
+    <row r="1089" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1089" s="3"/>
+    </row>
+    <row r="1090" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1090" s="3"/>
+    </row>
+    <row r="1091" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1091" s="3"/>
+    </row>
+    <row r="1092" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1092" s="3"/>
+    </row>
+    <row r="1093" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1093" s="3"/>
+    </row>
+    <row r="1094" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1094" s="3"/>
+    </row>
+    <row r="1095" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1095" s="3"/>
+    </row>
+    <row r="1096" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1096" s="3"/>
+    </row>
+    <row r="1097" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1097" s="3"/>
+    </row>
+    <row r="1098" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1098" s="3"/>
+    </row>
+    <row r="1099" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1099" s="3"/>
+    </row>
+    <row r="1100" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1100" s="3"/>
+    </row>
+    <row r="1101" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1101" s="3"/>
+    </row>
+    <row r="1102" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1102" s="3"/>
+    </row>
+    <row r="1103" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1103" s="3"/>
+    </row>
+    <row r="1104" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1104" s="3"/>
+    </row>
+    <row r="1105" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1105" s="3"/>
+    </row>
+    <row r="1106" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1106" s="3"/>
+    </row>
+    <row r="1107" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1107" s="3"/>
+    </row>
+    <row r="1108" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1108" s="3"/>
+    </row>
+    <row r="1109" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1109" s="3"/>
+    </row>
+    <row r="1110" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1110" s="3"/>
+    </row>
+    <row r="1111" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1111" s="3"/>
+    </row>
+    <row r="1112" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1112" s="3"/>
+    </row>
+    <row r="1113" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1113" s="3"/>
+    </row>
+    <row r="1114" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1114" s="3"/>
+    </row>
+    <row r="1115" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1115" s="3"/>
+    </row>
+    <row r="1116" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1116" s="3"/>
+    </row>
+    <row r="1117" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1117" s="3"/>
+    </row>
+    <row r="1118" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1118" s="3"/>
+    </row>
+    <row r="1119" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1119" s="3"/>
+    </row>
+    <row r="1120" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1120" s="3"/>
+    </row>
+    <row r="1121" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1121" s="3"/>
+    </row>
+    <row r="1122" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1122" s="3"/>
+    </row>
+    <row r="1123" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1123" s="3"/>
+    </row>
+    <row r="1124" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1124" s="3"/>
+    </row>
+    <row r="1125" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1125" s="3"/>
+    </row>
+    <row r="1126" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1126" s="3"/>
+    </row>
+    <row r="1127" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1127" s="3"/>
+    </row>
+    <row r="1128" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1128" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600E26E5-C34F-4145-8C11-1B3B1C7C8123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980FF0C2-0F8A-430D-9AFB-B7067F2287D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4893" uniqueCount="1141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5040" uniqueCount="1179">
   <si>
     <t>AB</t>
   </si>
@@ -3462,6 +3462,120 @@
   </si>
   <si>
     <t>CKN 8</t>
+  </si>
+  <si>
+    <t>Nipawin</t>
+  </si>
+  <si>
+    <t>CYBU</t>
+  </si>
+  <si>
+    <t>North Battleford</t>
+  </si>
+  <si>
+    <t>CYQW</t>
+  </si>
+  <si>
+    <t>North Seal River</t>
+  </si>
+  <si>
+    <t>CEG8</t>
+  </si>
+  <si>
+    <t>Norway House</t>
+  </si>
+  <si>
+    <t>CYNE</t>
+  </si>
+  <si>
+    <t>RAAS Kenora rdo</t>
+  </si>
+  <si>
+    <t>Nueltin Lake</t>
+  </si>
+  <si>
+    <t>Treeline UNICOM</t>
+  </si>
+  <si>
+    <t>ltd hrs Jun 15 - Sep 15 O/T tfc</t>
+  </si>
+  <si>
+    <t>CNL9</t>
+  </si>
+  <si>
+    <t>Oak Hammock Air Park</t>
+  </si>
+  <si>
+    <t>CAV9</t>
+  </si>
+  <si>
+    <t>Odessa / Strawberry Lakes</t>
+  </si>
+  <si>
+    <t>CSL7</t>
+  </si>
+  <si>
+    <t>Outlook (South)</t>
+  </si>
+  <si>
+    <t>CCL9</t>
+  </si>
+  <si>
+    <t>Oxbow</t>
+  </si>
+  <si>
+    <t>CJW2</t>
+  </si>
+  <si>
+    <t>Oxford House</t>
+  </si>
+  <si>
+    <t>CYOH</t>
+  </si>
+  <si>
+    <t>Pangman</t>
+  </si>
+  <si>
+    <t>CKC9</t>
+  </si>
+  <si>
+    <t>Patuanak</t>
+  </si>
+  <si>
+    <t>CKB2</t>
+  </si>
+  <si>
+    <t>Pelican Narrows</t>
+  </si>
+  <si>
+    <t>CJW4</t>
+  </si>
+  <si>
+    <t>Pierceland (Turchyn Field)</t>
+  </si>
+  <si>
+    <t>CTF5</t>
+  </si>
+  <si>
+    <t>Pikwitonei</t>
+  </si>
+  <si>
+    <t>CZMN</t>
+  </si>
+  <si>
+    <t>Pinehouse Lake</t>
+  </si>
+  <si>
+    <t>CZPO</t>
+  </si>
+  <si>
+    <t>Points North Landing</t>
+  </si>
+  <si>
+    <t>CYNL</t>
+  </si>
+  <si>
+    <t>68 Points North UNICOM ltd hrs O/T tfc</t>
   </si>
 </sst>
 </file>
@@ -22707,7 +22821,7 @@
       <c r="D935" t="s">
         <v>1121</v>
       </c>
-      <c r="E935" t="s">
+      <c r="F935" t="s">
         <v>1120</v>
       </c>
     </row>
@@ -23063,120 +23177,619 @@
       </c>
     </row>
     <row r="954" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G954" s="3"/>
+      <c r="A954" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B954" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C954" t="s">
+        <v>719</v>
+      </c>
+      <c r="D954" t="s">
+        <v>64</v>
+      </c>
+      <c r="E954" t="s">
+        <v>65</v>
+      </c>
+      <c r="F954" t="s">
+        <v>87</v>
+      </c>
+      <c r="G954" s="3">
+        <v>122.8</v>
+      </c>
     </row>
     <row r="955" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G955" s="3"/>
+      <c r="A955" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B955" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C955" t="s">
+        <v>719</v>
+      </c>
+      <c r="D955" t="s">
+        <v>2</v>
+      </c>
+      <c r="G955" s="3">
+        <v>128.75</v>
+      </c>
     </row>
     <row r="956" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G956" s="3"/>
+      <c r="A956" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B956" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C956" t="s">
+        <v>719</v>
+      </c>
+      <c r="D956" t="s">
+        <v>74</v>
+      </c>
+      <c r="E956" t="s">
+        <v>386</v>
+      </c>
+      <c r="G956" s="3">
+        <v>123.375</v>
+      </c>
     </row>
     <row r="957" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G957" s="3"/>
+      <c r="A957" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B957" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C957" t="s">
+        <v>719</v>
+      </c>
+      <c r="D957" t="s">
+        <v>74</v>
+      </c>
+      <c r="E957" t="s">
+        <v>69</v>
+      </c>
+      <c r="G957" s="3">
+        <v>126.7</v>
+      </c>
     </row>
     <row r="958" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G958" s="3"/>
+      <c r="A958" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B958" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C958" t="s">
+        <v>719</v>
+      </c>
+      <c r="D958" t="s">
+        <v>12</v>
+      </c>
+      <c r="E958" t="s">
+        <v>921</v>
+      </c>
+      <c r="G958" s="3">
+        <v>122.1</v>
+      </c>
     </row>
     <row r="959" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G959" s="3"/>
+      <c r="A959" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B959" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C959" t="s">
+        <v>719</v>
+      </c>
+      <c r="D959" t="s">
+        <v>2</v>
+      </c>
+      <c r="G959" s="3">
+        <v>128.125</v>
+      </c>
     </row>
     <row r="960" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G960" s="3"/>
-    </row>
-    <row r="961" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G961" s="3"/>
-    </row>
-    <row r="962" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G962" s="3"/>
-    </row>
-    <row r="963" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G963" s="3"/>
-    </row>
-    <row r="964" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G964" s="3"/>
-    </row>
-    <row r="965" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G965" s="3"/>
-    </row>
-    <row r="966" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G966" s="3"/>
-    </row>
-    <row r="967" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G967" s="3"/>
-    </row>
-    <row r="968" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G968" s="3"/>
-    </row>
-    <row r="969" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G969" s="3"/>
-    </row>
-    <row r="970" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G970" s="3"/>
-    </row>
-    <row r="971" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G971" s="3"/>
-    </row>
-    <row r="972" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G972" s="3"/>
-    </row>
-    <row r="973" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G973" s="3"/>
-    </row>
-    <row r="974" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G974" s="3"/>
-    </row>
-    <row r="975" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G975" s="3"/>
-    </row>
-    <row r="976" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G976" s="3"/>
-    </row>
-    <row r="977" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G977" s="3"/>
-    </row>
-    <row r="978" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G978" s="3"/>
-    </row>
-    <row r="979" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G979" s="3"/>
-    </row>
-    <row r="980" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G980" s="3"/>
-    </row>
-    <row r="981" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G981" s="3"/>
-    </row>
-    <row r="982" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G982" s="3"/>
-    </row>
-    <row r="983" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="A960" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B960" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C960" t="s">
+        <v>722</v>
+      </c>
+      <c r="D960" t="s">
+        <v>64</v>
+      </c>
+      <c r="E960" t="s">
+        <v>65</v>
+      </c>
+      <c r="F960" t="s">
+        <v>87</v>
+      </c>
+      <c r="G960" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="961" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A961" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B961" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C961" t="s">
+        <v>722</v>
+      </c>
+      <c r="D961" t="s">
+        <v>74</v>
+      </c>
+      <c r="E961" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F961" t="s">
+        <v>841</v>
+      </c>
+      <c r="G961" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="962" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A962" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B962" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C962" t="s">
+        <v>722</v>
+      </c>
+      <c r="D962" t="s">
+        <v>74</v>
+      </c>
+      <c r="E962" t="s">
+        <v>386</v>
+      </c>
+      <c r="G962" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="963" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A963" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B963" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C963" t="s">
+        <v>722</v>
+      </c>
+      <c r="D963" t="s">
+        <v>74</v>
+      </c>
+      <c r="E963" t="s">
+        <v>69</v>
+      </c>
+      <c r="G963" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="964" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A964" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B964" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C964" t="s">
+        <v>722</v>
+      </c>
+      <c r="D964" t="s">
+        <v>12</v>
+      </c>
+      <c r="E964" t="s">
+        <v>223</v>
+      </c>
+      <c r="F964" t="s">
+        <v>843</v>
+      </c>
+      <c r="G964" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="965" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A965" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B965" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C965" t="s">
+        <v>722</v>
+      </c>
+      <c r="D965" t="s">
+        <v>76</v>
+      </c>
+      <c r="E965" t="s">
+        <v>200</v>
+      </c>
+      <c r="G965" s="3">
+        <v>135.1</v>
+      </c>
+    </row>
+    <row r="966" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A966" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B966" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C966" t="s">
+        <v>722</v>
+      </c>
+      <c r="D966" t="s">
+        <v>2</v>
+      </c>
+      <c r="G966" s="3">
+        <v>127.7</v>
+      </c>
+    </row>
+    <row r="967" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A967" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B967" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C967" t="s">
+        <v>722</v>
+      </c>
+      <c r="D967" t="s">
+        <v>64</v>
+      </c>
+      <c r="E967" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F967" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G967" s="3">
+        <v>129.6</v>
+      </c>
+    </row>
+    <row r="968" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A968" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B968" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C968" t="s">
+        <v>722</v>
+      </c>
+      <c r="D968" t="s">
+        <v>64</v>
+      </c>
+      <c r="E968" t="s">
+        <v>67</v>
+      </c>
+      <c r="G968" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="969" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A969" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B969" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C969" t="s">
+        <v>719</v>
+      </c>
+      <c r="D969" t="s">
+        <v>64</v>
+      </c>
+      <c r="E969" t="s">
+        <v>65</v>
+      </c>
+      <c r="F969" t="s">
+        <v>87</v>
+      </c>
+      <c r="G969" s="3">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="970" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A970" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B970" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C970" t="s">
+        <v>719</v>
+      </c>
+      <c r="D970" t="s">
+        <v>64</v>
+      </c>
+      <c r="E970" t="s">
+        <v>67</v>
+      </c>
+      <c r="G970" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="971" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A971" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B971" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C971" t="s">
+        <v>719</v>
+      </c>
+      <c r="D971" t="s">
+        <v>64</v>
+      </c>
+      <c r="E971" t="s">
+        <v>67</v>
+      </c>
+      <c r="G971" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="972" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A972" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B972" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C972" t="s">
+        <v>722</v>
+      </c>
+      <c r="D972" t="s">
+        <v>64</v>
+      </c>
+      <c r="E972" t="s">
+        <v>65</v>
+      </c>
+      <c r="F972" t="s">
+        <v>87</v>
+      </c>
+      <c r="G972" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="973" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A973" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B973" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C973" t="s">
+        <v>722</v>
+      </c>
+      <c r="D973" t="s">
+        <v>113</v>
+      </c>
+      <c r="G973" s="3">
+        <v>122.125</v>
+      </c>
+    </row>
+    <row r="974" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A974" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B974" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C974" t="s">
+        <v>719</v>
+      </c>
+      <c r="D974" t="s">
+        <v>64</v>
+      </c>
+      <c r="E974" t="s">
+        <v>67</v>
+      </c>
+      <c r="G974" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="975" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A975" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B975" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C975" t="s">
+        <v>719</v>
+      </c>
+      <c r="D975" t="s">
+        <v>64</v>
+      </c>
+      <c r="E975" t="s">
+        <v>67</v>
+      </c>
+      <c r="G975" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="976" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A976" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B976" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C976" t="s">
+        <v>719</v>
+      </c>
+      <c r="D976" t="s">
+        <v>64</v>
+      </c>
+      <c r="E976" t="s">
+        <v>67</v>
+      </c>
+      <c r="G976" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="977" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A977" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B977" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C977" t="s">
+        <v>719</v>
+      </c>
+      <c r="D977" t="s">
+        <v>64</v>
+      </c>
+      <c r="E977" t="s">
+        <v>67</v>
+      </c>
+      <c r="G977" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="978" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A978" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B978" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C978" t="s">
+        <v>722</v>
+      </c>
+      <c r="D978" t="s">
+        <v>64</v>
+      </c>
+      <c r="E978" t="s">
+        <v>65</v>
+      </c>
+      <c r="F978" t="s">
+        <v>87</v>
+      </c>
+      <c r="G978" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="979" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A979" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B979" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C979" t="s">
+        <v>719</v>
+      </c>
+      <c r="D979" t="s">
+        <v>64</v>
+      </c>
+      <c r="E979" t="s">
+        <v>67</v>
+      </c>
+      <c r="G979" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="980" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A980" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B980" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C980" t="s">
+        <v>719</v>
+      </c>
+      <c r="D980" t="s">
+        <v>113</v>
+      </c>
+      <c r="G980" s="3">
+        <v>123.175</v>
+      </c>
+    </row>
+    <row r="981" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A981" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B981" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C981" t="s">
+        <v>719</v>
+      </c>
+      <c r="D981" t="s">
+        <v>64</v>
+      </c>
+      <c r="E981" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G981" s="3">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="982" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A982" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B982" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C982" t="s">
+        <v>719</v>
+      </c>
+      <c r="D982" t="s">
+        <v>113</v>
+      </c>
+      <c r="G982" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="983" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G983" s="3"/>
     </row>
-    <row r="984" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G984" s="3"/>
     </row>
-    <row r="985" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G985" s="3"/>
     </row>
-    <row r="986" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G986" s="3"/>
     </row>
-    <row r="987" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G987" s="3"/>
     </row>
-    <row r="988" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G988" s="3"/>
     </row>
-    <row r="989" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G989" s="3"/>
     </row>
-    <row r="990" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G990" s="3"/>
     </row>
-    <row r="991" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G991" s="3"/>
     </row>
-    <row r="992" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G992" s="3"/>
     </row>
     <row r="993" spans="7:7" x14ac:dyDescent="0.25">

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980FF0C2-0F8A-430D-9AFB-B7067F2287D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA0BF81-A0DC-403F-BC27-76EAA7C30B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5040" uniqueCount="1179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5066" uniqueCount="1188">
   <si>
     <t>AB</t>
   </si>
@@ -3576,6 +3576,33 @@
   </si>
   <si>
     <t>68 Points North UNICOM ltd hrs O/T tfc</t>
+  </si>
+  <si>
+    <t>Pokemouche</t>
+  </si>
+  <si>
+    <t>CDA4</t>
+  </si>
+  <si>
+    <t>FISE Quebec rdo (Bathrust)</t>
+  </si>
+  <si>
+    <t>Poplar River</t>
+  </si>
+  <si>
+    <t>CZNG</t>
+  </si>
+  <si>
+    <t>Porcupine Plain</t>
+  </si>
+  <si>
+    <t>CKD2</t>
+  </si>
+  <si>
+    <t>Portage La Prairie (North)</t>
+  </si>
+  <si>
+    <t>CJZ2</t>
   </si>
 </sst>
 </file>
@@ -23763,19 +23790,107 @@
       </c>
     </row>
     <row r="983" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G983" s="3"/>
+      <c r="A983" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B983" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C983" t="s">
+        <v>736</v>
+      </c>
+      <c r="D983" t="s">
+        <v>74</v>
+      </c>
+      <c r="E983" t="s">
+        <v>1181</v>
+      </c>
+      <c r="G983" s="3">
+        <v>123.47499999999999</v>
+      </c>
     </row>
     <row r="984" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G984" s="3"/>
+      <c r="A984" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B984" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C984" t="s">
+        <v>736</v>
+      </c>
+      <c r="D984" t="s">
+        <v>74</v>
+      </c>
+      <c r="E984" t="s">
+        <v>69</v>
+      </c>
+      <c r="G984" s="3">
+        <v>126.7</v>
+      </c>
     </row>
     <row r="985" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G985" s="3"/>
+      <c r="A985" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B985" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C985" t="s">
+        <v>722</v>
+      </c>
+      <c r="D985" t="s">
+        <v>64</v>
+      </c>
+      <c r="E985" t="s">
+        <v>65</v>
+      </c>
+      <c r="F985" t="s">
+        <v>87</v>
+      </c>
+      <c r="G985" s="3">
+        <v>122.8</v>
+      </c>
     </row>
     <row r="986" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G986" s="3"/>
+      <c r="A986" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B986" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C986" t="s">
+        <v>719</v>
+      </c>
+      <c r="D986" t="s">
+        <v>64</v>
+      </c>
+      <c r="E986" t="s">
+        <v>67</v>
+      </c>
+      <c r="G986" s="3">
+        <v>123.2</v>
+      </c>
     </row>
     <row r="987" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G987" s="3"/>
+      <c r="A987" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B987" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C987" t="s">
+        <v>722</v>
+      </c>
+      <c r="D987" t="s">
+        <v>64</v>
+      </c>
+      <c r="E987" t="s">
+        <v>67</v>
+      </c>
+      <c r="G987" s="3">
+        <v>122.8</v>
+      </c>
     </row>
     <row r="988" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G988" s="3"/>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA0BF81-A0DC-403F-BC27-76EAA7C30B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DBC6E8-36F0-460C-8383-30779DF350C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5066" uniqueCount="1188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5289" uniqueCount="1240">
   <si>
     <t>AB</t>
   </si>
@@ -3603,6 +3603,162 @@
   </si>
   <si>
     <t>CJZ2</t>
+  </si>
+  <si>
+    <t>Portage La Prairie / Southport</t>
+  </si>
+  <si>
+    <t>CYPG</t>
+  </si>
+  <si>
+    <t>Winnipeg Tml</t>
+  </si>
+  <si>
+    <t>VFR ADV</t>
+  </si>
+  <si>
+    <t>14-24Z‡ Mon-Fri exc hols</t>
+  </si>
+  <si>
+    <t>00-14Z‡ Mon-Fri, H24 Sat, Sun, &amp; hols</t>
+  </si>
+  <si>
+    <t>Port Au Choix</t>
+  </si>
+  <si>
+    <t>CCM4</t>
+  </si>
+  <si>
+    <t>Port Hope Simpson</t>
+  </si>
+  <si>
+    <t>CCP4</t>
+  </si>
+  <si>
+    <t>Postville</t>
+  </si>
+  <si>
+    <t>CCD4</t>
+  </si>
+  <si>
+    <t>Poverty Valley</t>
+  </si>
+  <si>
+    <t>CPV9</t>
+  </si>
+  <si>
+    <t>Preeceville</t>
+  </si>
+  <si>
+    <t>CJK9</t>
+  </si>
+  <si>
+    <t>Prince Albert (Glass Field)</t>
+  </si>
+  <si>
+    <t>CYPA</t>
+  </si>
+  <si>
+    <t>12-03Z</t>
+  </si>
+  <si>
+    <t>12-03Z O/T tfc</t>
+  </si>
+  <si>
+    <t>03-12Z</t>
+  </si>
+  <si>
+    <t>Pukatawagan</t>
+  </si>
+  <si>
+    <t>CZFG</t>
+  </si>
+  <si>
+    <t>Quill Lake</t>
+  </si>
+  <si>
+    <t>CKE2</t>
+  </si>
+  <si>
+    <t>Radville</t>
+  </si>
+  <si>
+    <t>CKF2</t>
+  </si>
+  <si>
+    <t>Red Sucker Lake</t>
+  </si>
+  <si>
+    <t>CYRS</t>
+  </si>
+  <si>
+    <t>Regina / Aerogate</t>
+  </si>
+  <si>
+    <t>CAG2</t>
+  </si>
+  <si>
+    <t>Regina Beach</t>
+  </si>
+  <si>
+    <t>CKL9</t>
+  </si>
+  <si>
+    <t>Regina Intl</t>
+  </si>
+  <si>
+    <t>CYQR</t>
+  </si>
+  <si>
+    <t>04-12Z</t>
+  </si>
+  <si>
+    <t>12-04Z</t>
+  </si>
+  <si>
+    <t>120.100, 123.800</t>
+  </si>
+  <si>
+    <t>Reindeer Lake</t>
+  </si>
+  <si>
+    <t>CRL7</t>
+  </si>
+  <si>
+    <t>CRP2</t>
+  </si>
+  <si>
+    <t>Reston / R.M. Of Pipestone</t>
+  </si>
+  <si>
+    <t>Riding Mountain</t>
+  </si>
+  <si>
+    <t>CRM2</t>
+  </si>
+  <si>
+    <t>Rigolet</t>
+  </si>
+  <si>
+    <t>CCZ2</t>
+  </si>
+  <si>
+    <t>Riverton</t>
+  </si>
+  <si>
+    <t>CKG2</t>
+  </si>
+  <si>
+    <t>Roblin</t>
+  </si>
+  <si>
+    <t>CKB7</t>
+  </si>
+  <si>
+    <t>Rockglen</t>
+  </si>
+  <si>
+    <t>CKC7</t>
   </si>
 </sst>
 </file>
@@ -23893,162 +24049,911 @@
       </c>
     </row>
     <row r="988" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G988" s="3"/>
+      <c r="A988" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B988" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C988" t="s">
+        <v>722</v>
+      </c>
+      <c r="D988" t="s">
+        <v>41</v>
+      </c>
+      <c r="F988" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G988" s="3">
+        <v>120.85</v>
+      </c>
     </row>
     <row r="989" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G989" s="3"/>
+      <c r="A989" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B989" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C989" t="s">
+        <v>722</v>
+      </c>
+      <c r="D989" t="s">
+        <v>14</v>
+      </c>
+      <c r="F989" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G989" s="3">
+        <v>121.7</v>
+      </c>
     </row>
     <row r="990" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G990" s="3"/>
+      <c r="A990" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B990" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C990" t="s">
+        <v>722</v>
+      </c>
+      <c r="D990" t="s">
+        <v>15</v>
+      </c>
+      <c r="F990" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G990" s="3">
+        <v>126.2</v>
+      </c>
     </row>
     <row r="991" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G991" s="3"/>
+      <c r="A991" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B991" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C991" t="s">
+        <v>722</v>
+      </c>
+      <c r="D991" t="s">
+        <v>64</v>
+      </c>
+      <c r="E991" t="s">
+        <v>67</v>
+      </c>
+      <c r="F991" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G991" s="3">
+        <v>126.2</v>
+      </c>
     </row>
     <row r="992" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G992" s="3"/>
-    </row>
-    <row r="993" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G993" s="3"/>
-    </row>
-    <row r="994" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G994" s="3"/>
-    </row>
-    <row r="995" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G995" s="3"/>
-    </row>
-    <row r="996" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G996" s="3"/>
-    </row>
-    <row r="997" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G997" s="3"/>
-    </row>
-    <row r="998" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G998" s="3"/>
-    </row>
-    <row r="999" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G999" s="3"/>
-    </row>
-    <row r="1000" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1000" s="3"/>
-    </row>
-    <row r="1001" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1001" s="3"/>
-    </row>
-    <row r="1002" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1002" s="3"/>
-    </row>
-    <row r="1003" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1003" s="3"/>
-    </row>
-    <row r="1004" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1004" s="3"/>
-    </row>
-    <row r="1005" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1005" s="3"/>
-    </row>
-    <row r="1006" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1006" s="3"/>
-    </row>
-    <row r="1007" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1007" s="3"/>
-    </row>
-    <row r="1008" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1008" s="3"/>
-    </row>
-    <row r="1009" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1009" s="3"/>
-    </row>
-    <row r="1010" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1010" s="3"/>
-    </row>
-    <row r="1011" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1011" s="3"/>
-    </row>
-    <row r="1012" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1012" s="3"/>
-    </row>
-    <row r="1013" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1013" s="3"/>
-    </row>
-    <row r="1014" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1014" s="3"/>
-    </row>
-    <row r="1015" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1015" s="3"/>
-    </row>
-    <row r="1016" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1016" s="3"/>
-    </row>
-    <row r="1017" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1017" s="3"/>
-    </row>
-    <row r="1018" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1018" s="3"/>
-    </row>
-    <row r="1019" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1019" s="3"/>
-    </row>
-    <row r="1020" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1020" s="3"/>
-    </row>
-    <row r="1021" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1021" s="3"/>
-    </row>
-    <row r="1022" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1022" s="3"/>
-    </row>
-    <row r="1023" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1023" s="3"/>
-    </row>
-    <row r="1024" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1024" s="3"/>
-    </row>
-    <row r="1025" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1025" s="3"/>
-    </row>
-    <row r="1026" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1026" s="3"/>
-    </row>
-    <row r="1027" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1027" s="3"/>
-    </row>
-    <row r="1028" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1028" s="3"/>
-    </row>
-    <row r="1029" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1029" s="3"/>
-    </row>
-    <row r="1030" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1030" s="3"/>
-    </row>
-    <row r="1031" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="A992" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B992" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C992" t="s">
+        <v>722</v>
+      </c>
+      <c r="D992" t="s">
+        <v>16</v>
+      </c>
+      <c r="E992" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F992" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G992" s="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="993" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A993" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B993" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C993" t="s">
+        <v>722</v>
+      </c>
+      <c r="D993" t="s">
+        <v>17</v>
+      </c>
+      <c r="E993" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G993" s="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="994" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A994" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B994" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C994" t="s">
+        <v>722</v>
+      </c>
+      <c r="D994" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E994" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G994" s="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="995" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A995" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B995" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C995" t="s">
+        <v>722</v>
+      </c>
+      <c r="D995" t="s">
+        <v>113</v>
+      </c>
+      <c r="G995" s="3">
+        <v>123.175</v>
+      </c>
+    </row>
+    <row r="996" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A996" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B996" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C996" t="s">
+        <v>741</v>
+      </c>
+      <c r="D996" t="s">
+        <v>64</v>
+      </c>
+      <c r="E996" t="s">
+        <v>67</v>
+      </c>
+      <c r="G996" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="997" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A997" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B997" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C997" t="s">
+        <v>741</v>
+      </c>
+      <c r="D997" t="s">
+        <v>64</v>
+      </c>
+      <c r="E997" t="s">
+        <v>67</v>
+      </c>
+      <c r="G997" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="998" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A998" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B998" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C998" t="s">
+        <v>741</v>
+      </c>
+      <c r="D998" t="s">
+        <v>64</v>
+      </c>
+      <c r="E998" t="s">
+        <v>67</v>
+      </c>
+      <c r="G998" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="999" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A999" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B999" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C999" t="s">
+        <v>719</v>
+      </c>
+      <c r="D999" t="s">
+        <v>64</v>
+      </c>
+      <c r="E999" t="s">
+        <v>67</v>
+      </c>
+      <c r="G999" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1000" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C1000" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1000" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1000" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1000" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1001" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C1001" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1001" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G1001" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1002" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C1002" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1002" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1002" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1002" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1003" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B1003" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C1003" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1003" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1003" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1003" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1004" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B1004" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C1004" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1004" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1004" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1004" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G1004" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1005" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B1005" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C1005" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1005" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1005" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1005" s="3">
+        <v>133.9</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1006" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B1006" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C1006" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1006" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1006" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1006" s="3">
+        <v>133.9</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1007" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B1007" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1007" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1007" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G1007" s="3">
+        <v>128.05000000000001</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1008" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B1008" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C1008" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1008" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1008" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1008" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1008" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1009" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B1009" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C1009" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1009" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1009" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1009" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1010" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B1010" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C1010" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1010" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1010" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1010" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1011" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B1011" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C1011" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1011" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1011" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1011" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1011" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1012" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B1012" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C1012" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1012" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1012" s="3">
+        <v>122.075</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1013" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B1013" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C1013" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1013" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1013" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1013" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1014" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B1014" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C1014" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1014" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1014" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1014" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1015" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B1015" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C1015" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1015" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1015" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G1015" s="3">
+        <v>118.6</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1016" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B1016" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C1016" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1016" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1016" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1016" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1017" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B1017" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C1017" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1017" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1017" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1017" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1018" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B1018" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C1018" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1018" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1018" s="3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1019" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B1019" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C1019" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1019" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1019" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G1019" s="3">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1020" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B1020" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C1020" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1020" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1020" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G1020" s="3">
+        <v>118.6</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1021" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B1021" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C1021" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1021" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1021" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1021" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G1021" s="3">
+        <v>118.6</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1022" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B1022" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C1022" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1022" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1022" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1022" s="3" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1023" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B1023" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1023" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1023" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1023" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1023" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1023" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1024" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B1024" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C1024" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1024" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1024" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1024" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1025" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B1025" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C1025" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1025" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1025" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1025" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1026" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B1026" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C1026" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1026" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1026" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1026" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1027" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B1027" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C1027" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1027" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1027" t="s">
+        <v>938</v>
+      </c>
+      <c r="F1027" t="s">
+        <v>945</v>
+      </c>
+      <c r="G1027" s="3" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1028" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C1028" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1028" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1028" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1028" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1028" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1029" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B1029" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C1029" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1029" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1029" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1029" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1030" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B1030" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C1030" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1030" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1030" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1030" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G1031" s="3"/>
     </row>
-    <row r="1032" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G1032" s="3"/>
     </row>
-    <row r="1033" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G1033" s="3"/>
     </row>
-    <row r="1034" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G1034" s="3"/>
     </row>
-    <row r="1035" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G1035" s="3"/>
     </row>
-    <row r="1036" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G1036" s="3"/>
     </row>
-    <row r="1037" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G1037" s="3"/>
     </row>
-    <row r="1038" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G1038" s="3"/>
     </row>
-    <row r="1039" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G1039" s="3"/>
     </row>
-    <row r="1040" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G1040" s="3"/>
     </row>
     <row r="1041" spans="7:7" x14ac:dyDescent="0.25">

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DBC6E8-36F0-460C-8383-30779DF350C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6583D95C-F40F-4FA1-B9E4-944A7ECDEAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5289" uniqueCount="1240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5500" uniqueCount="1291">
   <si>
     <t>AB</t>
   </si>
@@ -3759,6 +3759,159 @@
   </si>
   <si>
     <t>CKC7</t>
+  </si>
+  <si>
+    <t>Roland (Graham Field)</t>
+  </si>
+  <si>
+    <t>CKD7</t>
+  </si>
+  <si>
+    <t>Roland tfc</t>
+  </si>
+  <si>
+    <t>Rosenort</t>
+  </si>
+  <si>
+    <t>CKJ2</t>
+  </si>
+  <si>
+    <t>Rosetown</t>
+  </si>
+  <si>
+    <t>CJX4</t>
+  </si>
+  <si>
+    <t>Russell</t>
+  </si>
+  <si>
+    <t>CJW5</t>
+  </si>
+  <si>
+    <t>14-23Z‡ Mon-Fri, O/T tfc</t>
+  </si>
+  <si>
+    <t>Saint John</t>
+  </si>
+  <si>
+    <t>CYSJ</t>
+  </si>
+  <si>
+    <t>118.500, 236.600</t>
+  </si>
+  <si>
+    <t>St. Andrews (Codroy Valley)</t>
+  </si>
+  <si>
+    <t>CDA5</t>
+  </si>
+  <si>
+    <t>Gander  Centre</t>
+  </si>
+  <si>
+    <t>St. Anthony</t>
+  </si>
+  <si>
+    <t>CYAY</t>
+  </si>
+  <si>
+    <t>Deer Lake rdo</t>
+  </si>
+  <si>
+    <t>RAAS Deer Lake rdo</t>
+  </si>
+  <si>
+    <t>123.275, 5680</t>
+  </si>
+  <si>
+    <t>133.000, 371.900</t>
+  </si>
+  <si>
+    <t>119.850, 122.375</t>
+  </si>
+  <si>
+    <t>St. Brieux</t>
+  </si>
+  <si>
+    <t>CKK2</t>
+  </si>
+  <si>
+    <t>St. Francois Xavier</t>
+  </si>
+  <si>
+    <t>CKA8</t>
+  </si>
+  <si>
+    <t>St. John's Intl</t>
+  </si>
+  <si>
+    <t>CYYT</t>
+  </si>
+  <si>
+    <t>120.600, 236.600</t>
+  </si>
+  <si>
+    <t>133.150, 135.350, 227.300</t>
+  </si>
+  <si>
+    <t>Air Reserve Torbay Ops</t>
+  </si>
+  <si>
+    <t>122.375, 135.350</t>
+  </si>
+  <si>
+    <t>St. Leonard</t>
+  </si>
+  <si>
+    <t>CYSL</t>
+  </si>
+  <si>
+    <t>St. Lewis (Fox Harbour)</t>
+  </si>
+  <si>
+    <t>CCK4</t>
+  </si>
+  <si>
+    <t>Fox Harbour tfc</t>
+  </si>
+  <si>
+    <t>St-Pierre-Jolys (Carl's Field)</t>
+  </si>
+  <si>
+    <t>CPJ6</t>
+  </si>
+  <si>
+    <t>St. Stephen</t>
+  </si>
+  <si>
+    <t>CCS3</t>
+  </si>
+  <si>
+    <t>St. Theresa Point</t>
+  </si>
+  <si>
+    <t>CYST</t>
+  </si>
+  <si>
+    <t>RAAS Thunder Bay rdo (Island Lake)</t>
+  </si>
+  <si>
+    <t>FISE Edmonton rdo (Island Lake)</t>
+  </si>
+  <si>
+    <t>Thunder bay rdo</t>
+  </si>
+  <si>
+    <t>Sandy Bay</t>
+  </si>
+  <si>
+    <t>CJY4</t>
+  </si>
+  <si>
+    <t>Saskatoon / Banga Air</t>
+  </si>
+  <si>
+    <t>CJN5</t>
   </si>
 </sst>
 </file>
@@ -24927,129 +25080,817 @@
       </c>
     </row>
     <row r="1031" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1031" s="3"/>
+      <c r="A1031" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B1031" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C1031" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1031" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1031" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G1031" s="3">
+        <v>123.2</v>
+      </c>
     </row>
     <row r="1032" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1032" s="3"/>
+      <c r="A1032" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B1032" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C1032" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1032" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1032" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1032" s="3">
+        <v>123.2</v>
+      </c>
     </row>
     <row r="1033" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1033" s="3"/>
+      <c r="A1033" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B1033" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C1033" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1033" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1033" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1033" s="3">
+        <v>122.8</v>
+      </c>
     </row>
     <row r="1034" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1034" s="3"/>
+      <c r="A1034" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B1034" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C1034" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1034" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1034" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1034" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G1034" s="3">
+        <v>122.8</v>
+      </c>
     </row>
     <row r="1035" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1035" s="3"/>
+      <c r="A1035" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B1035" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C1035" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1035" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1035" s="3" t="s">
+        <v>1252</v>
+      </c>
     </row>
     <row r="1036" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1036" s="3"/>
+      <c r="A1036" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B1036" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C1036" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1036" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1036" t="s">
+        <v>275</v>
+      </c>
+      <c r="G1036" s="3">
+        <v>123.47499999999999</v>
+      </c>
     </row>
     <row r="1037" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1037" s="3"/>
+      <c r="A1037" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B1037" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C1037" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1037" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1037" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1037" s="3">
+        <v>126.7</v>
+      </c>
     </row>
     <row r="1038" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1038" s="3"/>
+      <c r="A1038" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B1038" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C1038" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1038" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1038" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1038" s="3">
+        <v>118.5</v>
+      </c>
     </row>
     <row r="1039" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1039" s="3"/>
+      <c r="A1039" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B1039" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C1039" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1039" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1039" t="s">
+        <v>524</v>
+      </c>
+      <c r="G1039" s="3" t="s">
+        <v>910</v>
+      </c>
     </row>
     <row r="1040" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1040" s="3"/>
-    </row>
-    <row r="1041" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1041" s="3"/>
-    </row>
-    <row r="1042" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1042" s="3"/>
-    </row>
-    <row r="1043" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1043" s="3"/>
-    </row>
-    <row r="1044" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1044" s="3"/>
-    </row>
-    <row r="1045" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1045" s="3"/>
-    </row>
-    <row r="1046" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1046" s="3"/>
-    </row>
-    <row r="1047" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1047" s="3"/>
-    </row>
-    <row r="1048" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1048" s="3"/>
-    </row>
-    <row r="1049" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1049" s="3"/>
-    </row>
-    <row r="1050" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1050" s="3"/>
-    </row>
-    <row r="1051" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1051" s="3"/>
-    </row>
-    <row r="1052" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1052" s="3"/>
-    </row>
-    <row r="1053" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1053" s="3"/>
-    </row>
-    <row r="1054" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1054" s="3"/>
-    </row>
-    <row r="1055" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1055" s="3"/>
-    </row>
-    <row r="1056" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1056" s="3"/>
-    </row>
-    <row r="1057" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1057" s="3"/>
-    </row>
-    <row r="1058" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1058" s="3"/>
-    </row>
-    <row r="1059" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1059" s="3"/>
-    </row>
-    <row r="1060" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1060" s="3"/>
-    </row>
-    <row r="1061" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1061" s="3"/>
-    </row>
-    <row r="1062" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1062" s="3"/>
-    </row>
-    <row r="1063" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1063" s="3"/>
-    </row>
-    <row r="1064" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1064" s="3"/>
-    </row>
-    <row r="1065" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1065" s="3"/>
-    </row>
-    <row r="1066" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1066" s="3"/>
-    </row>
-    <row r="1067" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1067" s="3"/>
-    </row>
-    <row r="1068" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1068" s="3"/>
-    </row>
-    <row r="1069" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1069" s="3"/>
-    </row>
-    <row r="1070" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1070" s="3"/>
-    </row>
-    <row r="1071" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1071" s="3"/>
-    </row>
-    <row r="1072" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="A1040" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B1040" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C1040" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1040" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1040" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1040" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1041" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B1041" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C1041" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1041" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1041" t="s">
+        <v>1255</v>
+      </c>
+      <c r="G1041" s="3">
+        <v>120.325</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1042" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B1042" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C1042" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1042" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1042" t="s">
+        <v>1255</v>
+      </c>
+      <c r="G1042" s="3">
+        <v>120.325</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1043" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B1043" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C1043" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1043" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1043" t="s">
+        <v>1259</v>
+      </c>
+      <c r="G1043" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1044" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B1044" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C1044" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1044" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1044" t="s">
+        <v>275</v>
+      </c>
+      <c r="G1044" s="3" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1045" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B1045" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C1045" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1045" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1045" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1045" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1046" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B1046" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C1046" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1046" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1046" t="s">
+        <v>1258</v>
+      </c>
+      <c r="G1046" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1047" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B1047" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C1047" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1047" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1047" t="s">
+        <v>807</v>
+      </c>
+      <c r="G1047" s="3" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1048" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B1048" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C1048" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1048" t="s">
+        <v>404</v>
+      </c>
+      <c r="E1048" t="s">
+        <v>405</v>
+      </c>
+      <c r="G1048" s="3" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1049" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B1049" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C1049" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1049" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1049" s="3">
+        <v>118.65</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1050" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B1050" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C1050" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1050" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1050" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1050" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1050" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1051" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B1051" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C1051" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1051" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1051" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1051" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1052" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B1052" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C1052" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1052" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1052" t="s">
+        <v>275</v>
+      </c>
+      <c r="G1052" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1053" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B1053" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C1053" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1053" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1053" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1053" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1054" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B1054" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C1054" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1054" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1054" s="3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1055" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C1055" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1055" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1055" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1056" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B1056" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C1056" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1056" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1056" s="3" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1057" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B1057" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C1057" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1057" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1057" t="s">
+        <v>807</v>
+      </c>
+      <c r="G1057" s="3" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1058" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B1058" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C1058" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1058" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1058" t="s">
+        <v>1271</v>
+      </c>
+      <c r="G1058" s="3">
+        <v>131.02000000000001</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1059" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C1059" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1059" t="s">
+        <v>404</v>
+      </c>
+      <c r="E1059" t="s">
+        <v>405</v>
+      </c>
+      <c r="G1059" s="3" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1060" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C1060" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1060" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1060" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1060" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1061" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B1061" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C1061" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1061" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1061" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1061" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1062" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B1062" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C1062" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1062" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1062" t="s">
+        <v>1277</v>
+      </c>
+      <c r="G1062" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1063" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B1063" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C1063" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1063" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1063" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1063" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1064" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B1064" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C1064" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1064" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1064" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1064" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1064" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1065" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B1065" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C1065" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1065" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1065" t="s">
+        <v>1284</v>
+      </c>
+      <c r="G1065" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1066" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B1066" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C1066" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1066" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1066" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G1066" s="3">
+        <v>122.375</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1067" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B1067" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C1067" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1067" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1067" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1067" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1068" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B1068" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C1068" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1068" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1068" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G1068" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1069" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B1069" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C1069" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1069" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1069" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1069" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1070" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B1070" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C1070" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1070" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1070" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1071" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B1071" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C1071" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1071" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1071" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1071" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G1072" s="3"/>
     </row>
     <row r="1073" spans="7:7" x14ac:dyDescent="0.25">

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6583D95C-F40F-4FA1-B9E4-944A7ECDEAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0705847-0B49-485C-A6FC-5E96550B586C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5500" uniqueCount="1291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6136" uniqueCount="1431">
   <si>
     <t>AB</t>
   </si>
@@ -3912,6 +3912,426 @@
   </si>
   <si>
     <t>CJN5</t>
+  </si>
+  <si>
+    <t>Saskatoon / John G. Diefenbaker Intl</t>
+  </si>
+  <si>
+    <t>CYXE</t>
+  </si>
+  <si>
+    <t>Saskatoon</t>
+  </si>
+  <si>
+    <t>0445-1200Z Mon-Fri Mar 09-Oct 31, 0445-1245Z Sat-Sun Mar 09-Oct 31, 0445-1245Z Nov 1-Mar 8</t>
+  </si>
+  <si>
+    <t>1200-0445Z Mon-Fri Mar 09-Oct 31, 1245-0445Z Sat-Sun Mar 09-Oct 31, 1245-0445Z Nov 1-Mar 8</t>
+  </si>
+  <si>
+    <t>Saskatoon / Richter Field</t>
+  </si>
+  <si>
+    <t>CRF5</t>
+  </si>
+  <si>
+    <t>Scottsfield Airpark</t>
+  </si>
+  <si>
+    <t>CCF9</t>
+  </si>
+  <si>
+    <t>Seabee Mine</t>
+  </si>
+  <si>
+    <t>CCB2</t>
+  </si>
+  <si>
+    <t>Selkirk</t>
+  </si>
+  <si>
+    <t>CKL2</t>
+  </si>
+  <si>
+    <t>Sevogle</t>
+  </si>
+  <si>
+    <t>CCM3</t>
+  </si>
+  <si>
+    <t>Shamattawa</t>
+  </si>
+  <si>
+    <t>CZTM</t>
+  </si>
+  <si>
+    <t>Shaunavon</t>
+  </si>
+  <si>
+    <t>CJC5</t>
+  </si>
+  <si>
+    <t>Shedian Bridge</t>
+  </si>
+  <si>
+    <t>CSB5</t>
+  </si>
+  <si>
+    <t>Shellbrook</t>
+  </si>
+  <si>
+    <t>CJZ4</t>
+  </si>
+  <si>
+    <t>Shoal Lake</t>
+  </si>
+  <si>
+    <t>CKL5</t>
+  </si>
+  <si>
+    <t>Silver Falls</t>
+  </si>
+  <si>
+    <t>CKB8</t>
+  </si>
+  <si>
+    <t>Snow Lake</t>
+  </si>
+  <si>
+    <t>CJE4</t>
+  </si>
+  <si>
+    <t>Somerset</t>
+  </si>
+  <si>
+    <t>CKC8</t>
+  </si>
+  <si>
+    <t>Souris Glenwood Industrial Air Park</t>
+  </si>
+  <si>
+    <t>CJX5</t>
+  </si>
+  <si>
+    <t>Southend / Hans Ulricksen Field</t>
+  </si>
+  <si>
+    <t>CKA9</t>
+  </si>
+  <si>
+    <t>South Indian Lake</t>
+  </si>
+  <si>
+    <t>CZSN</t>
+  </si>
+  <si>
+    <t>Spiritwood / H &amp; M Fast Farms</t>
+  </si>
+  <si>
+    <t>CHM2</t>
+  </si>
+  <si>
+    <t>Springdale</t>
+  </si>
+  <si>
+    <t>CCD2</t>
+  </si>
+  <si>
+    <t>Spring Valley (North)</t>
+  </si>
+  <si>
+    <t>CKP2</t>
+  </si>
+  <si>
+    <t>Starbuck</t>
+  </si>
+  <si>
+    <t>CKJ7</t>
+  </si>
+  <si>
+    <t>Steinbach</t>
+  </si>
+  <si>
+    <t>CJB3</t>
+  </si>
+  <si>
+    <t>Steinbach (South)</t>
+  </si>
+  <si>
+    <t>CKK7</t>
+  </si>
+  <si>
+    <t>Stenen / Clayton Air 3</t>
+  </si>
+  <si>
+    <t>CCA5</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Stephenville Dymond Airport</t>
+  </si>
+  <si>
+    <t>CYJT</t>
+  </si>
+  <si>
+    <t>aprt  rdo</t>
+  </si>
+  <si>
+    <t>Stony Rapids</t>
+  </si>
+  <si>
+    <t>CYSF</t>
+  </si>
+  <si>
+    <t>13-04Z</t>
+  </si>
+  <si>
+    <t>13-04Z O/T tfc</t>
+  </si>
+  <si>
+    <t>Strathclair</t>
+  </si>
+  <si>
+    <t>CJY5</t>
+  </si>
+  <si>
+    <t>Sussex</t>
+  </si>
+  <si>
+    <t>CCY3</t>
+  </si>
+  <si>
+    <t>Swan River</t>
+  </si>
+  <si>
+    <t>CZJN</t>
+  </si>
+  <si>
+    <t>Swan River / PVA1</t>
+  </si>
+  <si>
+    <t>CSR2</t>
+  </si>
+  <si>
+    <t>Swift Current</t>
+  </si>
+  <si>
+    <t>CYYN</t>
+  </si>
+  <si>
+    <t>123.375, 351.300</t>
+  </si>
+  <si>
+    <t>Tadoule Lake</t>
+  </si>
+  <si>
+    <t>CYBQ</t>
+  </si>
+  <si>
+    <t>CYQD</t>
+  </si>
+  <si>
+    <t>The Pas</t>
+  </si>
+  <si>
+    <t>The Pas / Grace Lake</t>
+  </si>
+  <si>
+    <t>CJR3</t>
+  </si>
+  <si>
+    <t>FISE Edmonton rdo (The Pas)</t>
+  </si>
+  <si>
+    <t>Thicket Portage</t>
+  </si>
+  <si>
+    <t>CZLQ</t>
+  </si>
+  <si>
+    <t>Thompson</t>
+  </si>
+  <si>
+    <t>CYTH</t>
+  </si>
+  <si>
+    <t>Tisdale</t>
+  </si>
+  <si>
+    <t>CJY3</t>
+  </si>
+  <si>
+    <t>Treherne</t>
+  </si>
+  <si>
+    <t>CKU2</t>
+  </si>
+  <si>
+    <t>Treherne (South Norfolk Airpark)</t>
+  </si>
+  <si>
+    <t>CTN6</t>
+  </si>
+  <si>
+    <t>Tyndall / Outback 40 Farm</t>
+  </si>
+  <si>
+    <t>CTO4</t>
+  </si>
+  <si>
+    <t>Unity</t>
+  </si>
+  <si>
+    <t>CKE8</t>
+  </si>
+  <si>
+    <t>Upper Kent</t>
+  </si>
+  <si>
+    <t>CCH2</t>
+  </si>
+  <si>
+    <t>Uranium City</t>
+  </si>
+  <si>
+    <t>CYBE</t>
+  </si>
+  <si>
+    <t>Utik Lake / Dennis G Punches Field</t>
+  </si>
+  <si>
+    <t>CDP3</t>
+  </si>
+  <si>
+    <t>Oxford House UNICOM</t>
+  </si>
+  <si>
+    <t>Oxford House (CYOH)</t>
+  </si>
+  <si>
+    <t>Virden (Gabrielle Farm)</t>
+  </si>
+  <si>
+    <t>CKR7</t>
+  </si>
+  <si>
+    <t>Virden Gabrielle tfc</t>
+  </si>
+  <si>
+    <t>Virden / R.J. (Bob) Andrew Field Regional</t>
+  </si>
+  <si>
+    <t>CYVD</t>
+  </si>
+  <si>
+    <t>Voisey's Bay</t>
+  </si>
+  <si>
+    <t>CVB2</t>
+  </si>
+  <si>
+    <t>Wabush</t>
+  </si>
+  <si>
+    <t>CYWK</t>
+  </si>
+  <si>
+    <t>122.000, 296.200</t>
+  </si>
+  <si>
+    <t>1100-0330Z‡</t>
+  </si>
+  <si>
+    <t>1100-0330Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Wadena</t>
+  </si>
+  <si>
+    <t>CKS7</t>
+  </si>
+  <si>
+    <t>Wakaw</t>
+  </si>
+  <si>
+    <t>CKT7</t>
+  </si>
+  <si>
+    <t>Watrous</t>
+  </si>
+  <si>
+    <t>CKU7</t>
+  </si>
+  <si>
+    <t>Weyburn</t>
+  </si>
+  <si>
+    <t>CJE3</t>
+  </si>
+  <si>
+    <t>Weyman Airpark</t>
+  </si>
+  <si>
+    <t>CCG3</t>
+  </si>
+  <si>
+    <t>Wheatland / Spud Plains</t>
+  </si>
+  <si>
+    <t>CRS5</t>
+  </si>
+  <si>
+    <t>Whitewood</t>
+  </si>
+  <si>
+    <t>CKY2</t>
+  </si>
+  <si>
+    <t>Winkler</t>
+  </si>
+  <si>
+    <t>CKZ7</t>
+  </si>
+  <si>
+    <t>Winnipeg / James Armstrong Richardson Intl</t>
+  </si>
+  <si>
+    <t>CYWG</t>
+  </si>
+  <si>
+    <t>118.300, 125.400</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>East</t>
+  </si>
+  <si>
+    <t>Base Ops</t>
+  </si>
+  <si>
+    <t>131.400, 308.800</t>
+  </si>
+  <si>
+    <t>Winnipeg / Lyncrest</t>
+  </si>
+  <si>
+    <t>CJL5</t>
+  </si>
+  <si>
+    <t>Winnipeg / St. Andrews</t>
+  </si>
+  <si>
+    <t>CYAV</t>
+  </si>
+  <si>
+    <t>Winnipeg Tml East</t>
+  </si>
+  <si>
+    <t>Winnipeg Tml West</t>
   </si>
 </sst>
 </file>
@@ -4301,7 +4721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1128"/>
+  <dimension ref="A1:G1196"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -25891,175 +26311,2522 @@
       </c>
     </row>
     <row r="1072" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1072" s="3"/>
-    </row>
-    <row r="1073" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1073" s="3"/>
-    </row>
-    <row r="1074" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1074" s="3"/>
-    </row>
-    <row r="1075" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1075" s="3"/>
-    </row>
-    <row r="1076" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1076" s="3"/>
-    </row>
-    <row r="1077" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1077" s="3"/>
-    </row>
-    <row r="1078" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1078" s="3"/>
-    </row>
-    <row r="1079" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1079" s="3"/>
-    </row>
-    <row r="1080" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1080" s="3"/>
-    </row>
-    <row r="1081" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1081" s="3"/>
-    </row>
-    <row r="1082" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1082" s="3"/>
-    </row>
-    <row r="1083" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1083" s="3"/>
-    </row>
-    <row r="1084" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1084" s="3"/>
-    </row>
-    <row r="1085" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1085" s="3"/>
-    </row>
-    <row r="1086" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1086" s="3"/>
-    </row>
-    <row r="1087" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1087" s="3"/>
-    </row>
-    <row r="1088" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1088" s="3"/>
-    </row>
-    <row r="1089" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1089" s="3"/>
-    </row>
-    <row r="1090" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1090" s="3"/>
-    </row>
-    <row r="1091" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1091" s="3"/>
-    </row>
-    <row r="1092" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1092" s="3"/>
-    </row>
-    <row r="1093" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1093" s="3"/>
-    </row>
-    <row r="1094" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1094" s="3"/>
-    </row>
-    <row r="1095" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1095" s="3"/>
-    </row>
-    <row r="1096" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1096" s="3"/>
-    </row>
-    <row r="1097" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1097" s="3"/>
-    </row>
-    <row r="1098" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1098" s="3"/>
-    </row>
-    <row r="1099" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1099" s="3"/>
-    </row>
-    <row r="1100" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1100" s="3"/>
-    </row>
-    <row r="1101" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1101" s="3"/>
-    </row>
-    <row r="1102" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1102" s="3"/>
-    </row>
-    <row r="1103" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1103" s="3"/>
-    </row>
-    <row r="1104" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1104" s="3"/>
-    </row>
-    <row r="1105" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1105" s="3"/>
-    </row>
-    <row r="1106" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1106" s="3"/>
-    </row>
-    <row r="1107" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1107" s="3"/>
-    </row>
-    <row r="1108" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1108" s="3"/>
-    </row>
-    <row r="1109" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1109" s="3"/>
-    </row>
-    <row r="1110" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1110" s="3"/>
-    </row>
-    <row r="1111" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1111" s="3"/>
-    </row>
-    <row r="1112" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1112" s="3"/>
-    </row>
-    <row r="1113" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1113" s="3"/>
-    </row>
-    <row r="1114" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1114" s="3"/>
-    </row>
-    <row r="1115" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1115" s="3"/>
-    </row>
-    <row r="1116" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1116" s="3"/>
-    </row>
-    <row r="1117" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1117" s="3"/>
-    </row>
-    <row r="1118" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1118" s="3"/>
-    </row>
-    <row r="1119" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1119" s="3"/>
-    </row>
-    <row r="1120" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1120" s="3"/>
-    </row>
-    <row r="1121" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1121" s="3"/>
-    </row>
-    <row r="1122" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1122" s="3"/>
-    </row>
-    <row r="1123" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1123" s="3"/>
-    </row>
-    <row r="1124" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1124" s="3"/>
-    </row>
-    <row r="1125" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1125" s="3"/>
-    </row>
-    <row r="1126" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1126" s="3"/>
-    </row>
-    <row r="1127" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1127" s="3"/>
-    </row>
-    <row r="1128" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1128" s="3"/>
+      <c r="A1072" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B1072" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C1072" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1072" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1072" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F1072" t="s">
+        <v>1294</v>
+      </c>
+      <c r="G1072" s="3">
+        <v>118.3</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1073" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B1073" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C1073" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1073" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1073" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1073" s="3">
+        <v>122.375</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1074" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B1074" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C1074" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1074" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1074" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1074" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1075" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B1075" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C1075" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1075" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1075" s="3">
+        <v>128.4</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1076" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B1076" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C1076" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1076" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1076" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F1076" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G1076" s="3">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1077" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B1077" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C1077" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1077" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1077" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F1077" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G1077" s="3">
+        <v>118.3</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1078" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B1078" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C1078" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1078" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1078" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1078" t="s">
+        <v>1294</v>
+      </c>
+      <c r="G1078" s="3">
+        <v>118.3</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1079" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B1079" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C1079" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1079" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1079" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1079" s="3">
+        <v>119.9</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1080" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B1080" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C1080" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1080" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1080" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1080" s="3">
+        <v>119.9</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1081" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B1081" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C1081" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1081" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1081" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1081" s="3">
+        <v>134.32499999999999</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1082" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B1082" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C1082" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1082" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1082" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1082" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1083" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B1083" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C1083" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1083" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1083" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1083" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1084" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B1084" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C1084" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1084" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1084" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1084" s="3">
+        <v>122.9</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1085" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B1085" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C1085" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1085" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1085" s="3">
+        <v>122.175</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1086" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B1086" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C1086" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1086" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1086" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1086" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1086" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1087" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B1087" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C1087" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1087" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1087" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1087" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1088" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B1088" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C1088" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1088" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1088" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1088" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1088" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1089" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B1089" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C1089" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1089" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1089" s="3">
+        <v>122.175</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1090" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B1090" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C1090" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1090" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1090" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1090" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1090" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1091" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B1091" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C1091" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1091" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1091" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1092" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B1092" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C1092" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1092" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1092" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1092" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1093" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B1093" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C1093" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1093" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1093" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1093" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1094" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B1094" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1094" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1094" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1094" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1094" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1094" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1095" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B1095" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C1095" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1095" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1095" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1095" s="3">
+        <v>122.9</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1096" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B1096" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C1096" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1096" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1096" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1096" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1097" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B1097" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C1097" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1097" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1097" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1097" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1098" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B1098" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C1098" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1098" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1098" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1098" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1099" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B1099" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C1099" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1099" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1099" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1099" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1100" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B1100" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C1100" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1100" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1100" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1100" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1100" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1101" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B1101" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C1101" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1101" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1101" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1101" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1102" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B1102" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C1102" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1102" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1102" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1102" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1103" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B1103" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C1103" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1103" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1103" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1103" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1104" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B1104" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C1104" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1104" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1104" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1104" s="3">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1105" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B1105" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C1105" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1105" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1105" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1105" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1106" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B1106" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C1106" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1106" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1106" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1106" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1106" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1107" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B1107" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C1107" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1107" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1107" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1107" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1108" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B1108" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C1108" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1108" t="s">
+        <v>235</v>
+      </c>
+      <c r="E1108" t="s">
+        <v>1342</v>
+      </c>
+      <c r="G1108" s="3" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1109" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B1109" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C1109" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1109" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1109" t="s">
+        <v>275</v>
+      </c>
+      <c r="G1109" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1110" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B1110" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C1110" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1110" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1110" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1110" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1111" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B1111" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C1111" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1111" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1111" t="s">
+        <v>1345</v>
+      </c>
+      <c r="G1111" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1112" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B1112" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C1112" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1112" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1112" t="s">
+        <v>807</v>
+      </c>
+      <c r="G1112" s="3">
+        <v>120.325</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1113" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B1113" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C1113" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1113" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1113" t="s">
+        <v>777</v>
+      </c>
+      <c r="F1113" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G1113" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1114" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B1114" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C1114" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1114" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1114" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1114" s="3">
+        <v>122.375</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1115" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B1115" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C1115" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1115" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1115" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1115" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1116" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B1116" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C1116" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1116" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1116" t="s">
+        <v>779</v>
+      </c>
+      <c r="F1116" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G1116" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1117" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B1117" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C1117" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1117" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1117" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1117" s="3">
+        <v>124.47499999999999</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1118" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B1118" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C1118" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1118" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1118" s="3">
+        <v>128.75</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1119" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B1119" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C1119" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1119" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1119" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1119" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1120" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B1120" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C1120" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1120" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1120" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1120" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1121" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1121" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C1121" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1121" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1121" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1121" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1122" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B1122" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1122" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1122" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1122" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1122" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1123" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B1123" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C1123" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1123" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1123" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1123" s="3" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1124" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B1124" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C1124" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1124" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1124" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1124" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1125" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B1125" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C1125" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1125" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1125" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1125" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1126" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B1126" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C1126" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1126" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1126" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1126" s="3">
+        <v>132.80000000000001</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1127" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B1127" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C1127" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1127" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1127" s="3">
+        <v>124.7</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1128" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B1128" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C1128" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1128" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1128" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1128" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1129" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B1129" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C1129" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1129" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1129" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1129" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1129" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1130" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B1130" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C1130" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1130" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1130" s="3">
+        <v>128.625</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1131" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B1131" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C1131" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1131" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1131" t="s">
+        <v>891</v>
+      </c>
+      <c r="F1131" t="s">
+        <v>892</v>
+      </c>
+      <c r="G1131" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1132" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B1132" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C1132" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1132" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1132" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1132" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1133" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B1133" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C1133" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1133" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1133" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1133" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1134" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B1134" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C1134" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1134" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1134" t="s">
+        <v>893</v>
+      </c>
+      <c r="F1134" t="s">
+        <v>894</v>
+      </c>
+      <c r="G1134" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1135" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B1135" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C1135" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1135" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1135" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1135" s="3">
+        <v>135.625</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1136" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B1136" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C1136" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1136" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1136" s="3">
+        <v>124.7</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1137" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B1137" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1137" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1137" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1137" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G1137" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1138" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B1138" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1138" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1138" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1138" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1138" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1139" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B1139" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1139" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1139" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1139" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1139" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1139" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1140" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B1140" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C1140" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1140" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1140" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1140" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1140" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1141" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B1141" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C1141" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1141" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1141" s="3">
+        <v>122.5</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1142" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B1142" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C1142" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1142" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1142" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1142" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1143" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B1143" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C1143" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1143" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1143" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1143" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1144" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B1144" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C1144" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1144" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1144" s="3">
+        <v>127.65</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1145" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B1145" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C1145" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1145" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1145" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1145" s="3">
+        <v>122.5</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1146" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B1146" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C1146" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1146" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1146" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1146" s="3">
+        <v>133.15</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1147" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B1147" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C1147" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1147" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1147" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1147" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1148" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B1148" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C1148" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1148" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1148" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1148" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1149" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B1149" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C1149" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1149" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1149" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1149" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1150" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B1150" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C1150" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1150" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1150" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1150" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1151" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B1151" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C1151" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1151" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1151" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1151" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1151" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1152" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B1152" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C1152" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1152" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1152" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1152" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1153" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B1153" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C1153" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1153" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1153" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1153" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1154" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B1154" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C1154" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1154" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1154" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F1154" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1154" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1155" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B1155" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C1155" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1155" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1155" t="s">
+        <v>1389</v>
+      </c>
+      <c r="G1155" s="3">
+        <v>122.125</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1156" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B1156" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C1156" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1156" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1156" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G1156" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1157" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B1157" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C1157" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1157" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1157" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1157" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1158" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B1158" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C1158" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1158" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1158" s="3">
+        <v>122.175</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1159" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B1159" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C1159" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1159" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1159" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1159" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1159" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1160" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B1160" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C1160" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1160" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1160" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1161" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B1161" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C1161" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1161" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1161" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1161" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1162" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B1162" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C1162" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1162" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1162" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1162" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1163" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B1163" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C1163" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1163" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1163" t="s">
+        <v>1400</v>
+      </c>
+      <c r="G1163" s="3">
+        <v>128.125</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1164" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B1164" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C1164" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1164" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1164" s="3">
+        <v>122.6</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1165" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B1165" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C1165" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1165" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1165" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1165" t="s">
+        <v>1401</v>
+      </c>
+      <c r="G1165" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1166" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B1166" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C1166" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1166" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1166" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1166" s="3">
+        <v>132.25</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1167" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B1167" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C1167" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1167" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1167" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1167" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1168" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B1168" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C1168" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1168" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1168" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1168" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1169" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B1169" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1169" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1169" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1169" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1169" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1170" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B1170" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1170" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1170" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1170" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1170" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1170" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1171" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B1171" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C1171" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1171" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1171" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1171" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1172" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B1172" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C1172" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1172" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1172" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1172" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1173" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B1173" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C1173" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1173" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1173" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1173" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1174" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B1174" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C1174" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1174" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1174" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1174" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1174" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1175" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B1175" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C1175" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1175" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1175" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1175" s="3">
+        <v>123.25</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1176" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B1176" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C1176" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1176" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1176" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1176" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1177" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B1177" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C1177" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1177" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1177" s="3">
+        <v>120.2</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1178" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B1178" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C1178" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1178" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1178" s="3">
+        <v>121.3</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1179" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B1179" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C1179" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1179" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1179" s="3">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1180" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C1180" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1180" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1180" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1181" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C1181" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1181" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1181" s="3">
+        <v>119.5</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1182" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C1182" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1182" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1182" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G1182" s="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1183" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C1183" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1183" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1183" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G1183" s="3">
+        <v>119.9</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1184" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C1184" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1184" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E1184" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G1184" s="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1185" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C1185" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1185" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E1185" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G1185" s="3">
+        <v>119.9</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1186" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C1186" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1186" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1186" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G1186" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1187" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B1187" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C1187" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1187" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1187" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1187" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1188" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B1188" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C1188" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1188" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1188" t="s">
+        <v>765</v>
+      </c>
+      <c r="G1188" s="3">
+        <v>125.8</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1189" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B1189" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C1189" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1189" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1189" t="s">
+        <v>765</v>
+      </c>
+      <c r="G1189" s="3">
+        <v>121.8</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1190" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C1190" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1190" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1190" t="s">
+        <v>765</v>
+      </c>
+      <c r="G1190" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1191" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C1191" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1191" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1191" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1191" t="s">
+        <v>766</v>
+      </c>
+      <c r="G1191" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1192" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C1192" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1192" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1192" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G1192" s="3">
+        <v>119.9</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1193" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C1193" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1193" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1193" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G1193" s="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1194" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B1194" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C1194" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1194" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1194" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G1194" s="3">
+        <v>119.9</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1195" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C1195" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1195" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E1195" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G1195" s="3">
+        <v>119.9</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1196" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C1196" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1196" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E1196" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G1196" s="3">
+        <v>121</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0705847-0B49-485C-A6FC-5E96550B586C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24779ABA-B8AD-4852-8DBA-EC15034D4B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6136" uniqueCount="1431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6219" uniqueCount="1451">
   <si>
     <t>AB</t>
   </si>
@@ -4332,6 +4332,66 @@
   </si>
   <si>
     <t>Winnipeg Tml West</t>
+  </si>
+  <si>
+    <t>Winterland</t>
+  </si>
+  <si>
+    <t>CCC2</t>
+  </si>
+  <si>
+    <t>Wollaston Lake</t>
+  </si>
+  <si>
+    <t>CZWL</t>
+  </si>
+  <si>
+    <t>Woodland / Kendall Farm</t>
+  </si>
+  <si>
+    <t>CWL4</t>
+  </si>
+  <si>
+    <t>Woodstock</t>
+  </si>
+  <si>
+    <t>CCD3</t>
+  </si>
+  <si>
+    <t>Wrong Lake Airport</t>
+  </si>
+  <si>
+    <t>CJG4</t>
+  </si>
+  <si>
+    <t>Wynyard / W.B. Needham Field</t>
+  </si>
+  <si>
+    <t>CYYO</t>
+  </si>
+  <si>
+    <t>York Landing</t>
+  </si>
+  <si>
+    <t>CZAC</t>
+  </si>
+  <si>
+    <t>Yorkton Regional</t>
+  </si>
+  <si>
+    <t>CYQV</t>
+  </si>
+  <si>
+    <t>119.650, 296.600</t>
+  </si>
+  <si>
+    <t>12-04Z O/T tfc</t>
+  </si>
+  <si>
+    <t>Zhoda</t>
+  </si>
+  <si>
+    <t>CKA4</t>
   </si>
 </sst>
 </file>
@@ -4721,7 +4781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1196"/>
+  <dimension ref="A1:G1212"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -28828,6 +28888,329 @@
         <v>121</v>
       </c>
     </row>
+    <row r="1197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1197" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C1197" t="s">
+        <v>741</v>
+      </c>
+      <c r="D1197" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1197" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1197" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1198" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C1198" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1198" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1198" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1198" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1199" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B1199" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C1199" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1199" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1199" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1199" s="3">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1200" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B1200" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C1200" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1200" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1200" s="3">
+        <v>122.075</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1201" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1201" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C1201" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1201" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1201" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1201" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1202" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B1202" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C1202" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1202" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1202" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1202" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1203" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B1203" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C1203" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1203" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1203" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1203" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1204" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B1204" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C1204" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1204" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1204" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1204" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1205" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B1205" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C1205" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1205" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1205" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1205" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1205" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1206" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B1206" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C1206" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1206" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1206" t="s">
+        <v>777</v>
+      </c>
+      <c r="F1206" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G1206" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1207" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B1207" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1207" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1207" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1207" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1208" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B1208" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C1208" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1208" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1208" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1208" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1209" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B1209" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1209" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1209" t="s">
+        <v>779</v>
+      </c>
+      <c r="F1209" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G1209" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1210" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B1210" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1210" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1210" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1210" s="3">
+        <v>132.52500000000001</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1211" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B1211" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C1211" t="s">
+        <v>719</v>
+      </c>
+      <c r="D1211" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1211" s="3">
+        <v>128.72499999999999</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1212" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B1212" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C1212" t="s">
+        <v>722</v>
+      </c>
+      <c r="D1212" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1212" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1212" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24779ABA-B8AD-4852-8DBA-EC15034D4B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BFE7D4-3DDC-4C6E-985C-8716F3FEC201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6219" uniqueCount="1451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6339" uniqueCount="1486">
   <si>
     <t>AB</t>
   </si>
@@ -4392,6 +4392,111 @@
   </si>
   <si>
     <t>CKA4</t>
+  </si>
+  <si>
+    <t>Ajax (Pr Ajax)</t>
+  </si>
+  <si>
+    <t>CAJ5</t>
+  </si>
+  <si>
+    <t>Akulivik</t>
+  </si>
+  <si>
+    <t>QC</t>
+  </si>
+  <si>
+    <t>CYKO</t>
+  </si>
+  <si>
+    <t>1230-2230Z‡</t>
+  </si>
+  <si>
+    <t>Alexandria</t>
+  </si>
+  <si>
+    <t>CNS4</t>
+  </si>
+  <si>
+    <t>Allan Park</t>
+  </si>
+  <si>
+    <t>CAP2</t>
+  </si>
+  <si>
+    <t>Alma</t>
+  </si>
+  <si>
+    <t>CYTF</t>
+  </si>
+  <si>
+    <t>Bagotville Tml</t>
+  </si>
+  <si>
+    <t>127.200, 227.600</t>
+  </si>
+  <si>
+    <t>1330-2030Z‡ Mon-Fri O/T tfc</t>
+  </si>
+  <si>
+    <t>Bagotville</t>
+  </si>
+  <si>
+    <t>Amos / Magny</t>
+  </si>
+  <si>
+    <t>CYEY</t>
+  </si>
+  <si>
+    <t>11-23Z Mon-Fri, 13-23Z‡ Sat-Sun O/T tfc</t>
+  </si>
+  <si>
+    <t>Angling Lake / Wapekeka</t>
+  </si>
+  <si>
+    <t>CKB6</t>
+  </si>
+  <si>
+    <t>Arthur (Damascus Field)</t>
+  </si>
+  <si>
+    <t>CDF6</t>
+  </si>
+  <si>
+    <t>Arthur (Peskett Field)</t>
+  </si>
+  <si>
+    <t>CPK9</t>
+  </si>
+  <si>
+    <t>Arthur (Walter's Field)</t>
+  </si>
+  <si>
+    <t>CPC3</t>
+  </si>
+  <si>
+    <t>CYAT</t>
+  </si>
+  <si>
+    <t>Attawapiskat</t>
+  </si>
+  <si>
+    <t>Atwood / Coghlin</t>
+  </si>
+  <si>
+    <t>CAT1</t>
+  </si>
+  <si>
+    <t>Aupaluk</t>
+  </si>
+  <si>
+    <t>CYLA</t>
+  </si>
+  <si>
+    <t>Ayr / Eagle Valley Private Airfield</t>
+  </si>
+  <si>
+    <t>CAY5</t>
   </si>
 </sst>
 </file>
@@ -4781,7 +4886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1212"/>
+  <dimension ref="A1:G1235"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -29211,6 +29316,475 @@
         <v>123.2</v>
       </c>
     </row>
+    <row r="1213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1213" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B1213" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C1213" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1213" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1213" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1213" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1214" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B1214" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C1214" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1214" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1214" t="s">
+        <v>367</v>
+      </c>
+      <c r="F1214" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1214" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1215" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B1215" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C1215" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1215" t="s">
+        <v>366</v>
+      </c>
+      <c r="F1215" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G1215" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1216" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B1216" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C1216" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1216" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1216" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1216" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1217" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B1217" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C1217" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1217" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1217" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1217" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1218" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B1218" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C1218" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1218" t="s">
+        <v>146</v>
+      </c>
+      <c r="E1218" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G1218" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1219" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B1219" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C1219" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1219" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1219" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1219" t="s">
+        <v>1465</v>
+      </c>
+      <c r="G1219" s="3">
+        <v>122.35</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1220" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B1220" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C1220" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1220" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1220" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1220" t="s">
+        <v>1465</v>
+      </c>
+      <c r="G1220" s="3">
+        <v>122.35</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1221" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B1221" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C1221" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1221" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1221" t="s">
+        <v>1466</v>
+      </c>
+      <c r="G1221" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1222" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B1222" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C1222" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1222" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E1222" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G1222" s="3">
+        <v>121.2</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1223" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B1223" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C1223" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1223" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1223" s="3">
+        <v>123.175</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1224" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B1224" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C1224" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1224" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1224" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1224" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G1224" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1225" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B1225" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C1225" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1225" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1225" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1225" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1226" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B1226" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C1226" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1226" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1226" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1226" s="3">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1227" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B1227" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C1227" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1227" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1227" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1227" s="3">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1228" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B1228" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C1228" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1228" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1228" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1228" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1228" s="3">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1229" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B1229" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C1229" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1229" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1229" t="s">
+        <v>275</v>
+      </c>
+      <c r="G1229" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1230" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B1230" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C1230" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1230" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1230" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1230" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1231" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B1231" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C1231" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1231" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1231" s="3">
+        <v>128.77500000000001</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1232" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B1232" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C1232" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1232" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1232" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1232" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1233" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B1233" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C1233" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1233" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1233" t="s">
+        <v>367</v>
+      </c>
+      <c r="F1233" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1233" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1234" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B1234" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C1234" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1234" t="s">
+        <v>366</v>
+      </c>
+      <c r="G1234" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1235" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B1235" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C1235" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1235" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1235" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1235" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BFE7D4-3DDC-4C6E-985C-8716F3FEC201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819E7E6E-29FB-4A3A-A5B1-E235ED95C50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6339" uniqueCount="1486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6461" uniqueCount="1521">
   <si>
     <t>AB</t>
   </si>
@@ -4497,6 +4497,111 @@
   </si>
   <si>
     <t>CAY5</t>
+  </si>
+  <si>
+    <t>CYBG</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>French</t>
+  </si>
+  <si>
+    <t>125.800, 302.500</t>
+  </si>
+  <si>
+    <t>119.000, 384.500</t>
+  </si>
+  <si>
+    <t>121.700, 275.800</t>
+  </si>
+  <si>
+    <t>126.200, 236.600, 337.700</t>
+  </si>
+  <si>
+    <t>Baie-Comeau</t>
+  </si>
+  <si>
+    <t>CYBC</t>
+  </si>
+  <si>
+    <t>RAAS Mont-Joli rdo</t>
+  </si>
+  <si>
+    <t>Mont-Joli rdo</t>
+  </si>
+  <si>
+    <t>Baie-Comeau (Manic 1)</t>
+  </si>
+  <si>
+    <t>CSL9</t>
+  </si>
+  <si>
+    <t>Bala</t>
+  </si>
+  <si>
+    <t>CBL8</t>
+  </si>
+  <si>
+    <t>Bala (Medora Lake)</t>
+  </si>
+  <si>
+    <t>CME3</t>
+  </si>
+  <si>
+    <t>Baldwin</t>
+  </si>
+  <si>
+    <t>CPB9</t>
+  </si>
+  <si>
+    <t>Baldwin West</t>
+  </si>
+  <si>
+    <t>CBW8</t>
+  </si>
+  <si>
+    <t>Bancroft</t>
+  </si>
+  <si>
+    <t>CNW3</t>
+  </si>
+  <si>
+    <t>Barry's Bay / Madawaska Valley Airpark</t>
+  </si>
+  <si>
+    <t>CNZ4</t>
+  </si>
+  <si>
+    <t>Bearskin Lake</t>
+  </si>
+  <si>
+    <t>CNE3</t>
+  </si>
+  <si>
+    <t>Beeton Field</t>
+  </si>
+  <si>
+    <t>CBF3</t>
+  </si>
+  <si>
+    <t>Belleville (Marker Field)</t>
+  </si>
+  <si>
+    <t>CNU4</t>
+  </si>
+  <si>
+    <t>Belwood (Baird Field)</t>
+  </si>
+  <si>
+    <t>CBF2</t>
+  </si>
+  <si>
+    <t>Bethany / Whitetail Valley Farm</t>
+  </si>
+  <si>
+    <t>CVF3</t>
   </si>
 </sst>
 </file>
@@ -4886,7 +4991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1235"/>
+  <dimension ref="A1:G1260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -29785,6 +29890,480 @@
         <v>123.2</v>
       </c>
     </row>
+    <row r="1236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1236" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B1236" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C1236" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1236" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1236" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1236" s="3">
+        <v>124.2</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1237" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B1237" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C1237" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1237" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1237" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1237" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1238" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B1238" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C1238" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1238" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1238" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1239" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B1239" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1239" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1239" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1240" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B1240" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1240" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1240" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1241" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B1241" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1241" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1242" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B1242" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1242" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G1242" s="3">
+        <v>121.2</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1243" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B1243" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1243" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1243" t="s">
+        <v>191</v>
+      </c>
+      <c r="G1243" s="3">
+        <v>344.6</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1244" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B1244" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1244" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1244" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G1244" s="3">
+        <v>118.3</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1245" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B1245" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1245" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1245" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1245" s="3">
+        <v>118.3</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1246" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B1246" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C1246" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1246" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1246" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1246" s="3">
+        <v>125.85</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1247" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B1247" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1247" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1247" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1247" s="3">
+        <v>128.15</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1248" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B1248" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1248" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1248" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1248" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1249" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B1249" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1249" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1249" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1249" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1250" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B1250" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C1250" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1250" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1250" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1250" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1251" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B1251" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C1251" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1251" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1251" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1251" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1251" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1252" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B1252" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1252" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1252" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1252" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1252" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1253" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B1253" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C1253" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1253" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1253" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1253" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1253" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1254" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B1254" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C1254" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1254" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1254" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1254" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1255" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B1255" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C1255" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1255" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1255" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1255" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1256" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B1256" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C1256" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1256" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1256" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1256" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1257" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B1257" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C1257" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1257" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1257" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1257" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1258" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B1258" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C1258" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1258" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1258" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1258" s="3">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1259" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B1259" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C1259" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1259" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1259" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1259" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G1260" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819E7E6E-29FB-4A3A-A5B1-E235ED95C50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{491A0533-000A-4891-B8F9-2B82C0040F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6461" uniqueCount="1521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6515" uniqueCount="1530">
   <si>
     <t>AB</t>
   </si>
@@ -4602,6 +4602,33 @@
   </si>
   <si>
     <t>CVF3</t>
+  </si>
+  <si>
+    <t>Big Trout Lake</t>
+  </si>
+  <si>
+    <t>CYTL</t>
+  </si>
+  <si>
+    <t>BlackStock / Martyn</t>
+  </si>
+  <si>
+    <t>CBM2</t>
+  </si>
+  <si>
+    <t>Bobcaygeon / Chesher Lakehurst</t>
+  </si>
+  <si>
+    <t>CLH5</t>
+  </si>
+  <si>
+    <t>Bonaventure</t>
+  </si>
+  <si>
+    <t>CYVB</t>
+  </si>
+  <si>
+    <t>11-23Z‡ Sun-Fri, ltd hrs Sat O/T tfc</t>
   </si>
 </sst>
 </file>
@@ -4991,7 +5018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1260"/>
+  <dimension ref="A1:G1270"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -30362,7 +30389,221 @@
       </c>
     </row>
     <row r="1260" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G1260" s="3"/>
+      <c r="A1260" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C1260" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1260" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1260" t="s">
+        <v>275</v>
+      </c>
+      <c r="G1260" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1261" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1261" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1261" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1261" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1262" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1262" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1262" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1262" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1263" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B1263" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1263" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1263" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1263" s="3">
+        <v>135.15</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1264" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B1264" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C1264" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1264" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1264" s="3">
+        <v>128.69999999999999</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1265" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B1265" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C1265" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1265" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1265" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1265" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1266" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B1266" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1266" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1266" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1266" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1267" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B1267" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1267" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1267" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1267" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1268" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B1268" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C1268" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1268" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1268" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1268" t="s">
+        <v>1529</v>
+      </c>
+      <c r="G1268" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1269" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B1269" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1269" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1269" t="s">
+        <v>1529</v>
+      </c>
+      <c r="G1269" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1270" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B1270" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C1270" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1270" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1270" s="3">
+        <v>122.05</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{491A0533-000A-4891-B8F9-2B82C0040F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C19BFE-E222-46AF-A0FC-83C1B20C8191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6515" uniqueCount="1530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6715" uniqueCount="1588">
   <si>
     <t>AB</t>
   </si>
@@ -4629,6 +4629,180 @@
   </si>
   <si>
     <t>11-23Z‡ Sun-Fri, ltd hrs Sat O/T tfc</t>
+  </si>
+  <si>
+    <t>Bracebridge (Goltz Farm)</t>
+  </si>
+  <si>
+    <t>CBG3</t>
+  </si>
+  <si>
+    <t>Bracebridge (Stone Wall Farm)</t>
+  </si>
+  <si>
+    <t>CSW4</t>
+  </si>
+  <si>
+    <t>Bracebridge (Tinkham Field)</t>
+  </si>
+  <si>
+    <t>CTA6</t>
+  </si>
+  <si>
+    <t>Bracebridge West</t>
+  </si>
+  <si>
+    <t>CWB2</t>
+  </si>
+  <si>
+    <t>Bradford</t>
+  </si>
+  <si>
+    <t>CPM7</t>
+  </si>
+  <si>
+    <t>Brechin / Ronan Aircraft</t>
+  </si>
+  <si>
+    <t>CDU7</t>
+  </si>
+  <si>
+    <t>Bromont (Roland Desourdy)</t>
+  </si>
+  <si>
+    <t>CZBM</t>
+  </si>
+  <si>
+    <t>12-22Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Bruce Mines / Kerr Field</t>
+  </si>
+  <si>
+    <t>CBM3</t>
+  </si>
+  <si>
+    <t>Brussels (Armstrong Field)</t>
+  </si>
+  <si>
+    <t>CPD4</t>
+  </si>
+  <si>
+    <t>No frequency assigned</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Camden East</t>
+  </si>
+  <si>
+    <t>CCE6</t>
+  </si>
+  <si>
+    <t>Camden East / Varty Lake</t>
+  </si>
+  <si>
+    <t>CVL3</t>
+  </si>
+  <si>
+    <t>Campbellville (Bellshill Airpark)</t>
+  </si>
+  <si>
+    <t>CMB5</t>
+  </si>
+  <si>
+    <t>Carey Lake</t>
+  </si>
+  <si>
+    <t>CNX3</t>
+  </si>
+  <si>
+    <t>Carignan (Bouthillier)</t>
+  </si>
+  <si>
+    <t>CRG3</t>
+  </si>
+  <si>
+    <t>Montreal</t>
+  </si>
+  <si>
+    <t>Carleton Place</t>
+  </si>
+  <si>
+    <t>CNR6</t>
+  </si>
+  <si>
+    <t>Carnarvon / Whistlewing</t>
+  </si>
+  <si>
+    <t>CRV3</t>
+  </si>
+  <si>
+    <t>Casey (Camp De Base)</t>
+  </si>
+  <si>
+    <t>SCQ4</t>
+  </si>
+  <si>
+    <t>Cat Lake</t>
+  </si>
+  <si>
+    <t>CYAC</t>
+  </si>
+  <si>
+    <t>Causapscal</t>
+  </si>
+  <si>
+    <t>CTF3</t>
+  </si>
+  <si>
+    <t>Cayuga (Bruce Field)</t>
+  </si>
+  <si>
+    <t>CCG5</t>
+  </si>
+  <si>
+    <t>Cayuga East</t>
+  </si>
+  <si>
+    <t>CAF2</t>
+  </si>
+  <si>
+    <t>Centralia (Essery Field)</t>
+  </si>
+  <si>
+    <t>CES5</t>
+  </si>
+  <si>
+    <t>Charlevoix</t>
+  </si>
+  <si>
+    <t>CYML</t>
+  </si>
+  <si>
+    <t>Chevery</t>
+  </si>
+  <si>
+    <t>CYHR</t>
+  </si>
+  <si>
+    <t>Chibougamau / Chapais</t>
+  </si>
+  <si>
+    <t>CYMT</t>
+  </si>
+  <si>
+    <t>RAAS Val d'Or rdo</t>
+  </si>
+  <si>
+    <t>11-01Z‡</t>
+  </si>
+  <si>
+    <t>Val d'Or rdo</t>
+  </si>
+  <si>
+    <t>11-01Z‡ O/T tfc</t>
   </si>
 </sst>
 </file>
@@ -4675,7 +4849,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4684,6 +4858,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5018,7 +5193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1270"/>
+  <dimension ref="A1:G1309"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -30605,6 +30780,798 @@
         <v>122.05</v>
       </c>
     </row>
+    <row r="1271" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1271" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B1271" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C1271" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1271" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1271" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1271" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1272" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B1272" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C1272" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1272" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1272" t="s">
+        <v>420</v>
+      </c>
+      <c r="G1272" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1273" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B1273" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1273" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1273" t="s">
+        <v>275</v>
+      </c>
+      <c r="G1273" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1274" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B1274" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C1274" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1274" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1274" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1274" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1275" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B1275" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C1275" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1275" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1275" t="s">
+        <v>124</v>
+      </c>
+      <c r="G1275" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1276" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B1276" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1276" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1276" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1276" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1277" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B1277" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1277" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1277" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1278" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B1278" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C1278" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1278" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1278" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1278" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1279" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B1279" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C1279" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1279" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1279" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1279" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1279" s="3">
+        <v>122.95</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1280" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B1280" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C1280" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1280" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1280" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1280" t="s">
+        <v>1544</v>
+      </c>
+      <c r="G1280" s="3">
+        <v>122.15</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1281" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B1281" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C1281" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1281" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1281" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1281" t="s">
+        <v>1544</v>
+      </c>
+      <c r="G1281" s="3">
+        <v>122.15</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1282" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B1282" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C1282" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1282" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1282" s="3">
+        <v>122.97499999999999</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1283" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B1283" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C1283" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1283" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1283" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1283" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1284" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B1284" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C1284" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1284" t="s">
+        <v>1549</v>
+      </c>
+      <c r="G1284" s="4" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1285" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B1285" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C1285" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1285" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1285" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1285" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1286" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B1286" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C1286" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1286" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1286" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1286" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1287" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B1287" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C1287" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1287" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1287" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1288" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B1288" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C1288" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1288" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1288" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1288" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1288" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1289" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B1289" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C1289" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1289" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1289" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1289" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1290" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B1290" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C1290" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1290" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1290" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G1290" s="3">
+        <v>134.15</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1291" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B1291" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C1291" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1291" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1291" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1291" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1292" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B1292" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C1292" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1292" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1292" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1292" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1293" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B1293" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C1293" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1293" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1293" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1293" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1294" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B1294" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1294" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1294" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1294" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1294" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1295" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B1295" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C1295" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1295" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1295" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1295" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1296" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B1296" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C1296" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1296" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1296" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1296" s="3">
+        <v>122.77500000000001</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1297" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B1297" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1297" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1297" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1297" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1297" s="3">
+        <v>122.77500000000001</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1298" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B1298" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C1298" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1298" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1298" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1298" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1299" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B1299" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C1299" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1299" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1299" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1299" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1299" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1300" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B1300" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C1300" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1300" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1300" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1300" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1301" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B1301" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C1301" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1301" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1301" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1301" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1302" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B1302" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C1302" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1302" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1302" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1302" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1303" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B1303" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C1303" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1303" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1303" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F1303" t="s">
+        <v>1585</v>
+      </c>
+      <c r="G1303" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1304" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B1304" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C1304" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1304" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1304" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1304" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1305" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B1305" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C1305" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1305" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1305" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1305" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1306" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B1306" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C1306" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1306" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1306" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F1306" t="s">
+        <v>1587</v>
+      </c>
+      <c r="G1306" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1307" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B1307" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C1307" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1307" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1307" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1307" s="3">
+        <v>127.3</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1308" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B1308" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C1308" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1308" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1308" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1308" s="3">
+        <v>126.25</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1309" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B1309" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C1309" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1309" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1309" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1309" s="3">
+        <v>128.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C19BFE-E222-46AF-A0FC-83C1B20C8191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B36B06-34C7-4CC9-8458-24FAE05E1A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6715" uniqueCount="1588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6844" uniqueCount="1625">
   <si>
     <t>AB</t>
   </si>
@@ -4803,6 +4803,117 @@
   </si>
   <si>
     <t>11-01Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Chicoutimi / St-Honore</t>
+  </si>
+  <si>
+    <t>CYRC</t>
+  </si>
+  <si>
+    <t>Bagotville Tml 888-813-8508</t>
+  </si>
+  <si>
+    <t>St-Honore</t>
+  </si>
+  <si>
+    <t>1300-0130Z‡; 13-03Z‡ Mon-Fri 1300-0130Z‡ Sat-Sun Oct 15-Nov 16 and Feb 15-Mar 2</t>
+  </si>
+  <si>
+    <t>0130-1300Z‡; 03-13Z‡ Mon-Fri 0130-1300Z‡ Sat-Sun Oct 15-Nov 16 and Feb 15-Mar 2</t>
+  </si>
+  <si>
+    <t>Chisasibi</t>
+  </si>
+  <si>
+    <t>CSU2</t>
+  </si>
+  <si>
+    <t>FISE Quebec rdo (La Grande)</t>
+  </si>
+  <si>
+    <t>Churchill / Truway Field</t>
+  </si>
+  <si>
+    <t>CKS3</t>
+  </si>
+  <si>
+    <t>Chute-St-Philippe</t>
+  </si>
+  <si>
+    <t>CCP3</t>
+  </si>
+  <si>
+    <t>Cobden / Bruce McPhail Mem</t>
+  </si>
+  <si>
+    <t>CPF4</t>
+  </si>
+  <si>
+    <t>CMB8</t>
+  </si>
+  <si>
+    <t>Combermere / Bonnie Brae Airfield</t>
+  </si>
+  <si>
+    <t>Conestogo / Largo Woods Field</t>
+  </si>
+  <si>
+    <t>CLW6</t>
+  </si>
+  <si>
+    <t>Conn</t>
+  </si>
+  <si>
+    <t>CCN4</t>
+  </si>
+  <si>
+    <t>Cookstown</t>
+  </si>
+  <si>
+    <t>CCT2</t>
+  </si>
+  <si>
+    <t>Cookstown / Kirby Field</t>
+  </si>
+  <si>
+    <t>CKF8</t>
+  </si>
+  <si>
+    <t>CRJ2</t>
+  </si>
+  <si>
+    <t>Cookstown / Platinum Park</t>
+  </si>
+  <si>
+    <t>CTH8</t>
+  </si>
+  <si>
+    <t>Cookstown / Tally-Ho Field</t>
+  </si>
+  <si>
+    <t>Copper Falls</t>
+  </si>
+  <si>
+    <t>COP5</t>
+  </si>
+  <si>
+    <t>Cottam</t>
+  </si>
+  <si>
+    <t>CRB2</t>
+  </si>
+  <si>
+    <t>Coulson / Norwood Dale Field</t>
+  </si>
+  <si>
+    <t>CAD9</t>
+  </si>
+  <si>
+    <t>Creemore</t>
+  </si>
+  <si>
+    <t>CCR9</t>
   </si>
 </sst>
 </file>
@@ -5193,7 +5304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1309"/>
+  <dimension ref="A1:G1334"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -31572,6 +31683,512 @@
         <v>128.75</v>
       </c>
     </row>
+    <row r="1310" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1310" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B1310" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C1310" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1310" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1310" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1310" s="3">
+        <v>134.80000000000001</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1311" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B1311" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C1311" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1311" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1311" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1311" s="3">
+        <v>124.95</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1312" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B1312" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C1312" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1312" t="s">
+        <v>146</v>
+      </c>
+      <c r="E1312" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1313" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B1313" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C1313" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1313" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1313" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F1313" t="s">
+        <v>1592</v>
+      </c>
+      <c r="G1313" s="3">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1314" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B1314" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C1314" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1314" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1314" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F1314" t="s">
+        <v>1592</v>
+      </c>
+      <c r="G1314" s="3">
+        <v>118.4</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1315" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B1315" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C1315" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1315" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1315" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1315" t="s">
+        <v>1593</v>
+      </c>
+      <c r="G1315" s="3">
+        <v>118.4</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1316" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B1316" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C1316" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1316" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1316" t="s">
+        <v>1466</v>
+      </c>
+      <c r="G1316" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1317" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B1317" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C1317" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1317" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E1317" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G1317" s="3">
+        <v>121.2</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1318" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B1318" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C1318" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1318" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1318" t="s">
+        <v>1596</v>
+      </c>
+      <c r="G1318" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1319" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B1319" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C1319" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1319" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1319" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1319" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1320" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B1320" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C1320" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1320" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1320" s="3">
+        <v>122.175</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1321" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B1321" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C1321" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1321" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1321" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1321" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1322" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B1322" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C1322" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1322" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1322" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1322" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1323" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B1323" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C1323" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1323" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1323" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1323" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1324" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B1324" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C1324" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1324" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1324" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1324" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1325" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B1325" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C1325" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1325" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1325" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1325" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1326" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B1326" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C1326" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1326" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1326" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1326" s="3">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1327" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B1327" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C1327" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1327" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1327" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1327" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1328" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B1328" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C1328" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1328" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1328" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1328" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1329" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B1329" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C1329" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1329" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1329" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1329" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1330" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B1330" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C1330" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1330" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1330" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1330" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1331" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B1331" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C1331" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1331" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1331" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1331" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1332" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B1332" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C1332" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1332" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1332" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1332" s="3">
+        <v>122.9</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1333" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B1333" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C1333" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1333" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1333" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1333" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1333" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1334" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B1334" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C1334" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1334" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1334" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1334" s="3">
+        <v>122.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B36B06-34C7-4CC9-8458-24FAE05E1A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96335B49-2BB8-4B8C-A8E9-E5FABE9FAE12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6844" uniqueCount="1625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6923" uniqueCount="1650">
   <si>
     <t>AB</t>
   </si>
@@ -4914,6 +4914,81 @@
   </si>
   <si>
     <t>CCR9</t>
+  </si>
+  <si>
+    <t>Danville</t>
+  </si>
+  <si>
+    <t>CDN2</t>
+  </si>
+  <si>
+    <t>Deep River / Rolph</t>
+  </si>
+  <si>
+    <t>CPH2</t>
+  </si>
+  <si>
+    <t>CYVZ</t>
+  </si>
+  <si>
+    <t>Detour Lake</t>
+  </si>
+  <si>
+    <t>CDT9</t>
+  </si>
+  <si>
+    <t>Drummondville</t>
+  </si>
+  <si>
+    <t>CSC3</t>
+  </si>
+  <si>
+    <t>Dundalk (Tripp Field)</t>
+  </si>
+  <si>
+    <t>CTF4</t>
+  </si>
+  <si>
+    <t>Dungannon</t>
+  </si>
+  <si>
+    <t>CDG3</t>
+  </si>
+  <si>
+    <t>Dunrobin / Django Field</t>
+  </si>
+  <si>
+    <t>CDJ8</t>
+  </si>
+  <si>
+    <t>Dunrobin / Parti Field</t>
+  </si>
+  <si>
+    <t>CPF3</t>
+  </si>
+  <si>
+    <t>Dunsford</t>
+  </si>
+  <si>
+    <t>CDU5</t>
+  </si>
+  <si>
+    <t>Du Rocher-Perce (Pabok)</t>
+  </si>
+  <si>
+    <t>CTG3</t>
+  </si>
+  <si>
+    <t>Dwight</t>
+  </si>
+  <si>
+    <t>CNF8</t>
+  </si>
+  <si>
+    <t>East Linton (Kerr Field)</t>
+  </si>
+  <si>
+    <t>CEL3</t>
   </si>
 </sst>
 </file>
@@ -5304,7 +5379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1334"/>
+  <dimension ref="A1:G1350"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -32189,6 +32264,323 @@
         <v>122.85</v>
       </c>
     </row>
+    <row r="1335" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1335" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B1335" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C1335" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1335" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1335" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1335" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1336" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B1336" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C1336" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1336" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1336" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1336" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1337" t="s">
+        <v>848</v>
+      </c>
+      <c r="B1337" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C1337" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1337" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1337" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1337" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1338" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B1338" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C1338" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1338" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1338" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1338" s="3">
+        <v>122.95</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1339" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B1339" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C1339" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1339" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1339" s="3">
+        <v>122.175</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1340" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B1340" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C1340" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1340" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1340" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1340" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1340" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1341" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B1341" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C1341" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1341" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1341" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1342" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B1342" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C1342" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1342" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1342" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1342" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1343" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B1343" t="s">
+        <v>1637</v>
+      </c>
+      <c r="C1343" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1343" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1343" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1343" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1344" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B1344" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C1344" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1344" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1344" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1344" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1345" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B1345" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C1345" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1345" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1345" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1345" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1346" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B1346" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C1346" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1346" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1346" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1346" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1347" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B1347" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C1347" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1347" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1347" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1347" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1347" s="3">
+        <v>122.35</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1348" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B1348" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C1348" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1348" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1348" s="3">
+        <v>122.97499999999999</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1349" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B1349" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C1349" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1349" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1349" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1349" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1350" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B1350" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C1350" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1350" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1350" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1350" s="3">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96335B49-2BB8-4B8C-A8E9-E5FABE9FAE12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1D4420-64B6-4299-A16D-8F59CC9FB967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6923" uniqueCount="1650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7051" uniqueCount="1695">
   <si>
     <t>AB</t>
   </si>
@@ -4989,6 +4989,141 @@
   </si>
   <si>
     <t>CEL3</t>
+  </si>
+  <si>
+    <t>Eastmain River</t>
+  </si>
+  <si>
+    <t>CZEM</t>
+  </si>
+  <si>
+    <t>aprt rdo English</t>
+  </si>
+  <si>
+    <t>14-21Z‡ Mon-Fri; 15-20Z‡ Sun</t>
+  </si>
+  <si>
+    <t>Eleonore</t>
+  </si>
+  <si>
+    <t>CEL8</t>
+  </si>
+  <si>
+    <t>Emsdale</t>
+  </si>
+  <si>
+    <t>CNA4</t>
+  </si>
+  <si>
+    <t>Englehart (Dave's Field)</t>
+  </si>
+  <si>
+    <t>CDF3</t>
+  </si>
+  <si>
+    <t>Essex</t>
+  </si>
+  <si>
+    <t>CNE9</t>
+  </si>
+  <si>
+    <t>Essex / Billing Airstrip</t>
+  </si>
+  <si>
+    <t>CEB8</t>
+  </si>
+  <si>
+    <t>Ethel</t>
+  </si>
+  <si>
+    <t>CPD2</t>
+  </si>
+  <si>
+    <t>Farnham</t>
+  </si>
+  <si>
+    <t>CSN7</t>
+  </si>
+  <si>
+    <t>Fergus (Holyoake Airfield)</t>
+  </si>
+  <si>
+    <t>CPY9</t>
+  </si>
+  <si>
+    <t>Fergus (Juergensen Field)</t>
+  </si>
+  <si>
+    <t>CPG7</t>
+  </si>
+  <si>
+    <t>Fergus (Vodarek Field)</t>
+  </si>
+  <si>
+    <t>CVF2</t>
+  </si>
+  <si>
+    <t>Flamboro Centre</t>
+  </si>
+  <si>
+    <t>CFC8</t>
+  </si>
+  <si>
+    <t>Flesherton (Smithorrs Field)</t>
+  </si>
+  <si>
+    <t>CFL4</t>
+  </si>
+  <si>
+    <t>Fontanges</t>
+  </si>
+  <si>
+    <t>CTU2</t>
+  </si>
+  <si>
+    <t>12-21Z‡ Thu only O/T tfc</t>
+  </si>
+  <si>
+    <t>Fordwich</t>
+  </si>
+  <si>
+    <t>CPH9</t>
+  </si>
+  <si>
+    <t>Forestville</t>
+  </si>
+  <si>
+    <t>CYFE</t>
+  </si>
+  <si>
+    <t>Fort Albany</t>
+  </si>
+  <si>
+    <t>CYFA</t>
+  </si>
+  <si>
+    <t>Fort Hope</t>
+  </si>
+  <si>
+    <t>CYFH</t>
+  </si>
+  <si>
+    <t>Fort Severn</t>
+  </si>
+  <si>
+    <t>CYER</t>
+  </si>
+  <si>
+    <t>French River / Alban</t>
+  </si>
+  <si>
+    <t>CFR5</t>
+  </si>
+  <si>
+    <t>Fullarton / Munro</t>
+  </si>
+  <si>
+    <t>CMR3</t>
   </si>
 </sst>
 </file>
@@ -5379,7 +5514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1350"/>
+  <dimension ref="A1:G1376"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -32581,6 +32716,517 @@
         <v>123</v>
       </c>
     </row>
+    <row r="1351" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1351" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B1351" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C1351" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1351" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1351" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F1351" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1351" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1352" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B1352" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C1352" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1352" t="s">
+        <v>366</v>
+      </c>
+      <c r="F1352" t="s">
+        <v>1653</v>
+      </c>
+      <c r="G1352" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1353" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B1353" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C1353" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1353" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1353" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1353" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1354" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B1354" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C1354" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1354" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1354" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1355" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B1355" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C1355" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1355" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1355" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1355" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1356" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B1356" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C1356" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1356" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1356" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1356" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1357" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B1357" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C1357" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1357" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1357" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1357" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1358" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B1358" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C1358" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1358" t="s">
+        <v>1549</v>
+      </c>
+      <c r="G1358" s="4" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1359" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B1359" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C1359" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1359" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1359" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1359" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1360" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B1360" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C1360" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1360" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1360" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1360" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1361" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B1361" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C1361" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1361" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1361" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1361" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1362" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B1362" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C1362" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1362" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1362" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1362" s="3">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1363" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B1363" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C1363" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1363" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1363" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1363" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1364" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B1364" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C1364" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1364" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1364" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1364" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1365" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B1365" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C1365" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1365" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1365" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1365" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1366" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B1366" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C1366" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1366" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1366" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1366" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G1366" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1367" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B1367" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C1367" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1367" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1367" s="3">
+        <v>122.175</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1368" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B1368" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C1368" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1368" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1368" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1368" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1369" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B1369" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C1369" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1369" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1369" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1369" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1370" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B1370" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C1370" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1370" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1370" s="3">
+        <v>122.97499999999999</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1371" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B1371" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C1371" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1371" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1371" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1371" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1372" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B1372" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C1372" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1372" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1372" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1372" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1373" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B1373" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C1373" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1373" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1373" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1373" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1374" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B1374" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C1374" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1374" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1374" s="3">
+        <v>124.55</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1375" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B1375" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C1375" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1375" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1375" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1375" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1376" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B1376" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C1376" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1376" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1376" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1376" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1D4420-64B6-4299-A16D-8F59CC9FB967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A212E24-9357-4DE0-B41F-759DEEB46DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7051" uniqueCount="1695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7111" uniqueCount="1705">
   <si>
     <t>AB</t>
   </si>
@@ -5124,6 +5124,36 @@
   </si>
   <si>
     <t>CMR3</t>
+  </si>
+  <si>
+    <t>Gaspe (Michel-Pouliot)</t>
+  </si>
+  <si>
+    <t>CYGP</t>
+  </si>
+  <si>
+    <t>Gilford</t>
+  </si>
+  <si>
+    <t>CGF6</t>
+  </si>
+  <si>
+    <t>Greenbank</t>
+  </si>
+  <si>
+    <t>CNP8</t>
+  </si>
+  <si>
+    <t>Harrow</t>
+  </si>
+  <si>
+    <t>CGL2</t>
+  </si>
+  <si>
+    <t>CSW6</t>
+  </si>
+  <si>
+    <t>Hastings / Sweetwater Farms</t>
   </si>
 </sst>
 </file>
@@ -5514,7 +5544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1376"/>
+  <dimension ref="A1:G1388"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -33227,6 +33257,246 @@
         <v>122.8</v>
       </c>
     </row>
+    <row r="1377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1377" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B1377" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C1377" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1377" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1377" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G1377" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1378" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B1378" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C1378" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1378" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1378" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1378" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1379" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B1379" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C1379" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1379" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1379" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1379" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1380" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B1380" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C1380" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1380" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1380" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1380" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1381" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B1381" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C1381" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1381" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1381" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1381" s="3">
+        <v>134.17500000000001</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1382" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C1382" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1382" t="s">
+        <v>235</v>
+      </c>
+      <c r="G1382" s="3">
+        <v>123.02500000000001</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1383" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B1383" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C1383" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1383" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1383" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1383" s="3">
+        <v>127.8</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1384" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C1384" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1384" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1384" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1384" s="3">
+        <v>124.9</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1385" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B1385" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C1385" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1385" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1385" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1385" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1386" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C1386" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1386" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1386" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1386" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1386" s="3">
+        <v>122.72499999999999</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1387" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C1387" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1387" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1387" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1387" s="3">
+        <v>122.9</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1388" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C1388" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1388" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1388" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1388" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A212E24-9357-4DE0-B41F-759DEEB46DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E413BF9B-B398-455B-876B-A748CC9AD63B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7111" uniqueCount="1705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7276" uniqueCount="1746">
   <si>
     <t>AB</t>
   </si>
@@ -5154,6 +5154,129 @@
   </si>
   <si>
     <t>Hastings / Sweetwater Farms</t>
+  </si>
+  <si>
+    <t>Havre St-Pierre</t>
+  </si>
+  <si>
+    <t>CYGV</t>
+  </si>
+  <si>
+    <t>RAAS Madeleine rdo</t>
+  </si>
+  <si>
+    <t>11-03Z‡</t>
+  </si>
+  <si>
+    <t>Madeleine rdo</t>
+  </si>
+  <si>
+    <t>11-03Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Hawkesbury (East)</t>
+  </si>
+  <si>
+    <t>CPG5</t>
+  </si>
+  <si>
+    <t>Hawkesbury</t>
+  </si>
+  <si>
+    <t>CNV4</t>
+  </si>
+  <si>
+    <t>Heathcote / Wilkinson Field</t>
+  </si>
+  <si>
+    <t>CWF4</t>
+  </si>
+  <si>
+    <t>Highgate</t>
+  </si>
+  <si>
+    <t>CNA2</t>
+  </si>
+  <si>
+    <t>Ile Aux Coudres</t>
+  </si>
+  <si>
+    <t>CTA3</t>
+  </si>
+  <si>
+    <t>Iles-De-La-Madeleine</t>
+  </si>
+  <si>
+    <t>CYGR</t>
+  </si>
+  <si>
+    <t>1000-0330Z‡</t>
+  </si>
+  <si>
+    <t>0330-1000Z‡</t>
+  </si>
+  <si>
+    <t>1000-0330Z‡ O/T Mont-Joli</t>
+  </si>
+  <si>
+    <t>Moncton Ctr (Grindstone)</t>
+  </si>
+  <si>
+    <t>Innerkip</t>
+  </si>
+  <si>
+    <t>CNR2</t>
+  </si>
+  <si>
+    <t>Inukjuak</t>
+  </si>
+  <si>
+    <t>CYPH</t>
+  </si>
+  <si>
+    <t>Iona Station (Bobier Strip)</t>
+  </si>
+  <si>
+    <t>COS2</t>
+  </si>
+  <si>
+    <t>Isle-Aux-Grues</t>
+  </si>
+  <si>
+    <t>CSH2</t>
+  </si>
+  <si>
+    <t>Montmagny Unicom</t>
+  </si>
+  <si>
+    <t>Ivujivik</t>
+  </si>
+  <si>
+    <t>CYIK</t>
+  </si>
+  <si>
+    <t>Joliette</t>
+  </si>
+  <si>
+    <t>CSG3</t>
+  </si>
+  <si>
+    <t>Joliette / St-Thomas</t>
+  </si>
+  <si>
+    <t>CLO2</t>
+  </si>
+  <si>
+    <t>Kakabeka Falls</t>
+  </si>
+  <si>
+    <t>CKG8</t>
+  </si>
+  <si>
+    <t>Kanawata Aeroparc</t>
+  </si>
+  <si>
+    <t>CSJ2</t>
   </si>
 </sst>
 </file>
@@ -5544,7 +5667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1388"/>
+  <dimension ref="A1:G1419"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -33497,6 +33620,656 @@
         <v>123.2</v>
       </c>
     </row>
+    <row r="1389" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1389" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C1389" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1389" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1389" t="s">
+        <v>1707</v>
+      </c>
+      <c r="F1389" t="s">
+        <v>1708</v>
+      </c>
+      <c r="G1389" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1390" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C1390" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1390" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1390" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F1390" t="s">
+        <v>1710</v>
+      </c>
+      <c r="G1390" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1391" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C1391" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1391" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1391" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1391" s="3">
+        <v>125.95</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1392" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C1392" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1392" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1392" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1392" s="3">
+        <v>128.30000000000001</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1393" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C1393" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1393" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1393" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1393" s="3">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1394" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C1394" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1394" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1394" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1394" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1395" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C1395" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1395" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1395" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1395" s="3">
+        <v>122.85</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1396" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B1396" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C1396" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1396" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1396" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1396" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1397" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1397" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1397" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1397" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1397" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1398" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C1398" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1398" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1398" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F1398" t="s">
+        <v>1723</v>
+      </c>
+      <c r="G1398" s="3">
+        <v>123.15</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1399" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C1399" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1399" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1399" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F1399" t="s">
+        <v>1724</v>
+      </c>
+      <c r="G1399" s="3">
+        <v>123.15</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1400" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1400" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1400" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1400" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1401" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B1401" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C1401" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1401" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1401" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1401" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1402" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C1402" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1402" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1402" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1402" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1402" s="3">
+        <v>123.15</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1403" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C1403" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1403" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1403" t="s">
+        <v>1726</v>
+      </c>
+      <c r="G1403" s="3">
+        <v>134.35</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1404" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C1404" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1404" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1404" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1404" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1405" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B1405" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C1405" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1405" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1405" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1405" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1406" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B1406" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C1406" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1406" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1406" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1406" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1407" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B1407" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C1407" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1407" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1407" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1407" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1407" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1408" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B1408" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C1408" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1408" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1408" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1408" s="3">
+        <v>119.15</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1409" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B1409" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C1409" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1409" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1409" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G1409" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1410" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B1410" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C1410" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1410" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1410" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1410" s="3">
+        <v>125.3</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1411" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B1411" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C1411" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1411" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1411" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1411" s="3">
+        <v>127.7</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1412" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B1412" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C1412" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1412" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1412" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1412" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1413" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B1413" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C1413" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1413" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1413" t="s">
+        <v>1735</v>
+      </c>
+      <c r="F1413" t="s">
+        <v>1544</v>
+      </c>
+      <c r="G1413" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1414" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B1414" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C1414" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1414" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1414" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F1414" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1414" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1415" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B1415" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C1415" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1415" t="s">
+        <v>366</v>
+      </c>
+      <c r="F1415" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G1415" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1416" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B1416" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C1416" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1416" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1416" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1416" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1417" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B1417" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C1417" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1417" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1417" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1417" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1418" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B1418" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C1418" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1418" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1418" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1418" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1419" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B1419" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C1419" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1419" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1419" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1419" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1419" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E413BF9B-B398-455B-876B-A748CC9AD63B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342C081F-BE1B-4BFB-8E60-D846915D2872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7276" uniqueCount="1746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7446" uniqueCount="1787">
   <si>
     <t>AB</t>
   </si>
@@ -5277,6 +5277,129 @@
   </si>
   <si>
     <t>CSJ2</t>
+  </si>
+  <si>
+    <t>Kangiqsualujjuaq (Georges River)</t>
+  </si>
+  <si>
+    <t>CYLU</t>
+  </si>
+  <si>
+    <t>Kangiqsujuaq (Wakeham Bay)</t>
+  </si>
+  <si>
+    <t>CYKG</t>
+  </si>
+  <si>
+    <t>Kangirsuk</t>
+  </si>
+  <si>
+    <t>CYAS</t>
+  </si>
+  <si>
+    <t>Kars / Rideau Valley Air Park</t>
+  </si>
+  <si>
+    <t>CPL3</t>
+  </si>
+  <si>
+    <t>Kasabonika</t>
+  </si>
+  <si>
+    <t>CYAQ</t>
+  </si>
+  <si>
+    <t>Kashechewan</t>
+  </si>
+  <si>
+    <t>CZKE</t>
+  </si>
+  <si>
+    <t>Kattiniq / Donaldson</t>
+  </si>
+  <si>
+    <t>CTP9</t>
+  </si>
+  <si>
+    <t>1230-2300Z‡ Mon-Fri O/T tfc</t>
+  </si>
+  <si>
+    <t>Keene / Elmhirst's Resort</t>
+  </si>
+  <si>
+    <t>CPS2</t>
+  </si>
+  <si>
+    <t>Keewaywin</t>
+  </si>
+  <si>
+    <t>CPV8</t>
+  </si>
+  <si>
+    <t>Kincardine / Shepherd's Landing</t>
+  </si>
+  <si>
+    <t>CKS9</t>
+  </si>
+  <si>
+    <t>Kingfisher Lake</t>
+  </si>
+  <si>
+    <t>CNM5</t>
+  </si>
+  <si>
+    <t>Kingston / Riverland</t>
+  </si>
+  <si>
+    <t>CRL9</t>
+  </si>
+  <si>
+    <t>Kirkfield / Balsam Lake</t>
+  </si>
+  <si>
+    <t>CKD8</t>
+  </si>
+  <si>
+    <t>Kirkfield / Dimkovski Airpark</t>
+  </si>
+  <si>
+    <t>CDM3</t>
+  </si>
+  <si>
+    <t>Kirkfield / Palestine</t>
+  </si>
+  <si>
+    <t>CKP4</t>
+  </si>
+  <si>
+    <t>Kleinburg (Tavares Field)</t>
+  </si>
+  <si>
+    <t>CTV4</t>
+  </si>
+  <si>
+    <t>Kuujjuaq</t>
+  </si>
+  <si>
+    <t>CYVP</t>
+  </si>
+  <si>
+    <t>122.300, 296.600</t>
+  </si>
+  <si>
+    <t>Kuujjuarapik</t>
+  </si>
+  <si>
+    <t>CYGW</t>
+  </si>
+  <si>
+    <t>RAAS La Grande rdo</t>
+  </si>
+  <si>
+    <t>123.475, 5680</t>
+  </si>
+  <si>
+    <t>La Grande rdo</t>
   </si>
 </sst>
 </file>
@@ -5667,7 +5790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1419"/>
+  <dimension ref="A1:G1452"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -34270,6 +34393,675 @@
         <v>122.8</v>
       </c>
     </row>
+    <row r="1420" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1420" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B1420" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C1420" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1420" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1420" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F1420" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1420" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1421" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B1421" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C1421" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1421" t="s">
+        <v>366</v>
+      </c>
+      <c r="G1421" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1422" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B1422" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C1422" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1422" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1422" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1422" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1423" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B1423" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C1423" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1423" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1423" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1423" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1424" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B1424" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C1424" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1424" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1424" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F1424" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1424" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1425" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B1425" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C1425" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1425" t="s">
+        <v>366</v>
+      </c>
+      <c r="F1425" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G1425" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1426" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B1426" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C1426" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1426" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1426" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1426" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1427" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B1427" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C1427" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1427" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1427" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F1427" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1427" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1428" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B1428" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C1428" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1428" t="s">
+        <v>366</v>
+      </c>
+      <c r="F1428" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G1428" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1429" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B1429" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C1429" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1429" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1429" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1429" s="3">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1430" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B1430" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C1430" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1430" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1430" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1430" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1431" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B1431" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C1431" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1431" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1431" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1431" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1432" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B1432" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C1432" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1432" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1432" t="s">
+        <v>1760</v>
+      </c>
+      <c r="G1432" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1433" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B1433" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C1433" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1433" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1433" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1433" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1433" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1434" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B1434" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C1434" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1434" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1434" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1434" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1435" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B1435" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C1435" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1435" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1435" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1435" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1436" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B1436" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C1436" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1436" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1436" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1436" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1437" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B1437" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C1437" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1437" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1437" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1437" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1438" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B1438" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C1438" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1438" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1438" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1438" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1438" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1439" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B1439" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C1439" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1439" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1439" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1439" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1440" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B1440" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C1440" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1440" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1440" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1440" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1441" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B1441" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C1441" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1441" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1441" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1441" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1442" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1442" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C1442" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1442" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1442" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1443" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1443" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C1443" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1443" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1443" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1443" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1444" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1444" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C1444" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1444" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1444" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1444" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1445" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1445" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C1445" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1445" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1445" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1445" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1446" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1446" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C1446" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1446" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1446" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1446" s="3">
+        <v>135.1</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1447" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B1447" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C1447" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1447" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1447" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G1447" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1448" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B1448" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C1448" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1448" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1448" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1448" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1449" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B1449" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C1449" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1449" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1449" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1449" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1450" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B1450" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C1450" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1450" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1450" t="s">
+        <v>1786</v>
+      </c>
+      <c r="G1450" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1451" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B1451" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C1451" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1451" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1451" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1451" s="3">
+        <v>124.35</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1452" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B1452" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C1452" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1452" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1452" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1452" s="3">
+        <v>125.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342C081F-BE1B-4BFB-8E60-D846915D2872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8D30FC-7363-4DAD-B60F-D5D2D4E38B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7446" uniqueCount="1787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7622" uniqueCount="1824">
   <si>
     <t>AB</t>
   </si>
@@ -5400,6 +5400,117 @@
   </si>
   <si>
     <t>La Grande rdo</t>
+  </si>
+  <si>
+    <t>La Agile (Mascouche)</t>
+  </si>
+  <si>
+    <t>CSA2</t>
+  </si>
+  <si>
+    <t>Lac-A-La-Tortue</t>
+  </si>
+  <si>
+    <t>CSL3</t>
+  </si>
+  <si>
+    <t>Lac Etchemin</t>
+  </si>
+  <si>
+    <t>CSC5</t>
+  </si>
+  <si>
+    <t>Lachute</t>
+  </si>
+  <si>
+    <t>CSE4</t>
+  </si>
+  <si>
+    <t>124.650, 268.300</t>
+  </si>
+  <si>
+    <t>Lac-Saint-Jean</t>
+  </si>
+  <si>
+    <t>CYDO</t>
+  </si>
+  <si>
+    <t>La Grand Riviere</t>
+  </si>
+  <si>
+    <t>CYGL</t>
+  </si>
+  <si>
+    <t>La Grande</t>
+  </si>
+  <si>
+    <t>La Grande-3</t>
+  </si>
+  <si>
+    <t>CYAD</t>
+  </si>
+  <si>
+    <t>La Grande-4</t>
+  </si>
+  <si>
+    <t>CYAH</t>
+  </si>
+  <si>
+    <t>La Macaza / Mont-Tremblant</t>
+  </si>
+  <si>
+    <t>CYFJ</t>
+  </si>
+  <si>
+    <t>Lancaster Airpark</t>
+  </si>
+  <si>
+    <t>CLA6</t>
+  </si>
+  <si>
+    <t>Lansdowne House</t>
+  </si>
+  <si>
+    <t>CYLH</t>
+  </si>
+  <si>
+    <t>La Romaine</t>
+  </si>
+  <si>
+    <t>CTT5</t>
+  </si>
+  <si>
+    <t>UNICOM French only</t>
+  </si>
+  <si>
+    <t>11-24Z Mon-Fri, 13-16Z, 17-20Z Sun O/T tfc</t>
+  </si>
+  <si>
+    <t>La Sarre</t>
+  </si>
+  <si>
+    <t>CSR8</t>
+  </si>
+  <si>
+    <t>La Tabatiere</t>
+  </si>
+  <si>
+    <t>CTU5</t>
+  </si>
+  <si>
+    <t>La Tuque</t>
+  </si>
+  <si>
+    <t>CYLQ</t>
+  </si>
+  <si>
+    <t>13-22Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Laurel / Whittington</t>
+  </si>
+  <si>
+    <t>CLW3</t>
   </si>
 </sst>
 </file>
@@ -5790,7 +5901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1452"/>
+  <dimension ref="A1:G1486"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -35062,6 +35173,701 @@
         <v>125.15</v>
       </c>
     </row>
+    <row r="1453" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1453" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B1453" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1453" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1453" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1453" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1453" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1454" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B1454" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C1454" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1454" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1454" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1454" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1454" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1455" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B1455" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C1455" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1455" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1455" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1455" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1455" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1456" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B1456" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C1456" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1456" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1456" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1456" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1456" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1457" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B1457" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C1457" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1457" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1457" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G1457" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1458" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B1458" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C1458" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1458" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1458" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1458" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1459" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B1459" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C1459" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1459" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1459" t="s">
+        <v>1800</v>
+      </c>
+      <c r="G1459" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1460" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B1460" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C1460" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1460" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1460" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1460" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1461" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B1461" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C1461" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1461" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1461" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1461" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1462" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B1462" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C1462" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1462" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1462" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1462" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1463" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B1463" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C1463" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1463" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1463" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1463" s="3">
+        <v>132.1</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1464" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B1464" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C1464" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1464" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1464" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1464" t="s">
+        <v>1544</v>
+      </c>
+      <c r="G1464" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1465" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B1465" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C1465" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1465" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1465" s="3">
+        <v>123.175</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1466" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B1466" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C1466" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1466" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1466" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1466" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1467" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B1467" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C1467" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1467" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1467" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1467" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1468" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B1468" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C1468" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1468" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1468" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1468" t="s">
+        <v>1544</v>
+      </c>
+      <c r="G1468" s="3">
+        <v>131.19999999999999</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1469" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B1469" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C1469" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1469" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1469" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1469" s="3">
+        <v>118.45</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1470" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B1470" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C1470" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1470" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1470" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1470" s="3">
+        <v>119.65</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1471" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B1471" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C1471" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1471" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1471" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1471" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1471" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1472" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B1472" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C1472" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1472" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1472" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1472" s="3">
+        <v>133.9</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1473" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B1473" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C1473" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1473" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1473" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1473" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1474" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B1474" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C1474" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1474" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1474" t="s">
+        <v>275</v>
+      </c>
+      <c r="G1474" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1475" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B1475" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C1475" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1475" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1475" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1475" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1476" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B1476" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C1476" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1476" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1476" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1476" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1477" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B1477" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C1477" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1477" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1477" s="3">
+        <v>128.4</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1478" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B1478" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C1478" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1478" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1478" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F1478" t="s">
+        <v>1814</v>
+      </c>
+      <c r="G1478" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1479" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B1479" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C1479" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1479" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1479" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1479" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1480" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B1480" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C1480" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1480" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1480" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1480" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1481" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B1481" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C1481" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1481" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1481" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1481" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1482" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B1482" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C1482" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1482" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1482" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1482" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1483" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B1483" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C1483" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1483" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1483" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1483" t="s">
+        <v>1821</v>
+      </c>
+      <c r="G1483" s="3">
+        <v>122.325</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1484" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B1484" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C1484" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1484" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1484" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1484" s="3">
+        <v>134.5</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1485" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B1485" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C1485" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1485" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1485" s="3">
+        <v>122.97499999999999</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1486" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B1486" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C1486" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1486" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1486" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1486" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8D30FC-7363-4DAD-B60F-D5D2D4E38B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0FE189-4F6A-4D68-86F9-6C1ED36F2826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7622" uniqueCount="1824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7778" uniqueCount="1864">
   <si>
     <t>AB</t>
   </si>
@@ -5511,6 +5511,126 @@
   </si>
   <si>
     <t>CLW3</t>
+  </si>
+  <si>
+    <t>Lebel-Sur-Quevillon</t>
+  </si>
+  <si>
+    <t>CSH4</t>
+  </si>
+  <si>
+    <t>Les Bergeronnes</t>
+  </si>
+  <si>
+    <t>CTH3</t>
+  </si>
+  <si>
+    <t>London / Chapeskie Field</t>
+  </si>
+  <si>
+    <t>CLC2</t>
+  </si>
+  <si>
+    <t>London / Pioneer Airpark</t>
+  </si>
+  <si>
+    <t>CPN8</t>
+  </si>
+  <si>
+    <t>London / Watson Airfield</t>
+  </si>
+  <si>
+    <t>CLW4</t>
+  </si>
+  <si>
+    <t>Louiseville</t>
+  </si>
+  <si>
+    <t>CSJ4</t>
+  </si>
+  <si>
+    <t>Lourdes-De-Blanc-Sablon</t>
+  </si>
+  <si>
+    <t>CYBX</t>
+  </si>
+  <si>
+    <t>Lourdes-De-Joliette</t>
+  </si>
+  <si>
+    <t>CSE3</t>
+  </si>
+  <si>
+    <t>Lucan</t>
+  </si>
+  <si>
+    <t>CPS4</t>
+  </si>
+  <si>
+    <t>Manic-5</t>
+  </si>
+  <si>
+    <t>CMN5</t>
+  </si>
+  <si>
+    <t>Maniwaki</t>
+  </si>
+  <si>
+    <t>CYMW</t>
+  </si>
+  <si>
+    <t>FISE Quebec rdo (Mont-Laurier)</t>
+  </si>
+  <si>
+    <t>Mansfield</t>
+  </si>
+  <si>
+    <t>CPV4</t>
+  </si>
+  <si>
+    <t>Matagami</t>
+  </si>
+  <si>
+    <t>CYNM</t>
+  </si>
+  <si>
+    <t>Matane / Russell-Burnett</t>
+  </si>
+  <si>
+    <t>CYME</t>
+  </si>
+  <si>
+    <t>Matane UNICOM</t>
+  </si>
+  <si>
+    <t>Matawatchan</t>
+  </si>
+  <si>
+    <t>CMW3</t>
+  </si>
+  <si>
+    <t>Mattawa</t>
+  </si>
+  <si>
+    <t>CMA2</t>
+  </si>
+  <si>
+    <t>Maxville</t>
+  </si>
+  <si>
+    <t>CMX2</t>
+  </si>
+  <si>
+    <t>Melbourne</t>
+  </si>
+  <si>
+    <t>CMN2</t>
+  </si>
+  <si>
+    <t>Miminiska</t>
+  </si>
+  <si>
+    <t>CPS5</t>
   </si>
 </sst>
 </file>
@@ -5901,7 +6021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1486"/>
+  <dimension ref="A1:G1516"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -35868,6 +35988,618 @@
         <v>123.2</v>
       </c>
     </row>
+    <row r="1487" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1487" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B1487" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C1487" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1487" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1487" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1487" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1488" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1488" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C1488" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1488" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1488" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1488" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1489" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B1489" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C1489" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1489" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1489" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1489" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1490" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B1490" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C1490" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1490" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1490" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1490" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1490" s="3">
+        <v>119.4</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1491" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B1491" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C1491" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1491" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1491" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1491" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1491" s="3">
+        <v>119.4</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1492" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B1492" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C1492" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1492" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1492" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1492" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1493" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B1493" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C1493" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1493" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1493" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1493" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1493" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1494" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B1494" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C1494" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1494" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1494" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G1494" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1495" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B1495" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C1495" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1495" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1495" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1495" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1496" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B1496" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C1496" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1496" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1496" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1496" s="3">
+        <v>128.15</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1497" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B1497" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C1497" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1497" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1497" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1497" s="3">
+        <v>124.35</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1498" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B1498" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C1498" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1498" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1498" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1498" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1499" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B1499" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C1499" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1499" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1499" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1499" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1500" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B1500" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C1500" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1500" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1500" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1500" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1501" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B1501" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C1501" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1501" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1501" t="s">
+        <v>1846</v>
+      </c>
+      <c r="G1501" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1502" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B1502" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C1502" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1502" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1502" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1502" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1502" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1503" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B1503" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C1503" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1503" t="s">
+        <v>1549</v>
+      </c>
+      <c r="G1503" s="4" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1504" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B1504" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C1504" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1504" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1504" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1504" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1505" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B1505" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C1505" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1505" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1505" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1505" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1506" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B1506" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C1506" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1506" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1506" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1506" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1507" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B1507" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C1507" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1507" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1507" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1507" s="3">
+        <v>127.45</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1508" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B1508" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C1508" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1508" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1508" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1508" s="3">
+        <v>125.3</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1509" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B1509" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C1509" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1509" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1509" t="s">
+        <v>1853</v>
+      </c>
+      <c r="F1509" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1509" s="3">
+        <v>122.72499999999999</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1510" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B1510" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C1510" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1510" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1510" s="3">
+        <v>122.175</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1511" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B1511" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C1511" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1511" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1511" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1511" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1512" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B1512" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C1512" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1512" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1512" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1512" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1513" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B1513" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C1513" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1513" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1513" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1513" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1514" t="s">
+        <v>261</v>
+      </c>
+      <c r="B1514" t="s">
+        <v>262</v>
+      </c>
+      <c r="C1514" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1514" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1514" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1514" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1515" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B1515" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C1515" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1515" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1515" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1515" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1516" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B1516" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C1516" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1516" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1516" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1516" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1516" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0FE189-4F6A-4D68-86F9-6C1ED36F2826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10A870D-3AB2-42DA-A014-9D1C43427E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7778" uniqueCount="1864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7844" uniqueCount="1876">
   <si>
     <t>AB</t>
   </si>
@@ -5631,6 +5631,42 @@
   </si>
   <si>
     <t>CPS5</t>
+  </si>
+  <si>
+    <t>Mont-Joli</t>
+  </si>
+  <si>
+    <t>CYYY</t>
+  </si>
+  <si>
+    <t>FISE Quebec</t>
+  </si>
+  <si>
+    <t>134.650, 227.200</t>
+  </si>
+  <si>
+    <t>Mont-Laurier</t>
+  </si>
+  <si>
+    <t>CSD4</t>
+  </si>
+  <si>
+    <t>Montmagny</t>
+  </si>
+  <si>
+    <t>CSE5</t>
+  </si>
+  <si>
+    <t>1100-2130Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Montreal / Aeroparc Ile Perrot</t>
+  </si>
+  <si>
+    <t>CSP6</t>
+  </si>
+  <si>
+    <t>Montreal Tml</t>
   </si>
 </sst>
 </file>
@@ -6021,7 +6057,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1516"/>
+  <dimension ref="A1:G1529"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -36600,6 +36636,266 @@
         <v>122.8</v>
       </c>
     </row>
+    <row r="1517" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1517" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B1517" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C1517" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1517" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1517" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1518" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B1518" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C1518" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1518" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1518" t="s">
+        <v>1866</v>
+      </c>
+      <c r="G1518" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1519" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B1519" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C1519" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1519" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1519" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1519" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1520" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B1520" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C1520" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1520" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1520" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1520" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1521" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B1521" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C1521" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1521" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1521" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1521" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1522" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B1522" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C1522" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1522" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1522" t="s">
+        <v>1846</v>
+      </c>
+      <c r="G1522" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1523" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B1523" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C1523" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1523" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1523" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1523" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1523" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1524" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B1524" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C1524" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1524" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1524" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1524" s="3">
+        <v>126.575</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1525" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B1525" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C1525" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1525" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1525" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1525" s="3">
+        <v>123.425</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1526" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B1526" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C1526" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1526" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1526" t="s">
+        <v>1872</v>
+      </c>
+      <c r="G1526" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1527" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B1527" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C1527" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1527" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1527" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G1527" s="3">
+        <v>119.9</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1528" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B1528" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C1528" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1528" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1528" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1528" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1529" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B1529" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C1529" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1529" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E1529" t="s">
+        <v>1875</v>
+      </c>
+      <c r="G1529" s="3">
+        <v>134.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10A870D-3AB2-42DA-A014-9D1C43427E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1DF776-0CAD-4C3E-BA31-4DBC4F2878FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7844" uniqueCount="1876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8117" uniqueCount="1918">
   <si>
     <t>AB</t>
   </si>
@@ -5667,6 +5667,132 @@
   </si>
   <si>
     <t>Montreal Tml</t>
+  </si>
+  <si>
+    <t>Montreal / Met (Aeroport Metropolitain De Montreal)</t>
+  </si>
+  <si>
+    <t>CYHU</t>
+  </si>
+  <si>
+    <t>RAAS Rouyn rdo</t>
+  </si>
+  <si>
+    <t>1045-0500Z‡ Mon-Fri, 1045-0300Z‡ Sat-Sun Apr-Oct; 1045-0400Z‡Mon-Fi, 1045-0100Z‡ Sat-Sun Nov-Mar</t>
+  </si>
+  <si>
+    <t>0500-1045Z‡ Tue-Sat, 0300-1045Z‡ Sun-Mon Apr-Oct; 0400-1045Z‡Tue-Sat, 0100-1045Z‡ Sun-Mon Nov-Mar</t>
+  </si>
+  <si>
+    <t>St-Hubert</t>
+  </si>
+  <si>
+    <t>St-Hubert (VFR ARR North)</t>
+  </si>
+  <si>
+    <t>St-Hubert (VFR ARR South &amp; East)</t>
+  </si>
+  <si>
+    <t>Rouyn rdo</t>
+  </si>
+  <si>
+    <t>125.150, 268.300</t>
+  </si>
+  <si>
+    <t>VFR ADF</t>
+  </si>
+  <si>
+    <t>Mil</t>
+  </si>
+  <si>
+    <t>438 Sqn Ops</t>
+  </si>
+  <si>
+    <t>322.100, 135.900</t>
+  </si>
+  <si>
+    <t>Montreal / (Mirabel)</t>
+  </si>
+  <si>
+    <t>CYMX</t>
+  </si>
+  <si>
+    <t>Mirabel</t>
+  </si>
+  <si>
+    <t>03-11Z‡</t>
+  </si>
+  <si>
+    <t>GND ADV</t>
+  </si>
+  <si>
+    <t>Montreal / Pierre Elliott Trudeau Intl</t>
+  </si>
+  <si>
+    <t>CYUL</t>
+  </si>
+  <si>
+    <t>APRON</t>
+  </si>
+  <si>
+    <t>Montreal (West)</t>
+  </si>
+  <si>
+    <t>Montreal (East)</t>
+  </si>
+  <si>
+    <t>121.000, 275.800</t>
+  </si>
+  <si>
+    <t>119.300, 119.900, 124.300, 267.100</t>
+  </si>
+  <si>
+    <t>118.900, 126.900, 132.850, 268.300</t>
+  </si>
+  <si>
+    <t>120.420, 124.650, 268.300</t>
+  </si>
+  <si>
+    <t>Montral / St-Lazare</t>
+  </si>
+  <si>
+    <t>CST3</t>
+  </si>
+  <si>
+    <t>Mont-Tremblant / St-Jovite</t>
+  </si>
+  <si>
+    <t>CSZ3</t>
+  </si>
+  <si>
+    <t>Mount Brydges / Warren Field</t>
+  </si>
+  <si>
+    <t>CWF3</t>
+  </si>
+  <si>
+    <t>Muskrat Dam</t>
+  </si>
+  <si>
+    <t>CZMD</t>
+  </si>
+  <si>
+    <t>Nairn (Triple Nickel)</t>
+  </si>
+  <si>
+    <t>CTN8</t>
+  </si>
+  <si>
+    <t>CYNA</t>
+  </si>
+  <si>
+    <t>Natashquan</t>
+  </si>
+  <si>
+    <t>13-23Z‡</t>
+  </si>
+  <si>
+    <t>13-23Z‡ O/T tfc</t>
   </si>
 </sst>
 </file>
@@ -6057,7 +6183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1529"/>
+  <dimension ref="A1:G1579"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -36896,6 +37022,1045 @@
         <v>134.15</v>
       </c>
     </row>
+    <row r="1530" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1530" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1530" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C1530" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1530" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1530" t="s">
+        <v>1878</v>
+      </c>
+      <c r="F1530" t="s">
+        <v>1880</v>
+      </c>
+      <c r="G1530" s="3">
+        <v>118.4</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1531" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1531" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C1531" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1531" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1531" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F1531" t="s">
+        <v>1879</v>
+      </c>
+      <c r="G1531" s="3">
+        <v>124.9</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1532" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1532" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C1532" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1532" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1532" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F1532" t="s">
+        <v>1879</v>
+      </c>
+      <c r="G1532" s="3">
+        <v>124.1</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1533" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1533" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C1533" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1533" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1533" t="s">
+        <v>1881</v>
+      </c>
+      <c r="F1533" t="s">
+        <v>1879</v>
+      </c>
+      <c r="G1533" s="3">
+        <v>126.4</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1534" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1534" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C1534" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1534" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1534" t="s">
+        <v>1882</v>
+      </c>
+      <c r="F1534" t="s">
+        <v>1879</v>
+      </c>
+      <c r="G1534" s="3">
+        <v>118.4</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1535" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1535" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C1535" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1535" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1535" t="s">
+        <v>1883</v>
+      </c>
+      <c r="F1535" t="s">
+        <v>1879</v>
+      </c>
+      <c r="G1535" s="3">
+        <v>121.3</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1536" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1536" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C1536" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1536" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1536" t="s">
+        <v>1884</v>
+      </c>
+      <c r="F1536" t="s">
+        <v>1880</v>
+      </c>
+      <c r="G1536" s="3">
+        <v>118.4</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1537" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1537" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C1537" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1537" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1537" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G1537" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1538" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1538" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C1538" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1538" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1538" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G1538" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1539" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1539" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C1539" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1539" t="s">
+        <v>1886</v>
+      </c>
+      <c r="E1539" t="s">
+        <v>1875</v>
+      </c>
+      <c r="G1539" s="3">
+        <v>125.15</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1540" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1540" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C1540" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1540" t="s">
+        <v>1887</v>
+      </c>
+      <c r="E1540" t="s">
+        <v>1888</v>
+      </c>
+      <c r="G1540" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1541" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1541" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C1541" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1541" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1541" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F1541" t="s">
+        <v>1880</v>
+      </c>
+      <c r="G1541" s="3">
+        <v>124.9</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1542" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1542" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C1542" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1542" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1542" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F1542" t="s">
+        <v>1880</v>
+      </c>
+      <c r="G1542" s="3">
+        <v>124.1</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1543" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B1543" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C1543" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1543" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1543" t="s">
+        <v>1892</v>
+      </c>
+      <c r="F1543" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1543" s="3">
+        <v>119.1</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1544" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B1544" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C1544" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1544" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1544" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1544" s="3">
+        <v>125.7</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1545" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B1545" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C1545" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1545" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1545" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1545" s="3">
+        <v>126.1</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1546" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B1546" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C1546" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1546" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1546" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1546" s="3">
+        <v>122.4</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1547" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B1547" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C1547" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1547" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1547" t="s">
+        <v>1708</v>
+      </c>
+      <c r="G1547" s="3">
+        <v>121.8</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1548" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B1548" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C1548" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1548" t="s">
+        <v>1894</v>
+      </c>
+      <c r="F1548" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1548" s="3">
+        <v>121.8</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1549" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B1549" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C1549" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1549" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1549" t="s">
+        <v>1708</v>
+      </c>
+      <c r="G1549" s="3">
+        <v>119.1</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1550" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B1550" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C1550" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1550" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1550" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1550" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1550" s="3">
+        <v>119.1</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1551" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B1551" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C1551" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1551" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1551" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G1551" s="3" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1552" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B1552" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C1552" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1552" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1552" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G1552" s="3" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1553" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B1553" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C1553" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1553" t="s">
+        <v>1886</v>
+      </c>
+      <c r="E1553" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G1553" s="3">
+        <v>134.15</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1554" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1554" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C1554" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1554" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1554" t="s">
+        <v>1866</v>
+      </c>
+      <c r="G1554" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1555" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1555" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C1555" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1555" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1555" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1555" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1556" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1556" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C1556" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1556" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1556" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1556" s="3">
+        <v>133.69999999999999</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1557" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1557" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C1557" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1557" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1557" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1557" s="3">
+        <v>127.5</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1558" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1558" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C1558" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1558" t="s">
+        <v>146</v>
+      </c>
+      <c r="E1558" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G1558" s="3">
+        <v>125.6</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1559" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1559" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C1559" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1559" t="s">
+        <v>1897</v>
+      </c>
+      <c r="E1559" t="s">
+        <v>1898</v>
+      </c>
+      <c r="G1559" s="3">
+        <v>122.27500000000001</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1560" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1560" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C1560" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1560" t="s">
+        <v>1897</v>
+      </c>
+      <c r="E1560" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G1560" s="3">
+        <v>122.075</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1561" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1561" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C1561" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1561" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1561" t="s">
+        <v>1898</v>
+      </c>
+      <c r="G1561" s="3" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1562" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1562" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C1562" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1562" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1562" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G1562" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1563" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1563" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C1563" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1563" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1563" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G1563" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1564" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1564" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C1564" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1564" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1564" t="s">
+        <v>1875</v>
+      </c>
+      <c r="G1564" s="3" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1565" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1565" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C1565" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1565" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1565" t="s">
+        <v>1875</v>
+      </c>
+      <c r="G1565" s="3" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1566" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1566" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C1566" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1566" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E1566" t="s">
+        <v>1875</v>
+      </c>
+      <c r="G1566" s="3">
+        <v>134.15</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1567" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B1567" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C1567" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1567" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1567" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1567" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1567" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1568" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B1568" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C1568" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1568" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1568" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1568" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1569" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B1569" t="s">
+        <v>1909</v>
+      </c>
+      <c r="C1569" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1569" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1569" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1569" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1570" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B1570" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C1570" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1570" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1570" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1570" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1571" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B1571" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C1571" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1571" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1571" s="3">
+        <v>124.45</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1572" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B1572" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C1572" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1572" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1572" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1572" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1573" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B1573" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C1573" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1573" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1573" t="s">
+        <v>1707</v>
+      </c>
+      <c r="F1573" t="s">
+        <v>1916</v>
+      </c>
+      <c r="G1573" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1574" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B1574" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C1574" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1574" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1574" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1574" s="3">
+        <v>123.85</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1575" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B1575" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C1575" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1575" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1575" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1575" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1576" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B1576" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C1576" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1576" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1576" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F1576" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G1576" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1577" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B1577" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C1577" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1577" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1577" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1577" s="3">
+        <v>134.82499999999999</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1578" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B1578" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C1578" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1578" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1578" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1578" s="3">
+        <v>126.25</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1579" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B1579" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C1579" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1579" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1579" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1579" s="3">
+        <v>125.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1DF776-0CAD-4C3E-BA31-4DBC4F2878FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29A04C2-93FA-4B41-8917-64B32E431BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8117" uniqueCount="1918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8321" uniqueCount="1980">
   <si>
     <t>AB</t>
   </si>
@@ -5793,6 +5793,192 @@
   </si>
   <si>
     <t>13-23Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Nemiscau</t>
+  </si>
+  <si>
+    <t>CYHH</t>
+  </si>
+  <si>
+    <t>Newburgh</t>
+  </si>
+  <si>
+    <t>CNB6</t>
+  </si>
+  <si>
+    <t>Newtonville / Steeves Field</t>
+  </si>
+  <si>
+    <t>CNT9</t>
+  </si>
+  <si>
+    <t>Nixon</t>
+  </si>
+  <si>
+    <t>CNX8</t>
+  </si>
+  <si>
+    <t>Norland / Trotter</t>
+  </si>
+  <si>
+    <t>CNR5</t>
+  </si>
+  <si>
+    <t>North Spirit Lake</t>
+  </si>
+  <si>
+    <t>CKQ3</t>
+  </si>
+  <si>
+    <t>Ogoki Post</t>
+  </si>
+  <si>
+    <t>CYKP</t>
+  </si>
+  <si>
+    <t>Omemee</t>
+  </si>
+  <si>
+    <t>CME2</t>
+  </si>
+  <si>
+    <t>Opapimiskan Lake</t>
+  </si>
+  <si>
+    <t>CKM8</t>
+  </si>
+  <si>
+    <t>Orangeville / Castlewood Field</t>
+  </si>
+  <si>
+    <t>CPV2</t>
+  </si>
+  <si>
+    <t>Orangeville / Laurel</t>
+  </si>
+  <si>
+    <t>COL2</t>
+  </si>
+  <si>
+    <t>Orono Field</t>
+  </si>
+  <si>
+    <t>COR3</t>
+  </si>
+  <si>
+    <t>Orono / Hawkefield</t>
+  </si>
+  <si>
+    <t>CHF4</t>
+  </si>
+  <si>
+    <t>Ottawa / Casselman (Shea Field)</t>
+  </si>
+  <si>
+    <t>CSF7</t>
+  </si>
+  <si>
+    <t>Ottawa / Embrun</t>
+  </si>
+  <si>
+    <t>CPR2</t>
+  </si>
+  <si>
+    <t>Embrun tfc</t>
+  </si>
+  <si>
+    <t>Ottawa / Gatineau</t>
+  </si>
+  <si>
+    <t>CYND</t>
+  </si>
+  <si>
+    <t>Gatineau</t>
+  </si>
+  <si>
+    <t>1130-0215Z‡</t>
+  </si>
+  <si>
+    <t>Gatineau rdo</t>
+  </si>
+  <si>
+    <t>1130-0215Z‡ O/T ATF</t>
+  </si>
+  <si>
+    <t>127.700, 128.175</t>
+  </si>
+  <si>
+    <t>Ottawa Tml</t>
+  </si>
+  <si>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>CYPP</t>
+  </si>
+  <si>
+    <t>Parkhill (Yellow Gold)</t>
+  </si>
+  <si>
+    <t>CYG2</t>
+  </si>
+  <si>
+    <t>Peawanuck</t>
+  </si>
+  <si>
+    <t>CYPO</t>
+  </si>
+  <si>
+    <t>Winnigep Ctr</t>
+  </si>
+  <si>
+    <t>Petrolia / Butler Airfield</t>
+  </si>
+  <si>
+    <t>CBA7</t>
+  </si>
+  <si>
+    <t>Picton (Greenbush)</t>
+  </si>
+  <si>
+    <t>CGB3</t>
+  </si>
+  <si>
+    <t>Pikangikum</t>
+  </si>
+  <si>
+    <t>CYPM</t>
+  </si>
+  <si>
+    <t>Pintendre</t>
+  </si>
+  <si>
+    <t>CPT9</t>
+  </si>
+  <si>
+    <t>Plattsville (Edward's Air Base)</t>
+  </si>
+  <si>
+    <t>CLB2</t>
+  </si>
+  <si>
+    <t>Plevna / Tomvale</t>
+  </si>
+  <si>
+    <t>CNA9</t>
+  </si>
+  <si>
+    <t>Poplar Hill</t>
+  </si>
+  <si>
+    <t>CPV7</t>
+  </si>
+  <si>
+    <t>Port Carling</t>
+  </si>
+  <si>
+    <t>CPC2</t>
   </si>
 </sst>
 </file>
@@ -6183,7 +6369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1579"/>
+  <dimension ref="A1:G1619"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -38061,6 +38247,815 @@
         <v>125.3</v>
       </c>
     </row>
+    <row r="1580" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1580" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B1580" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C1580" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1580" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1580" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1580" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1581" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B1581" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C1581" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1581" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1581" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1581" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1582" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B1582" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C1582" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1582" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1582" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1582" t="s">
+        <v>1544</v>
+      </c>
+      <c r="G1582" s="3">
+        <v>131.69999999999999</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1583" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B1583" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C1583" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1583" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1583" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1583" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1584" t="s">
+        <v>1922</v>
+      </c>
+      <c r="B1584" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C1584" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1584" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1584" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1584" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1585" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B1585" t="s">
+        <v>1925</v>
+      </c>
+      <c r="C1585" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1585" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1585" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1585" s="3">
+        <v>122.9</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1586" t="s">
+        <v>1926</v>
+      </c>
+      <c r="B1586" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C1586" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1586" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1586" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1586" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1587" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B1587" t="s">
+        <v>1929</v>
+      </c>
+      <c r="C1587" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1587" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1587" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1587" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1588" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B1588" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C1588" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1588" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1588" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1588" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1589" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B1589" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C1589" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1589" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1589" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1589" s="3">
+        <v>135.47499999999999</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1590" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B1590" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C1590" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1590" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1590" s="3">
+        <v>128.125</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1591" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B1591" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C1591" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1591" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1591" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1591" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1592" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B1592" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C1592" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1592" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1592" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1592" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1592" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1593" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B1593" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C1593" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1593" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1593" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1593" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1594" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B1594" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C1594" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1594" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1594" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1594" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1595" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B1595" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C1595" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1595" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1595" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1595" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1596" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B1596" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C1596" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1596" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1596" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1596" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1597" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B1597" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C1597" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1597" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1597" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1597" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1598" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B1598" t="s">
+        <v>1947</v>
+      </c>
+      <c r="C1598" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1598" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1598" t="s">
+        <v>1948</v>
+      </c>
+      <c r="G1598" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1599" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B1599" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C1599" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1599" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1599" t="s">
+        <v>1951</v>
+      </c>
+      <c r="F1599" t="s">
+        <v>1952</v>
+      </c>
+      <c r="G1599" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1600" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B1600" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C1600" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1600" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1600" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1600" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1601" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B1601" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C1601" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1601" t="s">
+        <v>1894</v>
+      </c>
+      <c r="F1601" t="s">
+        <v>1952</v>
+      </c>
+      <c r="G1601" s="3">
+        <v>122.6</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1602" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B1602" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C1602" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1602" t="s">
+        <v>641</v>
+      </c>
+      <c r="E1602" t="s">
+        <v>1953</v>
+      </c>
+      <c r="F1602" t="s">
+        <v>1954</v>
+      </c>
+      <c r="G1602" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1603" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B1603" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C1603" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1603" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1603" t="s">
+        <v>147</v>
+      </c>
+      <c r="G1603" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1604" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B1604" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C1604" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1604" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E1604" t="s">
+        <v>1956</v>
+      </c>
+      <c r="G1604" s="3">
+        <v>127.7</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1605" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B1605" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C1605" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1605" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1605" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1605" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1606" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B1606" t="s">
+        <v>1960</v>
+      </c>
+      <c r="C1606" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1606" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1606" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1606" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1607" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B1607" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C1607" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1607" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1607" t="s">
+        <v>275</v>
+      </c>
+      <c r="G1607" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1608" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B1608" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C1608" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1608" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1608" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1608" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1609" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B1609" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C1609" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1609" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1609" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1609" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1610" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B1610" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C1610" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1610" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1610" t="s">
+        <v>1963</v>
+      </c>
+      <c r="G1610" s="3">
+        <v>133.94999999999999</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1611" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B1611" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C1611" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1611" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1611" s="3">
+        <v>128.52500000000001</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1612" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B1612" t="s">
+        <v>1965</v>
+      </c>
+      <c r="C1612" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1612" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1612" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1612" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1613" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B1613" t="s">
+        <v>1967</v>
+      </c>
+      <c r="C1613" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1613" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1613" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1613" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1614" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B1614" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C1614" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1614" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1614" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1614" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1615" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B1615" t="s">
+        <v>1971</v>
+      </c>
+      <c r="C1615" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1615" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1615" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1615" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1616" t="s">
+        <v>1972</v>
+      </c>
+      <c r="B1616" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C1616" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1616" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1616" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1616" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1617" t="s">
+        <v>1974</v>
+      </c>
+      <c r="B1617" t="s">
+        <v>1975</v>
+      </c>
+      <c r="C1617" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1617" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1617" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1617" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1617" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1618" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B1618" t="s">
+        <v>1977</v>
+      </c>
+      <c r="C1618" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1618" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1618" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1618" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1619" t="s">
+        <v>1978</v>
+      </c>
+      <c r="B1619" t="s">
+        <v>1979</v>
+      </c>
+      <c r="C1619" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1619" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1619" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1619" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29A04C2-93FA-4B41-8917-64B32E431BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8592342C-5AB7-44DE-987F-65DAF3D1C5F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8321" uniqueCount="1980">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8381" uniqueCount="1999">
   <si>
     <t>AB</t>
   </si>
@@ -5979,6 +5979,63 @@
   </si>
   <si>
     <t>CPC2</t>
+  </si>
+  <si>
+    <t>Port Colborne</t>
+  </si>
+  <si>
+    <t>CPE5</t>
+  </si>
+  <si>
+    <t>Port Elgin</t>
+  </si>
+  <si>
+    <t>CNL4</t>
+  </si>
+  <si>
+    <t>Port Hope (Millson Field)</t>
+  </si>
+  <si>
+    <t>CMF4</t>
+  </si>
+  <si>
+    <t>Port Hope (Peter's Field)</t>
+  </si>
+  <si>
+    <t>CPH3</t>
+  </si>
+  <si>
+    <t>Port-Menier</t>
+  </si>
+  <si>
+    <t>CYPN</t>
+  </si>
+  <si>
+    <t>11-23Z‡ Sun-Fri, ltd hrs Sat French only O/T corridor tfc</t>
+  </si>
+  <si>
+    <t>Port Perry / Hoskin</t>
+  </si>
+  <si>
+    <t>CPP3</t>
+  </si>
+  <si>
+    <t>Port Perry / Utica Field</t>
+  </si>
+  <si>
+    <t>CUT2</t>
+  </si>
+  <si>
+    <t>Poste Montagnais (Mile 134)</t>
+  </si>
+  <si>
+    <t>CSF3</t>
+  </si>
+  <si>
+    <t>Pourvoirie Mirage</t>
+  </si>
+  <si>
+    <t>CPM3</t>
   </si>
 </sst>
 </file>
@@ -6369,7 +6426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1619"/>
+  <dimension ref="A1:G1631"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -39056,6 +39113,246 @@
         <v>122.8</v>
       </c>
     </row>
+    <row r="1620" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1620" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B1620" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C1620" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1620" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1620" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1620" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1621" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B1621" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C1621" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1621" t="s">
+        <v>235</v>
+      </c>
+      <c r="G1621" s="3">
+        <v>122.9</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1622" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B1622" t="s">
+        <v>1983</v>
+      </c>
+      <c r="C1622" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1622" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1622" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1622" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1622" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1623" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B1623" t="s">
+        <v>1985</v>
+      </c>
+      <c r="C1623" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1623" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1623" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1623" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1624" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B1624" t="s">
+        <v>1987</v>
+      </c>
+      <c r="C1624" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1624" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1624" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1624" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1625" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B1625" t="s">
+        <v>1989</v>
+      </c>
+      <c r="C1625" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1625" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1625" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1625" t="s">
+        <v>1990</v>
+      </c>
+      <c r="G1625" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1626" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B1626" t="s">
+        <v>1989</v>
+      </c>
+      <c r="C1626" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1626" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1626" s="3">
+        <v>122.175</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1627" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B1627" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C1627" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1627" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1627" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1627" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1628" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B1628" t="s">
+        <v>1994</v>
+      </c>
+      <c r="C1628" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1628" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1628" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1628" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1629" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B1629" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C1629" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1629" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1629" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1629" t="s">
+        <v>1544</v>
+      </c>
+      <c r="G1629" s="3">
+        <v>131.69999999999999</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1630" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B1630" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C1630" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1630" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1630" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1631" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B1631" t="s">
+        <v>1998</v>
+      </c>
+      <c r="C1631" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1631" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1631" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1631" s="3">
+        <v>122.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8592342C-5AB7-44DE-987F-65DAF3D1C5F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A846444-64EA-45AB-BC9F-EBF7226044AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8381" uniqueCount="1999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8557" uniqueCount="2028">
   <si>
     <t>AB</t>
   </si>
@@ -6036,6 +6036,93 @@
   </si>
   <si>
     <t>CPM3</t>
+  </si>
+  <si>
+    <t>Puvirnituq</t>
+  </si>
+  <si>
+    <t>CYPX</t>
+  </si>
+  <si>
+    <t>Quaqtaq</t>
+  </si>
+  <si>
+    <t>CYHA</t>
+  </si>
+  <si>
+    <t>Quebec / Jean Lesage Intl</t>
+  </si>
+  <si>
+    <t>CYQB</t>
+  </si>
+  <si>
+    <t>Quebec</t>
+  </si>
+  <si>
+    <t>121.900, 250.000</t>
+  </si>
+  <si>
+    <t>118.650, 236.600</t>
+  </si>
+  <si>
+    <t>Quebec (VFR)</t>
+  </si>
+  <si>
+    <t>Quebec (IFR)</t>
+  </si>
+  <si>
+    <t>124.000, 322.800</t>
+  </si>
+  <si>
+    <t>127.850, 322.800</t>
+  </si>
+  <si>
+    <t>135.025, 270.900</t>
+  </si>
+  <si>
+    <t>Quebec / Neuville</t>
+  </si>
+  <si>
+    <t>CNV9</t>
+  </si>
+  <si>
+    <t>Rendersville / Aery</t>
+  </si>
+  <si>
+    <t>CRA3</t>
+  </si>
+  <si>
+    <t>Reservoir Gouin / Pourvoirie Escapade</t>
+  </si>
+  <si>
+    <t>CGN2</t>
+  </si>
+  <si>
+    <t>Rimouski</t>
+  </si>
+  <si>
+    <t>CYXK</t>
+  </si>
+  <si>
+    <t>Riviere-Aux-Saumons</t>
+  </si>
+  <si>
+    <t>CTH7</t>
+  </si>
+  <si>
+    <t>Riviere Bonnard</t>
+  </si>
+  <si>
+    <t>CRB4</t>
+  </si>
+  <si>
+    <t>Riviere-Du-Loup</t>
+  </si>
+  <si>
+    <t>CYRI</t>
+  </si>
+  <si>
+    <t>125.100, 299.600</t>
   </si>
 </sst>
 </file>
@@ -6426,7 +6513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1631"/>
+  <dimension ref="A1:G1674"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -39353,6 +39440,708 @@
         <v>122.85</v>
       </c>
     </row>
+    <row r="1632" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1632" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1632" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C1632" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1632" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1632" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1632" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1633" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1633" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C1633" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1633" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1633" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1633" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1634" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1634" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C1634" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1634" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1634" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1634" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1634" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1635" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1635" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C1635" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1635" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1635" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1635" s="3">
+        <v>132.27500000000001</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1636" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1636" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C1636" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1636" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1636" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G1636" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1637" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1637" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C1637" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1637" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1637" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1637" s="3">
+        <v>128.65</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1638" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1638" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C1638" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1638" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1638" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1638" s="3">
+        <v>120.45</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1639" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B1639" t="s">
+        <v>2002</v>
+      </c>
+      <c r="C1639" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1639" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1639" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F1639" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1639" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1640" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B1640" t="s">
+        <v>2002</v>
+      </c>
+      <c r="C1640" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1640" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1640" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1640" s="3">
+        <v>128.25</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1641" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B1641" t="s">
+        <v>2002</v>
+      </c>
+      <c r="C1641" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1641" t="s">
+        <v>366</v>
+      </c>
+      <c r="F1641" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G1641" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1642" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1642" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C1642" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1642" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1642" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1642" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1643" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1643" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C1643" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1643" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1643" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1643" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1644" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1644" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C1644" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1644" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1644" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1644" s="3">
+        <v>134.6</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1645" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1645" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C1645" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1645" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1645" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1645" s="3">
+        <v>128.30000000000001</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1646" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1646" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C1646" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1646" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1646" t="s">
+        <v>2005</v>
+      </c>
+      <c r="G1646" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1647" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1647" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C1647" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1647" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1647" t="s">
+        <v>2005</v>
+      </c>
+      <c r="G1647" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1648" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1648" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C1648" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1648" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1648" t="s">
+        <v>2008</v>
+      </c>
+      <c r="G1648" s="3" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1649" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1649" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C1649" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1649" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1649" t="s">
+        <v>2009</v>
+      </c>
+      <c r="G1649" s="3" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1650" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1650" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C1650" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1650" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1650" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1650" s="3" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1651" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B1651" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C1651" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1651" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1651" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1651" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1651" s="3">
+        <v>123.35</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1652" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B1652" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C1652" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1652" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1652" t="s">
+        <v>2005</v>
+      </c>
+      <c r="G1652" s="3" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1653" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B1653" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C1653" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1653" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1653" t="s">
+        <v>2005</v>
+      </c>
+      <c r="G1653" s="3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1654" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B1654" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C1654" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1654" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1654" t="s">
+        <v>2008</v>
+      </c>
+      <c r="G1654" s="3">
+        <v>127.85</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1655" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B1655" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C1655" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1655" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1655" t="s">
+        <v>2009</v>
+      </c>
+      <c r="G1655" s="3">
+        <v>322.8</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1656" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1656" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C1656" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1656" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1656" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1656" s="3">
+        <v>128.69999999999999</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1657" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B1657" t="s">
+        <v>2018</v>
+      </c>
+      <c r="C1657" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1657" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1657" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1657" s="3">
+        <v>122.75</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1658" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B1658" t="s">
+        <v>2020</v>
+      </c>
+      <c r="C1658" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1658" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1658" t="s">
+        <v>1864</v>
+      </c>
+      <c r="G1658" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1659" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B1659" t="s">
+        <v>2020</v>
+      </c>
+      <c r="C1659" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1659" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1659" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1659" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1660" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B1660" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C1660" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1660" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1660" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1660" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1660" s="3">
+        <v>122.9</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1661" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B1661" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C1661" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1661" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1661" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1661" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1662" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B1662" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C1662" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1662" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1662" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1662" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1662" s="3">
+        <v>122.77500000000001</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1663" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B1663" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C1663" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1663" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1663" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1663" s="3" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1664" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B1664" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C1664" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1664" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1664" s="3">
+        <v>122.02500000000001</v>
+      </c>
+    </row>
+    <row r="1665" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1665" s="3"/>
+    </row>
+    <row r="1666" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1666" s="3"/>
+    </row>
+    <row r="1667" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1667" s="3"/>
+    </row>
+    <row r="1668" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1668" s="3"/>
+    </row>
+    <row r="1669" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1669" s="3"/>
+    </row>
+    <row r="1670" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1670" s="3"/>
+    </row>
+    <row r="1671" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1671" s="3"/>
+    </row>
+    <row r="1672" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1672" s="3"/>
+    </row>
+    <row r="1673" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1673" s="3"/>
+    </row>
+    <row r="1674" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1674" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A846444-64EA-45AB-BC9F-EBF7226044AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E381716-1F27-4F7B-B84B-C7187BA0AE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8557" uniqueCount="2028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8902" uniqueCount="2117">
   <si>
     <t>AB</t>
   </si>
@@ -6123,6 +6123,273 @@
   </si>
   <si>
     <t>125.100, 299.600</t>
+  </si>
+  <si>
+    <t>Roberval</t>
+  </si>
+  <si>
+    <t>CYRJ</t>
+  </si>
+  <si>
+    <t>123.550, 5680</t>
+  </si>
+  <si>
+    <t>Rockton</t>
+  </si>
+  <si>
+    <t>CPT3</t>
+  </si>
+  <si>
+    <t>Rodney / Pinder Airfield</t>
+  </si>
+  <si>
+    <t>CPN2</t>
+  </si>
+  <si>
+    <t>Rosseau</t>
+  </si>
+  <si>
+    <t>CRS4</t>
+  </si>
+  <si>
+    <t>Rougemont</t>
+  </si>
+  <si>
+    <t>CTY5</t>
+  </si>
+  <si>
+    <t>Round Lake (Meagamow Lake)</t>
+  </si>
+  <si>
+    <t>CZRJ</t>
+  </si>
+  <si>
+    <t>Round Lake tfc</t>
+  </si>
+  <si>
+    <t>Rouyn-Noranda</t>
+  </si>
+  <si>
+    <t>CYUY</t>
+  </si>
+  <si>
+    <t>Rouyn</t>
+  </si>
+  <si>
+    <t>Sachigo Lake</t>
+  </si>
+  <si>
+    <t>CZPB</t>
+  </si>
+  <si>
+    <t>Saintfield / Stone</t>
+  </si>
+  <si>
+    <t>CST4</t>
+  </si>
+  <si>
+    <t>St-Andre-Avellin</t>
+  </si>
+  <si>
+    <t>CAA2</t>
+  </si>
+  <si>
+    <t>Ste-Anne-Des-Monts</t>
+  </si>
+  <si>
+    <t>CYSZ</t>
+  </si>
+  <si>
+    <t>St-Apollinaire (Airpro)</t>
+  </si>
+  <si>
+    <t>CAA4</t>
+  </si>
+  <si>
+    <t>CYIF</t>
+  </si>
+  <si>
+    <t>St-Augustin</t>
+  </si>
+  <si>
+    <t>11-23Z Mon-Fri, 13-19Z Sun O/T tfc</t>
+  </si>
+  <si>
+    <t>St-Basile (Marcotte)</t>
+  </si>
+  <si>
+    <t>CTR6</t>
+  </si>
+  <si>
+    <t>St-Bruno-De-Guigues</t>
+  </si>
+  <si>
+    <t>CTA4</t>
+  </si>
+  <si>
+    <t>St-Cuthbert (Ulm Quebec)</t>
+  </si>
+  <si>
+    <t>CCU2</t>
+  </si>
+  <si>
+    <t>St-Dominique</t>
+  </si>
+  <si>
+    <t>CSS4</t>
+  </si>
+  <si>
+    <t>St-Donat</t>
+  </si>
+  <si>
+    <t>CSY4</t>
+  </si>
+  <si>
+    <t>St-Esprit</t>
+  </si>
+  <si>
+    <t>CES2</t>
+  </si>
+  <si>
+    <t>St-Ferdinand</t>
+  </si>
+  <si>
+    <t>CSH5</t>
+  </si>
+  <si>
+    <t>St-Frederic</t>
+  </si>
+  <si>
+    <t>CSZ4</t>
+  </si>
+  <si>
+    <t>St-Georges</t>
+  </si>
+  <si>
+    <t>CYSG</t>
+  </si>
+  <si>
+    <t>13-01Z‡ Wed-Sun, 13-23Z‡ Mon-Tue May 1-Sep 30; 14-23Z‡ Sat, 13-23Z‡ Sun-Fri Oct 1-Apr 30 O/T tfc</t>
+  </si>
+  <si>
+    <t>St-Hyacinthe</t>
+  </si>
+  <si>
+    <t>CSU3</t>
+  </si>
+  <si>
+    <t>St-Jean</t>
+  </si>
+  <si>
+    <t>CYJN</t>
+  </si>
+  <si>
+    <t>1230-0230Z‡ Apr-Oct; 13-02Z‡ Nov-Mar</t>
+  </si>
+  <si>
+    <t>0230-1230Z‡ Apr-Oct; 02-13Z‡ Nov-Mar</t>
+  </si>
+  <si>
+    <t>St-Jean Chrysostome</t>
+  </si>
+  <si>
+    <t>CSG5</t>
+  </si>
+  <si>
+    <t>St-Lambert-De-Lauzon</t>
+  </si>
+  <si>
+    <t>CST7</t>
+  </si>
+  <si>
+    <t>St-Loius-De-France</t>
+  </si>
+  <si>
+    <t>CSJ5</t>
+  </si>
+  <si>
+    <t>St-Mathias</t>
+  </si>
+  <si>
+    <t>CSP5</t>
+  </si>
+  <si>
+    <t>St-Mathias / Grant</t>
+  </si>
+  <si>
+    <t>CSX5</t>
+  </si>
+  <si>
+    <t>St-Mathieu-De-Beloeil (Gilles Beaudet)</t>
+  </si>
+  <si>
+    <t>CSB3</t>
+  </si>
+  <si>
+    <t>St. Mathieu-De-Laprairie</t>
+  </si>
+  <si>
+    <t>CML8</t>
+  </si>
+  <si>
+    <t>St-Michel-Des-Saints</t>
+  </si>
+  <si>
+    <t>CSM5</t>
+  </si>
+  <si>
+    <t>St-Raymond / Paquel</t>
+  </si>
+  <si>
+    <t>CSK5</t>
+  </si>
+  <si>
+    <t>St-Victor-De-Beauce</t>
+  </si>
+  <si>
+    <t>CSL5</t>
+  </si>
+  <si>
+    <t>Salaberry-De-Valleyfield</t>
+  </si>
+  <si>
+    <t>CSD3</t>
+  </si>
+  <si>
+    <t>Salluit</t>
+  </si>
+  <si>
+    <t>CYZG</t>
+  </si>
+  <si>
+    <t>Sandy Lake</t>
+  </si>
+  <si>
+    <t>CZSJ</t>
+  </si>
+  <si>
+    <t>Schefferville</t>
+  </si>
+  <si>
+    <t>CYKL</t>
+  </si>
+  <si>
+    <t>132.900, 312.700</t>
+  </si>
+  <si>
+    <t>Schomberg (Sloan Field)</t>
+  </si>
+  <si>
+    <t>CSV8</t>
+  </si>
+  <si>
+    <t>Seagrave / North Port</t>
+  </si>
+  <si>
+    <t>CNP4</t>
+  </si>
+  <si>
+    <t>CJA2</t>
   </si>
 </sst>
 </file>
@@ -6513,7 +6780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1674"/>
+  <dimension ref="A1:G1731"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -40112,35 +40379,1357 @@
         <v>122.02500000000001</v>
       </c>
     </row>
-    <row r="1665" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1665" s="3"/>
-    </row>
-    <row r="1666" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1666" s="3"/>
-    </row>
-    <row r="1667" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1667" s="3"/>
-    </row>
-    <row r="1668" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1668" s="3"/>
-    </row>
-    <row r="1669" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1669" s="3"/>
-    </row>
-    <row r="1670" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1670" s="3"/>
-    </row>
-    <row r="1671" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1671" s="3"/>
-    </row>
-    <row r="1672" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1672" s="3"/>
-    </row>
-    <row r="1673" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1673" s="3"/>
-    </row>
-    <row r="1674" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1674" s="3"/>
+    <row r="1665" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1665" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B1665" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C1665" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1665" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1665" t="s">
+        <v>1878</v>
+      </c>
+      <c r="F1665" t="s">
+        <v>1710</v>
+      </c>
+      <c r="G1665" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1666" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B1666" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C1666" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1666" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1666" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1666" s="3" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1667" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B1667" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C1667" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1667" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1667" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1667" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1668" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B1668" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C1668" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1668" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1668" t="s">
+        <v>1884</v>
+      </c>
+      <c r="F1668" t="s">
+        <v>1710</v>
+      </c>
+      <c r="G1668" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1669" t="s">
+        <v>2031</v>
+      </c>
+      <c r="B1669" t="s">
+        <v>2032</v>
+      </c>
+      <c r="C1669" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1669" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1669" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1669" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1669" s="3">
+        <v>122.72499999999999</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1670" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B1670" t="s">
+        <v>2034</v>
+      </c>
+      <c r="C1670" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1670" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1670" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1670" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1671" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B1671" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C1671" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1671" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1671" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1671" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1672" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B1672" t="s">
+        <v>2038</v>
+      </c>
+      <c r="C1672" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1672" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1672" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1672" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1673" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B1673" t="s">
+        <v>2040</v>
+      </c>
+      <c r="C1673" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1673" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1673" t="s">
+        <v>2041</v>
+      </c>
+      <c r="G1673" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1674" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B1674" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C1674" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1674" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1674" t="s">
+        <v>2044</v>
+      </c>
+      <c r="G1674" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1675" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B1675" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C1675" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1675" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1675" t="s">
+        <v>1866</v>
+      </c>
+      <c r="G1675" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1676" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B1676" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C1676" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1676" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1676" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1676" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1677" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B1677" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C1677" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1677" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1677" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1677" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1678" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B1678" t="s">
+        <v>2046</v>
+      </c>
+      <c r="C1678" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1678" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1678" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1678" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1679" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B1679" t="s">
+        <v>2048</v>
+      </c>
+      <c r="C1679" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1679" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1679" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1679" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1680" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B1680" t="s">
+        <v>2050</v>
+      </c>
+      <c r="C1680" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1680" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1680" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1680" s="3">
+        <v>122.75</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1681" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B1681" t="s">
+        <v>2052</v>
+      </c>
+      <c r="C1681" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1681" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1681" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1681" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1682" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B1682" t="s">
+        <v>2052</v>
+      </c>
+      <c r="C1682" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1682" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1682" s="3">
+        <v>122.02500000000001</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1683" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B1683" t="s">
+        <v>2054</v>
+      </c>
+      <c r="C1683" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1683" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1683" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1683" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1684" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B1684" t="s">
+        <v>2055</v>
+      </c>
+      <c r="C1684" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1684" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1684" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1684" s="3">
+        <v>119.575</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1685" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B1685" t="s">
+        <v>2055</v>
+      </c>
+      <c r="C1685" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1685" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1685" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1685" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1686" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B1686" t="s">
+        <v>2055</v>
+      </c>
+      <c r="C1686" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1686" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1686" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1686" t="s">
+        <v>2057</v>
+      </c>
+      <c r="G1686" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1687" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B1687" t="s">
+        <v>2059</v>
+      </c>
+      <c r="C1687" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1687" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1687" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1687" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1688" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B1688" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C1688" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1688" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1688" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1688" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1689" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1689" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C1689" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1689" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1689" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1689" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1690" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B1690" t="s">
+        <v>2065</v>
+      </c>
+      <c r="C1690" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1690" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1690" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1690" s="3">
+        <v>122.47499999999999</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1691" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B1691" t="s">
+        <v>2067</v>
+      </c>
+      <c r="C1691" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1691" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1691" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1691" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1692" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B1692" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C1692" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1692" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1692" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1692" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1693" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B1693" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C1693" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1693" t="s">
+        <v>235</v>
+      </c>
+      <c r="G1693" s="3">
+        <v>129.85</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1694" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B1694" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C1694" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1694" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1694" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1694" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1695" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B1695" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1695" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1695" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1695" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1695" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1696" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B1696" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1696" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1696" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1696" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1696" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1697" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B1697" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1697" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1697" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1697" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1697" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1698" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B1698" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C1698" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1698" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1698" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1698" t="s">
+        <v>2076</v>
+      </c>
+      <c r="G1698" s="3">
+        <v>122.15</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1699" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B1699" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C1699" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1699" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1699" s="3">
+        <v>123.175</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1700" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B1700" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C1700" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1700" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1700" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1700" s="3">
+        <v>123.22499999999999</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1701" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B1701" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C1701" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1701" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1701" t="s">
+        <v>2081</v>
+      </c>
+      <c r="G1701" s="3">
+        <v>121.7</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1702" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B1702" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C1702" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1702" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1702" t="s">
+        <v>2081</v>
+      </c>
+      <c r="G1702" s="3">
+        <v>118.2</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1703" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B1703" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C1703" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1703" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1703" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1703" t="s">
+        <v>2082</v>
+      </c>
+      <c r="G1703" s="3">
+        <v>118.2</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1704" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B1704" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C1704" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1704" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1704" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G1704" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1705" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B1705" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C1705" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1705" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1705" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G1705" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1706" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B1706" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C1706" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1706" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E1706" t="s">
+        <v>1875</v>
+      </c>
+      <c r="G1706" s="3">
+        <v>125.15</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1707" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B1707" t="s">
+        <v>2084</v>
+      </c>
+      <c r="C1707" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1707" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1707" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1707" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1708" t="s">
+        <v>2085</v>
+      </c>
+      <c r="B1708" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1708" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1708" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1708" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1708" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1709" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B1709" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1709" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1709" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1709" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1709" s="3">
+        <v>122.35</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1710" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B1710" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C1710" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1710" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1710" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1710" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1711" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B1711" t="s">
+        <v>2092</v>
+      </c>
+      <c r="C1711" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1711" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1711" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1711" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1712" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B1712" t="s">
+        <v>2094</v>
+      </c>
+      <c r="C1712" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1712" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1712" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1712" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1713" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B1713" t="s">
+        <v>2096</v>
+      </c>
+      <c r="C1713" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1713" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1713" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1713" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1714" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B1714" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C1714" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1714" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1714" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1714" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1715" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B1715" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1715" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1715" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1715" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1715" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1715" s="3">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1716" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B1716" t="s">
+        <v>2102</v>
+      </c>
+      <c r="C1716" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1716" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1716" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1716" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1717" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B1717" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C1717" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1717" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1717" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1717" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1718" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B1718" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C1718" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1718" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1718" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1718" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1719" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B1719" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C1719" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1719" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1719" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F1719" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1719" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1720" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B1720" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C1720" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1720" t="s">
+        <v>366</v>
+      </c>
+      <c r="F1720" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G1720" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1721" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B1721" t="s">
+        <v>2108</v>
+      </c>
+      <c r="C1721" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1721" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1721" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1721" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1722" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B1722" t="s">
+        <v>2108</v>
+      </c>
+      <c r="C1722" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1722" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1722" s="3">
+        <v>124.825</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1723" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C1723" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1723" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1723" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1723" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1724" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C1724" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1724" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1724" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1724" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1725" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C1725" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1725" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1725" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1725" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1726" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C1726" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1726" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1726" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1726" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1727" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C1727" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1727" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1727" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1727" s="3">
+        <v>124.6</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1728" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C1728" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1728" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1728" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1728" s="3">
+        <v>127.5</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1729" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C1729" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1729" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1729" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1729" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1730" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>2115</v>
+      </c>
+      <c r="C1730" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1730" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1730" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1730" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1731" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C1731" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1731" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1731" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1731" s="3">
+        <v>122.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E381716-1F27-4F7B-B84B-C7187BA0AE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22B909E-2C64-41B2-86E1-6756CFD6B42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8902" uniqueCount="2117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8963" uniqueCount="2129">
   <si>
     <t>AB</t>
   </si>
@@ -6390,6 +6390,42 @@
   </si>
   <si>
     <t>CJA2</t>
+  </si>
+  <si>
+    <t>Sept-Iles</t>
+  </si>
+  <si>
+    <t>CYZV</t>
+  </si>
+  <si>
+    <t>1103Z‡</t>
+  </si>
+  <si>
+    <t>135.550, 381.900</t>
+  </si>
+  <si>
+    <t>Severn Bridge</t>
+  </si>
+  <si>
+    <t>CSB7</t>
+  </si>
+  <si>
+    <t>Sexsmith / Exeter</t>
+  </si>
+  <si>
+    <t>CSX7</t>
+  </si>
+  <si>
+    <t>Shelburne / Fisherfield</t>
+  </si>
+  <si>
+    <t>CNN3</t>
+  </si>
+  <si>
+    <t>Shelburne (Schaefer Field)</t>
+  </si>
+  <si>
+    <t>CSF4</t>
   </si>
 </sst>
 </file>
@@ -6780,7 +6816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1731"/>
+  <dimension ref="A1:G1743"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -41731,6 +41767,246 @@
         <v>122.9</v>
       </c>
     </row>
+    <row r="1732" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1732" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C1732" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1732" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1732" s="3">
+        <v>118.1</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1733" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C1733" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1733" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1733" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1733" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1734" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C1734" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1734" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1734" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1734" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1735" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C1735" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1735" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1735" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F1735" t="s">
+        <v>2119</v>
+      </c>
+      <c r="G1735" s="3">
+        <v>124.8</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1736" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B1736" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C1736" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1736" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1736" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F1736" t="s">
+        <v>2119</v>
+      </c>
+      <c r="G1736" s="3">
+        <v>134.9</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1737" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C1737" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1737" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1737" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1737" s="3">
+        <v>118.1</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1738" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C1738" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1738" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1738" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1738" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1739" t="s">
+        <v>2121</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>2122</v>
+      </c>
+      <c r="C1739" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1739" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1739" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1739" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1740" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C1740" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1740" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1740" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1740" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1741" t="s">
+        <v>2125</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>2126</v>
+      </c>
+      <c r="C1741" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1741" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1741" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1741" s="3">
+        <v>122.72499999999999</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1742" t="s">
+        <v>2125</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>2126</v>
+      </c>
+      <c r="C1742" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1742" t="s">
+        <v>235</v>
+      </c>
+      <c r="G1742" s="3">
+        <v>122.9</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1743" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C1743" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1743" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1743" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1743" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22B909E-2C64-41B2-86E1-6756CFD6B42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45467284-6059-4862-9358-81259E322098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8963" uniqueCount="2129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9185" uniqueCount="2185">
   <si>
     <t>AB</t>
   </si>
@@ -6426,6 +6426,174 @@
   </si>
   <si>
     <t>CSF4</t>
+  </si>
+  <si>
+    <t>Sherbrooke</t>
+  </si>
+  <si>
+    <t>CYSC</t>
+  </si>
+  <si>
+    <t>FISE Quebec rdo (Mont-Megantic)</t>
+  </si>
+  <si>
+    <t>12-24Z‡ May-Sep, 12-22Z‡ Oct-Apr; O/T tfc</t>
+  </si>
+  <si>
+    <t>PAl</t>
+  </si>
+  <si>
+    <t>Simcoe (Dennison Field)</t>
+  </si>
+  <si>
+    <t>CPA4</t>
+  </si>
+  <si>
+    <t>Slate Falls</t>
+  </si>
+  <si>
+    <t>CKD9</t>
+  </si>
+  <si>
+    <t>Sorel</t>
+  </si>
+  <si>
+    <t>CSY3</t>
+  </si>
+  <si>
+    <t>Southampton</t>
+  </si>
+  <si>
+    <t>Springvale</t>
+  </si>
+  <si>
+    <t>CGV7</t>
+  </si>
+  <si>
+    <t>Stayner (Clearview Field)</t>
+  </si>
+  <si>
+    <t>CLV2</t>
+  </si>
+  <si>
+    <t>Stoney Point (Le Cunff)</t>
+  </si>
+  <si>
+    <t>CRML</t>
+  </si>
+  <si>
+    <t>Stouffville</t>
+  </si>
+  <si>
+    <t>CBB2</t>
+  </si>
+  <si>
+    <t>Straffordville / Bushhawk Creek</t>
+  </si>
+  <si>
+    <t>CBH5</t>
+  </si>
+  <si>
+    <t>Sudbury / Coniston</t>
+  </si>
+  <si>
+    <t>CSC9</t>
+  </si>
+  <si>
+    <t>Summer Beaver</t>
+  </si>
+  <si>
+    <t>CJV7</t>
+  </si>
+  <si>
+    <t>Tasiujaq</t>
+  </si>
+  <si>
+    <t>CYTQ</t>
+  </si>
+  <si>
+    <t>Teeswater (Dent Field)</t>
+  </si>
+  <si>
+    <t>CDF2</t>
+  </si>
+  <si>
+    <t>Teeswater (Thompson Field)</t>
+  </si>
+  <si>
+    <t>CPC6</t>
+  </si>
+  <si>
+    <t>Tete-A-La-Baleine</t>
+  </si>
+  <si>
+    <t>CTB6</t>
+  </si>
+  <si>
+    <t>Thetford Mines</t>
+  </si>
+  <si>
+    <t>CSM3</t>
+  </si>
+  <si>
+    <t>Thunder Bay / Eldorado</t>
+  </si>
+  <si>
+    <t>Thunder Bay (Martin's Landing)</t>
+  </si>
+  <si>
+    <t>CML5</t>
+  </si>
+  <si>
+    <t>Torrance / Walkers Point</t>
+  </si>
+  <si>
+    <t>CWP5</t>
+  </si>
+  <si>
+    <t>Tottenham / Mardon</t>
+  </si>
+  <si>
+    <t>CMA6</t>
+  </si>
+  <si>
+    <t>Tottenham / Ronan</t>
+  </si>
+  <si>
+    <t>CTR3</t>
+  </si>
+  <si>
+    <t>Tottenham / Volk</t>
+  </si>
+  <si>
+    <t>CPM5</t>
+  </si>
+  <si>
+    <t>Trois-Rivieres</t>
+  </si>
+  <si>
+    <t>CYRQ</t>
+  </si>
+  <si>
+    <t>12-01Z‡ ltd hrs O/T tfc</t>
+  </si>
+  <si>
+    <t>Ullswater</t>
+  </si>
+  <si>
+    <t>CLW2</t>
+  </si>
+  <si>
+    <t>Umiujaq</t>
+  </si>
+  <si>
+    <t>CYMU</t>
+  </si>
+  <si>
+    <t>Valcourt</t>
+  </si>
+  <si>
+    <t>CSQ3</t>
   </si>
 </sst>
 </file>
@@ -6816,7 +6984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1743"/>
+  <dimension ref="A1:G1786"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -42007,6 +42175,887 @@
         <v>123.2</v>
       </c>
     </row>
+    <row r="1744" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1744" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C1744" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1744" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1744" t="s">
+        <v>2131</v>
+      </c>
+      <c r="G1744" s="3">
+        <v>123.25</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1745" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C1745" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1745" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1745" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1745" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1746" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C1746" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1746" t="s">
+        <v>641</v>
+      </c>
+      <c r="E1746" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1746" t="s">
+        <v>2132</v>
+      </c>
+      <c r="G1746" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1747" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C1747" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1747" t="s">
+        <v>2133</v>
+      </c>
+      <c r="E1747" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1747" s="3">
+        <v>132.55000000000001</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1748" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C1748" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1748" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1748" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1748" s="3">
+        <v>126.25</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1749" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C1749" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1749" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1749" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1749" s="3">
+        <v>128.15</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1750" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C1750" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1750" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1750" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1750" s="3">
+        <v>122.9</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1751" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C1751" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1751" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1751" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1751" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1752" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C1752" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1752" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1752" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1752" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1753" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1753" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1753" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1753" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1753" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1754" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C1754" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1754" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1754" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1754" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1755" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C1755" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1755" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1755" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1755" s="3">
+        <v>122.85</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1756" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>2146</v>
+      </c>
+      <c r="C1756" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1756" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1756" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1756" s="3">
+        <v>122.9</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1757" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C1757" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1757" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1757" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1757" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1758" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C1758" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1758" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1758" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1758" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1759" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C1759" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1759" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1759" t="s">
+        <v>275</v>
+      </c>
+      <c r="G1759" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1760" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C1760" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1760" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1760" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1760" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1761" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C1761" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1761" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1761" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1761" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1762" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C1762" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1762" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1762" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1762" s="3">
+        <v>135.5</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1763" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C1763" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1763" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1763" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1763" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1764" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1764" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1764" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1764" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1764" s="3">
+        <v>122.9</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1765" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C1765" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1765" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1765" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F1765" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1765" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1766" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C1766" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1766" t="s">
+        <v>366</v>
+      </c>
+      <c r="F1766" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G1766" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1767" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>2158</v>
+      </c>
+      <c r="C1767" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1767" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1767" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1767" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1768" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C1768" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1768" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1768" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1768" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1769" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B1769" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C1769" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1769" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1769" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1769" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1770" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B1770" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C1770" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1770" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1770" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1770" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1770" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1771" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B1771" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1771" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1771" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1771" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1771" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1771" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1772" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B1772" t="s">
+        <v>2167</v>
+      </c>
+      <c r="C1772" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1772" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1772" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1772" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1773" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B1773" t="s">
+        <v>2169</v>
+      </c>
+      <c r="C1773" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1773" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1773" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1773" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1774" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B1774" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C1774" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1774" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1774" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1774" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1775" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B1775" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C1775" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1775" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1775" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1775" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1776" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B1776" t="s">
+        <v>2175</v>
+      </c>
+      <c r="C1776" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1776" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1776" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1776" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1777" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B1777" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C1777" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1777" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1777" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1777" t="s">
+        <v>2178</v>
+      </c>
+      <c r="G1777" s="3">
+        <v>122.35</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1778" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B1778" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C1778" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1778" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1778" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1778" s="3">
+        <v>128.22499999999999</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1779" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B1779" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C1779" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1779" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1779" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1779" s="3">
+        <v>128.22499999999999</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1780" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B1780" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C1780" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1780" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1780" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1780" s="3">
+        <v>128.22499999999999</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1781" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B1781" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C1781" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1781" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1781" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1781" s="3">
+        <v>120.27500000000001</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1782" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B1782" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C1782" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1782" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1782" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G1782" s="3">
+        <v>124.825</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1783" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B1783" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C1783" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1783" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1783" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1783" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1784" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B1784" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C1784" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1784" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1784" t="s">
+        <v>367</v>
+      </c>
+      <c r="F1784" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1784" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1785" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B1785" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C1785" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1785" t="s">
+        <v>366</v>
+      </c>
+      <c r="F1785" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G1785" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1786" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B1786" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C1786" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1786" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1786" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1786" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1786" s="3">
+        <v>122.72499999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45467284-6059-4862-9358-81259E322098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC5EE85-C1E4-4CE5-B0D6-3471C0AE67F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9185" uniqueCount="2185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9332" uniqueCount="2227">
   <si>
     <t>AB</t>
   </si>
@@ -6594,6 +6594,132 @@
   </si>
   <si>
     <t>CSQ3</t>
+  </si>
+  <si>
+    <t>CYVO</t>
+  </si>
+  <si>
+    <t>125.900, 308.300</t>
+  </si>
+  <si>
+    <t>1030-0325Z‡</t>
+  </si>
+  <si>
+    <t>0325-1030Z‡</t>
+  </si>
+  <si>
+    <t>1030-0325Z‡ O/T Rouyn rdo</t>
+  </si>
+  <si>
+    <t>Val-D'OR</t>
+  </si>
+  <si>
+    <t>Vermilion Bay</t>
+  </si>
+  <si>
+    <t>CKQ7</t>
+  </si>
+  <si>
+    <t>Victoriaville</t>
+  </si>
+  <si>
+    <t>CSR3</t>
+  </si>
+  <si>
+    <t>UNICOM (French only)</t>
+  </si>
+  <si>
+    <t>Walsingham / Ceilidh</t>
+  </si>
+  <si>
+    <t>CCL7</t>
+  </si>
+  <si>
+    <t>Walter's Falls (Piper Way)</t>
+  </si>
+  <si>
+    <t>CWF2</t>
+  </si>
+  <si>
+    <t>Waskaganish</t>
+  </si>
+  <si>
+    <t>CYKQ</t>
+  </si>
+  <si>
+    <t>aprt rdo (English only)</t>
+  </si>
+  <si>
+    <t>14-22Z‡ Sun-Fri</t>
+  </si>
+  <si>
+    <t>Wemindji</t>
+  </si>
+  <si>
+    <t>CYNC</t>
+  </si>
+  <si>
+    <t>14-21Z‡ Mon-Fri, 17-22Z‡ Sun</t>
+  </si>
+  <si>
+    <t>Westport / Rideau Lakes</t>
+  </si>
+  <si>
+    <t>CRL2</t>
+  </si>
+  <si>
+    <t>Weymontachie</t>
+  </si>
+  <si>
+    <t>CSU5</t>
+  </si>
+  <si>
+    <t>CRM5</t>
+  </si>
+  <si>
+    <t>Wheatley (Robinson Motorcycles)</t>
+  </si>
+  <si>
+    <t>Wiarton / Hay Island</t>
+  </si>
+  <si>
+    <t>CHA4</t>
+  </si>
+  <si>
+    <t>Wiebenville</t>
+  </si>
+  <si>
+    <t>CXX2</t>
+  </si>
+  <si>
+    <t>Wingham (Inglis Field)</t>
+  </si>
+  <si>
+    <t>CWH5</t>
+  </si>
+  <si>
+    <t>Woodstock (Norm Beckham / Bob Hewitt Field)</t>
+  </si>
+  <si>
+    <t>CPR5</t>
+  </si>
+  <si>
+    <t>Wroxeter / HarkesField</t>
+  </si>
+  <si>
+    <t>Wunnumin Lake</t>
+  </si>
+  <si>
+    <t>CKL3</t>
+  </si>
+  <si>
+    <t>CHF5</t>
+  </si>
+  <si>
+    <t>Zephyr / Dillon Field</t>
+  </si>
+  <si>
+    <t>CZF2</t>
   </si>
 </sst>
 </file>
@@ -6984,7 +7110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1786"/>
+  <dimension ref="A1:G1814"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -43056,6 +43182,584 @@
         <v>122.72499999999999</v>
       </c>
     </row>
+    <row r="1787" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1787" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1787" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1787" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1787" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1787" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1788" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1788" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1788" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1788" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1788" t="s">
+        <v>1878</v>
+      </c>
+      <c r="F1788" t="s">
+        <v>2187</v>
+      </c>
+      <c r="G1788" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1789" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1789" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1789" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1789" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1789" t="s">
+        <v>414</v>
+      </c>
+      <c r="F1789" t="s">
+        <v>2188</v>
+      </c>
+      <c r="G1789" s="3">
+        <v>122.375</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1790" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1790" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1790" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1790" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1790" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1790" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1791" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1791" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1791" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1791" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1791" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1791" t="s">
+        <v>2189</v>
+      </c>
+      <c r="G1791" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1792" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1792" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1792" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1792" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1792" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1792" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1793" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1793" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1793" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1793" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1793" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F1793" t="s">
+        <v>2188</v>
+      </c>
+      <c r="G1793" s="3">
+        <v>128.15</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1794" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1794" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1794" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1794" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1794" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F1794" t="s">
+        <v>2188</v>
+      </c>
+      <c r="G1794" s="3">
+        <v>120.55</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1795" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B1795" t="s">
+        <v>2192</v>
+      </c>
+      <c r="C1795" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1795" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1795" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1795" s="3">
+        <v>130.69999999999999</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1796" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B1796" t="s">
+        <v>2194</v>
+      </c>
+      <c r="C1796" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1796" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1796" t="s">
+        <v>2195</v>
+      </c>
+      <c r="F1796" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1796" s="3">
+        <v>123.35</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1797" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B1797" t="s">
+        <v>2194</v>
+      </c>
+      <c r="C1797" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1797" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1797" s="3">
+        <v>122.175</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1798" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B1798" t="s">
+        <v>2197</v>
+      </c>
+      <c r="C1798" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1798" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1798" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1798" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1799" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B1799" t="s">
+        <v>2199</v>
+      </c>
+      <c r="C1799" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1799" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1799" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1799" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1800" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B1800" t="s">
+        <v>2201</v>
+      </c>
+      <c r="C1800" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1800" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1800" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F1800" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1800" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1801" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B1801" t="s">
+        <v>2201</v>
+      </c>
+      <c r="C1801" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1801" t="s">
+        <v>366</v>
+      </c>
+      <c r="F1801" t="s">
+        <v>2203</v>
+      </c>
+      <c r="G1801" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1802" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1802" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1802" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1802" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1802" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1802" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1803" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B1803" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C1803" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1803" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1803" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F1803" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1803" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1804" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B1804" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C1804" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1804" t="s">
+        <v>366</v>
+      </c>
+      <c r="F1804" t="s">
+        <v>2206</v>
+      </c>
+      <c r="G1804" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1805" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B1805" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C1805" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1805" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1805" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1805" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1806" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B1806" t="s">
+        <v>2210</v>
+      </c>
+      <c r="C1806" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1806" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1806" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1806" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1807" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B1807" t="s">
+        <v>2211</v>
+      </c>
+      <c r="C1807" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1807" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1807" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1807" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1808" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B1808" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C1808" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1808" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1808" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1808" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1809" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B1809" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C1809" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1809" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1809" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1809" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1810" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B1810" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C1810" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1810" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1810" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1810" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1811" t="s">
+        <v>2219</v>
+      </c>
+      <c r="B1811" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C1811" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1811" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1811" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1811" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1811" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1812" t="s">
+        <v>2221</v>
+      </c>
+      <c r="B1812" t="s">
+        <v>2224</v>
+      </c>
+      <c r="C1812" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1812" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1812" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1812" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1813" t="s">
+        <v>2222</v>
+      </c>
+      <c r="B1813" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C1813" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1813" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1813" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1813" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1814" t="s">
+        <v>2225</v>
+      </c>
+      <c r="B1814" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C1814" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1814" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1814" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC5EE85-C1E4-4CE5-B0D6-3471C0AE67F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12C2DBD-B999-4C20-B809-3BD379D4585D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9332" uniqueCount="2227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9650" uniqueCount="2307">
   <si>
     <t>AB</t>
   </si>
@@ -6720,6 +6720,246 @@
   </si>
   <si>
     <t>CZF2</t>
+  </si>
+  <si>
+    <t>Abbotsford</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
+  <si>
+    <t>CYXX</t>
+  </si>
+  <si>
+    <t>RAAS  Cranbrook</t>
+  </si>
+  <si>
+    <t>07-15Z‡</t>
+  </si>
+  <si>
+    <t>FISE Pacific rdo</t>
+  </si>
+  <si>
+    <t>15-07Z‡</t>
+  </si>
+  <si>
+    <t>inner</t>
+  </si>
+  <si>
+    <t>outer</t>
+  </si>
+  <si>
+    <t>119.400, 295.000</t>
+  </si>
+  <si>
+    <t>121.000, 295.000</t>
+  </si>
+  <si>
+    <t>Cranbrook rdo</t>
+  </si>
+  <si>
+    <t>Victoria</t>
+  </si>
+  <si>
+    <t>Victoria Tml</t>
+  </si>
+  <si>
+    <t>Alert Bay</t>
+  </si>
+  <si>
+    <t>CYAL</t>
+  </si>
+  <si>
+    <t>CAM4</t>
+  </si>
+  <si>
+    <t>Alhambra / Ahlstrom</t>
+  </si>
+  <si>
+    <t>Anahim Lake</t>
+  </si>
+  <si>
+    <t>CAJ4</t>
+  </si>
+  <si>
+    <t>Athabasca</t>
+  </si>
+  <si>
+    <t>CYWM</t>
+  </si>
+  <si>
+    <t>Edmonton Ctr (Flatbush)</t>
+  </si>
+  <si>
+    <t>Atlin</t>
+  </si>
+  <si>
+    <t>CYSQ</t>
+  </si>
+  <si>
+    <t>Banff</t>
+  </si>
+  <si>
+    <t>CYBA</t>
+  </si>
+  <si>
+    <t>Barrhead</t>
+  </si>
+  <si>
+    <t>CEP3</t>
+  </si>
+  <si>
+    <t>Bashaw</t>
+  </si>
+  <si>
+    <t>CFK2</t>
+  </si>
+  <si>
+    <t>Bassano</t>
+  </si>
+  <si>
+    <t>CEN2</t>
+  </si>
+  <si>
+    <t>CFR2</t>
+  </si>
+  <si>
+    <t>Bawlf (Blackwells)</t>
+  </si>
+  <si>
+    <t>Beaverley</t>
+  </si>
+  <si>
+    <t>CBA8</t>
+  </si>
+  <si>
+    <t>Beaverlodge</t>
+  </si>
+  <si>
+    <t>CEU2</t>
+  </si>
+  <si>
+    <t>Beaverlodge / Clanaechan</t>
+  </si>
+  <si>
+    <t>CLN4</t>
+  </si>
+  <si>
+    <t>Beiseker</t>
+  </si>
+  <si>
+    <t>CFV2</t>
+  </si>
+  <si>
+    <t>Bella Bella (Campbell Island)</t>
+  </si>
+  <si>
+    <t>CBBC</t>
+  </si>
+  <si>
+    <t>Bella Coola</t>
+  </si>
+  <si>
+    <t>CYBD</t>
+  </si>
+  <si>
+    <t>Benalto / Hillman's Farm</t>
+  </si>
+  <si>
+    <t>CBH7</t>
+  </si>
+  <si>
+    <t>Birch Mountain</t>
+  </si>
+  <si>
+    <t>CFM2</t>
+  </si>
+  <si>
+    <t>CEH2</t>
+  </si>
+  <si>
+    <t>Black Diamond / Cu Nim</t>
+  </si>
+  <si>
+    <t>Black Diamond / Flying R Ranch</t>
+  </si>
+  <si>
+    <t>CBD8</t>
+  </si>
+  <si>
+    <t>Blackie / Wilderman Farm</t>
+  </si>
+  <si>
+    <t>CFT2</t>
+  </si>
+  <si>
+    <t>Blue River</t>
+  </si>
+  <si>
+    <t>CYCP</t>
+  </si>
+  <si>
+    <t>Bob Quinn Lake</t>
+  </si>
+  <si>
+    <t>CBW4</t>
+  </si>
+  <si>
+    <t>Bonnyville</t>
+  </si>
+  <si>
+    <t>CYBF</t>
+  </si>
+  <si>
+    <t>Bottrel / Anchor 9 Ranch</t>
+  </si>
+  <si>
+    <t>CBR9</t>
+  </si>
+  <si>
+    <t>Bow Island</t>
+  </si>
+  <si>
+    <t>CEF3</t>
+  </si>
+  <si>
+    <t>Boyle</t>
+  </si>
+  <si>
+    <t>CFM7</t>
+  </si>
+  <si>
+    <t>Brant (Dixon Farm)</t>
+  </si>
+  <si>
+    <t>CEX9</t>
+  </si>
+  <si>
+    <t>Brooks Regional</t>
+  </si>
+  <si>
+    <t>CYBP</t>
+  </si>
+  <si>
+    <t>125.050, 132.650, 229.300</t>
+  </si>
+  <si>
+    <t>Buffalo (Jaques Farms)</t>
+  </si>
+  <si>
+    <t>CJF4</t>
+  </si>
+  <si>
+    <t>Burns Lake</t>
+  </si>
+  <si>
+    <t>CYPZ</t>
+  </si>
+  <si>
+    <t>Vancouver Ctr</t>
+  </si>
+  <si>
+    <t>123.875, 132.525</t>
   </si>
 </sst>
 </file>
@@ -7110,7 +7350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1814"/>
+  <dimension ref="A1:G1876"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -43760,6 +44000,1255 @@
         <v>122.8</v>
       </c>
     </row>
+    <row r="1815" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1815" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1815" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C1815" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1815" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1815" t="s">
+        <v>2230</v>
+      </c>
+      <c r="F1815" t="s">
+        <v>2231</v>
+      </c>
+      <c r="G1815" s="3">
+        <v>119.4</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1816" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1816" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C1816" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1816" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1816" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G1816" s="3">
+        <v>122.5</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1817" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1817" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C1817" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1817" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1817" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1817" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1818" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1818" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C1818" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1818" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1818" t="s">
+        <v>2233</v>
+      </c>
+      <c r="G1818" s="3">
+        <v>119.8</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1819" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1819" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C1819" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1819" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1819" t="s">
+        <v>2233</v>
+      </c>
+      <c r="G1819" s="3">
+        <v>121.8</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1820" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1820" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C1820" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1820" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1820" t="s">
+        <v>2234</v>
+      </c>
+      <c r="F1820" t="s">
+        <v>2233</v>
+      </c>
+      <c r="G1820" s="3" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1821" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1821" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C1821" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1821" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1821" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F1821" t="s">
+        <v>2233</v>
+      </c>
+      <c r="G1821" s="3" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1822" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1822" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C1822" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1822" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1822" t="s">
+        <v>2238</v>
+      </c>
+      <c r="F1822" t="s">
+        <v>2231</v>
+      </c>
+      <c r="G1822" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1823" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1823" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C1823" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1823" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1823" t="s">
+        <v>2239</v>
+      </c>
+      <c r="G1823" s="3">
+        <v>135.47</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1824" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1824" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C1824" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1824" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1824" t="s">
+        <v>2240</v>
+      </c>
+      <c r="G1824" s="3">
+        <v>132.69999999999999</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1825" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1825" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C1825" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1825" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1825" t="s">
+        <v>2240</v>
+      </c>
+      <c r="G1825" s="3">
+        <v>132.69999999999999</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1826" t="s">
+        <v>2241</v>
+      </c>
+      <c r="B1826" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C1826" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1826" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1826" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1826" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1827" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B1827" t="s">
+        <v>2243</v>
+      </c>
+      <c r="C1827" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1827" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1827" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1827" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1828" t="s">
+        <v>2245</v>
+      </c>
+      <c r="B1828" t="s">
+        <v>2246</v>
+      </c>
+      <c r="C1828" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1828" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1828" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1828" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1828" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1829" t="s">
+        <v>2247</v>
+      </c>
+      <c r="B1829" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C1829" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1829" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1829" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1829" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1830" t="s">
+        <v>2247</v>
+      </c>
+      <c r="B1830" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C1830" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1830" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1830" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G1830" s="3">
+        <v>134.69999999999999</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1831" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B1831" t="s">
+        <v>2251</v>
+      </c>
+      <c r="C1831" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1831" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1831" t="s">
+        <v>391</v>
+      </c>
+      <c r="G1831" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1832" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B1832" t="s">
+        <v>2251</v>
+      </c>
+      <c r="C1832" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1832" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1832" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1832" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1833" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B1833" t="s">
+        <v>2251</v>
+      </c>
+      <c r="C1833" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1833" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1833" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1833" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1834" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B1834" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C1834" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1834" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1834" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1834" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1835" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B1835" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C1835" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1835" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1835" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1835" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1836" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B1836" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C1836" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1836" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1836" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1836" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1837" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B1837" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C1837" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1837" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1837" t="s">
+        <v>402</v>
+      </c>
+      <c r="G1837" s="3">
+        <v>133.75</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1838" t="s">
+        <v>2254</v>
+      </c>
+      <c r="B1838" t="s">
+        <v>2255</v>
+      </c>
+      <c r="C1838" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1838" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1838" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1838" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1839" t="s">
+        <v>2254</v>
+      </c>
+      <c r="B1839" t="s">
+        <v>2255</v>
+      </c>
+      <c r="C1839" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1839" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1839" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1840" t="s">
+        <v>2256</v>
+      </c>
+      <c r="B1840" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C1840" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1840" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1840" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1840" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1841" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B1841" t="s">
+        <v>2259</v>
+      </c>
+      <c r="C1841" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1841" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1841" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1841" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1842" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B1842" t="s">
+        <v>2260</v>
+      </c>
+      <c r="C1842" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1842" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1842" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1842" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1843" t="s">
+        <v>2262</v>
+      </c>
+      <c r="B1843" t="s">
+        <v>2263</v>
+      </c>
+      <c r="C1843" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1843" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1843" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1843" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1844" t="s">
+        <v>2264</v>
+      </c>
+      <c r="B1844" t="s">
+        <v>2265</v>
+      </c>
+      <c r="C1844" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1844" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1844" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1844" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1845" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B1845" t="s">
+        <v>2267</v>
+      </c>
+      <c r="C1845" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1845" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1845" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1845" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1846" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B1846" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C1846" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1846" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1846" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1846" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1847" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B1847" t="s">
+        <v>2269</v>
+      </c>
+      <c r="C1847" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1847" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1847" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1847" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1848" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B1848" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C1848" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1848" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1848" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G1848" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1849" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B1849" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C1849" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1849" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1849" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1849" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1850" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B1850" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C1850" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1850" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1850" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1850" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1851" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B1851" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C1851" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1851" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1851" s="3">
+        <v>128.69999999999999</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1852" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B1852" t="s">
+        <v>2273</v>
+      </c>
+      <c r="C1852" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1852" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1852" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G1852" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1853" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B1853" t="s">
+        <v>2273</v>
+      </c>
+      <c r="C1853" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1853" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1853" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1853" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1854" t="s">
+        <v>2274</v>
+      </c>
+      <c r="B1854" t="s">
+        <v>2275</v>
+      </c>
+      <c r="C1854" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1854" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1854" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1854" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1855" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B1855" t="s">
+        <v>2277</v>
+      </c>
+      <c r="C1855" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1855" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1855" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1855" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1856" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B1856" t="s">
+        <v>2277</v>
+      </c>
+      <c r="C1856" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1856" t="s">
+        <v>235</v>
+      </c>
+      <c r="E1856" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1856" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1857" t="s">
+        <v>2279</v>
+      </c>
+      <c r="B1857" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C1857" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1857" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1857" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1857" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1857" s="3">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1858" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B1858" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C1858" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1858" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1858" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1858" s="3">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1859" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B1859" t="s">
+        <v>2283</v>
+      </c>
+      <c r="C1859" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1859" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1859" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1859" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1860" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B1860" t="s">
+        <v>2285</v>
+      </c>
+      <c r="C1860" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1860" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1860" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1860" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1861" t="s">
+        <v>2286</v>
+      </c>
+      <c r="B1861" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C1861" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1861" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1861" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G1861" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1862" t="s">
+        <v>2286</v>
+      </c>
+      <c r="B1862" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C1862" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1862" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1862" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1862" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1863" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B1863" t="s">
+        <v>2289</v>
+      </c>
+      <c r="C1863" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1863" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1863" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1863" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1864" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B1864" t="s">
+        <v>2289</v>
+      </c>
+      <c r="C1864" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1864" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1864" s="3">
+        <v>122.97499999999999</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1865" t="s">
+        <v>2290</v>
+      </c>
+      <c r="B1865" t="s">
+        <v>2291</v>
+      </c>
+      <c r="C1865" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1865" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1865" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1865" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1866" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B1866" t="s">
+        <v>2293</v>
+      </c>
+      <c r="C1866" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1866" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1866" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1866" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1867" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B1867" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C1867" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1867" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1867" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1867" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1868" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B1868" t="s">
+        <v>2297</v>
+      </c>
+      <c r="C1868" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1868" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1868" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1868" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1869" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B1869" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C1869" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1869" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1869" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1869" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1869" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1870" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B1870" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C1870" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1870" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1870" t="s">
+        <v>402</v>
+      </c>
+      <c r="G1870" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1871" t="s">
+        <v>2301</v>
+      </c>
+      <c r="B1871" t="s">
+        <v>2302</v>
+      </c>
+      <c r="C1871" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1871" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1871" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1871" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1872" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B1872" t="s">
+        <v>2304</v>
+      </c>
+      <c r="C1872" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1872" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1872" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G1872" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1873" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B1873" t="s">
+        <v>2304</v>
+      </c>
+      <c r="C1873" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1873" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1873" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1873" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1874" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B1874" t="s">
+        <v>2304</v>
+      </c>
+      <c r="C1874" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1874" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1874" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1874" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1875" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B1875" t="s">
+        <v>2304</v>
+      </c>
+      <c r="C1875" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1875" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1875" t="s">
+        <v>2305</v>
+      </c>
+      <c r="G1875" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1876" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B1876" t="s">
+        <v>2304</v>
+      </c>
+      <c r="C1876" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1876" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1876" s="3">
+        <v>122.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12C2DBD-B999-4C20-B809-3BD379D4585D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00AAF79A-4E9A-4962-A7A4-AD3CCED3DDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9650" uniqueCount="2307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10228" uniqueCount="2437">
   <si>
     <t>AB</t>
   </si>
@@ -6960,6 +6960,396 @@
   </si>
   <si>
     <t>123.875, 132.525</t>
+  </si>
+  <si>
+    <t>Cache Creek</t>
+  </si>
+  <si>
+    <t>CAZ5</t>
+  </si>
+  <si>
+    <t>Calgary / Christiansen Field</t>
+  </si>
+  <si>
+    <t>CRS3</t>
+  </si>
+  <si>
+    <t>CFX2</t>
+  </si>
+  <si>
+    <t>Calgary / Okotoks Air Ranch Airport</t>
+  </si>
+  <si>
+    <t>Calgary / Okotoks (Rowland Field)</t>
+  </si>
+  <si>
+    <t>CRF4</t>
+  </si>
+  <si>
+    <t>Calgary / Springbank</t>
+  </si>
+  <si>
+    <t>CYBW</t>
+  </si>
+  <si>
+    <t>Outer</t>
+  </si>
+  <si>
+    <t>Inner</t>
+  </si>
+  <si>
+    <t>16-24Z‡</t>
+  </si>
+  <si>
+    <t>16-14Z‡ O/T</t>
+  </si>
+  <si>
+    <t>16-14Z‡</t>
+  </si>
+  <si>
+    <t>Calgary / YYC Calgary INTL</t>
+  </si>
+  <si>
+    <t>CYYC</t>
+  </si>
+  <si>
+    <t>APRON 1: Apron advisory</t>
+  </si>
+  <si>
+    <t>12-07Z‡ O/T</t>
+  </si>
+  <si>
+    <t>123.850, 127.150, 294.9</t>
+  </si>
+  <si>
+    <t>119.800, 255.100</t>
+  </si>
+  <si>
+    <t>124.520, 255.100</t>
+  </si>
+  <si>
+    <t>Calling Lake</t>
+  </si>
+  <si>
+    <t>CFK4</t>
+  </si>
+  <si>
+    <t>Calmar / Wizard Lake</t>
+  </si>
+  <si>
+    <t>CWL3</t>
+  </si>
+  <si>
+    <t>Campbell River</t>
+  </si>
+  <si>
+    <t>CYBL</t>
+  </si>
+  <si>
+    <t>Campbell rdo</t>
+  </si>
+  <si>
+    <t>1330-0530Z‡</t>
+  </si>
+  <si>
+    <t>1330-0530Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Comox</t>
+  </si>
+  <si>
+    <t>123.700, 227.600</t>
+  </si>
+  <si>
+    <t>Camrose</t>
+  </si>
+  <si>
+    <t>CEQ3</t>
+  </si>
+  <si>
+    <t>Cardston</t>
+  </si>
+  <si>
+    <t>CEA6</t>
+  </si>
+  <si>
+    <t>Carstairs / Bishell's</t>
+  </si>
+  <si>
+    <t>CGB2</t>
+  </si>
+  <si>
+    <t>Castlegar / West Kootenay Regional</t>
+  </si>
+  <si>
+    <t>CYCG</t>
+  </si>
+  <si>
+    <t>1330-0130Z (DT 1230-0430Z)</t>
+  </si>
+  <si>
+    <t>1330-0130Z (DT 1230-0430Z) O/T tfc</t>
+  </si>
+  <si>
+    <t>134.200, 227.300</t>
+  </si>
+  <si>
+    <t>Castor</t>
+  </si>
+  <si>
+    <t>CER2</t>
+  </si>
+  <si>
+    <t>Cayley / A.J. Flying Ranch</t>
+  </si>
+  <si>
+    <t>CAJ7</t>
+  </si>
+  <si>
+    <t>Cheadle / Country Lane Farms</t>
+  </si>
+  <si>
+    <t>CLF2</t>
+  </si>
+  <si>
+    <t>Chestermere (Kirby Field)</t>
+  </si>
+  <si>
+    <t>CFX8</t>
+  </si>
+  <si>
+    <t>Chetwynd</t>
+  </si>
+  <si>
+    <t>CYCQ</t>
+  </si>
+  <si>
+    <t>Chilko Lake (Tsylos Park Lodge)</t>
+  </si>
+  <si>
+    <t>CAG3</t>
+  </si>
+  <si>
+    <t>Chilko Lake (Wilderness Lodge)</t>
+  </si>
+  <si>
+    <t>CCL6</t>
+  </si>
+  <si>
+    <t>Chilliwack</t>
+  </si>
+  <si>
+    <t>CYCW</t>
+  </si>
+  <si>
+    <t>Chipewyan Lake</t>
+  </si>
+  <si>
+    <t>CEG5</t>
+  </si>
+  <si>
+    <t>CFU3</t>
+  </si>
+  <si>
+    <t>Chipman / M.Y. Airfield</t>
+  </si>
+  <si>
+    <t>CMY2</t>
+  </si>
+  <si>
+    <t>Christina Basin</t>
+  </si>
+  <si>
+    <t>CFF2</t>
+  </si>
+  <si>
+    <t>Christina Lake</t>
+  </si>
+  <si>
+    <t>CCL3</t>
+  </si>
+  <si>
+    <t>Clairmont / Meyer's Airstrip</t>
+  </si>
+  <si>
+    <t>CMY3</t>
+  </si>
+  <si>
+    <t>Claresholm Industrial</t>
+  </si>
+  <si>
+    <t>CEJ4</t>
+  </si>
+  <si>
+    <t>Clearwater River</t>
+  </si>
+  <si>
+    <t>CFS8</t>
+  </si>
+  <si>
+    <t>Coaldale (Rednek Air)</t>
+  </si>
+  <si>
+    <t>CRD2</t>
+  </si>
+  <si>
+    <t>Cochrane / Arkayla Springs</t>
+  </si>
+  <si>
+    <t>CKY8</t>
+  </si>
+  <si>
+    <t>Cold Lake / Group Captain R.W. McNair</t>
+  </si>
+  <si>
+    <t>CYOD</t>
+  </si>
+  <si>
+    <t>118.250, 260.000</t>
+  </si>
+  <si>
+    <t>120.600, 230.600</t>
+  </si>
+  <si>
+    <t>126.200, 226.500, 236.600, 255.700</t>
+  </si>
+  <si>
+    <t>ltd hrs O/T Cold Lake advsy</t>
+  </si>
+  <si>
+    <t>124.500, 322.800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.4x, 120.6x, 124.5x, 128.2x 134.1x, 269.6x, 279.8x, 294.6x, 324.3x, 336.0x, 350.5x, 378.5x </t>
+  </si>
+  <si>
+    <t>124.5x, 322.800</t>
+  </si>
+  <si>
+    <t>Wg Ops</t>
+  </si>
+  <si>
+    <t>Tran svcg</t>
+  </si>
+  <si>
+    <t>Cold Lake / Regional</t>
+  </si>
+  <si>
+    <t>CEN5</t>
+  </si>
+  <si>
+    <t>Cold Lake</t>
+  </si>
+  <si>
+    <t>Cold Lake / Three Bears Landing</t>
+  </si>
+  <si>
+    <t>CTB8</t>
+  </si>
+  <si>
+    <t>CYQQ</t>
+  </si>
+  <si>
+    <t>118.600, 282.200</t>
+  </si>
+  <si>
+    <t>127.000, 227.600</t>
+  </si>
+  <si>
+    <t>119.750, 250.300</t>
+  </si>
+  <si>
+    <t>126.200, 358.100, 236.6x</t>
+  </si>
+  <si>
+    <t>123.700, 128.1x, 134.1x, 227.600, 289.4x, 335.9x, 342.9x, 378.5x, 384.5x</t>
+  </si>
+  <si>
+    <t>Snake Ops</t>
+  </si>
+  <si>
+    <t>135.900, 363.000</t>
+  </si>
+  <si>
+    <t>Demon Ops</t>
+  </si>
+  <si>
+    <t>Conklin (Leismer)</t>
+  </si>
+  <si>
+    <t>CET2</t>
+  </si>
+  <si>
+    <t>Consort</t>
+  </si>
+  <si>
+    <t>CFG3</t>
+  </si>
+  <si>
+    <t>Coronation</t>
+  </si>
+  <si>
+    <t>CYCT</t>
+  </si>
+  <si>
+    <t>Cortes Island</t>
+  </si>
+  <si>
+    <t>CCI9</t>
+  </si>
+  <si>
+    <t>Courtenay Airpark</t>
+  </si>
+  <si>
+    <t>CAH3</t>
+  </si>
+  <si>
+    <t>Courtenay (Smit Field)</t>
+  </si>
+  <si>
+    <t>CCS6</t>
+  </si>
+  <si>
+    <t>Coutts / Ross</t>
+  </si>
+  <si>
+    <t>CEP4</t>
+  </si>
+  <si>
+    <t>Cowley</t>
+  </si>
+  <si>
+    <t>CYYM</t>
+  </si>
+  <si>
+    <t>Cranbrook / Canadian Rockies</t>
+  </si>
+  <si>
+    <t>CYXC</t>
+  </si>
+  <si>
+    <t>Creston</t>
+  </si>
+  <si>
+    <t>CAJ3</t>
+  </si>
+  <si>
+    <t>Dawson Creek</t>
+  </si>
+  <si>
+    <t>CYDQ</t>
+  </si>
+  <si>
+    <t>RAAS Yellowknife rdo</t>
+  </si>
+  <si>
+    <t>1330-0530Z</t>
+  </si>
+  <si>
+    <t>Yellowknife rdo</t>
+  </si>
+  <si>
+    <t>1330-0530Z O/T tfc</t>
   </si>
 </sst>
 </file>
@@ -7350,7 +7740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1876"/>
+  <dimension ref="A1:G1989"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -45249,6 +45639,2242 @@
         <v>122.95</v>
       </c>
     </row>
+    <row r="1877" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1877" t="s">
+        <v>2307</v>
+      </c>
+      <c r="B1877" t="s">
+        <v>2308</v>
+      </c>
+      <c r="C1877" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1877" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1877" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1877" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1878" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B1878" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C1878" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1878" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1878" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1878" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1879" t="s">
+        <v>2312</v>
+      </c>
+      <c r="B1879" t="s">
+        <v>2311</v>
+      </c>
+      <c r="C1879" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1879" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1879" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1879" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1879" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1880" t="s">
+        <v>2313</v>
+      </c>
+      <c r="B1880" t="s">
+        <v>2314</v>
+      </c>
+      <c r="C1880" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1880" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1880" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1880" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1880" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1881" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B1881" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C1881" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1881" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1881" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1881" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1882" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B1882" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C1882" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1882" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1882" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1882" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1883" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B1883" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C1883" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1883" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1883" t="s">
+        <v>676</v>
+      </c>
+      <c r="G1883" s="3">
+        <v>127.9</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1884" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B1884" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C1884" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1884" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1884" t="s">
+        <v>676</v>
+      </c>
+      <c r="G1884" s="3">
+        <v>121.8</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1885" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B1885" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C1885" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1885" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1885" t="s">
+        <v>2317</v>
+      </c>
+      <c r="F1885" t="s">
+        <v>2319</v>
+      </c>
+      <c r="G1885" s="3">
+        <v>118.2</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1886" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B1886" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C1886" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1886" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1886" t="s">
+        <v>2318</v>
+      </c>
+      <c r="F1886" t="s">
+        <v>2319</v>
+      </c>
+      <c r="G1886" s="3">
+        <v>120.7</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1887" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B1887" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C1887" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1887" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1887" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1887" t="s">
+        <v>2320</v>
+      </c>
+      <c r="G1887" s="3">
+        <v>118.2</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1888" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B1888" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C1888" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1888" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G1888" s="3">
+        <v>128.69999999999999</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1889" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B1889" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C1889" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1889" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1889" t="s">
+        <v>2321</v>
+      </c>
+      <c r="G1889" s="3">
+        <v>127.9</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1890" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1890" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1890" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1890" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1890" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1890" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1891" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1891" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1891" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1891" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1891" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1891" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1892" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1892" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1892" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1892" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1892" s="3">
+        <v>128.22499999999999</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1893" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1893" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1893" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1893" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1893" s="3">
+        <v>120.825</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1894" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1894" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1894" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1894" t="s">
+        <v>1897</v>
+      </c>
+      <c r="E1894" t="s">
+        <v>2324</v>
+      </c>
+      <c r="F1894" t="s">
+        <v>2325</v>
+      </c>
+      <c r="G1894" s="3">
+        <v>121.3</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1895" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1895" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1895" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1895" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1895" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G1895" s="3">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1896" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1896" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1896" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1896" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1896" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G1896" s="3">
+        <v>125.35</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1897" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1897" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1897" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1897" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1897" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G1897" s="3">
+        <v>118.4</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1898" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1898" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1898" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1898" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1898" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G1898" s="3">
+        <v>118.7</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1899" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1899" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1899" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1899" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1899" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G1899" s="3">
+        <v>126.52500000000001</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1900" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1900" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1900" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1900" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1900" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G1900" s="3">
+        <v>125.9</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1901" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1901" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1901" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1901" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1901" s="3" t="s">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1902" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1902" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1902" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1902" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1902" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G1902" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1903" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1903" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1903" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1903" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1903" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G1903" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1904" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1904" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1904" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1904" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G1904" s="3">
+        <v>119.4</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1905" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1905" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1905" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1905" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1905" t="s">
+        <v>402</v>
+      </c>
+      <c r="G1905" s="3">
+        <v>124.52500000000001</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1906" t="s">
+        <v>2329</v>
+      </c>
+      <c r="B1906" t="s">
+        <v>2330</v>
+      </c>
+      <c r="C1906" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1906" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1906" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1906" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1907" t="s">
+        <v>2331</v>
+      </c>
+      <c r="B1907" t="s">
+        <v>2332</v>
+      </c>
+      <c r="C1907" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1907" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1907" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1907" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1908" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B1908" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C1908" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1908" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1908" t="s">
+        <v>2335</v>
+      </c>
+      <c r="F1908" t="s">
+        <v>2336</v>
+      </c>
+      <c r="G1908" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1909" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B1909" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C1909" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1909" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1909" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G1909" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1910" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B1910" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C1910" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1910" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1910" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1910" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1911" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B1911" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C1911" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1911" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1911" t="s">
+        <v>715</v>
+      </c>
+      <c r="G1911" s="3">
+        <v>128.55000000000001</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1912" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B1912" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C1912" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1912" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1912" t="s">
+        <v>2335</v>
+      </c>
+      <c r="F1912" t="s">
+        <v>2337</v>
+      </c>
+      <c r="G1912" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1913" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B1913" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C1913" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1913" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1913" t="s">
+        <v>2338</v>
+      </c>
+      <c r="G1913" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1914" t="s">
+        <v>2340</v>
+      </c>
+      <c r="B1914" t="s">
+        <v>2341</v>
+      </c>
+      <c r="C1914" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1914" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1914" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1914" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1914" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1915" t="s">
+        <v>2340</v>
+      </c>
+      <c r="B1915" t="s">
+        <v>2341</v>
+      </c>
+      <c r="C1915" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1915" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1915" s="3">
+        <v>122.97499999999999</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1916" t="s">
+        <v>2342</v>
+      </c>
+      <c r="B1916" t="s">
+        <v>2343</v>
+      </c>
+      <c r="C1916" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1916" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1916" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1916" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1917" t="s">
+        <v>2344</v>
+      </c>
+      <c r="B1917" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C1917" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1917" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1917" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1917" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1918" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B1918" t="s">
+        <v>2347</v>
+      </c>
+      <c r="C1918" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1918" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1918" t="s">
+        <v>2348</v>
+      </c>
+      <c r="G1918" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1919" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B1919" t="s">
+        <v>2347</v>
+      </c>
+      <c r="C1919" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1919" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1919" t="s">
+        <v>2232</v>
+      </c>
+      <c r="F1919" t="s">
+        <v>2349</v>
+      </c>
+      <c r="G1919" s="3">
+        <v>125.85</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1920" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B1920" t="s">
+        <v>2347</v>
+      </c>
+      <c r="C1920" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1920" t="s">
+        <v>641</v>
+      </c>
+      <c r="E1920" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1920" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1921" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B1921" t="s">
+        <v>2347</v>
+      </c>
+      <c r="C1921" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1921" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1921" t="s">
+        <v>2305</v>
+      </c>
+      <c r="G1921" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1922" t="s">
+        <v>2351</v>
+      </c>
+      <c r="B1922" t="s">
+        <v>2352</v>
+      </c>
+      <c r="C1922" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1922" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1922" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1922" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1923" t="s">
+        <v>2353</v>
+      </c>
+      <c r="B1923" t="s">
+        <v>2354</v>
+      </c>
+      <c r="C1923" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1923" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1923" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1923" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1924" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B1924" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C1924" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1924" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1924" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1924" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1925" t="s">
+        <v>2357</v>
+      </c>
+      <c r="B1925" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C1925" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1925" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1925" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1925" s="3">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1926" t="s">
+        <v>2359</v>
+      </c>
+      <c r="B1926" t="s">
+        <v>2360</v>
+      </c>
+      <c r="C1926" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1926" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1926" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1926" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1927" t="s">
+        <v>2359</v>
+      </c>
+      <c r="B1927" t="s">
+        <v>2360</v>
+      </c>
+      <c r="C1927" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1927" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1927" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1928" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B1928" t="s">
+        <v>2362</v>
+      </c>
+      <c r="C1928" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1928" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1928" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1928" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1929" t="s">
+        <v>2363</v>
+      </c>
+      <c r="B1929" t="s">
+        <v>2364</v>
+      </c>
+      <c r="C1929" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1929" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1929" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1929" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1929" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1930" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B1930" t="s">
+        <v>2366</v>
+      </c>
+      <c r="C1930" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1930" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1930" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1930" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1931" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B1931" t="s">
+        <v>2366</v>
+      </c>
+      <c r="C1931" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1931" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1931" s="3">
+        <v>122.97499999999999</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1932" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B1932" t="s">
+        <v>2368</v>
+      </c>
+      <c r="C1932" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1932" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1932" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1932" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1933" t="s">
+        <v>801</v>
+      </c>
+      <c r="B1933" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C1933" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1933" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1933" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1933" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1933" s="3">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1934" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B1934" t="s">
+        <v>2371</v>
+      </c>
+      <c r="C1934" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1934" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1934" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1934" s="3">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1935" t="s">
+        <v>2372</v>
+      </c>
+      <c r="B1935" t="s">
+        <v>2373</v>
+      </c>
+      <c r="C1935" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1935" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1935" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1935" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1936" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B1936" t="s">
+        <v>2375</v>
+      </c>
+      <c r="C1936" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1936" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1936" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1936" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1937" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B1937" t="s">
+        <v>2375</v>
+      </c>
+      <c r="C1937" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1937" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1937" t="s">
+        <v>402</v>
+      </c>
+      <c r="G1937" s="3">
+        <v>133.72499999999999</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1938" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B1938" t="s">
+        <v>2375</v>
+      </c>
+      <c r="C1938" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1938" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1938" s="3">
+        <v>122.27500000000001</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1939" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B1939" t="s">
+        <v>2377</v>
+      </c>
+      <c r="C1939" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1939" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1939" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1939" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1940" t="s">
+        <v>2378</v>
+      </c>
+      <c r="B1940" t="s">
+        <v>2379</v>
+      </c>
+      <c r="C1940" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1940" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1940" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1940" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1940" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1941" t="s">
+        <v>2380</v>
+      </c>
+      <c r="B1941" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C1941" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1941" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1941" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1941" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1942" t="s">
+        <v>2382</v>
+      </c>
+      <c r="B1942" t="s">
+        <v>2383</v>
+      </c>
+      <c r="C1942" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1942" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1942" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1942" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1943" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B1943" t="s">
+        <v>2385</v>
+      </c>
+      <c r="C1943" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1943" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1943" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1943" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1944" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B1944" t="s">
+        <v>2387</v>
+      </c>
+      <c r="C1944" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1944" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1944" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1945" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B1945" t="s">
+        <v>2387</v>
+      </c>
+      <c r="C1945" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1945" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1945" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1946" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B1946" t="s">
+        <v>2387</v>
+      </c>
+      <c r="C1946" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1946" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1946" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1947" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B1947" t="s">
+        <v>2387</v>
+      </c>
+      <c r="C1947" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1947" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1947" t="s">
+        <v>2391</v>
+      </c>
+      <c r="G1947" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1948" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B1948" t="s">
+        <v>2387</v>
+      </c>
+      <c r="C1948" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1948" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1948" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1949" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B1949" t="s">
+        <v>2387</v>
+      </c>
+      <c r="C1949" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1949" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1949" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1950" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B1950" t="s">
+        <v>2387</v>
+      </c>
+      <c r="C1950" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1950" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1950" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1951" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B1951" t="s">
+        <v>2387</v>
+      </c>
+      <c r="C1951" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1951" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1951" t="s">
+        <v>2395</v>
+      </c>
+      <c r="G1951" s="3">
+        <v>340.2</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1952" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B1952" t="s">
+        <v>2387</v>
+      </c>
+      <c r="C1952" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1952" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1952" t="s">
+        <v>2396</v>
+      </c>
+      <c r="G1952" s="3">
+        <v>308.7</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1953" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B1953" t="s">
+        <v>2387</v>
+      </c>
+      <c r="C1953" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1953" t="s">
+        <v>190</v>
+      </c>
+      <c r="G1953" s="3">
+        <v>344.6</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1954" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B1954" t="s">
+        <v>2398</v>
+      </c>
+      <c r="C1954" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1954" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1954" t="s">
+        <v>2399</v>
+      </c>
+      <c r="G1954" s="3">
+        <v>126.2</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1955" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B1955" t="s">
+        <v>2398</v>
+      </c>
+      <c r="C1955" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1955" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1955" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1955" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1956" t="s">
+        <v>2400</v>
+      </c>
+      <c r="B1956" t="s">
+        <v>2401</v>
+      </c>
+      <c r="C1956" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1956" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1956" t="s">
+        <v>2399</v>
+      </c>
+      <c r="G1956" s="3">
+        <v>126.2</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1957" t="s">
+        <v>2400</v>
+      </c>
+      <c r="B1957" t="s">
+        <v>2401</v>
+      </c>
+      <c r="C1957" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1957" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1957" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1957" s="3">
+        <v>132.19999999999999</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1958" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B1958" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C1958" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1958" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1958" s="3" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1959" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B1959" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C1959" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1959" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1959" s="3" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1960" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B1960" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C1960" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1960" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1960" s="3" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1961" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B1961" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C1961" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1961" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1961" s="3" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1962" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B1962" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C1962" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1962" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1962" s="3" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1963" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B1963" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C1963" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1963" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1963" s="3" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1964" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B1964" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C1964" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1964" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1964" s="3" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1965" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B1965" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C1965" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1965" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1965" t="s">
+        <v>2408</v>
+      </c>
+      <c r="G1965" s="3" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1966" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B1966" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C1966" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1966" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1966" t="s">
+        <v>2410</v>
+      </c>
+      <c r="G1966" s="3">
+        <v>308.60000000000002</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1967" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B1967" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C1967" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1967" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1967" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G1967" s="3">
+        <v>316.5</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1968" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B1968" t="s">
+        <v>2412</v>
+      </c>
+      <c r="C1968" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1968" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1968" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1968" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1968" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1969" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B1969" t="s">
+        <v>2412</v>
+      </c>
+      <c r="C1969" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1969" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1969" t="s">
+        <v>402</v>
+      </c>
+      <c r="G1969" s="3">
+        <v>133.72499999999999</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1970" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B1970" t="s">
+        <v>2412</v>
+      </c>
+      <c r="C1970" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1970" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1970" s="3">
+        <v>123.175</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1971" t="s">
+        <v>2413</v>
+      </c>
+      <c r="B1971" t="s">
+        <v>2414</v>
+      </c>
+      <c r="C1971" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1971" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1971" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1971" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1972" t="s">
+        <v>2415</v>
+      </c>
+      <c r="B1972" t="s">
+        <v>2416</v>
+      </c>
+      <c r="C1972" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1972" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1972" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1972" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1972" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1973" t="s">
+        <v>2417</v>
+      </c>
+      <c r="B1973" t="s">
+        <v>2418</v>
+      </c>
+      <c r="C1973" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1973" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1973" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1973" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1974" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B1974" t="s">
+        <v>2420</v>
+      </c>
+      <c r="C1974" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1974" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1974" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1974" s="3">
+        <v>123.35</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1975" t="s">
+        <v>2421</v>
+      </c>
+      <c r="B1975" t="s">
+        <v>2422</v>
+      </c>
+      <c r="C1975" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1975" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1975" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1975" s="3">
+        <v>123.35</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1976" t="s">
+        <v>2423</v>
+      </c>
+      <c r="B1976" t="s">
+        <v>2424</v>
+      </c>
+      <c r="C1976" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1976" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1976" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1976" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1976" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1977" t="s">
+        <v>2425</v>
+      </c>
+      <c r="B1977" t="s">
+        <v>2426</v>
+      </c>
+      <c r="C1977" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1977" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1977" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1977" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1977" s="3">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1978" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B1978" t="s">
+        <v>2428</v>
+      </c>
+      <c r="C1978" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1978" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1978" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1979" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B1979" t="s">
+        <v>2428</v>
+      </c>
+      <c r="C1979" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1979" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1979" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G1979" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1980" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B1980" t="s">
+        <v>2428</v>
+      </c>
+      <c r="C1980" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1980" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1980" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1980" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1981" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B1981" t="s">
+        <v>2428</v>
+      </c>
+      <c r="C1981" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1981" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1981" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1981" s="3">
+        <v>122.3</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1982" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B1982" t="s">
+        <v>2428</v>
+      </c>
+      <c r="C1982" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1982" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1982" t="s">
+        <v>2305</v>
+      </c>
+      <c r="G1982" s="3">
+        <v>133.6</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1983" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B1983" t="s">
+        <v>2430</v>
+      </c>
+      <c r="C1983" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1983" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1983" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G1983" s="3">
+        <v>125.85</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1984" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B1984" t="s">
+        <v>2430</v>
+      </c>
+      <c r="C1984" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1984" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1984" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1984" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1985" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B1985" t="s">
+        <v>2430</v>
+      </c>
+      <c r="C1985" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1985" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1985" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1985" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1986" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B1986" t="s">
+        <v>2430</v>
+      </c>
+      <c r="C1986" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1986" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1986" s="3">
+        <v>129.17500000000001</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1987" t="s">
+        <v>2431</v>
+      </c>
+      <c r="B1987" t="s">
+        <v>2432</v>
+      </c>
+      <c r="C1987" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1987" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1987" t="s">
+        <v>2433</v>
+      </c>
+      <c r="F1987" t="s">
+        <v>2434</v>
+      </c>
+      <c r="G1987" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1988" t="s">
+        <v>2431</v>
+      </c>
+      <c r="B1988" t="s">
+        <v>2432</v>
+      </c>
+      <c r="C1988" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1988" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1988" t="s">
+        <v>2435</v>
+      </c>
+      <c r="F1988" t="s">
+        <v>2436</v>
+      </c>
+      <c r="G1988" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1989" t="s">
+        <v>2431</v>
+      </c>
+      <c r="B1989" t="s">
+        <v>2432</v>
+      </c>
+      <c r="C1989" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1989" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1989" s="3">
+        <v>128.55000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00AAF79A-4E9A-4962-A7A4-AD3CCED3DDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8A731B-D394-45B7-ABFD-DA96ED327FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10228" uniqueCount="2437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10331" uniqueCount="2465">
   <si>
     <t>AB</t>
   </si>
@@ -7350,6 +7350,90 @@
   </si>
   <si>
     <t>1330-0530Z O/T tfc</t>
+  </si>
+  <si>
+    <t>Dawson Creek (Flying L Ranch)</t>
+  </si>
+  <si>
+    <t>CDC3</t>
+  </si>
+  <si>
+    <t>Dease Lake</t>
+  </si>
+  <si>
+    <t>CYDL</t>
+  </si>
+  <si>
+    <t>Debolt</t>
+  </si>
+  <si>
+    <t>CFG4</t>
+  </si>
+  <si>
+    <t>Del Bonita / Whetstone</t>
+  </si>
+  <si>
+    <t>CEQ4</t>
+  </si>
+  <si>
+    <t>Delburne / Stonehill Farms</t>
+  </si>
+  <si>
+    <t>CSF6</t>
+  </si>
+  <si>
+    <t>Delta / Delta Heritage Air Park</t>
+  </si>
+  <si>
+    <t>CAK3</t>
+  </si>
+  <si>
+    <t>Boundary Bay</t>
+  </si>
+  <si>
+    <t>Denny Island</t>
+  </si>
+  <si>
+    <t>CYJQ</t>
+  </si>
+  <si>
+    <t>FISE Pacific rdo (Bella Bella (Campbell Is.))</t>
+  </si>
+  <si>
+    <t>De Winton / South Calgary</t>
+  </si>
+  <si>
+    <t>CEH4</t>
+  </si>
+  <si>
+    <t>Didsbury / Minty Field</t>
+  </si>
+  <si>
+    <t>CDM2</t>
+  </si>
+  <si>
+    <t>Donnelly</t>
+  </si>
+  <si>
+    <t>CFM4</t>
+  </si>
+  <si>
+    <t>Douglas Lake</t>
+  </si>
+  <si>
+    <t>CAL3</t>
+  </si>
+  <si>
+    <t>Dryaton Valley Industrial</t>
+  </si>
+  <si>
+    <t>CER3</t>
+  </si>
+  <si>
+    <t>Drumheller Muni</t>
+  </si>
+  <si>
+    <t>CEG4</t>
   </si>
 </sst>
 </file>
@@ -7740,7 +7824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G1989"/>
+  <dimension ref="A1:G2009"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -47875,6 +47959,415 @@
         <v>128.55000000000001</v>
       </c>
     </row>
+    <row r="1990" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1990" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B1990" t="s">
+        <v>2438</v>
+      </c>
+      <c r="C1990" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1990" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1990" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1990" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1991" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B1991" t="s">
+        <v>2440</v>
+      </c>
+      <c r="C1991" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1991" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1991" t="s">
+        <v>391</v>
+      </c>
+      <c r="G1991" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1992" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B1992" t="s">
+        <v>2440</v>
+      </c>
+      <c r="C1992" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1992" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1992" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1992" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1993" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B1993" t="s">
+        <v>2440</v>
+      </c>
+      <c r="C1993" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1993" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1993" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1993" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1994" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B1994" t="s">
+        <v>2440</v>
+      </c>
+      <c r="C1994" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1994" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1994" s="3">
+        <v>128.69999999999999</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1995" t="s">
+        <v>2441</v>
+      </c>
+      <c r="B1995" t="s">
+        <v>2442</v>
+      </c>
+      <c r="C1995" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1995" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1995" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1995" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1996" t="s">
+        <v>2443</v>
+      </c>
+      <c r="B1996" t="s">
+        <v>2444</v>
+      </c>
+      <c r="C1996" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1996" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1996" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1996" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1996" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1997" t="s">
+        <v>2445</v>
+      </c>
+      <c r="B1997" t="s">
+        <v>2446</v>
+      </c>
+      <c r="C1997" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1997" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1997" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1997" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1998" t="s">
+        <v>2447</v>
+      </c>
+      <c r="B1998" t="s">
+        <v>2448</v>
+      </c>
+      <c r="C1998" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1998" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1998" t="s">
+        <v>2449</v>
+      </c>
+      <c r="F1998" t="s">
+        <v>2233</v>
+      </c>
+      <c r="G1998" s="3">
+        <v>125.5</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1999" t="s">
+        <v>2447</v>
+      </c>
+      <c r="B1999" t="s">
+        <v>2448</v>
+      </c>
+      <c r="C1999" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1999" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1999" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1999" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2000" t="s">
+        <v>2450</v>
+      </c>
+      <c r="B2000" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C2000" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2000" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2000" t="s">
+        <v>2452</v>
+      </c>
+      <c r="G2000" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2001" t="s">
+        <v>2450</v>
+      </c>
+      <c r="B2001" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C2001" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2001" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2001" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2001" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2002" t="s">
+        <v>2450</v>
+      </c>
+      <c r="B2002" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C2002" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2002" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2002" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2002" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2003" t="s">
+        <v>2453</v>
+      </c>
+      <c r="B2003" t="s">
+        <v>2454</v>
+      </c>
+      <c r="C2003" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2003" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2003" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2003" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2003" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2004" t="s">
+        <v>2455</v>
+      </c>
+      <c r="B2004" t="s">
+        <v>2456</v>
+      </c>
+      <c r="C2004" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2004" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2004" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2004" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2005" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B2005" t="s">
+        <v>2458</v>
+      </c>
+      <c r="C2005" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2005" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2005" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2005" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2006" t="s">
+        <v>2459</v>
+      </c>
+      <c r="B2006" t="s">
+        <v>2460</v>
+      </c>
+      <c r="C2006" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2006" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2006" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2006" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2007" t="s">
+        <v>2461</v>
+      </c>
+      <c r="B2007" t="s">
+        <v>2462</v>
+      </c>
+      <c r="C2007" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2007" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2007" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2007" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2007" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2008" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B2008" t="s">
+        <v>2464</v>
+      </c>
+      <c r="C2008" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2008" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2008" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2008" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2008" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2009" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B2009" t="s">
+        <v>2464</v>
+      </c>
+      <c r="C2009" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2009" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2009" s="3">
+        <v>122.175</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8A731B-D394-45B7-ABFD-DA96ED327FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91725399-8A3C-4C9C-B313-1B8A7CCF9D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10331" uniqueCount="2465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10607" uniqueCount="2528">
   <si>
     <t>AB</t>
   </si>
@@ -7434,6 +7434,195 @@
   </si>
   <si>
     <t>CEG4</t>
+  </si>
+  <si>
+    <t>Duncan</t>
+  </si>
+  <si>
+    <t>CAM3</t>
+  </si>
+  <si>
+    <t>Eaglesham / Bice Farm</t>
+  </si>
+  <si>
+    <t>CBI2</t>
+  </si>
+  <si>
+    <t>Eaglesham / Codesa South</t>
+  </si>
+  <si>
+    <t>CCP7</t>
+  </si>
+  <si>
+    <t>Eaglesham / Delta Tango Field</t>
+  </si>
+  <si>
+    <t>CGL4</t>
+  </si>
+  <si>
+    <t>CDT8</t>
+  </si>
+  <si>
+    <t>Eaglesham / South</t>
+  </si>
+  <si>
+    <t>Echo Valley</t>
+  </si>
+  <si>
+    <t>CBJ4</t>
+  </si>
+  <si>
+    <t>Edmonton / Calmar (Maplelane Farm)</t>
+  </si>
+  <si>
+    <t>CMF2</t>
+  </si>
+  <si>
+    <t>Edmonton / Cooking Lake</t>
+  </si>
+  <si>
+    <t>CEZ3</t>
+  </si>
+  <si>
+    <t>Edmonton Tml</t>
+  </si>
+  <si>
+    <t>Edmonton / Edmonton Parkland Executive Airport</t>
+  </si>
+  <si>
+    <t>CYEP</t>
+  </si>
+  <si>
+    <t>Edmonton / Gartner</t>
+  </si>
+  <si>
+    <t>CFQ7</t>
+  </si>
+  <si>
+    <t>Edmonton Intl twr</t>
+  </si>
+  <si>
+    <t>Edmonton Intl</t>
+  </si>
+  <si>
+    <t>CYEG</t>
+  </si>
+  <si>
+    <t>121.700, 275.600</t>
+  </si>
+  <si>
+    <t>118.300, 381.200</t>
+  </si>
+  <si>
+    <t>120.500, 363.800</t>
+  </si>
+  <si>
+    <t>133.650, 363.800</t>
+  </si>
+  <si>
+    <t>Twr</t>
+  </si>
+  <si>
+    <t>118.300, 119.500</t>
+  </si>
+  <si>
+    <t>Edmonton / Josephburg</t>
+  </si>
+  <si>
+    <t>CFB6</t>
+  </si>
+  <si>
+    <t>Edmonton / Morinville (Currie Field)</t>
+  </si>
+  <si>
+    <t>CCF6</t>
+  </si>
+  <si>
+    <t>Edmonton / Morinville (Mike's Field)</t>
+  </si>
+  <si>
+    <t>CMN6</t>
+  </si>
+  <si>
+    <t>Edmonton / Twin Island Airpark</t>
+  </si>
+  <si>
+    <t>Edmonton / Villeneuve</t>
+  </si>
+  <si>
+    <t>CZVL</t>
+  </si>
+  <si>
+    <t>CEE6</t>
+  </si>
+  <si>
+    <t>Villeneuve</t>
+  </si>
+  <si>
+    <t>15-04Z‡</t>
+  </si>
+  <si>
+    <t>04-15Z‡</t>
+  </si>
+  <si>
+    <t>Edmonton / Villeneuve (Rose Field)</t>
+  </si>
+  <si>
+    <t>CRF3</t>
+  </si>
+  <si>
+    <t>Villeneuve Tower</t>
+  </si>
+  <si>
+    <t>Edson</t>
+  </si>
+  <si>
+    <t>CYET</t>
+  </si>
+  <si>
+    <t>Elkin Creek Guest Ranch</t>
+  </si>
+  <si>
+    <t>CBL9</t>
+  </si>
+  <si>
+    <t>Elko / Lionel P. Demers Memorial Airpark</t>
+  </si>
+  <si>
+    <t>CBE2</t>
+  </si>
+  <si>
+    <t>Elk Point</t>
+  </si>
+  <si>
+    <t>CEJ6</t>
+  </si>
+  <si>
+    <t>Empress</t>
+  </si>
+  <si>
+    <t>CYEA</t>
+  </si>
+  <si>
+    <t>Fairmont Hot Springs</t>
+  </si>
+  <si>
+    <t>CYCZ</t>
+  </si>
+  <si>
+    <t>FISE Pacific rdo (invermere)</t>
+  </si>
+  <si>
+    <t>Fairview</t>
+  </si>
+  <si>
+    <t>CEB5</t>
+  </si>
+  <si>
+    <t>Foremost</t>
+  </si>
+  <si>
+    <t>CFD4</t>
   </si>
 </sst>
 </file>
@@ -7824,7 +8013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G2009"/>
+  <dimension ref="A1:G2067"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -48368,6 +48557,1103 @@
         <v>122.175</v>
       </c>
     </row>
+    <row r="2010" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2010" t="s">
+        <v>2465</v>
+      </c>
+      <c r="B2010" t="s">
+        <v>2466</v>
+      </c>
+      <c r="C2010" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2010" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2010" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2010" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2011" t="s">
+        <v>2467</v>
+      </c>
+      <c r="B2011" t="s">
+        <v>2468</v>
+      </c>
+      <c r="C2011" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2011" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2011" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2011" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2012" t="s">
+        <v>2469</v>
+      </c>
+      <c r="B2012" t="s">
+        <v>2470</v>
+      </c>
+      <c r="C2012" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2012" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2012" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2012" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2013" t="s">
+        <v>2471</v>
+      </c>
+      <c r="B2013" t="s">
+        <v>2473</v>
+      </c>
+      <c r="C2013" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2013" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2013" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2013" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2014" t="s">
+        <v>2474</v>
+      </c>
+      <c r="B2014" t="s">
+        <v>2472</v>
+      </c>
+      <c r="C2014" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2014" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2014" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2014" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2015" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B2015" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C2015" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2015" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2015" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2015" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2016" t="s">
+        <v>2477</v>
+      </c>
+      <c r="B2016" t="s">
+        <v>2478</v>
+      </c>
+      <c r="C2016" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2016" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2016" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2016" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2017" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B2017" t="s">
+        <v>2480</v>
+      </c>
+      <c r="C2017" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2017" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2017" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2017" s="3">
+        <v>123.35</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2018" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B2018" t="s">
+        <v>2480</v>
+      </c>
+      <c r="C2018" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2018" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2018" t="s">
+        <v>2481</v>
+      </c>
+      <c r="G2018" s="3">
+        <v>119.5</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2019" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B2019" t="s">
+        <v>2480</v>
+      </c>
+      <c r="C2019" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2019" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2019" t="s">
+        <v>2481</v>
+      </c>
+      <c r="G2019" s="3">
+        <v>119.5</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2020" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B2020" t="s">
+        <v>2480</v>
+      </c>
+      <c r="C2020" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2020" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E2020" t="s">
+        <v>2481</v>
+      </c>
+      <c r="G2020" s="3">
+        <v>127.4</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2021" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B2021" t="s">
+        <v>2483</v>
+      </c>
+      <c r="C2021" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2021" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2021" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2021" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2022" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B2022" t="s">
+        <v>2483</v>
+      </c>
+      <c r="C2022" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2022" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E2022" t="s">
+        <v>2481</v>
+      </c>
+      <c r="G2022" s="3">
+        <v>127.4</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2023" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B2023" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C2023" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2023" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2023" t="s">
+        <v>2486</v>
+      </c>
+      <c r="G2023" s="3">
+        <v>118.3</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2024" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B2024" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C2024" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2024" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2024" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2024" s="3">
+        <v>122.375</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2025" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B2025" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C2025" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2025" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2025" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2025" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2026" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B2026" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C2026" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2026" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2026" s="3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2027" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B2027" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C2027" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2027" t="s">
+        <v>146</v>
+      </c>
+      <c r="G2027" s="3">
+        <v>124.1</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2028" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B2028" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C2028" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2028" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2028" t="s">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2029" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B2029" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C2029" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2029" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2029" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2030" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B2030" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C2030" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2030" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2030" t="s">
+        <v>2481</v>
+      </c>
+      <c r="G2030" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2031" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B2031" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C2031" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2031" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2031" t="s">
+        <v>2481</v>
+      </c>
+      <c r="G2031" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2032" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B2032" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C2032" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2032" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E2032" t="s">
+        <v>2493</v>
+      </c>
+      <c r="G2032" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2033" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B2033" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C2033" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2033" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E2033" t="s">
+        <v>2481</v>
+      </c>
+      <c r="G2033" s="3">
+        <v>127.4</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2034" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B2034" t="s">
+        <v>2496</v>
+      </c>
+      <c r="C2034" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2034" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2034" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2034" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2035" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B2035" t="s">
+        <v>2496</v>
+      </c>
+      <c r="C2035" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2035" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2035" t="s">
+        <v>2481</v>
+      </c>
+      <c r="G2035" s="3">
+        <v>119.5</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2036" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B2036" t="s">
+        <v>2496</v>
+      </c>
+      <c r="C2036" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2036" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2036" t="s">
+        <v>2481</v>
+      </c>
+      <c r="G2036" s="3">
+        <v>119.5</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2037" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B2037" t="s">
+        <v>2496</v>
+      </c>
+      <c r="C2037" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2037" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E2037" t="s">
+        <v>2481</v>
+      </c>
+      <c r="G2037" s="3">
+        <v>127.4</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2038" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B2038" t="s">
+        <v>2496</v>
+      </c>
+      <c r="C2038" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2038" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2038" s="3">
+        <v>122.35</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2039" t="s">
+        <v>2497</v>
+      </c>
+      <c r="B2039" t="s">
+        <v>2498</v>
+      </c>
+      <c r="C2039" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2039" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2039" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2039" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2040" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B2040" t="s">
+        <v>2500</v>
+      </c>
+      <c r="C2040" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2040" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2040" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2040" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2041" t="s">
+        <v>2501</v>
+      </c>
+      <c r="B2041" t="s">
+        <v>2504</v>
+      </c>
+      <c r="C2041" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2041" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2041" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2041" s="3">
+        <v>123.35</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2042" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B2042" t="s">
+        <v>2503</v>
+      </c>
+      <c r="C2042" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2042" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2042" t="s">
+        <v>2506</v>
+      </c>
+      <c r="G2042" s="3">
+        <v>128.35</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2043" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B2043" t="s">
+        <v>2503</v>
+      </c>
+      <c r="C2043" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2043" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2043" t="s">
+        <v>2505</v>
+      </c>
+      <c r="F2043" t="s">
+        <v>2506</v>
+      </c>
+      <c r="G2043" s="3">
+        <v>120.8</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2044" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B2044" t="s">
+        <v>2503</v>
+      </c>
+      <c r="C2044" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2044" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2044" t="s">
+        <v>2505</v>
+      </c>
+      <c r="F2044" t="s">
+        <v>2506</v>
+      </c>
+      <c r="G2044" s="3">
+        <v>118.8</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2045" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B2045" t="s">
+        <v>2503</v>
+      </c>
+      <c r="C2045" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2045" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2045" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2045" t="s">
+        <v>2507</v>
+      </c>
+      <c r="G2045" s="3">
+        <v>118.8</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2046" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B2046" t="s">
+        <v>2503</v>
+      </c>
+      <c r="C2046" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2046" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2046" t="s">
+        <v>2481</v>
+      </c>
+      <c r="G2046" s="3">
+        <v>119.5</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2047" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B2047" t="s">
+        <v>2503</v>
+      </c>
+      <c r="C2047" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2047" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2047" t="s">
+        <v>2481</v>
+      </c>
+      <c r="G2047" s="3">
+        <v>119.5</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2048" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B2048" t="s">
+        <v>2503</v>
+      </c>
+      <c r="C2048" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2048" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E2048" t="s">
+        <v>2481</v>
+      </c>
+      <c r="G2048" s="3">
+        <v>127.4</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2049" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B2049" t="s">
+        <v>2503</v>
+      </c>
+      <c r="C2049" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2049" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2049" t="s">
+        <v>2507</v>
+      </c>
+      <c r="G2049" s="3">
+        <v>128.35</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2050" t="s">
+        <v>2508</v>
+      </c>
+      <c r="B2050" t="s">
+        <v>2509</v>
+      </c>
+      <c r="C2050" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2050" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2050" t="s">
+        <v>2510</v>
+      </c>
+      <c r="F2050" t="s">
+        <v>2506</v>
+      </c>
+      <c r="G2050" s="3">
+        <v>118.8</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2051" t="s">
+        <v>2508</v>
+      </c>
+      <c r="B2051" t="s">
+        <v>2509</v>
+      </c>
+      <c r="C2051" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2051" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2051" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2051" t="s">
+        <v>2507</v>
+      </c>
+      <c r="G2051" s="3">
+        <v>118.8</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2052" t="s">
+        <v>2511</v>
+      </c>
+      <c r="B2052" t="s">
+        <v>2512</v>
+      </c>
+      <c r="C2052" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2052" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2052" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2052" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2053" t="s">
+        <v>2511</v>
+      </c>
+      <c r="B2053" t="s">
+        <v>2512</v>
+      </c>
+      <c r="C2053" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2053" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2053" s="3">
+        <v>128.75</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2054" t="s">
+        <v>2513</v>
+      </c>
+      <c r="B2054" t="s">
+        <v>2514</v>
+      </c>
+      <c r="C2054" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2054" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2054" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2054" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2055" t="s">
+        <v>2515</v>
+      </c>
+      <c r="B2055" t="s">
+        <v>2516</v>
+      </c>
+      <c r="C2055" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2055" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2055" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2055" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2056" t="s">
+        <v>2517</v>
+      </c>
+      <c r="B2056" t="s">
+        <v>2518</v>
+      </c>
+      <c r="C2056" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2056" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2056" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2056" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2057" t="s">
+        <v>2519</v>
+      </c>
+      <c r="B2057" t="s">
+        <v>2520</v>
+      </c>
+      <c r="C2057" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2057" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2057" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2057" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2058" t="s">
+        <v>2521</v>
+      </c>
+      <c r="B2058" t="s">
+        <v>2522</v>
+      </c>
+      <c r="C2058" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2058" t="s">
+        <v>2523</v>
+      </c>
+      <c r="G2058" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2059" t="s">
+        <v>2521</v>
+      </c>
+      <c r="B2059" t="s">
+        <v>2522</v>
+      </c>
+      <c r="C2059" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2059" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2059" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2060" t="s">
+        <v>2521</v>
+      </c>
+      <c r="B2060" t="s">
+        <v>2522</v>
+      </c>
+      <c r="C2060" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2060" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2060" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2060" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2061" t="s">
+        <v>2521</v>
+      </c>
+      <c r="B2061" t="s">
+        <v>2522</v>
+      </c>
+      <c r="C2061" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2061" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2061" s="3">
+        <v>122.97499999999999</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2062" t="s">
+        <v>2524</v>
+      </c>
+      <c r="B2062" t="s">
+        <v>2525</v>
+      </c>
+      <c r="C2062" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2062" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2062" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2062" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2062" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2063" t="s">
+        <v>2524</v>
+      </c>
+      <c r="B2063" t="s">
+        <v>2525</v>
+      </c>
+      <c r="C2063" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2063" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2063" s="3">
+        <v>122.97499999999999</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2064" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B2064" t="s">
+        <v>2527</v>
+      </c>
+      <c r="C2064" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2064" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2064" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2064" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2065" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G2065" s="3"/>
+    </row>
+    <row r="2066" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G2066" s="3"/>
+    </row>
+    <row r="2067" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G2067" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91725399-8A3C-4C9C-B313-1B8A7CCF9D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A46984-E591-4FDE-BC48-268283B57E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10607" uniqueCount="2528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10864" uniqueCount="2563">
   <si>
     <t>AB</t>
   </si>
@@ -7623,6 +7623,111 @@
   </si>
   <si>
     <t>CFD4</t>
+  </si>
+  <si>
+    <t>Fort Chipewyan</t>
+  </si>
+  <si>
+    <t>CYPY</t>
+  </si>
+  <si>
+    <t>Fort Grahame</t>
+  </si>
+  <si>
+    <t>CBW3</t>
+  </si>
+  <si>
+    <t>Fort Langley</t>
+  </si>
+  <si>
+    <t>CBQ2</t>
+  </si>
+  <si>
+    <t>Fort Mackay / Albian</t>
+  </si>
+  <si>
+    <t>CAL4</t>
+  </si>
+  <si>
+    <t>FISE Edmonton rdo (Fort McMurray)</t>
+  </si>
+  <si>
+    <t>Fort Mackay / Firebag</t>
+  </si>
+  <si>
+    <t>CYFI</t>
+  </si>
+  <si>
+    <t>Fort Mackay / Horizon</t>
+  </si>
+  <si>
+    <t>CYNR</t>
+  </si>
+  <si>
+    <t>Fort Macleod</t>
+  </si>
+  <si>
+    <t>CEY3</t>
+  </si>
+  <si>
+    <t>Fort Macleod (Alcock Farm)</t>
+  </si>
+  <si>
+    <t>CFM8</t>
+  </si>
+  <si>
+    <t>Fort McMurray</t>
+  </si>
+  <si>
+    <t>CYMM</t>
+  </si>
+  <si>
+    <t>0545-1315Z‡</t>
+  </si>
+  <si>
+    <t>1315-0545Z‡</t>
+  </si>
+  <si>
+    <t>McMurray</t>
+  </si>
+  <si>
+    <t>Fort McMurray (Legend)</t>
+  </si>
+  <si>
+    <t>CLG7</t>
+  </si>
+  <si>
+    <t>Fort McMurray (North Liege)</t>
+  </si>
+  <si>
+    <t>CNL2</t>
+  </si>
+  <si>
+    <t>Fort McMurray (South Liege)</t>
+  </si>
+  <si>
+    <t>CLS3</t>
+  </si>
+  <si>
+    <t>Fort Nelson</t>
+  </si>
+  <si>
+    <t>CYYE</t>
+  </si>
+  <si>
+    <t>132.870, 134.850</t>
+  </si>
+  <si>
+    <t>Fort Nelson / Gordon Field</t>
+  </si>
+  <si>
+    <t>CBL3</t>
+  </si>
+  <si>
+    <t>Fort St. James (Perison)</t>
+  </si>
+  <si>
+    <t>CYJM</t>
   </si>
 </sst>
 </file>
@@ -8013,7 +8118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G2067"/>
+  <dimension ref="A1:G2115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -49645,14 +49750,1025 @@
         <v>123.2</v>
       </c>
     </row>
-    <row r="2065" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G2065" s="3"/>
-    </row>
-    <row r="2066" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G2066" s="3"/>
-    </row>
-    <row r="2067" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G2067" s="3"/>
+    <row r="2065" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2065" t="s">
+        <v>2528</v>
+      </c>
+      <c r="B2065" t="s">
+        <v>2529</v>
+      </c>
+      <c r="C2065" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2065" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2065" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2065" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2066" t="s">
+        <v>2528</v>
+      </c>
+      <c r="B2066" t="s">
+        <v>2529</v>
+      </c>
+      <c r="C2066" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2066" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2066" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2066" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2067" t="s">
+        <v>2528</v>
+      </c>
+      <c r="B2067" t="s">
+        <v>2529</v>
+      </c>
+      <c r="C2067" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2067" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2067" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2067" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2068" t="s">
+        <v>2528</v>
+      </c>
+      <c r="B2068" t="s">
+        <v>2529</v>
+      </c>
+      <c r="C2068" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2068" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2068" s="3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2069" t="s">
+        <v>2530</v>
+      </c>
+      <c r="B2069" t="s">
+        <v>2531</v>
+      </c>
+      <c r="C2069" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2069" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2069" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2069" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2070" t="s">
+        <v>2532</v>
+      </c>
+      <c r="B2070" t="s">
+        <v>2533</v>
+      </c>
+      <c r="C2070" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2070" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2070" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2070" s="3">
+        <v>122.72499999999999</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2071" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B2071" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C2071" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2071" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2071" t="s">
+        <v>2536</v>
+      </c>
+      <c r="G2071" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2072" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B2072" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C2072" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2072" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2072" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2072" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2073" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B2073" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C2073" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2073" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2073" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2073" s="3">
+        <v>134.02500000000001</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2074" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B2074" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C2074" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2074" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2074" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2074" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2075" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B2075" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C2075" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2075" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2075" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2075" s="3">
+        <v>134.02500000000001</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2076" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B2076" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C2076" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2076" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2076" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2076" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2076" s="3">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2077" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B2077" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C2077" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2077" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2077" s="3">
+        <v>122.97499999999999</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2078" t="s">
+        <v>2537</v>
+      </c>
+      <c r="B2078" t="s">
+        <v>2538</v>
+      </c>
+      <c r="C2078" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2078" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2078" t="s">
+        <v>2536</v>
+      </c>
+      <c r="G2078" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2079" t="s">
+        <v>2537</v>
+      </c>
+      <c r="B2079" t="s">
+        <v>2538</v>
+      </c>
+      <c r="C2079" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2079" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2079" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2079" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2080" t="s">
+        <v>2537</v>
+      </c>
+      <c r="B2080" t="s">
+        <v>2538</v>
+      </c>
+      <c r="C2080" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2080" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2080" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2080" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2081" t="s">
+        <v>2537</v>
+      </c>
+      <c r="B2081" t="s">
+        <v>2538</v>
+      </c>
+      <c r="C2081" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2081" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2081" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2081" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2082" t="s">
+        <v>2537</v>
+      </c>
+      <c r="B2082" t="s">
+        <v>2538</v>
+      </c>
+      <c r="C2082" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2082" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2082" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2082" s="3">
+        <v>134.02500000000001</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2083" t="s">
+        <v>2537</v>
+      </c>
+      <c r="B2083" t="s">
+        <v>2538</v>
+      </c>
+      <c r="C2083" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2083" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2083" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2083" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2083" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2084" t="s">
+        <v>2537</v>
+      </c>
+      <c r="B2084" t="s">
+        <v>2538</v>
+      </c>
+      <c r="C2084" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2084" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2084" s="3">
+        <v>129.65</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2085" t="s">
+        <v>2539</v>
+      </c>
+      <c r="B2085" t="s">
+        <v>2540</v>
+      </c>
+      <c r="C2085" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2085" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2085" t="s">
+        <v>2536</v>
+      </c>
+      <c r="G2085" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2086" t="s">
+        <v>2539</v>
+      </c>
+      <c r="B2086" t="s">
+        <v>2540</v>
+      </c>
+      <c r="C2086" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2086" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2086" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2086" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2087" t="s">
+        <v>2539</v>
+      </c>
+      <c r="B2087" t="s">
+        <v>2540</v>
+      </c>
+      <c r="C2087" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2087" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2087" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2087" s="3">
+        <v>134.02500000000001</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2088" t="s">
+        <v>2539</v>
+      </c>
+      <c r="B2088" t="s">
+        <v>2540</v>
+      </c>
+      <c r="C2088" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2088" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2088" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2088" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2089" t="s">
+        <v>2539</v>
+      </c>
+      <c r="B2089" t="s">
+        <v>2540</v>
+      </c>
+      <c r="C2089" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2089" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2089" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2089" s="3">
+        <v>134.02500000000001</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2090" t="s">
+        <v>2539</v>
+      </c>
+      <c r="B2090" t="s">
+        <v>2540</v>
+      </c>
+      <c r="C2090" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2090" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2090" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2090" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2090" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2091" t="s">
+        <v>2539</v>
+      </c>
+      <c r="B2091" t="s">
+        <v>2540</v>
+      </c>
+      <c r="C2091" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2091" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2091" s="3">
+        <v>122.075</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2092" t="s">
+        <v>2541</v>
+      </c>
+      <c r="B2092" t="s">
+        <v>2542</v>
+      </c>
+      <c r="C2092" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2092" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2092" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2092" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2093" t="s">
+        <v>2543</v>
+      </c>
+      <c r="B2093" t="s">
+        <v>2544</v>
+      </c>
+      <c r="C2093" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2093" t="s">
+        <v>1549</v>
+      </c>
+      <c r="G2093" s="4" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2094" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B2094" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C2094" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2094" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2094" t="s">
+        <v>2433</v>
+      </c>
+      <c r="F2094" t="s">
+        <v>2547</v>
+      </c>
+      <c r="G2094" s="3">
+        <v>118.1</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2095" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B2095" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C2095" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2095" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2095" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2095" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2096" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B2096" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C2096" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2096" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2096" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2096" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2097" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B2097" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C2097" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2097" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2097" t="s">
+        <v>2548</v>
+      </c>
+      <c r="G2097" s="3">
+        <v>128.5</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2098" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B2098" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C2098" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2098" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2098" t="s">
+        <v>2549</v>
+      </c>
+      <c r="F2098" t="s">
+        <v>2548</v>
+      </c>
+      <c r="G2098" s="3">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2099" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B2099" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C2099" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2099" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2099" t="s">
+        <v>2548</v>
+      </c>
+      <c r="G2099" s="3">
+        <v>118.1</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2100" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B2100" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C2100" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2100" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2100" t="s">
+        <v>2435</v>
+      </c>
+      <c r="F2100" t="s">
+        <v>2547</v>
+      </c>
+      <c r="G2100" s="3">
+        <v>118.1</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2101" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B2101" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C2101" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2101" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2101" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2101" s="3">
+        <v>135.69999999999999</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2102" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B2102" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C2102" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2102" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2102" t="s">
+        <v>2547</v>
+      </c>
+      <c r="G2102" s="3">
+        <v>128.5</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2103" t="s">
+        <v>2550</v>
+      </c>
+      <c r="B2103" t="s">
+        <v>2551</v>
+      </c>
+      <c r="C2103" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2103" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2103" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2103" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2104" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B2104" t="s">
+        <v>2553</v>
+      </c>
+      <c r="C2104" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2104" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2104" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2104" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2105" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B2105" t="s">
+        <v>2555</v>
+      </c>
+      <c r="C2105" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2105" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2105" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2105" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2106" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B2106" t="s">
+        <v>2557</v>
+      </c>
+      <c r="C2106" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2106" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2106" s="3">
+        <v>122.5</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2107" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B2107" t="s">
+        <v>2557</v>
+      </c>
+      <c r="C2107" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2107" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2107" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2107" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2108" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B2108" t="s">
+        <v>2557</v>
+      </c>
+      <c r="C2108" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2108" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2108" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2108" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2109" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B2109" t="s">
+        <v>2557</v>
+      </c>
+      <c r="C2109" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2109" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2109" t="s">
+        <v>191</v>
+      </c>
+      <c r="G2109" s="3">
+        <v>125.65</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2110" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B2110" t="s">
+        <v>2557</v>
+      </c>
+      <c r="C2110" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2110" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2110" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2110" s="3">
+        <v>122.5</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2111" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B2111" t="s">
+        <v>2557</v>
+      </c>
+      <c r="C2111" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2111" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2111" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2111" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2112" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B2112" t="s">
+        <v>2560</v>
+      </c>
+      <c r="C2112" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2112" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2112" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2112" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2113" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B2113" t="s">
+        <v>2560</v>
+      </c>
+      <c r="C2113" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2113" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2113" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2113" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2114" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B2114" t="s">
+        <v>2560</v>
+      </c>
+      <c r="C2114" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2114" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2114" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2114" s="3">
+        <v>122.5</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2115" t="s">
+        <v>2561</v>
+      </c>
+      <c r="B2115" t="s">
+        <v>2562</v>
+      </c>
+      <c r="C2115" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2115" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2115" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2115" s="3">
+        <v>123.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A46984-E591-4FDE-BC48-268283B57E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEE75A5-B820-435F-8BD2-A238A1BC7EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10864" uniqueCount="2563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11103" uniqueCount="2615">
   <si>
     <t>AB</t>
   </si>
@@ -7728,6 +7728,162 @@
   </si>
   <si>
     <t>CYJM</t>
+  </si>
+  <si>
+    <t>Fort St. John</t>
+  </si>
+  <si>
+    <t>CYXJ</t>
+  </si>
+  <si>
+    <t>132.600, 285.400</t>
+  </si>
+  <si>
+    <t>Fort Ware</t>
+  </si>
+  <si>
+    <t>CAJ9</t>
+  </si>
+  <si>
+    <t>Fort Creek</t>
+  </si>
+  <si>
+    <t>CED4</t>
+  </si>
+  <si>
+    <t>Fox Lake</t>
+  </si>
+  <si>
+    <t>CEC3</t>
+  </si>
+  <si>
+    <t>Fraser Lake</t>
+  </si>
+  <si>
+    <t>CBZ9</t>
+  </si>
+  <si>
+    <t>Garden River</t>
+  </si>
+  <si>
+    <t>CFU4</t>
+  </si>
+  <si>
+    <t>Glenwood</t>
+  </si>
+  <si>
+    <t>CGW2</t>
+  </si>
+  <si>
+    <t>Gordon Lake</t>
+  </si>
+  <si>
+    <t>CFW2</t>
+  </si>
+  <si>
+    <t>Grand Forks</t>
+  </si>
+  <si>
+    <t>CZGF</t>
+  </si>
+  <si>
+    <t>Grande</t>
+  </si>
+  <si>
+    <t>CFA5</t>
+  </si>
+  <si>
+    <t>Grande Prairie</t>
+  </si>
+  <si>
+    <t>CYQU</t>
+  </si>
+  <si>
+    <t>Green Lake</t>
+  </si>
+  <si>
+    <t>CBG2</t>
+  </si>
+  <si>
+    <t>Grimshaw</t>
+  </si>
+  <si>
+    <t>CFD5</t>
+  </si>
+  <si>
+    <t>Halkirk / Paintearth (Fetaz)</t>
+  </si>
+  <si>
+    <t>CPE8</t>
+  </si>
+  <si>
+    <t>Hanna</t>
+  </si>
+  <si>
+    <t>CEL4</t>
+  </si>
+  <si>
+    <t>Hardisty</t>
+  </si>
+  <si>
+    <t>CEA5</t>
+  </si>
+  <si>
+    <t>Helmet</t>
+  </si>
+  <si>
+    <t>CBH2</t>
+  </si>
+  <si>
+    <t>Hespero</t>
+  </si>
+  <si>
+    <t>CFB3</t>
+  </si>
+  <si>
+    <t>High Level</t>
+  </si>
+  <si>
+    <t>CYOJ</t>
+  </si>
+  <si>
+    <t>1500-0230Z‡</t>
+  </si>
+  <si>
+    <t>0230-1500Z‡</t>
+  </si>
+  <si>
+    <t>123.700, 135.100</t>
+  </si>
+  <si>
+    <t>High Prairie</t>
+  </si>
+  <si>
+    <t>CZHP</t>
+  </si>
+  <si>
+    <t>High River / Foothills Regional Airport</t>
+  </si>
+  <si>
+    <t>CEN4</t>
+  </si>
+  <si>
+    <t>Foorhills tfc</t>
+  </si>
+  <si>
+    <t>Hillspring (Beck Farm)</t>
+  </si>
+  <si>
+    <t>CHS3</t>
+  </si>
+  <si>
+    <t>Hinton / Entrance</t>
+  </si>
+  <si>
+    <t>CEE4</t>
+  </si>
+  <si>
+    <t>FISE Edmonton (Jasper-Hinton)</t>
   </si>
 </sst>
 </file>
@@ -8118,7 +8274,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G2115"/>
+  <dimension ref="A1:G2163"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -50770,6 +50926,957 @@
         <v>123.2</v>
       </c>
     </row>
+    <row r="2116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2116" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B2116" t="s">
+        <v>2564</v>
+      </c>
+      <c r="C2116" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2116" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2116" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2117" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B2117" t="s">
+        <v>2564</v>
+      </c>
+      <c r="C2117" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2117" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2117" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2117" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2118" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B2118" t="s">
+        <v>2564</v>
+      </c>
+      <c r="C2118" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2118" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2118" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2118" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2119" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B2119" t="s">
+        <v>2564</v>
+      </c>
+      <c r="C2119" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2119" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2119" t="s">
+        <v>191</v>
+      </c>
+      <c r="G2119" s="3">
+        <v>128.5</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2120" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B2120" t="s">
+        <v>2564</v>
+      </c>
+      <c r="C2120" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2120" t="s">
+        <v>146</v>
+      </c>
+      <c r="G2120" s="3">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2121" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B2121" t="s">
+        <v>2564</v>
+      </c>
+      <c r="C2121" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2121" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2121" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2121" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2122" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B2122" t="s">
+        <v>2564</v>
+      </c>
+      <c r="C2122" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2122" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2122" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2122" t="s">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2123" t="s">
+        <v>2566</v>
+      </c>
+      <c r="B2123" t="s">
+        <v>2567</v>
+      </c>
+      <c r="C2123" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2123" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2123" t="s">
+        <v>391</v>
+      </c>
+      <c r="G2123" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2124" t="s">
+        <v>2566</v>
+      </c>
+      <c r="B2124" t="s">
+        <v>2567</v>
+      </c>
+      <c r="C2124" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2124" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2124" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2125" t="s">
+        <v>2566</v>
+      </c>
+      <c r="B2125" t="s">
+        <v>2567</v>
+      </c>
+      <c r="C2125" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2125" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2125" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2125" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2126" t="s">
+        <v>2568</v>
+      </c>
+      <c r="B2126" t="s">
+        <v>2569</v>
+      </c>
+      <c r="C2126" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2126" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2126" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2126" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2127" t="s">
+        <v>2570</v>
+      </c>
+      <c r="B2127" t="s">
+        <v>2571</v>
+      </c>
+      <c r="C2127" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2127" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2127" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2127" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2128" t="s">
+        <v>2572</v>
+      </c>
+      <c r="B2128" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C2128" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2128" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2128" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2128" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2129" t="s">
+        <v>2574</v>
+      </c>
+      <c r="B2129" t="s">
+        <v>2575</v>
+      </c>
+      <c r="C2129" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2129" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2129" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2129" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2130" t="s">
+        <v>2576</v>
+      </c>
+      <c r="B2130" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C2130" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2130" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2130" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2130" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2131" t="s">
+        <v>2578</v>
+      </c>
+      <c r="B2131" t="s">
+        <v>2579</v>
+      </c>
+      <c r="C2131" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2131" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2131" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2131" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2132" t="s">
+        <v>2580</v>
+      </c>
+      <c r="B2132" t="s">
+        <v>2581</v>
+      </c>
+      <c r="C2132" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2132" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2132" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G2132" s="3">
+        <v>125.85</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2133" t="s">
+        <v>2580</v>
+      </c>
+      <c r="B2133" t="s">
+        <v>2581</v>
+      </c>
+      <c r="C2133" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2133" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2133" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2133" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2134" t="s">
+        <v>2580</v>
+      </c>
+      <c r="B2134" t="s">
+        <v>2581</v>
+      </c>
+      <c r="C2134" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2134" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2134" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2134" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2135" t="s">
+        <v>2580</v>
+      </c>
+      <c r="B2135" t="s">
+        <v>2581</v>
+      </c>
+      <c r="C2135" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2135" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2135" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2136" t="s">
+        <v>2582</v>
+      </c>
+      <c r="B2136" t="s">
+        <v>2583</v>
+      </c>
+      <c r="C2136" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2136" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2136" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2136" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2137" t="s">
+        <v>2584</v>
+      </c>
+      <c r="B2137" t="s">
+        <v>2585</v>
+      </c>
+      <c r="C2137" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2137" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2137" s="3">
+        <v>118.1</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2138" t="s">
+        <v>2584</v>
+      </c>
+      <c r="B2138" t="s">
+        <v>2585</v>
+      </c>
+      <c r="C2138" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2138" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2138" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2138" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2139" t="s">
+        <v>2584</v>
+      </c>
+      <c r="B2139" t="s">
+        <v>2585</v>
+      </c>
+      <c r="C2139" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2139" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2139" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2139" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2140" t="s">
+        <v>2584</v>
+      </c>
+      <c r="B2140" t="s">
+        <v>2585</v>
+      </c>
+      <c r="C2140" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2140" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2140" s="3">
+        <v>128.6</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2141" t="s">
+        <v>2584</v>
+      </c>
+      <c r="B2141" t="s">
+        <v>2585</v>
+      </c>
+      <c r="C2141" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2141" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2141" t="s">
+        <v>191</v>
+      </c>
+      <c r="G2141" s="3">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2142" t="s">
+        <v>2584</v>
+      </c>
+      <c r="B2142" t="s">
+        <v>2585</v>
+      </c>
+      <c r="C2142" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2142" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2142" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2142" s="3">
+        <v>118.1</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2143" t="s">
+        <v>2584</v>
+      </c>
+      <c r="B2143" t="s">
+        <v>2585</v>
+      </c>
+      <c r="C2143" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2143" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2143" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2143" s="3">
+        <v>134.5</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2144" t="s">
+        <v>2586</v>
+      </c>
+      <c r="B2144" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C2144" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2144" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2144" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2144" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2145" t="s">
+        <v>2588</v>
+      </c>
+      <c r="B2145" t="s">
+        <v>2589</v>
+      </c>
+      <c r="C2145" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2145" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2145" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2145" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2146" t="s">
+        <v>2590</v>
+      </c>
+      <c r="B2146" t="s">
+        <v>2591</v>
+      </c>
+      <c r="C2146" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2146" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2146" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2146" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2147" t="s">
+        <v>2592</v>
+      </c>
+      <c r="B2147" t="s">
+        <v>2593</v>
+      </c>
+      <c r="C2147" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2147" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2147" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2147" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2148" t="s">
+        <v>2594</v>
+      </c>
+      <c r="B2148" t="s">
+        <v>2595</v>
+      </c>
+      <c r="C2148" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2148" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2148" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2148" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2149" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B2149" t="s">
+        <v>2597</v>
+      </c>
+      <c r="C2149" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2149" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2149" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2149" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2149" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2150" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B2150" t="s">
+        <v>2597</v>
+      </c>
+      <c r="C2150" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2150" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2150" s="3">
+        <v>122.175</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2151" t="s">
+        <v>2598</v>
+      </c>
+      <c r="B2151" t="s">
+        <v>2599</v>
+      </c>
+      <c r="C2151" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2151" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2151" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2151" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2152" t="s">
+        <v>2600</v>
+      </c>
+      <c r="B2152" t="s">
+        <v>2601</v>
+      </c>
+      <c r="C2152" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2152" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2152" t="s">
+        <v>2602</v>
+      </c>
+      <c r="G2152" s="3">
+        <v>123.25</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2153" t="s">
+        <v>2600</v>
+      </c>
+      <c r="B2153" t="s">
+        <v>2601</v>
+      </c>
+      <c r="C2153" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2153" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2153" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2153" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2154" t="s">
+        <v>2600</v>
+      </c>
+      <c r="B2154" t="s">
+        <v>2601</v>
+      </c>
+      <c r="C2154" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2154" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2154" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2154" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2155" t="s">
+        <v>2600</v>
+      </c>
+      <c r="B2155" t="s">
+        <v>2601</v>
+      </c>
+      <c r="C2155" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2155" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2155" t="s">
+        <v>402</v>
+      </c>
+      <c r="F2155" t="s">
+        <v>2603</v>
+      </c>
+      <c r="G2155" s="3">
+        <v>135.1</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2156" t="s">
+        <v>2600</v>
+      </c>
+      <c r="B2156" t="s">
+        <v>2601</v>
+      </c>
+      <c r="C2156" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2156" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2156" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2156" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2156" s="3">
+        <v>123.25</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2157" t="s">
+        <v>2600</v>
+      </c>
+      <c r="B2157" t="s">
+        <v>2601</v>
+      </c>
+      <c r="C2157" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2157" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2157" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2157" t="s">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2158" t="s">
+        <v>2600</v>
+      </c>
+      <c r="B2158" t="s">
+        <v>2601</v>
+      </c>
+      <c r="C2158" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2158" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2158" t="s">
+        <v>2603</v>
+      </c>
+      <c r="G2158" s="3">
+        <v>128.22499999999999</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2159" t="s">
+        <v>2605</v>
+      </c>
+      <c r="B2159" t="s">
+        <v>2606</v>
+      </c>
+      <c r="C2159" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2159" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2159" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2159" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2160" t="s">
+        <v>2607</v>
+      </c>
+      <c r="B2160" t="s">
+        <v>2608</v>
+      </c>
+      <c r="C2160" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2160" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2160" t="s">
+        <v>2609</v>
+      </c>
+      <c r="G2160" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2161" t="s">
+        <v>2610</v>
+      </c>
+      <c r="B2161" t="s">
+        <v>2611</v>
+      </c>
+      <c r="C2161" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2161" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2161" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2161" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2162" t="s">
+        <v>2612</v>
+      </c>
+      <c r="B2162" t="s">
+        <v>2613</v>
+      </c>
+      <c r="C2162" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2162" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2162" t="s">
+        <v>2614</v>
+      </c>
+      <c r="G2162" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2163" t="s">
+        <v>2612</v>
+      </c>
+      <c r="B2163" t="s">
+        <v>2613</v>
+      </c>
+      <c r="C2163" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2163" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2163" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2163" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2163" s="3">
+        <v>123.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEE75A5-B820-435F-8BD2-A238A1BC7EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EF4F26-DDF0-4A6F-BB7F-3939404CC252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11103" uniqueCount="2615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11280" uniqueCount="2653">
   <si>
     <t>AB</t>
   </si>
@@ -7884,6 +7884,120 @@
   </si>
   <si>
     <t>FISE Edmonton (Jasper-Hinton)</t>
+  </si>
+  <si>
+    <t>Hinton / Jasper-Hinton</t>
+  </si>
+  <si>
+    <t>CEC4</t>
+  </si>
+  <si>
+    <t>Hope</t>
+  </si>
+  <si>
+    <t>CYHE</t>
+  </si>
+  <si>
+    <t>Houston</t>
+  </si>
+  <si>
+    <t>CAM5</t>
+  </si>
+  <si>
+    <t>Hudson's Hope</t>
+  </si>
+  <si>
+    <t>CYNH</t>
+  </si>
+  <si>
+    <t>Huggett / Goodwood Field</t>
+  </si>
+  <si>
+    <t>CGF5</t>
+  </si>
+  <si>
+    <t>Indus / Winters Aire Park</t>
+  </si>
+  <si>
+    <t>CFY4</t>
+  </si>
+  <si>
+    <t>Ingenika</t>
+  </si>
+  <si>
+    <t>CAP6</t>
+  </si>
+  <si>
+    <t>Innisfail / Big Bend</t>
+  </si>
+  <si>
+    <t>CEM4</t>
+  </si>
+  <si>
+    <t>Invermere</t>
+  </si>
+  <si>
+    <t>CAA8</t>
+  </si>
+  <si>
+    <t>Jasper</t>
+  </si>
+  <si>
+    <t>CYJA</t>
+  </si>
+  <si>
+    <t>Jean Lake</t>
+  </si>
+  <si>
+    <t>CFF3</t>
+  </si>
+  <si>
+    <t>John D'or Prairie</t>
+  </si>
+  <si>
+    <t>CFG5</t>
+  </si>
+  <si>
+    <t>Johnson Lake</t>
+  </si>
+  <si>
+    <t>CFL9</t>
+  </si>
+  <si>
+    <t>Kamloops</t>
+  </si>
+  <si>
+    <t>CYKA</t>
+  </si>
+  <si>
+    <t>132.350, 133.500, 134.400, 236.000</t>
+  </si>
+  <si>
+    <t>Kaslo</t>
+  </si>
+  <si>
+    <t>CBR2</t>
+  </si>
+  <si>
+    <t>Kelowna</t>
+  </si>
+  <si>
+    <t>CYLW</t>
+  </si>
+  <si>
+    <t>RAAS Penticton rdo</t>
+  </si>
+  <si>
+    <t>0630-1330Z‡</t>
+  </si>
+  <si>
+    <t>1330-0630Z‡</t>
+  </si>
+  <si>
+    <t>119.600, 292.200</t>
+  </si>
+  <si>
+    <t>Penticton rdo</t>
   </si>
 </sst>
 </file>
@@ -8274,7 +8388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G2163"/>
+  <dimension ref="A1:G2198"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -51877,6 +51991,706 @@
         <v>123.35</v>
       </c>
     </row>
+    <row r="2164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2164" t="s">
+        <v>2615</v>
+      </c>
+      <c r="B2164" t="s">
+        <v>2616</v>
+      </c>
+      <c r="C2164" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2164" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2164" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2164" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2165" t="s">
+        <v>2615</v>
+      </c>
+      <c r="B2165" t="s">
+        <v>2616</v>
+      </c>
+      <c r="C2165" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2165" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2165" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2165" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2166" t="s">
+        <v>2615</v>
+      </c>
+      <c r="B2166" t="s">
+        <v>2616</v>
+      </c>
+      <c r="C2166" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2166" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2166" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2166" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2166" s="3">
+        <v>123.35</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2167" t="s">
+        <v>2617</v>
+      </c>
+      <c r="B2167" t="s">
+        <v>2618</v>
+      </c>
+      <c r="C2167" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2167" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2167" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G2167" s="3">
+        <v>125.85</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2168" t="s">
+        <v>2617</v>
+      </c>
+      <c r="B2168" t="s">
+        <v>2618</v>
+      </c>
+      <c r="C2168" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2168" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2168" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2168" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2169" t="s">
+        <v>2617</v>
+      </c>
+      <c r="B2169" t="s">
+        <v>2618</v>
+      </c>
+      <c r="C2169" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2169" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2169" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2169" s="3">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2170" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B2170" t="s">
+        <v>2620</v>
+      </c>
+      <c r="C2170" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2170" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2170" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2170" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2171" t="s">
+        <v>2621</v>
+      </c>
+      <c r="B2171" t="s">
+        <v>2622</v>
+      </c>
+      <c r="C2171" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2171" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2171" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2171" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2172" t="s">
+        <v>2623</v>
+      </c>
+      <c r="B2172" t="s">
+        <v>2624</v>
+      </c>
+      <c r="C2172" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2172" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2172" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2172" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2173" t="s">
+        <v>2625</v>
+      </c>
+      <c r="B2173" t="s">
+        <v>2626</v>
+      </c>
+      <c r="C2173" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2173" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2173" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2173" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2174" t="s">
+        <v>2627</v>
+      </c>
+      <c r="B2174" t="s">
+        <v>2628</v>
+      </c>
+      <c r="C2174" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2174" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2174" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2174" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2175" t="s">
+        <v>2629</v>
+      </c>
+      <c r="B2175" t="s">
+        <v>2630</v>
+      </c>
+      <c r="C2175" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2175" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2175" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2175" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2176" t="s">
+        <v>2631</v>
+      </c>
+      <c r="B2176" t="s">
+        <v>2632</v>
+      </c>
+      <c r="C2176" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2176" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2176" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G2176" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2177" t="s">
+        <v>2631</v>
+      </c>
+      <c r="B2177" t="s">
+        <v>2632</v>
+      </c>
+      <c r="C2177" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2177" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2177" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2177" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2178" t="s">
+        <v>2631</v>
+      </c>
+      <c r="B2178" t="s">
+        <v>2632</v>
+      </c>
+      <c r="C2178" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2178" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2178" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2178" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2179" t="s">
+        <v>2633</v>
+      </c>
+      <c r="B2179" t="s">
+        <v>2634</v>
+      </c>
+      <c r="C2179" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2179" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2179" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2179" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2180" t="s">
+        <v>2635</v>
+      </c>
+      <c r="B2180" t="s">
+        <v>2636</v>
+      </c>
+      <c r="C2180" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2180" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2180" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2180" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2181" t="s">
+        <v>2637</v>
+      </c>
+      <c r="B2181" t="s">
+        <v>2638</v>
+      </c>
+      <c r="C2181" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2181" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2181" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2181" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2182" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B2182" t="s">
+        <v>2640</v>
+      </c>
+      <c r="C2182" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2182" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2182" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2182" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2183" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B2183" t="s">
+        <v>2640</v>
+      </c>
+      <c r="C2183" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2183" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2183" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2183" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2184" t="s">
+        <v>2641</v>
+      </c>
+      <c r="B2184" t="s">
+        <v>2642</v>
+      </c>
+      <c r="C2184" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2184" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2184" s="3">
+        <v>125.7</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2185" t="s">
+        <v>2641</v>
+      </c>
+      <c r="B2185" t="s">
+        <v>2642</v>
+      </c>
+      <c r="C2185" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2185" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2185" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G2185" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2186" t="s">
+        <v>2641</v>
+      </c>
+      <c r="B2186" t="s">
+        <v>2642</v>
+      </c>
+      <c r="C2186" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2186" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2186" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2186" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2187" t="s">
+        <v>2641</v>
+      </c>
+      <c r="B2187" t="s">
+        <v>2642</v>
+      </c>
+      <c r="C2187" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2187" t="s">
+        <v>146</v>
+      </c>
+      <c r="G2187" s="3">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2188" t="s">
+        <v>2641</v>
+      </c>
+      <c r="B2188" t="s">
+        <v>2642</v>
+      </c>
+      <c r="C2188" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2188" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2188" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2188" s="3">
+        <v>125.7</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2189" t="s">
+        <v>2641</v>
+      </c>
+      <c r="B2189" t="s">
+        <v>2642</v>
+      </c>
+      <c r="C2189" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2189" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2189" t="s">
+        <v>2305</v>
+      </c>
+      <c r="G2189" t="s">
+        <v>2643</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2190" t="s">
+        <v>2644</v>
+      </c>
+      <c r="B2190" t="s">
+        <v>2645</v>
+      </c>
+      <c r="C2190" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2190" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2190" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2190" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2191" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B2191" t="s">
+        <v>2647</v>
+      </c>
+      <c r="C2191" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2191" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2191" t="s">
+        <v>2648</v>
+      </c>
+      <c r="F2191" t="s">
+        <v>2649</v>
+      </c>
+      <c r="G2191" s="3">
+        <v>119.6</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2192" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B2192" t="s">
+        <v>2647</v>
+      </c>
+      <c r="C2192" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2192" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2192" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G2192" s="3">
+        <v>122.5</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2193" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B2193" t="s">
+        <v>2647</v>
+      </c>
+      <c r="C2193" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2193" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2193" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2193" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2194" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B2194" t="s">
+        <v>2647</v>
+      </c>
+      <c r="C2194" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2194" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2194" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G2194" s="3">
+        <v>127.5</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2195" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B2195" t="s">
+        <v>2647</v>
+      </c>
+      <c r="C2195" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2195" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2195" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G2195" s="3">
+        <v>121.7</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2196" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B2196" t="s">
+        <v>2647</v>
+      </c>
+      <c r="C2196" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2196" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2196" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G2196" t="s">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2197" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B2197" t="s">
+        <v>2647</v>
+      </c>
+      <c r="C2197" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2197" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2197" t="s">
+        <v>2652</v>
+      </c>
+      <c r="F2197" t="s">
+        <v>2649</v>
+      </c>
+      <c r="G2197" s="3">
+        <v>119.6</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2198" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B2198" t="s">
+        <v>2647</v>
+      </c>
+      <c r="C2198" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2198" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2198" s="3">
+        <v>127.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EF4F26-DDF0-4A6F-BB7F-3939404CC252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5B5F92-4C7B-4936-B226-57B1B11776A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11280" uniqueCount="2653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11661" uniqueCount="2744">
   <si>
     <t>AB</t>
   </si>
@@ -7998,6 +7998,279 @@
   </si>
   <si>
     <t>Penticton rdo</t>
+  </si>
+  <si>
+    <t>Kemess Creek</t>
+  </si>
+  <si>
+    <t>CBQ7</t>
+  </si>
+  <si>
+    <t>Killam-Sedgewick / Flagstaff Regional</t>
+  </si>
+  <si>
+    <t>CEK6</t>
+  </si>
+  <si>
+    <t>Kirby Lake</t>
+  </si>
+  <si>
+    <t>CRL4</t>
+  </si>
+  <si>
+    <t>1307Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Edmonton Ctr (South Oil Sands)</t>
+  </si>
+  <si>
+    <t>Kitimat</t>
+  </si>
+  <si>
+    <t>CBW2</t>
+  </si>
+  <si>
+    <t>Lac La Biche</t>
+  </si>
+  <si>
+    <t>CYLB</t>
+  </si>
+  <si>
+    <t>Lacombe</t>
+  </si>
+  <si>
+    <t>CEG3</t>
+  </si>
+  <si>
+    <t>La Crete (Lake Fehr Memorial)</t>
+  </si>
+  <si>
+    <t>CFN5</t>
+  </si>
+  <si>
+    <t>Langley Regional</t>
+  </si>
+  <si>
+    <t>CYNJ</t>
+  </si>
+  <si>
+    <t>1630-0230Z (DT 1530-0330Z)</t>
+  </si>
+  <si>
+    <t>0230-1630Z (DT 0330-1530Z)</t>
+  </si>
+  <si>
+    <t>Lethbridge</t>
+  </si>
+  <si>
+    <t>CYQL</t>
+  </si>
+  <si>
+    <t>1245-0545Z‡</t>
+  </si>
+  <si>
+    <t>132.750, 265.200</t>
+  </si>
+  <si>
+    <t>0545-1245Z‡</t>
+  </si>
+  <si>
+    <t>Lethbridge (Gunnlaugson)</t>
+  </si>
+  <si>
+    <t>CGN3</t>
+  </si>
+  <si>
+    <t>Lethbridge (J3 Airfield)</t>
+  </si>
+  <si>
+    <t>CLJ3</t>
+  </si>
+  <si>
+    <t>Lethbridge (Mercer Field)</t>
+  </si>
+  <si>
+    <t>CMF3</t>
+  </si>
+  <si>
+    <t>Lethbridge (Taylor Field)</t>
+  </si>
+  <si>
+    <t>CTF6</t>
+  </si>
+  <si>
+    <t>Likely</t>
+  </si>
+  <si>
+    <t>CAX5</t>
+  </si>
+  <si>
+    <t>Lillooet</t>
+  </si>
+  <si>
+    <t>CYLI</t>
+  </si>
+  <si>
+    <t>Lillooet (Blackcomb)</t>
+  </si>
+  <si>
+    <t>CBP5</t>
+  </si>
+  <si>
+    <t>Lloydminster</t>
+  </si>
+  <si>
+    <t>CYLL</t>
+  </si>
+  <si>
+    <t>Lloyd rdo</t>
+  </si>
+  <si>
+    <t>1400-0500Z‡</t>
+  </si>
+  <si>
+    <t>1400-0500Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Long Harbour</t>
+  </si>
+  <si>
+    <t>CLH3</t>
+  </si>
+  <si>
+    <t>Loon River</t>
+  </si>
+  <si>
+    <t>CFS6</t>
+  </si>
+  <si>
+    <t>Mabel Lake</t>
+  </si>
+  <si>
+    <t>CBF9</t>
+  </si>
+  <si>
+    <t>Mackenzie</t>
+  </si>
+  <si>
+    <t>CYZY</t>
+  </si>
+  <si>
+    <t>Manning</t>
+  </si>
+  <si>
+    <t>CFX4</t>
+  </si>
+  <si>
+    <t>Margaret Lake</t>
+  </si>
+  <si>
+    <t>CFV6</t>
+  </si>
+  <si>
+    <t>Markerville / Safron Farms</t>
+  </si>
+  <si>
+    <t>CSF5</t>
+  </si>
+  <si>
+    <t>Masset</t>
+  </si>
+  <si>
+    <t>CZMT</t>
+  </si>
+  <si>
+    <t>Mayerthorpe</t>
+  </si>
+  <si>
+    <t>CEV5</t>
+  </si>
+  <si>
+    <t>McBride</t>
+  </si>
+  <si>
+    <t>CAV4</t>
+  </si>
+  <si>
+    <t>Medicine Hat</t>
+  </si>
+  <si>
+    <t>CYXH</t>
+  </si>
+  <si>
+    <t>1245-0345Z</t>
+  </si>
+  <si>
+    <t>1245-0345Z O/T tfc</t>
+  </si>
+  <si>
+    <t>0345-1245Z</t>
+  </si>
+  <si>
+    <t>Medicine Hat / Schlenker</t>
+  </si>
+  <si>
+    <t>CFZ3</t>
+  </si>
+  <si>
+    <t>Merritt</t>
+  </si>
+  <si>
+    <t>CAD5</t>
+  </si>
+  <si>
+    <t>Midway</t>
+  </si>
+  <si>
+    <t>CBM6</t>
+  </si>
+  <si>
+    <t>Milk River</t>
+  </si>
+  <si>
+    <t>CEW5</t>
+  </si>
+  <si>
+    <t>Mobil Bistcho</t>
+  </si>
+  <si>
+    <t>CFV3</t>
+  </si>
+  <si>
+    <t>Moose Lake (Lodge)</t>
+  </si>
+  <si>
+    <t>CAS2</t>
+  </si>
+  <si>
+    <t>Mule Creek</t>
+  </si>
+  <si>
+    <t>CBS4</t>
+  </si>
+  <si>
+    <t>Muskeg Tower</t>
+  </si>
+  <si>
+    <t>CFW4</t>
+  </si>
+  <si>
+    <t>Nakusp</t>
+  </si>
+  <si>
+    <t>CAQ5</t>
+  </si>
+  <si>
+    <t>Nampa / Hockey</t>
+  </si>
+  <si>
+    <t>CNP6</t>
+  </si>
+  <si>
+    <t>Namur Lake</t>
+  </si>
+  <si>
+    <t>CFB5</t>
   </si>
 </sst>
 </file>
@@ -8388,7 +8661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G2198"/>
+  <dimension ref="A1:G2273"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -52691,6 +52964,1521 @@
         <v>127.5</v>
       </c>
     </row>
+    <row r="2199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2199" t="s">
+        <v>2653</v>
+      </c>
+      <c r="B2199" t="s">
+        <v>2654</v>
+      </c>
+      <c r="C2199" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2199" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2199" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2199" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2199" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2200" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B2200" t="s">
+        <v>2656</v>
+      </c>
+      <c r="C2200" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2200" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2200" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2200" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2201" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B2201" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C2201" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2201" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2201" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2201" t="s">
+        <v>2659</v>
+      </c>
+      <c r="G2201" s="3">
+        <v>123.35</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2202" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B2202" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C2202" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2202" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2202" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G2202" s="3">
+        <v>134.44999999999999</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2203" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B2203" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C2203" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2203" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2203" s="3">
+        <v>122.175</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2204" t="s">
+        <v>2661</v>
+      </c>
+      <c r="B2204" t="s">
+        <v>2662</v>
+      </c>
+      <c r="C2204" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2204" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2204" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2204" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2205" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B2205" t="s">
+        <v>2664</v>
+      </c>
+      <c r="C2205" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2205" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2205" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2205" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2206" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B2206" t="s">
+        <v>2664</v>
+      </c>
+      <c r="C2206" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2206" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2206" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2206" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2207" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B2207" t="s">
+        <v>2664</v>
+      </c>
+      <c r="C2207" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2207" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2207" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2207" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2208" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B2208" t="s">
+        <v>2664</v>
+      </c>
+      <c r="C2208" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2208" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2208" s="3">
+        <v>122.125</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2209" t="s">
+        <v>2665</v>
+      </c>
+      <c r="B2209" t="s">
+        <v>2666</v>
+      </c>
+      <c r="C2209" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2209" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2209" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2209" s="3">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2210" t="s">
+        <v>2667</v>
+      </c>
+      <c r="B2210" t="s">
+        <v>2668</v>
+      </c>
+      <c r="C2210" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2210" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2210" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2210" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2211" t="s">
+        <v>2669</v>
+      </c>
+      <c r="B2211" t="s">
+        <v>2670</v>
+      </c>
+      <c r="C2211" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2211" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2211" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G2211" s="3">
+        <v>124.5</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2212" t="s">
+        <v>2669</v>
+      </c>
+      <c r="B2212" t="s">
+        <v>2670</v>
+      </c>
+      <c r="C2212" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2212" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2212" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G2212" s="3">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2213" t="s">
+        <v>2669</v>
+      </c>
+      <c r="B2213" t="s">
+        <v>2670</v>
+      </c>
+      <c r="C2213" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2213" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2213" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G2213" s="3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2214" t="s">
+        <v>2669</v>
+      </c>
+      <c r="B2214" t="s">
+        <v>2670</v>
+      </c>
+      <c r="C2214" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2214" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2214" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2214" t="s">
+        <v>2672</v>
+      </c>
+      <c r="G2214" s="3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2215" t="s">
+        <v>2673</v>
+      </c>
+      <c r="B2215" t="s">
+        <v>2674</v>
+      </c>
+      <c r="C2215" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2215" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2215" t="s">
+        <v>2675</v>
+      </c>
+      <c r="G2215" s="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2216" t="s">
+        <v>2673</v>
+      </c>
+      <c r="B2216" t="s">
+        <v>2674</v>
+      </c>
+      <c r="C2216" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2216" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2216" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2216" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2217" t="s">
+        <v>2673</v>
+      </c>
+      <c r="B2217" t="s">
+        <v>2674</v>
+      </c>
+      <c r="C2217" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2217" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2217" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2217" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2218" t="s">
+        <v>2673</v>
+      </c>
+      <c r="B2218" t="s">
+        <v>2674</v>
+      </c>
+      <c r="C2218" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2218" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2218" t="s">
+        <v>2675</v>
+      </c>
+      <c r="G2218" s="3">
+        <v>124.4</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2219" t="s">
+        <v>2673</v>
+      </c>
+      <c r="B2219" t="s">
+        <v>2674</v>
+      </c>
+      <c r="C2219" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2219" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2219" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2219" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2219" s="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2220" t="s">
+        <v>2673</v>
+      </c>
+      <c r="B2220" t="s">
+        <v>2674</v>
+      </c>
+      <c r="C2220" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2220" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2220" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2220" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2221" t="s">
+        <v>2673</v>
+      </c>
+      <c r="B2221" t="s">
+        <v>2674</v>
+      </c>
+      <c r="C2221" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2221" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2221" t="s">
+        <v>2677</v>
+      </c>
+      <c r="G2221" s="3">
+        <v>124.4</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2222" t="s">
+        <v>2678</v>
+      </c>
+      <c r="B2222" t="s">
+        <v>2679</v>
+      </c>
+      <c r="C2222" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2222" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2222" t="s">
+        <v>2675</v>
+      </c>
+      <c r="G2222" s="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2223" t="s">
+        <v>2678</v>
+      </c>
+      <c r="B2223" t="s">
+        <v>2679</v>
+      </c>
+      <c r="C2223" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2223" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2223" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2223" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2223" s="3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2224" t="s">
+        <v>2680</v>
+      </c>
+      <c r="B2224" t="s">
+        <v>2681</v>
+      </c>
+      <c r="C2224" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2224" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2224" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2224" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2225" t="s">
+        <v>2682</v>
+      </c>
+      <c r="B2225" t="s">
+        <v>2683</v>
+      </c>
+      <c r="C2225" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2225" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2225" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2225" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2226" t="s">
+        <v>2684</v>
+      </c>
+      <c r="B2226" t="s">
+        <v>2685</v>
+      </c>
+      <c r="C2226" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2226" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2226" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2226" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2227" t="s">
+        <v>2686</v>
+      </c>
+      <c r="B2227" t="s">
+        <v>2687</v>
+      </c>
+      <c r="C2227" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2227" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2227" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2227" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2228" t="s">
+        <v>2688</v>
+      </c>
+      <c r="B2228" t="s">
+        <v>2689</v>
+      </c>
+      <c r="C2228" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2228" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2228" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2228" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2229" t="s">
+        <v>2690</v>
+      </c>
+      <c r="B2229" t="s">
+        <v>2691</v>
+      </c>
+      <c r="C2229" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2229" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2229" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2229" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2230" t="s">
+        <v>2690</v>
+      </c>
+      <c r="B2230" t="s">
+        <v>2691</v>
+      </c>
+      <c r="C2230" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2230" t="s">
+        <v>235</v>
+      </c>
+      <c r="G2230" s="3">
+        <v>129.625</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2231" t="s">
+        <v>2692</v>
+      </c>
+      <c r="B2231" t="s">
+        <v>2693</v>
+      </c>
+      <c r="C2231" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2231" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2231" t="s">
+        <v>2694</v>
+      </c>
+      <c r="F2231" t="s">
+        <v>2695</v>
+      </c>
+      <c r="G2231" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2232" t="s">
+        <v>2692</v>
+      </c>
+      <c r="B2232" t="s">
+        <v>2693</v>
+      </c>
+      <c r="C2232" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2232" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2232" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2232" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2233" t="s">
+        <v>2692</v>
+      </c>
+      <c r="B2233" t="s">
+        <v>2693</v>
+      </c>
+      <c r="C2233" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2233" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2233" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2233" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2234" t="s">
+        <v>2692</v>
+      </c>
+      <c r="B2234" t="s">
+        <v>2693</v>
+      </c>
+      <c r="C2234" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2234" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2234" t="s">
+        <v>2694</v>
+      </c>
+      <c r="F2234" t="s">
+        <v>2696</v>
+      </c>
+      <c r="G2234" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2235" t="s">
+        <v>2692</v>
+      </c>
+      <c r="B2235" t="s">
+        <v>2693</v>
+      </c>
+      <c r="C2235" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2235" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2235" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2235" s="3">
+        <v>133.44999999999999</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2236" t="s">
+        <v>2692</v>
+      </c>
+      <c r="B2236" t="s">
+        <v>2693</v>
+      </c>
+      <c r="C2236" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2236" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2236" t="s">
+        <v>716</v>
+      </c>
+      <c r="G2236" s="3">
+        <v>128.55000000000001</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2237" t="s">
+        <v>2697</v>
+      </c>
+      <c r="B2237" t="s">
+        <v>2698</v>
+      </c>
+      <c r="C2237" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2237" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2237" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2237" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2238" t="s">
+        <v>2699</v>
+      </c>
+      <c r="B2238" t="s">
+        <v>2700</v>
+      </c>
+      <c r="C2238" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2238" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2238" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2238" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2239" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B2239" t="s">
+        <v>2702</v>
+      </c>
+      <c r="C2239" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2239" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2239" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2239" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2240" t="s">
+        <v>2703</v>
+      </c>
+      <c r="B2240" t="s">
+        <v>2704</v>
+      </c>
+      <c r="C2240" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2240" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2240" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G2240" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2241" t="s">
+        <v>2703</v>
+      </c>
+      <c r="B2241" t="s">
+        <v>2704</v>
+      </c>
+      <c r="C2241" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2241" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2241" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2241" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2242" t="s">
+        <v>2703</v>
+      </c>
+      <c r="B2242" t="s">
+        <v>2704</v>
+      </c>
+      <c r="C2242" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2242" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2242" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2242" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2243" t="s">
+        <v>2703</v>
+      </c>
+      <c r="B2243" t="s">
+        <v>2704</v>
+      </c>
+      <c r="C2243" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2243" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2243" s="3">
+        <v>127.7</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2244" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B2244" t="s">
+        <v>2706</v>
+      </c>
+      <c r="C2244" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2244" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2244" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2244" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2245" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B2245" t="s">
+        <v>2706</v>
+      </c>
+      <c r="C2245" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2245" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2245" s="3">
+        <v>122.55</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2246" t="s">
+        <v>2707</v>
+      </c>
+      <c r="B2246" t="s">
+        <v>2708</v>
+      </c>
+      <c r="C2246" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2246" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2246" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2246" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2247" t="s">
+        <v>2709</v>
+      </c>
+      <c r="B2247" t="s">
+        <v>2710</v>
+      </c>
+      <c r="C2247" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2247" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2247" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2247" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2248" t="s">
+        <v>2711</v>
+      </c>
+      <c r="B2248" t="s">
+        <v>2712</v>
+      </c>
+      <c r="C2248" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2248" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2248" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2248" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2248" s="3">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2249" t="s">
+        <v>2713</v>
+      </c>
+      <c r="B2249" t="s">
+        <v>2714</v>
+      </c>
+      <c r="C2249" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2249" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2249" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2249" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2250" t="s">
+        <v>2715</v>
+      </c>
+      <c r="B2250" t="s">
+        <v>2716</v>
+      </c>
+      <c r="C2250" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2250" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2250" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G2250" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2251" t="s">
+        <v>2715</v>
+      </c>
+      <c r="B2251" t="s">
+        <v>2716</v>
+      </c>
+      <c r="C2251" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2251" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2251" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2251" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2252" t="s">
+        <v>2715</v>
+      </c>
+      <c r="B2252" t="s">
+        <v>2716</v>
+      </c>
+      <c r="C2252" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2252" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2252" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2252" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2253" t="s">
+        <v>2715</v>
+      </c>
+      <c r="B2253" t="s">
+        <v>2716</v>
+      </c>
+      <c r="C2253" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2253" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2253" s="3">
+        <v>123.175</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2254" t="s">
+        <v>2717</v>
+      </c>
+      <c r="B2254" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C2254" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2254" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2254" t="s">
+        <v>2719</v>
+      </c>
+      <c r="G2254" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2255" t="s">
+        <v>2717</v>
+      </c>
+      <c r="B2255" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C2255" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2255" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2255" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2255" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2256" t="s">
+        <v>2717</v>
+      </c>
+      <c r="B2256" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C2256" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2256" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2256" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2256" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2257" t="s">
+        <v>2717</v>
+      </c>
+      <c r="B2257" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C2257" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2257" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2257" t="s">
+        <v>2719</v>
+      </c>
+      <c r="G2257" s="3">
+        <v>124.875</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2258" t="s">
+        <v>2717</v>
+      </c>
+      <c r="B2258" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C2258" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2258" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2258" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2258" t="s">
+        <v>2720</v>
+      </c>
+      <c r="G2258" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2259" t="s">
+        <v>2717</v>
+      </c>
+      <c r="B2259" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C2259" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2259" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2259" t="s">
+        <v>2721</v>
+      </c>
+      <c r="G2259" s="3">
+        <v>124.875</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2260" t="s">
+        <v>2722</v>
+      </c>
+      <c r="B2260" t="s">
+        <v>2723</v>
+      </c>
+      <c r="C2260" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2260" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2260" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2260" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2261" t="s">
+        <v>2722</v>
+      </c>
+      <c r="B2261" t="s">
+        <v>2723</v>
+      </c>
+      <c r="C2261" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2261" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2261" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2261" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2262" t="s">
+        <v>2722</v>
+      </c>
+      <c r="B2262" t="s">
+        <v>2723</v>
+      </c>
+      <c r="C2262" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2262" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2262" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2262" t="s">
+        <v>2720</v>
+      </c>
+      <c r="G2262" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2263" t="s">
+        <v>2724</v>
+      </c>
+      <c r="B2263" t="s">
+        <v>2725</v>
+      </c>
+      <c r="C2263" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2263" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2263" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2263" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2264" t="s">
+        <v>2726</v>
+      </c>
+      <c r="B2264" t="s">
+        <v>2727</v>
+      </c>
+      <c r="C2264" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2264" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2264" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2264" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2265" t="s">
+        <v>2728</v>
+      </c>
+      <c r="B2265" t="s">
+        <v>2729</v>
+      </c>
+      <c r="C2265" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2265" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2265" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2265" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2266" t="s">
+        <v>2730</v>
+      </c>
+      <c r="B2266" t="s">
+        <v>2731</v>
+      </c>
+      <c r="C2266" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2266" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2266" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2266" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2267" t="s">
+        <v>2732</v>
+      </c>
+      <c r="B2267" t="s">
+        <v>2733</v>
+      </c>
+      <c r="C2267" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2267" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2267" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2267" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2268" t="s">
+        <v>2734</v>
+      </c>
+      <c r="B2268" t="s">
+        <v>2735</v>
+      </c>
+      <c r="C2268" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2268" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2268" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2268" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2269" t="s">
+        <v>2736</v>
+      </c>
+      <c r="B2269" t="s">
+        <v>2737</v>
+      </c>
+      <c r="C2269" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2269" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2269" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2269" s="3">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2270" t="s">
+        <v>2736</v>
+      </c>
+      <c r="B2270" t="s">
+        <v>2737</v>
+      </c>
+      <c r="C2270" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2270" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2270" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2270" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2271" t="s">
+        <v>2738</v>
+      </c>
+      <c r="B2271" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C2271" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2271" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2271" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2271" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2272" t="s">
+        <v>2740</v>
+      </c>
+      <c r="B2272" t="s">
+        <v>2741</v>
+      </c>
+      <c r="C2272" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2272" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2272" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2272" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2273" t="s">
+        <v>2742</v>
+      </c>
+      <c r="B2273" t="s">
+        <v>2743</v>
+      </c>
+      <c r="C2273" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2273" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2273" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2273" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5B5F92-4C7B-4936-B226-57B1B11776A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4053B865-4B0B-46CA-B873-E0ADB4BC5639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11661" uniqueCount="2744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11901" uniqueCount="2786">
   <si>
     <t>AB</t>
   </si>
@@ -8271,6 +8271,132 @@
   </si>
   <si>
     <t>CFB5</t>
+  </si>
+  <si>
+    <t>Nanaimo</t>
+  </si>
+  <si>
+    <t>CYCD</t>
+  </si>
+  <si>
+    <t>122.100, 291.800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCO </t>
+  </si>
+  <si>
+    <t>121.075, 252.300</t>
+  </si>
+  <si>
+    <t>Nelson</t>
+  </si>
+  <si>
+    <t>CZNL</t>
+  </si>
+  <si>
+    <t>Oie Lake / Dougall Campbell Field</t>
+  </si>
+  <si>
+    <t>CDC5</t>
+  </si>
+  <si>
+    <t>Olds-Didsbury</t>
+  </si>
+  <si>
+    <t>CEA3</t>
+  </si>
+  <si>
+    <t>Olds (Netbook)</t>
+  </si>
+  <si>
+    <t>CFK6</t>
+  </si>
+  <si>
+    <t>Oliver</t>
+  </si>
+  <si>
+    <t>CAU3</t>
+  </si>
+  <si>
+    <t>One Hundred Mile House</t>
+  </si>
+  <si>
+    <t>CAV3</t>
+  </si>
+  <si>
+    <t>Osoyoos</t>
+  </si>
+  <si>
+    <t>CBB9</t>
+  </si>
+  <si>
+    <t>FISE Pacific rdo (Oliver)</t>
+  </si>
+  <si>
+    <t>Ospika</t>
+  </si>
+  <si>
+    <t>CBA9</t>
+  </si>
+  <si>
+    <t>Oyen Muni</t>
+  </si>
+  <si>
+    <t>CED3</t>
+  </si>
+  <si>
+    <t>Peace River</t>
+  </si>
+  <si>
+    <t>CYPE</t>
+  </si>
+  <si>
+    <t>Pelican</t>
+  </si>
+  <si>
+    <t>CFT8</t>
+  </si>
+  <si>
+    <t>Pemberton</t>
+  </si>
+  <si>
+    <t>CYPS</t>
+  </si>
+  <si>
+    <t>Blackcomb Helicopters</t>
+  </si>
+  <si>
+    <t>Penticton</t>
+  </si>
+  <si>
+    <t>CYYF</t>
+  </si>
+  <si>
+    <t>Pincher Creek</t>
+  </si>
+  <si>
+    <t>CZPC</t>
+  </si>
+  <si>
+    <t>Pitt Meadows</t>
+  </si>
+  <si>
+    <t>CYPK</t>
+  </si>
+  <si>
+    <t>Pitt</t>
+  </si>
+  <si>
+    <t>Ponoka (Labrie Field)</t>
+  </si>
+  <si>
+    <t>CEH3</t>
+  </si>
+  <si>
+    <t>Port Alberni (Alberni Valley Regional)</t>
+  </si>
+  <si>
+    <t>CBS8</t>
   </si>
 </sst>
 </file>
@@ -8661,7 +8787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G2273"/>
+  <dimension ref="A1:G2320"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -54479,6 +54605,952 @@
         <v>123.2</v>
       </c>
     </row>
+    <row r="2274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2274" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B2274" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C2274" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2274" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2274" t="s">
+        <v>2336</v>
+      </c>
+      <c r="G2274" t="s">
+        <v>2746</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2275" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B2275" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C2275" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2275" t="s">
+        <v>2747</v>
+      </c>
+      <c r="E2275" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G2275" s="3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2276" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B2276" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C2276" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2276" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2276" t="s">
+        <v>715</v>
+      </c>
+      <c r="G2276" s="3">
+        <v>128.42500000000001</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2277" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B2277" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C2277" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2277" t="s">
+        <v>1894</v>
+      </c>
+      <c r="F2277" t="s">
+        <v>2336</v>
+      </c>
+      <c r="G2277" s="3">
+        <v>122.6</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2278" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B2278" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C2278" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2278" t="s">
+        <v>641</v>
+      </c>
+      <c r="E2278" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2278" t="s">
+        <v>2337</v>
+      </c>
+      <c r="G2278" s="3">
+        <v>122.1</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2279" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B2279" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C2279" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2279" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2279" t="s">
+        <v>2239</v>
+      </c>
+      <c r="G2279" s="3">
+        <v>120.8</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2280" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B2280" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C2280" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2280" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2280" t="s">
+        <v>2240</v>
+      </c>
+      <c r="G2280" t="s">
+        <v>2748</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2281" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B2281" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C2281" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2281" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2281" t="s">
+        <v>2240</v>
+      </c>
+      <c r="G2281" t="s">
+        <v>2748</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2282" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B2282" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C2282" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2282" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2282" t="s">
+        <v>716</v>
+      </c>
+      <c r="G2282" s="3">
+        <v>128.42500000000001</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2283" t="s">
+        <v>2749</v>
+      </c>
+      <c r="B2283" t="s">
+        <v>2750</v>
+      </c>
+      <c r="C2283" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2283" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2283" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G2283" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2284" t="s">
+        <v>2749</v>
+      </c>
+      <c r="B2284" t="s">
+        <v>2750</v>
+      </c>
+      <c r="C2284" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2284" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2284" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2284" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2285" t="s">
+        <v>2749</v>
+      </c>
+      <c r="B2285" t="s">
+        <v>2750</v>
+      </c>
+      <c r="C2285" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2285" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2285" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2285" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2286" t="s">
+        <v>2751</v>
+      </c>
+      <c r="B2286" t="s">
+        <v>2752</v>
+      </c>
+      <c r="C2286" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2286" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2286" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2286" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2287" t="s">
+        <v>2753</v>
+      </c>
+      <c r="B2287" t="s">
+        <v>2754</v>
+      </c>
+      <c r="C2287" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2287" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2287" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2287" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2288" t="s">
+        <v>2753</v>
+      </c>
+      <c r="B2288" t="s">
+        <v>2754</v>
+      </c>
+      <c r="C2288" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2288" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2288" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2288" s="3">
+        <v>132.85</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2289" t="s">
+        <v>2755</v>
+      </c>
+      <c r="B2289" t="s">
+        <v>2756</v>
+      </c>
+      <c r="C2289" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2289" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2289" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2289" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2289" s="3">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2290" t="s">
+        <v>2757</v>
+      </c>
+      <c r="B2290" t="s">
+        <v>2758</v>
+      </c>
+      <c r="C2290" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2290" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2290" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G2290" s="3">
+        <v>125.85</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2291" t="s">
+        <v>2757</v>
+      </c>
+      <c r="B2291" t="s">
+        <v>2758</v>
+      </c>
+      <c r="C2291" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2291" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2291" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2291" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2292" t="s">
+        <v>2757</v>
+      </c>
+      <c r="B2292" t="s">
+        <v>2758</v>
+      </c>
+      <c r="C2292" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2292" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2292" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2292" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2293" t="s">
+        <v>2759</v>
+      </c>
+      <c r="B2293" t="s">
+        <v>2760</v>
+      </c>
+      <c r="C2293" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2293" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2293" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2293" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2294" t="s">
+        <v>2761</v>
+      </c>
+      <c r="B2294" t="s">
+        <v>2762</v>
+      </c>
+      <c r="C2294" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2294" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2294" t="s">
+        <v>2763</v>
+      </c>
+      <c r="G2294" s="3">
+        <v>125.85</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2295" t="s">
+        <v>2761</v>
+      </c>
+      <c r="B2295" t="s">
+        <v>2762</v>
+      </c>
+      <c r="C2295" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2295" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2295" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2295" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2296" t="s">
+        <v>2761</v>
+      </c>
+      <c r="B2296" t="s">
+        <v>2762</v>
+      </c>
+      <c r="C2296" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2296" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2296" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2296" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2297" t="s">
+        <v>2764</v>
+      </c>
+      <c r="B2297" t="s">
+        <v>2765</v>
+      </c>
+      <c r="C2297" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2297" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2297" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2297" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2298" t="s">
+        <v>2766</v>
+      </c>
+      <c r="B2298" t="s">
+        <v>2767</v>
+      </c>
+      <c r="C2298" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2298" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2298" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2298" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2298" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2299" t="s">
+        <v>2766</v>
+      </c>
+      <c r="B2299" t="s">
+        <v>2767</v>
+      </c>
+      <c r="C2299" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2299" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2299" s="3">
+        <v>121.875</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2300" t="s">
+        <v>2768</v>
+      </c>
+      <c r="B2300" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2300" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2300" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2300" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2300" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2301" t="s">
+        <v>2768</v>
+      </c>
+      <c r="B2301" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2301" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2301" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2301" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2301" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2302" t="s">
+        <v>2768</v>
+      </c>
+      <c r="B2302" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2302" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2302" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2302" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2302" s="3">
+        <v>135.27000000000001</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2303" t="s">
+        <v>2768</v>
+      </c>
+      <c r="B2303" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2303" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2303" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2303" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2303" s="3">
+        <v>135.27500000000001</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2304" t="s">
+        <v>2768</v>
+      </c>
+      <c r="B2304" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C2304" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2304" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2304" s="3">
+        <v>128.1</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2305" t="s">
+        <v>2770</v>
+      </c>
+      <c r="B2305" t="s">
+        <v>2771</v>
+      </c>
+      <c r="C2305" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2305" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2305" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2305" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2305" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2306" t="s">
+        <v>2772</v>
+      </c>
+      <c r="B2306" t="s">
+        <v>2773</v>
+      </c>
+      <c r="C2306" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2306" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2306" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G2306" s="3">
+        <v>122.375</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2307" t="s">
+        <v>2772</v>
+      </c>
+      <c r="B2307" t="s">
+        <v>2773</v>
+      </c>
+      <c r="C2307" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2307" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2307" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2307" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2308" t="s">
+        <v>2772</v>
+      </c>
+      <c r="B2308" t="s">
+        <v>2773</v>
+      </c>
+      <c r="C2308" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2308" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2308" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2308" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2309" t="s">
+        <v>2772</v>
+      </c>
+      <c r="B2309" t="s">
+        <v>2773</v>
+      </c>
+      <c r="C2309" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2309" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2309" t="s">
+        <v>2774</v>
+      </c>
+      <c r="G2309" s="3">
+        <v>122.77500000000001</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2310" t="s">
+        <v>2775</v>
+      </c>
+      <c r="B2310" t="s">
+        <v>2776</v>
+      </c>
+      <c r="C2310" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2310" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2310" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2311" t="s">
+        <v>2775</v>
+      </c>
+      <c r="B2311" t="s">
+        <v>2776</v>
+      </c>
+      <c r="C2311" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2311" t="s">
+        <v>1894</v>
+      </c>
+      <c r="G2311" s="3">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2312" t="s">
+        <v>2775</v>
+      </c>
+      <c r="B2312" t="s">
+        <v>2776</v>
+      </c>
+      <c r="C2312" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2312" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2312" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2312" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2313" t="s">
+        <v>2777</v>
+      </c>
+      <c r="B2313" t="s">
+        <v>2778</v>
+      </c>
+      <c r="C2313" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2313" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2313" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2313" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2314" t="s">
+        <v>2777</v>
+      </c>
+      <c r="B2314" t="s">
+        <v>2778</v>
+      </c>
+      <c r="C2314" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2314" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2314" s="3">
+        <v>127.65</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2315" t="s">
+        <v>2779</v>
+      </c>
+      <c r="B2315" t="s">
+        <v>2780</v>
+      </c>
+      <c r="C2315" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2315" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2315" t="s">
+        <v>2233</v>
+      </c>
+      <c r="G2315" s="3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2316" t="s">
+        <v>2779</v>
+      </c>
+      <c r="B2316" t="s">
+        <v>2780</v>
+      </c>
+      <c r="C2316" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2316" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2316" t="s">
+        <v>2233</v>
+      </c>
+      <c r="G2316" s="3">
+        <v>123.8</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2317" t="s">
+        <v>2779</v>
+      </c>
+      <c r="B2317" t="s">
+        <v>2780</v>
+      </c>
+      <c r="C2317" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2317" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2317" t="s">
+        <v>2781</v>
+      </c>
+      <c r="F2317" t="s">
+        <v>2233</v>
+      </c>
+      <c r="G2317" s="3">
+        <v>126.3</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2318" t="s">
+        <v>2779</v>
+      </c>
+      <c r="B2318" t="s">
+        <v>2780</v>
+      </c>
+      <c r="C2318" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2318" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2318" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2318" t="s">
+        <v>2231</v>
+      </c>
+      <c r="G2318" s="3">
+        <v>126.3</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2319" t="s">
+        <v>2782</v>
+      </c>
+      <c r="B2319" t="s">
+        <v>2783</v>
+      </c>
+      <c r="C2319" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2319" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2319" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2319" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2319" s="3">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2320" t="s">
+        <v>2784</v>
+      </c>
+      <c r="B2320" t="s">
+        <v>2785</v>
+      </c>
+      <c r="C2320" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2320" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2320" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2320" s="3">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4053B865-4B0B-46CA-B873-E0ADB4BC5639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{601CE309-44D9-4774-B89C-AD12F722617B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11901" uniqueCount="2786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12195" uniqueCount="2835">
   <si>
     <t>AB</t>
   </si>
@@ -8397,6 +8397,153 @@
   </si>
   <si>
     <t>CBS8</t>
+  </si>
+  <si>
+    <t>Port Hardy</t>
+  </si>
+  <si>
+    <t>CYZT</t>
+  </si>
+  <si>
+    <t>Hardy</t>
+  </si>
+  <si>
+    <t>Hardy rdo</t>
+  </si>
+  <si>
+    <t>132.200, 266.300</t>
+  </si>
+  <si>
+    <t>Port McNeill</t>
+  </si>
+  <si>
+    <t>CAT5</t>
+  </si>
+  <si>
+    <t>FISE Pacific rdo (Port Hardy)</t>
+  </si>
+  <si>
+    <t>Powell River</t>
+  </si>
+  <si>
+    <t>CYPW</t>
+  </si>
+  <si>
+    <t>FISE Pacific rdo (Campbell River)</t>
+  </si>
+  <si>
+    <t>Primrose</t>
+  </si>
+  <si>
+    <t>CFN6</t>
+  </si>
+  <si>
+    <t>13-07Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Prince George</t>
+  </si>
+  <si>
+    <t>CYXS</t>
+  </si>
+  <si>
+    <t>RAAS Williams Lake rdo</t>
+  </si>
+  <si>
+    <t>Williams Lake rdo</t>
+  </si>
+  <si>
+    <t>Prince Rupert</t>
+  </si>
+  <si>
+    <t>CYPR</t>
+  </si>
+  <si>
+    <t>Princeton</t>
+  </si>
+  <si>
+    <t>CYDC</t>
+  </si>
+  <si>
+    <t>135.000, 351.300</t>
+  </si>
+  <si>
+    <t>Provost</t>
+  </si>
+  <si>
+    <t>CEH6</t>
+  </si>
+  <si>
+    <t>Puntzi Mountain</t>
+  </si>
+  <si>
+    <t>CYPU</t>
+  </si>
+  <si>
+    <t>Qualicum Beach</t>
+  </si>
+  <si>
+    <t>CAT4</t>
+  </si>
+  <si>
+    <t>Quamichan Lake (Raven Field)</t>
+  </si>
+  <si>
+    <t>CML2</t>
+  </si>
+  <si>
+    <t>Quesnel</t>
+  </si>
+  <si>
+    <t>CYQZ</t>
+  </si>
+  <si>
+    <t>14-06Z‡ O/T tfc</t>
+  </si>
+  <si>
+    <t>Quesnel Lake</t>
+  </si>
+  <si>
+    <t>CBK6</t>
+  </si>
+  <si>
+    <t>Radium Hot Springs</t>
+  </si>
+  <si>
+    <t>CBL6</t>
+  </si>
+  <si>
+    <t>Rainbow Lake</t>
+  </si>
+  <si>
+    <t>CYOP</t>
+  </si>
+  <si>
+    <t>Red Deer Forestry</t>
+  </si>
+  <si>
+    <t>CFR7</t>
+  </si>
+  <si>
+    <t>Red Deer Regional</t>
+  </si>
+  <si>
+    <t>CYQF</t>
+  </si>
+  <si>
+    <t>13-05Z‡</t>
+  </si>
+  <si>
+    <t>05-13Z‡</t>
+  </si>
+  <si>
+    <t>Red Deer / Truant</t>
+  </si>
+  <si>
+    <t>CRD5</t>
+  </si>
+  <si>
+    <t>Red Deer</t>
   </si>
 </sst>
 </file>
@@ -8787,7 +8934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G2320"/>
+  <dimension ref="A1:G2377"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -55551,6 +55698,1161 @@
         <v>123</v>
       </c>
     </row>
+    <row r="2321" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2321" t="s">
+        <v>2786</v>
+      </c>
+      <c r="B2321" t="s">
+        <v>2787</v>
+      </c>
+      <c r="C2321" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2321" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2321" t="s">
+        <v>2788</v>
+      </c>
+      <c r="G2321" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2322" t="s">
+        <v>2786</v>
+      </c>
+      <c r="B2322" t="s">
+        <v>2787</v>
+      </c>
+      <c r="C2322" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2322" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2322" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G2322" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2323" t="s">
+        <v>2786</v>
+      </c>
+      <c r="B2323" t="s">
+        <v>2787</v>
+      </c>
+      <c r="C2323" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2323" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2323" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2323" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2324" t="s">
+        <v>2786</v>
+      </c>
+      <c r="B2324" t="s">
+        <v>2787</v>
+      </c>
+      <c r="C2324" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2324" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2324" t="s">
+        <v>2789</v>
+      </c>
+      <c r="G2324" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2325" t="s">
+        <v>2786</v>
+      </c>
+      <c r="B2325" t="s">
+        <v>2787</v>
+      </c>
+      <c r="C2325" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2325" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2325" t="s">
+        <v>2305</v>
+      </c>
+      <c r="G2325" t="s">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2326" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B2326" t="s">
+        <v>2792</v>
+      </c>
+      <c r="C2326" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2326" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2326" t="s">
+        <v>2793</v>
+      </c>
+      <c r="G2326" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2327" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B2327" t="s">
+        <v>2792</v>
+      </c>
+      <c r="C2327" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2327" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2327" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2327" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2328" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B2328" t="s">
+        <v>2792</v>
+      </c>
+      <c r="C2328" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2328" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2328" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2328" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2329" t="s">
+        <v>2794</v>
+      </c>
+      <c r="B2329" t="s">
+        <v>2795</v>
+      </c>
+      <c r="C2329" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2329" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2329" t="s">
+        <v>2796</v>
+      </c>
+      <c r="G2329" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2330" t="s">
+        <v>2794</v>
+      </c>
+      <c r="B2330" t="s">
+        <v>2795</v>
+      </c>
+      <c r="C2330" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2330" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2330" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2330" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2331" t="s">
+        <v>2794</v>
+      </c>
+      <c r="B2331" t="s">
+        <v>2795</v>
+      </c>
+      <c r="C2331" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2331" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2331" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2331" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2332" t="s">
+        <v>2794</v>
+      </c>
+      <c r="B2332" t="s">
+        <v>2795</v>
+      </c>
+      <c r="C2332" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2332" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2332" t="s">
+        <v>2338</v>
+      </c>
+      <c r="G2332" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2333" t="s">
+        <v>2797</v>
+      </c>
+      <c r="B2333" t="s">
+        <v>2798</v>
+      </c>
+      <c r="C2333" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2333" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2333" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2333" t="s">
+        <v>2799</v>
+      </c>
+      <c r="G2333" s="3">
+        <v>122.95</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2334" t="s">
+        <v>2797</v>
+      </c>
+      <c r="B2334" t="s">
+        <v>2798</v>
+      </c>
+      <c r="C2334" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2334" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2334" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G2334" s="3">
+        <v>134.44999999999999</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2335" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B2335" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C2335" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2335" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2335" t="s">
+        <v>2802</v>
+      </c>
+      <c r="F2335" t="s">
+        <v>716</v>
+      </c>
+      <c r="G2335" s="3">
+        <v>118.3</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2336" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B2336" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C2336" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2336" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2336" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G2336" s="3">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2337" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B2337" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C2337" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2337" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2337" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2337" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2338" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B2338" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C2338" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2338" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2338" t="s">
+        <v>715</v>
+      </c>
+      <c r="G2338" s="3">
+        <v>128.72499999999999</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2339" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B2339" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C2339" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2339" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2339" t="s">
+        <v>715</v>
+      </c>
+      <c r="G2339" s="3">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2340" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B2340" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C2340" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2340" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2340" t="s">
+        <v>715</v>
+      </c>
+      <c r="G2340" s="3">
+        <v>118.3</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2341" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B2341" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C2341" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2341" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2341" t="s">
+        <v>2803</v>
+      </c>
+      <c r="F2341" t="s">
+        <v>716</v>
+      </c>
+      <c r="G2341" s="3">
+        <v>118.3</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2342" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B2342" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C2342" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2342" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2342" t="s">
+        <v>2305</v>
+      </c>
+      <c r="G2342" s="3">
+        <v>133.80000000000001</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2343" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B2343" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C2343" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2343" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2343" t="s">
+        <v>716</v>
+      </c>
+      <c r="G2343" s="3">
+        <v>128.72499999999999</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2344" t="s">
+        <v>2804</v>
+      </c>
+      <c r="B2344" t="s">
+        <v>2805</v>
+      </c>
+      <c r="C2344" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2344" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2344" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G2344" s="3">
+        <v>123.27500000000001</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2345" t="s">
+        <v>2804</v>
+      </c>
+      <c r="B2345" t="s">
+        <v>2805</v>
+      </c>
+      <c r="C2345" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2345" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2345" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2345" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2346" t="s">
+        <v>2804</v>
+      </c>
+      <c r="B2346" t="s">
+        <v>2805</v>
+      </c>
+      <c r="C2346" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2346" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2346" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2346" s="3">
+        <v>122.5</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2347" t="s">
+        <v>2804</v>
+      </c>
+      <c r="B2347" t="s">
+        <v>2805</v>
+      </c>
+      <c r="C2347" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2347" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2347" t="s">
+        <v>2305</v>
+      </c>
+      <c r="G2347" s="3">
+        <v>133.67500000000001</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2348" t="s">
+        <v>2804</v>
+      </c>
+      <c r="B2348" t="s">
+        <v>2805</v>
+      </c>
+      <c r="C2348" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2348" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2348" s="3">
+        <v>128.57499999999999</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2349" t="s">
+        <v>2806</v>
+      </c>
+      <c r="B2349" t="s">
+        <v>2807</v>
+      </c>
+      <c r="C2349" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2349" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2349" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G2349" s="3">
+        <v>125.85</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2350" t="s">
+        <v>2806</v>
+      </c>
+      <c r="B2350" t="s">
+        <v>2807</v>
+      </c>
+      <c r="C2350" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2350" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2350" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2350" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2351" t="s">
+        <v>2806</v>
+      </c>
+      <c r="B2351" t="s">
+        <v>2807</v>
+      </c>
+      <c r="C2351" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2351" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2351" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2351" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2352" t="s">
+        <v>2806</v>
+      </c>
+      <c r="B2352" t="s">
+        <v>2807</v>
+      </c>
+      <c r="C2352" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2352" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2352" t="s">
+        <v>2305</v>
+      </c>
+      <c r="G2352" t="s">
+        <v>2808</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2353" t="s">
+        <v>2809</v>
+      </c>
+      <c r="B2353" t="s">
+        <v>2810</v>
+      </c>
+      <c r="C2353" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2353" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2353" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2353" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2353" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2354" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B2354" t="s">
+        <v>2812</v>
+      </c>
+      <c r="C2354" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2354" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2354" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G2354" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2355" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B2355" t="s">
+        <v>2812</v>
+      </c>
+      <c r="C2355" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2355" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2355" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2355" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2356" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B2356" t="s">
+        <v>2812</v>
+      </c>
+      <c r="C2356" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2356" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2356" t="s">
+        <v>2305</v>
+      </c>
+      <c r="G2356" s="3">
+        <v>135.05000000000001</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2357" t="s">
+        <v>2813</v>
+      </c>
+      <c r="B2357" t="s">
+        <v>2814</v>
+      </c>
+      <c r="C2357" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2357" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2357" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2357" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2358" t="s">
+        <v>2813</v>
+      </c>
+      <c r="B2358" t="s">
+        <v>2814</v>
+      </c>
+      <c r="C2358" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2358" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2358" t="s">
+        <v>2338</v>
+      </c>
+      <c r="G2358" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2359" t="s">
+        <v>2815</v>
+      </c>
+      <c r="B2359" t="s">
+        <v>2816</v>
+      </c>
+      <c r="C2359" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2359" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2359" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2359" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2360" t="s">
+        <v>2817</v>
+      </c>
+      <c r="B2360" t="s">
+        <v>2818</v>
+      </c>
+      <c r="C2360" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2360" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2360" t="s">
+        <v>2802</v>
+      </c>
+      <c r="F2360" t="s">
+        <v>676</v>
+      </c>
+      <c r="G2360" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2361" t="s">
+        <v>2817</v>
+      </c>
+      <c r="B2361" t="s">
+        <v>2818</v>
+      </c>
+      <c r="C2361" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2361" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2361" t="s">
+        <v>2803</v>
+      </c>
+      <c r="F2361" t="s">
+        <v>2819</v>
+      </c>
+      <c r="G2361" s="3">
+        <v>122.2</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2362" t="s">
+        <v>2817</v>
+      </c>
+      <c r="B2362" t="s">
+        <v>2818</v>
+      </c>
+      <c r="C2362" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2362" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2362" s="3">
+        <v>124.4</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2363" t="s">
+        <v>2820</v>
+      </c>
+      <c r="B2363" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C2363" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2363" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2363" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2363" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2364" t="s">
+        <v>2822</v>
+      </c>
+      <c r="B2364" t="s">
+        <v>2823</v>
+      </c>
+      <c r="C2364" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D2364" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2364" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2364" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2365" t="s">
+        <v>2824</v>
+      </c>
+      <c r="B2365" t="s">
+        <v>2825</v>
+      </c>
+      <c r="C2365" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2365" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2365" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2365" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2365" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2366" t="s">
+        <v>2824</v>
+      </c>
+      <c r="B2366" t="s">
+        <v>2825</v>
+      </c>
+      <c r="C2366" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2366" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2366" s="3">
+        <v>123.3</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2367" t="s">
+        <v>2826</v>
+      </c>
+      <c r="B2367" t="s">
+        <v>2827</v>
+      </c>
+      <c r="C2367" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2367" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2367" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2367" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2368" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B2368" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C2368" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2368" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2368" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2368" s="3">
+        <v>123.47499999999999</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2369" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B2369" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C2369" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2369" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2369" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2369" s="3">
+        <v>126.7</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2370" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B2370" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C2370" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2370" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2370" t="s">
+        <v>2830</v>
+      </c>
+      <c r="G2370" s="3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2371" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B2371" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C2371" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2371" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2371" t="s">
+        <v>2830</v>
+      </c>
+      <c r="G2371" s="3">
+        <v>121.9</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2372" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B2372" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C2372" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2372" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2372" t="s">
+        <v>2830</v>
+      </c>
+      <c r="G2372" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2373" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B2373" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C2373" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2373" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2373" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2373" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2374" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B2374" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C2374" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2374" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2374" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2374" s="3">
+        <v>132.85</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2375" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B2375" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C2375" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2375" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2375" t="s">
+        <v>2831</v>
+      </c>
+      <c r="G2375" s="3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2376" t="s">
+        <v>2832</v>
+      </c>
+      <c r="B2376" t="s">
+        <v>2833</v>
+      </c>
+      <c r="C2376" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2376" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2376" t="s">
+        <v>2834</v>
+      </c>
+      <c r="F2376" t="s">
+        <v>2830</v>
+      </c>
+      <c r="G2376" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2377" t="s">
+        <v>2832</v>
+      </c>
+      <c r="B2377" t="s">
+        <v>2833</v>
+      </c>
+      <c r="C2377" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2377" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2377" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2377" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{601CE309-44D9-4774-B89C-AD12F722617B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF12F6A1-4FA6-44AA-B699-774E7430F70A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12195" uniqueCount="2835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12270" uniqueCount="2851">
   <si>
     <t>AB</t>
   </si>
@@ -8544,6 +8544,54 @@
   </si>
   <si>
     <t>Red Deer</t>
+  </si>
+  <si>
+    <t>Red Deer / Truant South</t>
+  </si>
+  <si>
+    <t>CRD6</t>
+  </si>
+  <si>
+    <t>Red Earth Creek</t>
+  </si>
+  <si>
+    <t>CEH5</t>
+  </si>
+  <si>
+    <t>Rimbey</t>
+  </si>
+  <si>
+    <t>CFC7</t>
+  </si>
+  <si>
+    <t>Rockyford</t>
+  </si>
+  <si>
+    <t>CFC6</t>
+  </si>
+  <si>
+    <t>Rockyford / Early Bird Air</t>
+  </si>
+  <si>
+    <t>CEB4</t>
+  </si>
+  <si>
+    <t>Rocky Mountain House</t>
+  </si>
+  <si>
+    <t>CYRM</t>
+  </si>
+  <si>
+    <t>St. Paul</t>
+  </si>
+  <si>
+    <t>CEW3</t>
+  </si>
+  <si>
+    <t>Slave Lake</t>
+  </si>
+  <si>
+    <t>CYZH</t>
   </si>
 </sst>
 </file>
@@ -8934,7 +8982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G2377"/>
+  <dimension ref="A1:G2392"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -56853,6 +56901,306 @@
         <v>118.5</v>
       </c>
     </row>
+    <row r="2378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2378" t="s">
+        <v>2835</v>
+      </c>
+      <c r="B2378" t="s">
+        <v>2836</v>
+      </c>
+      <c r="C2378" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2378" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2378" t="s">
+        <v>2834</v>
+      </c>
+      <c r="F2378" t="s">
+        <v>2830</v>
+      </c>
+      <c r="G2378" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2379" t="s">
+        <v>2835</v>
+      </c>
+      <c r="B2379" t="s">
+        <v>2836</v>
+      </c>
+      <c r="C2379" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2379" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2379" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2379" s="3">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2380" t="s">
+        <v>2837</v>
+      </c>
+      <c r="B2380" t="s">
+        <v>2838</v>
+      </c>
+      <c r="C2380" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2380" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2380" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2380" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2381" t="s">
+        <v>2837</v>
+      </c>
+      <c r="B2381" t="s">
+        <v>2838</v>
+      </c>
+      <c r="C2381" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2381" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2381" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2381" s="3">
+        <v>135.27500000000001</v>
+      </c>
+    </row>
+    <row r="2382" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2382" t="s">
+        <v>2839</v>
+      </c>
+      <c r="B2382" t="s">
+        <v>2840</v>
+      </c>
+      <c r="C2382" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2382" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2382" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2382" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2383" t="s">
+        <v>2841</v>
+      </c>
+      <c r="B2383" t="s">
+        <v>2842</v>
+      </c>
+      <c r="C2383" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2383" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2383" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2383" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2384" t="s">
+        <v>2843</v>
+      </c>
+      <c r="B2384" t="s">
+        <v>2844</v>
+      </c>
+      <c r="C2384" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2384" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2384" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2384" s="3">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2385" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2385" t="s">
+        <v>2846</v>
+      </c>
+      <c r="C2385" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2385" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2385" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2385" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2386" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2386" t="s">
+        <v>2846</v>
+      </c>
+      <c r="C2386" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2386" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2386" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2386" s="3">
+        <v>134.30000000000001</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2387" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2387" t="s">
+        <v>2846</v>
+      </c>
+      <c r="C2387" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2387" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2387" s="3">
+        <v>131.97499999999999</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2388" t="s">
+        <v>2847</v>
+      </c>
+      <c r="B2388" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C2388" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2388" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2388" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2388" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2388" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2389" t="s">
+        <v>2849</v>
+      </c>
+      <c r="B2389" t="s">
+        <v>2850</v>
+      </c>
+      <c r="C2389" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2389" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2389" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2389" s="3">
+        <v>123.375</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2390" t="s">
+        <v>2849</v>
+      </c>
+      <c r="B2390" t="s">
+        <v>2850</v>
+      </c>
+      <c r="C2390" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2390" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2390" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2390" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2391" t="s">
+        <v>2849</v>
+      </c>
+      <c r="B2391" t="s">
+        <v>2850</v>
+      </c>
+      <c r="C2391" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2391" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2391" t="s">
+        <v>402</v>
+      </c>
+      <c r="G2391" s="3">
+        <v>124.85</v>
+      </c>
+    </row>
+    <row r="2392" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2392" t="s">
+        <v>2849</v>
+      </c>
+      <c r="B2392" t="s">
+        <v>2850</v>
+      </c>
+      <c r="C2392" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2392" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2392" s="3">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/airports.xlsx
+++ b/data/airports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Documents\Websites\ChatGPT 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF12F6A1-4FA6-44AA-B699-774E7430F70A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3162F130-8AE6-4588-A136-70566D9BD51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3ED75E5D-7D71-45D8-A38B-3CCEF78FCE20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12270" uniqueCount="2851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12341" uniqueCount="2879">
   <si>
     <t>AB</t>
   </si>
@@ -8592,6 +8592,90 @@
   </si>
   <si>
     <t>CYZH</t>
+  </si>
+  <si>
+    <t>Spirit River</t>
+  </si>
+  <si>
+    <t>CFS5</t>
+  </si>
+  <si>
+    <t>Stettler</t>
+  </si>
+  <si>
+    <t>CEJ3</t>
+  </si>
+  <si>
+    <t>Stettler / Lyster Field</t>
+  </si>
+  <si>
+    <t>CLY3</t>
+  </si>
+  <si>
+    <t>Stony Plain (Stony Field)</t>
+  </si>
+  <si>
+    <t>CSP3</t>
+  </si>
+  <si>
+    <t>Strathmore (Appleton Field)</t>
+  </si>
+  <si>
+    <t>CAP9</t>
+  </si>
+  <si>
+    <t>Strathmore (D.j. Murray)</t>
+  </si>
+  <si>
+    <t>CDJ5</t>
+  </si>
+  <si>
+    <t>Sundre</t>
+  </si>
+  <si>
+    <t>CFN7</t>
+  </si>
+  <si>
+    <t>Sundre / Goodwins Farm</t>
+  </si>
+  <si>
+    <t>CFZ5</t>
+  </si>
+  <si>
+    <t>Swan Hills</t>
+  </si>
+  <si>
+    <t>CEM5</t>
+  </si>
+  <si>
+    <t>Taber</t>
+  </si>
+  <si>
+    <t>CED5</t>
+  </si>
+  <si>
+    <t>Teepee</t>
+  </si>
+  <si>
+    <t>CFM6</t>
+  </si>
+  <si>
+    <t>Three Hills</t>
+  </si>
+  <si>
+    <t>CEN3</t>
+  </si>
+  <si>
+    <t>Tofield</t>
+  </si>
+  <si>
+    <t>CEV7</t>
+  </si>
+  <si>
+    <t>Trout Lake</t>
+  </si>
+  <si>
+    <t>CFB4</t>
   </si>
 </sst>
 </file>
@@ -8982,7 +9066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165AB9F5-6370-4EB3-871E-293566FC6032}">
-  <dimension ref="A1:G2392"/>
+  <dimension ref="A1:G2406"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -57201,6 +57285,289 @@
         <v>127</v>
       </c>
     </row>
+    <row r="2393" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2393" t="s">
+        <v>2851</v>
+      </c>
+      <c r="B2393" t="s">
+        <v>2852</v>
+      </c>
+      <c r="C2393" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2393" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2393" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2393" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2394" t="s">
+        <v>2853</v>
+      </c>
+      <c r="B2394" t="s">
+        <v>2854</v>
+      </c>
+      <c r="C2394" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2394" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2394" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2394" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2394" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2395" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B2395" t="s">
+        <v>2856</v>
+      </c>
+      <c r="C2395" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2395" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2395" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2395" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2396" t="s">
+        <v>2857</v>
+      </c>
+      <c r="B2396" t="s">
+        <v>2858</v>
+      </c>
+      <c r="C2396" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2396" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2396" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2396" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2397" t="s">
+        <v>2859</v>
+      </c>
+      <c r="B2397" t="s">
+        <v>2860</v>
+      </c>
+      <c r="C2397" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2397" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2397" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2397" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2398" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2398" t="s">
+        <v>2861</v>
+      </c>
+      <c r="B2398" t="s">
+        <v>2862</v>
+      </c>
+      <c r="C2398" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2398" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2398" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2398" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2399" t="s">
+        <v>2863</v>
+      </c>
+      <c r="B2399" t="s">
+        <v>2864</v>
+      </c>
+      <c r="C2399" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2399" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2399" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2399" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2400" t="s">
+        <v>2865</v>
+      </c>
+      <c r="B2400" t="s">
+        <v>2866</v>
+      </c>
+      <c r="C2400" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2400" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2400" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2400" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2401" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2401" t="s">
+        <v>2867</v>
+      </c>
+      <c r="B2401" t="s">
+        <v>2868</v>
+      </c>
+      <c r="C2401" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2401" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2401" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2401" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2402" t="s">
+        <v>2869</v>
+      </c>
+      <c r="B2402" t="s">
+        <v>2870</v>
+      </c>
+      <c r="C2402" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2402" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2402" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2402" s="3">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2403" t="s">
+        <v>2871</v>
+      </c>
+      <c r="B2403" t="s">
+        <v>2872</v>
+      </c>
+      <c r="C2403" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2403" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2403" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2403" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2404" t="s">
+        <v>2873</v>
+      </c>
+      <c r="B2404" t="s">
+        <v>2874</v>
+      </c>
+      <c r="C2404" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2404" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2404" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2404" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2405" t="s">
+        <v>2875</v>
+      </c>
+      <c r="B2405" t="s">
+        <v>2876</v>
+      </c>
+      <c r="C2405" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2405" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2405" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2405" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2406" t="s">
+        <v>2877</v>
+      </c>
+      <c r="B2406" t="s">
+        <v>2878</v>
+      </c>
+      <c r="C2406" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2406" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2406" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2406" s="3">
+        <v>123.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
